--- a/зо.xlsx
+++ b/зо.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="24">
   <si>
     <t>№</t>
   </si>
@@ -81,16 +81,13 @@
     <t>Суббота</t>
   </si>
   <si>
-    <t>Иностранный язык (зачёт)</t>
+    <t>Расписание занятий заочного отделения групп Ту-255,254</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Эу-485,486</t>
+    <t>Информатика</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Эу-358,359,360</t>
-  </si>
-  <si>
-    <t>Расписание занятий заочного отделения групп Эу-245</t>
+    <t xml:space="preserve">Расписание занятий заочного отделения групп </t>
   </si>
 </sst>
 </file>
@@ -232,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -267,11 +264,14 @@
     <xf numFmtId="16" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -279,11 +279,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +583,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="7.28515625" customWidth="1"/>
     <col min="6" max="6" width="6.42578125" style="1" customWidth="1"/>
@@ -597,20 +597,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="B1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -651,44 +651,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="16"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="17"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
@@ -741,7 +741,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>6</v>
@@ -753,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>6</v>
@@ -767,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -779,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>8</v>
@@ -791,7 +791,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>8</v>
@@ -805,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>8</v>
@@ -817,7 +817,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>8</v>
@@ -829,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>8</v>
@@ -843,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>10</v>
@@ -915,44 +915,44 @@
       </c>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="16"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="17"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
@@ -970,7 +970,9 @@
       <c r="J14" s="8">
         <v>1</v>
       </c>
-      <c r="K14" s="7"/>
+      <c r="K14" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
@@ -990,7 +992,9 @@
       <c r="J15" s="8">
         <v>2</v>
       </c>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
@@ -999,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>12</v>
@@ -1016,7 +1020,9 @@
       <c r="J16" s="8">
         <v>3</v>
       </c>
-      <c r="K16" s="7"/>
+      <c r="K16" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
@@ -1025,7 +1031,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>6</v>
@@ -1037,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>8</v>
@@ -1059,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>6</v>
@@ -1071,7 +1077,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>6</v>
@@ -1103,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>6</v>
@@ -1153,78 +1159,78 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="16"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B22" s="17"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="5">
         <v>46309</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="11">
         <v>46316</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
       <c r="K22" s="11">
         <v>46323</v>
       </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="16">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="16">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="16">
-        <v>1</v>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
+      <c r="B23" s="13">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="13">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="13">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
     </row>
     <row r="24" spans="2:13" ht="7.5" customHeight="1" thickBot="1">
-      <c r="B24" s="17"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B25" s="6">
@@ -1405,44 +1411,44 @@
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="16"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B32" s="17"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="5">
         <v>46310</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
       <c r="G32" s="5">
         <v>46317</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
       <c r="K32" s="5">
         <v>46324</v>
       </c>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
@@ -1653,44 +1659,44 @@
       <c r="M39" s="9"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="16"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
       <c r="K40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B41" s="17"/>
+      <c r="B41" s="14"/>
       <c r="C41" s="5">
         <v>46311</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
       <c r="G41" s="5">
         <v>46318</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
       <c r="K41" s="5">
         <v>46325</v>
       </c>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
@@ -1889,44 +1895,44 @@
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B49" s="16"/>
+      <c r="B49" s="13"/>
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
       <c r="K49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B50" s="17"/>
+      <c r="B50" s="14"/>
       <c r="C50" s="5">
         <v>46312</v>
       </c>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
       <c r="G50" s="5">
         <v>46319</v>
       </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
       <c r="K50" s="5">
         <v>46326</v>
       </c>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
     </row>
     <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
@@ -2135,20 +2141,20 @@
       <c r="M57" s="7"/>
     </row>
     <row r="60" spans="2:13" ht="21" thickBot="1">
-      <c r="B60" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
+      <c r="B60" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" thickBot="1">
       <c r="B61" s="2" t="s">
@@ -2189,44 +2195,32 @@
       </c>
     </row>
     <row r="62" spans="2:13" ht="15.75">
-      <c r="B62" s="16"/>
-      <c r="C62" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
     </row>
     <row r="63" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B63" s="17"/>
-      <c r="C63" s="5">
-        <v>46307</v>
-      </c>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="5">
-        <v>46314</v>
-      </c>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="5">
-        <v>46321</v>
-      </c>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" thickBot="1">
       <c r="B64" s="6">
@@ -2268,7 +2262,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="30.75" thickBot="1">
+    <row r="66" spans="2:13" ht="15.75" thickBot="1">
       <c r="B66" s="6">
         <v>3</v>
       </c>
@@ -2278,219 +2272,123 @@
       <c r="F66" s="8">
         <v>3</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I66" s="7">
-        <v>423</v>
-      </c>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
       <c r="J66" s="8">
         <v>3</v>
       </c>
-      <c r="K66" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M66" s="7">
-        <v>423</v>
-      </c>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" spans="2:13" ht="15.75" thickBot="1">
       <c r="B67" s="6">
         <v>4</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="7">
-        <v>318</v>
-      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
       <c r="F67" s="8">
         <v>4</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I67" s="7">
-        <v>318</v>
-      </c>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
       <c r="J67" s="8">
         <v>4</v>
       </c>
-      <c r="K67" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M67" s="7">
-        <v>318</v>
-      </c>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
     </row>
     <row r="68" spans="2:13" ht="15.75" thickBot="1">
       <c r="B68" s="6">
         <v>5</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="7">
-        <v>318</v>
-      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
       <c r="F68" s="8">
         <v>5</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I68" s="7">
-        <v>318</v>
-      </c>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
       <c r="J68" s="8">
         <v>5</v>
       </c>
-      <c r="K68" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M68" s="7">
-        <v>318</v>
-      </c>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
     </row>
     <row r="69" spans="2:13" ht="15.75" thickBot="1">
       <c r="B69" s="6">
         <v>6</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="7">
-        <v>318</v>
-      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
       <c r="F69" s="8">
         <v>6</v>
       </c>
-      <c r="G69" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="7">
-        <v>318</v>
-      </c>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
       <c r="J69" s="8">
         <v>6</v>
       </c>
-      <c r="K69" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M69" s="7">
-        <v>318</v>
-      </c>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
     </row>
     <row r="70" spans="2:13" ht="15.75" thickBot="1">
       <c r="B70" s="6">
         <v>7</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="7">
-        <v>318</v>
-      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
       <c r="F70" s="8">
         <v>7</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="7">
-        <v>318</v>
-      </c>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
       <c r="J70" s="8">
         <v>7</v>
       </c>
-      <c r="K70" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M70" s="7">
-        <v>318</v>
-      </c>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" spans="2:13" ht="15.75">
-      <c r="B71" s="16"/>
-      <c r="C71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
     </row>
     <row r="72" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B72" s="17"/>
-      <c r="C72" s="5">
-        <v>46308</v>
-      </c>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="5">
-        <v>46315</v>
-      </c>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="5">
-        <v>46322</v>
-      </c>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
@@ -2532,19 +2430,13 @@
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" ht="30.75" thickBot="1">
+    <row r="75" spans="2:13" ht="15.75" thickBot="1">
       <c r="B75" s="6">
         <v>3</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="7">
-        <v>312</v>
-      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
       <c r="F75" s="8">
         <v>3</v>
       </c>
@@ -2558,79 +2450,47 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" ht="30.75" thickBot="1">
+    <row r="76" spans="2:13" ht="15.75" thickBot="1">
       <c r="B76" s="6">
         <v>4</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="7">
-        <v>423</v>
-      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
       <c r="F76" s="8">
         <v>4</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="8">
         <v>4</v>
       </c>
-      <c r="K76" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L76" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" ht="30.75" thickBot="1">
+    <row r="77" spans="2:13" ht="15.75" thickBot="1">
       <c r="B77" s="6">
         <v>5</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E77" s="7">
-        <v>423</v>
-      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
       <c r="F77" s="8">
         <v>5</v>
       </c>
-      <c r="G77" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I77" s="7">
-        <v>423</v>
-      </c>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
       <c r="J77" s="8">
         <v>5</v>
       </c>
-      <c r="K77" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M77" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+    </row>
+    <row r="78" spans="2:13" ht="15.75" thickBot="1">
       <c r="B78" s="6">
         <v>6</v>
       </c>
@@ -2640,27 +2500,15 @@
       <c r="F78" s="8">
         <v>6</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I78" s="7">
-        <v>423</v>
-      </c>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
       <c r="J78" s="8">
         <v>6</v>
       </c>
-      <c r="K78" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M78" s="7">
-        <v>423</v>
-      </c>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" spans="2:13" ht="15.75" thickBot="1">
       <c r="B79" s="6">
@@ -2672,97 +2520,77 @@
       <c r="F79" s="8">
         <v>7</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
       <c r="I79" s="7"/>
       <c r="J79" s="8">
         <v>7</v>
       </c>
-      <c r="K79" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="2:13" ht="15.75">
-      <c r="B80" s="16"/>
-      <c r="C80" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="16"/>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="10"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
     </row>
     <row r="81" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B81" s="17"/>
-      <c r="C81" s="5">
-        <v>46309</v>
-      </c>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="11">
-        <v>46316</v>
-      </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="11">
-        <v>46323</v>
-      </c>
-      <c r="L81" s="17"/>
-      <c r="M81" s="17"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="16">
-        <v>1</v>
-      </c>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="16">
-        <v>1</v>
-      </c>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="16">
-        <v>1</v>
-      </c>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
+      <c r="B82" s="13">
+        <v>1</v>
+      </c>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="13">
+        <v>1</v>
+      </c>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="13">
+        <v>1</v>
+      </c>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
     </row>
     <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="17"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="17"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
-      <c r="M83" s="15"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
+      <c r="M83" s="16"/>
     </row>
     <row r="84" spans="2:13" ht="15.75" thickBot="1">
       <c r="B84" s="6">
@@ -2814,173 +2642,103 @@
       <c r="F86" s="8">
         <v>4</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
       <c r="I86" s="7"/>
       <c r="J86" s="8">
         <v>4</v>
       </c>
-      <c r="K86" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="30.75" thickBot="1">
+    <row r="87" spans="2:13" ht="15.75" thickBot="1">
       <c r="B87" s="6">
         <v>5</v>
       </c>
-      <c r="C87" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="7">
-        <v>318</v>
-      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
       <c r="F87" s="8">
         <v>5</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I87" s="7">
-        <v>423</v>
-      </c>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
       <c r="J87" s="8">
         <v>5</v>
       </c>
-      <c r="K87" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M87" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" spans="2:13" ht="15.75" thickBot="1">
       <c r="B88" s="6">
         <v>6</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="7">
-        <v>318</v>
-      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
       <c r="F88" s="8">
         <v>6</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I88" s="7">
-        <v>423</v>
-      </c>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
       <c r="J88" s="8">
         <v>6</v>
       </c>
-      <c r="K88" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M88" s="7">
-        <v>423</v>
-      </c>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
+      <c r="M88" s="7"/>
     </row>
     <row r="89" spans="2:13" ht="15.75" thickBot="1">
       <c r="B89" s="6">
         <v>7</v>
       </c>
-      <c r="C89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="7">
-        <v>318</v>
-      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
       <c r="F89" s="8">
         <v>7</v>
       </c>
-      <c r="G89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="8">
         <v>7</v>
       </c>
-      <c r="K89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" spans="2:13" ht="15.75">
-      <c r="B90" s="16"/>
-      <c r="C90" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L90" s="16"/>
-      <c r="M90" s="16"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
     </row>
     <row r="91" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B91" s="17"/>
-      <c r="C91" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
-      <c r="G91" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L91" s="17"/>
-      <c r="M91" s="17"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="14"/>
     </row>
     <row r="92" spans="2:13" ht="16.5" thickBot="1">
       <c r="B92" s="6">
@@ -3002,7 +2760,7 @@
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
     </row>
-    <row r="93" spans="2:13" ht="30.75" thickBot="1">
+    <row r="93" spans="2:13" ht="15.75" thickBot="1">
       <c r="B93" s="6">
         <v>2</v>
       </c>
@@ -3012,27 +2770,15 @@
       <c r="F93" s="8">
         <v>2</v>
       </c>
-      <c r="G93" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" s="7">
-        <v>312</v>
-      </c>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
       <c r="J93" s="8">
         <v>2</v>
       </c>
-      <c r="K93" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L93" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M93" s="7">
-        <v>304</v>
-      </c>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
     </row>
     <row r="94" spans="2:13" ht="15.75" thickBot="1">
       <c r="B94" s="6">
@@ -3044,115 +2790,63 @@
       <c r="F94" s="8">
         <v>3</v>
       </c>
-      <c r="G94" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="7">
-        <v>423</v>
-      </c>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
       <c r="J94" s="8">
         <v>3</v>
       </c>
-      <c r="K94" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L94" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="30.75" thickBot="1">
+    <row r="95" spans="2:13" ht="15.75" thickBot="1">
       <c r="B95" s="6">
         <v>4</v>
       </c>
-      <c r="C95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95" s="7">
-        <v>312</v>
-      </c>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
       <c r="F95" s="8">
         <v>4</v>
       </c>
-      <c r="G95" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I95" s="7">
-        <v>423</v>
-      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
       <c r="J95" s="8">
         <v>4</v>
       </c>
-      <c r="K95" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M95" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+    </row>
+    <row r="96" spans="2:13" ht="15.75" thickBot="1">
       <c r="B96" s="6">
         <v>5</v>
       </c>
-      <c r="C96" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="7">
-        <v>423</v>
-      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
       <c r="F96" s="8">
         <v>5</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I96" s="7">
-        <v>423</v>
-      </c>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
       <c r="J96" s="8">
         <v>5</v>
       </c>
-      <c r="K96" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M96" s="7">
-        <v>423</v>
-      </c>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
     </row>
     <row r="97" spans="2:13" ht="16.5" thickBot="1">
       <c r="B97" s="6">
         <v>6</v>
       </c>
-      <c r="C97" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="7">
-        <v>423</v>
-      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
       <c r="F97" s="8">
         <v>6</v>
       </c>
@@ -3170,12 +2864,8 @@
       <c r="B98" s="6">
         <v>7</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="8">
         <v>7</v>
@@ -3191,44 +2881,32 @@
       <c r="M98" s="9"/>
     </row>
     <row r="99" spans="2:13" ht="15.75">
-      <c r="B99" s="16"/>
-      <c r="C99" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H99" s="16"/>
-      <c r="I99" s="16"/>
-      <c r="J99" s="16"/>
-      <c r="K99" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L99" s="16"/>
-      <c r="M99" s="16"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="13"/>
+      <c r="M99" s="13"/>
     </row>
     <row r="100" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B100" s="17"/>
-      <c r="C100" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="17"/>
-      <c r="G100" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-      <c r="J100" s="17"/>
-      <c r="K100" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L100" s="17"/>
-      <c r="M100" s="17"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="14"/>
     </row>
     <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
@@ -3240,15 +2918,9 @@
       <c r="F101" s="8">
         <v>1</v>
       </c>
-      <c r="G101" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I101" s="7">
-        <v>423</v>
-      </c>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
       <c r="J101" s="6">
         <v>1</v>
       </c>
@@ -3266,15 +2938,9 @@
       <c r="F102" s="8">
         <v>2</v>
       </c>
-      <c r="G102" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I102" s="7">
-        <v>423</v>
-      </c>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
       <c r="J102" s="6">
         <v>2</v>
       </c>
@@ -3302,19 +2968,13 @@
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="30.75" thickBot="1">
+    <row r="104" spans="2:13" ht="15.75" thickBot="1">
       <c r="B104" s="6">
         <v>4</v>
       </c>
-      <c r="C104" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E104" s="7">
-        <v>312</v>
-      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
       <c r="F104" s="8">
         <v>4</v>
       </c>
@@ -3324,29 +2984,17 @@
       <c r="J104" s="6">
         <v>4</v>
       </c>
-      <c r="K104" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M104" s="7">
-        <v>312</v>
-      </c>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
     </row>
     <row r="105" spans="2:13" ht="15.75" thickBot="1">
       <c r="B105" s="6">
         <v>5</v>
       </c>
-      <c r="C105" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E105" s="7">
-        <v>423</v>
-      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
       <c r="F105" s="8">
         <v>5</v>
       </c>
@@ -3356,29 +3004,17 @@
       <c r="J105" s="6">
         <v>5</v>
       </c>
-      <c r="K105" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L105" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M105" s="7">
-        <v>423</v>
-      </c>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7"/>
     </row>
     <row r="106" spans="2:13" ht="15.75" thickBot="1">
       <c r="B106" s="6">
         <v>6</v>
       </c>
-      <c r="C106" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E106" s="7">
-        <v>423</v>
-      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
       <c r="F106" s="8">
         <v>6</v>
       </c>
@@ -3388,26 +3024,16 @@
       <c r="J106" s="6">
         <v>6</v>
       </c>
-      <c r="K106" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M106" s="7">
-        <v>423</v>
-      </c>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7"/>
     </row>
     <row r="107" spans="2:13" ht="15.75" thickBot="1">
       <c r="B107" s="6">
         <v>7</v>
       </c>
-      <c r="C107" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
       <c r="E107" s="7"/>
       <c r="F107" s="8">
         <v>4</v>
@@ -3418,53 +3044,37 @@
       <c r="J107" s="6">
         <v>7</v>
       </c>
-      <c r="K107" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L107" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7"/>
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="2:13" ht="15.75">
-      <c r="B108" s="16"/>
-      <c r="C108" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
-      <c r="G108" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H108" s="16"/>
-      <c r="I108" s="16"/>
-      <c r="J108" s="16"/>
-      <c r="K108" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L108" s="16"/>
-      <c r="M108" s="16"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="13"/>
+      <c r="M108" s="13"/>
     </row>
     <row r="109" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B109" s="17"/>
-      <c r="C109" s="5">
-        <v>46312</v>
-      </c>
-      <c r="D109" s="17"/>
-      <c r="E109" s="17"/>
-      <c r="F109" s="17"/>
-      <c r="G109" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H109" s="17"/>
-      <c r="I109" s="17"/>
-      <c r="J109" s="17"/>
-      <c r="K109" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L109" s="17"/>
-      <c r="M109" s="17"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="14"/>
+      <c r="M109" s="14"/>
     </row>
     <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
@@ -3526,167 +3136,101 @@
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="30.75" thickBot="1">
+    <row r="113" spans="2:13" ht="15.75" thickBot="1">
       <c r="B113" s="6">
         <v>4</v>
       </c>
-      <c r="C113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E113" s="7">
-        <v>312</v>
-      </c>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
       <c r="F113" s="6">
         <v>4</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I113" s="7">
-        <v>312</v>
-      </c>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
       <c r="J113" s="6">
         <v>4</v>
       </c>
-      <c r="K113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L113" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M113" s="7">
-        <v>312</v>
-      </c>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" spans="2:13" ht="15.75" thickBot="1">
       <c r="B114" s="6">
         <v>5</v>
       </c>
-      <c r="C114" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E114" s="7">
-        <v>423</v>
-      </c>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
       <c r="F114" s="6">
         <v>5</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I114" s="7">
-        <v>423</v>
-      </c>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
       <c r="J114" s="6">
         <v>5</v>
       </c>
-      <c r="K114" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M114" s="7">
-        <v>423</v>
-      </c>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
     </row>
     <row r="115" spans="2:13" ht="15.75" thickBot="1">
       <c r="B115" s="6">
         <v>6</v>
       </c>
-      <c r="C115" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="7">
-        <v>423</v>
-      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
       <c r="F115" s="6">
         <v>6</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I115" s="7">
-        <v>423</v>
-      </c>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
       <c r="J115" s="6">
         <v>6</v>
       </c>
-      <c r="K115" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M115" s="7">
-        <v>423</v>
-      </c>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7"/>
+      <c r="M115" s="7"/>
     </row>
     <row r="116" spans="2:13" ht="15.75" thickBot="1">
       <c r="B116" s="6">
         <v>7</v>
       </c>
-      <c r="C116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
       <c r="E116" s="7"/>
       <c r="F116" s="6">
         <v>7</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="6">
         <v>7</v>
       </c>
-      <c r="K116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L116" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7"/>
       <c r="M116" s="7"/>
     </row>
     <row r="119" spans="2:13" ht="21" thickBot="1">
-      <c r="B119" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C119" s="13"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
-      <c r="J119" s="13"/>
-      <c r="K119" s="13"/>
-      <c r="L119" s="13"/>
-      <c r="M119" s="13"/>
+      <c r="B119" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="18"/>
+      <c r="I119" s="18"/>
+      <c r="J119" s="18"/>
+      <c r="K119" s="18"/>
+      <c r="L119" s="18"/>
+      <c r="M119" s="18"/>
     </row>
     <row r="120" spans="2:13" ht="15.75" thickBot="1">
       <c r="B120" s="2" t="s">
@@ -3727,47 +3271,35 @@
       </c>
     </row>
     <row r="121" spans="2:13" ht="15.75">
-      <c r="B121" s="16"/>
-      <c r="C121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
-      <c r="F121" s="16"/>
-      <c r="G121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H121" s="16"/>
-      <c r="I121" s="16"/>
-      <c r="J121" s="16"/>
-      <c r="K121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L121" s="16"/>
-      <c r="M121" s="16"/>
+      <c r="B121" s="13"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="13"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="13"/>
     </row>
     <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="17"/>
-      <c r="C122" s="5">
-        <v>46307</v>
-      </c>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="17"/>
-      <c r="G122" s="5">
-        <v>46314</v>
-      </c>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="17"/>
-      <c r="K122" s="5">
-        <v>46321</v>
-      </c>
-      <c r="L122" s="17"/>
-      <c r="M122" s="17"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
     </row>
     <row r="123" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B123" s="6">
+      <c r="B123" s="12">
         <v>1</v>
       </c>
       <c r="C123" s="7"/>
@@ -3787,7 +3319,7 @@
       <c r="M123" s="7"/>
     </row>
     <row r="124" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B124" s="6">
+      <c r="B124" s="12">
         <v>2</v>
       </c>
       <c r="C124" s="9"/>
@@ -3806,8 +3338,8 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B125" s="6">
+    <row r="125" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B125" s="12">
         <v>3</v>
       </c>
       <c r="C125" s="7"/>
@@ -3816,222 +3348,126 @@
       <c r="F125" s="8">
         <v>3</v>
       </c>
-      <c r="G125" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I125" s="7">
-        <v>423</v>
-      </c>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
       <c r="J125" s="8">
         <v>3</v>
       </c>
-      <c r="K125" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L125" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M125" s="7">
-        <v>423</v>
-      </c>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7"/>
+      <c r="M125" s="7"/>
     </row>
     <row r="126" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B126" s="6">
-        <v>4</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" s="7">
-        <v>318</v>
-      </c>
+      <c r="B126" s="12">
+        <v>4</v>
+      </c>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
       <c r="F126" s="8">
         <v>4</v>
       </c>
-      <c r="G126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I126" s="7">
-        <v>318</v>
-      </c>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
       <c r="J126" s="8">
         <v>4</v>
       </c>
-      <c r="K126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L126" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M126" s="7">
-        <v>318</v>
-      </c>
+      <c r="K126" s="7"/>
+      <c r="L126" s="7"/>
+      <c r="M126" s="7"/>
     </row>
     <row r="127" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B127" s="6">
-        <v>5</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="7">
-        <v>318</v>
-      </c>
+      <c r="B127" s="12">
+        <v>5</v>
+      </c>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
       <c r="F127" s="8">
         <v>5</v>
       </c>
-      <c r="G127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I127" s="7">
-        <v>318</v>
-      </c>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="7"/>
       <c r="J127" s="8">
         <v>5</v>
       </c>
-      <c r="K127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M127" s="7">
-        <v>318</v>
-      </c>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7"/>
+      <c r="M127" s="7"/>
     </row>
     <row r="128" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B128" s="6">
-        <v>6</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="7">
-        <v>318</v>
-      </c>
+      <c r="B128" s="12">
+        <v>6</v>
+      </c>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
       <c r="F128" s="8">
         <v>6</v>
       </c>
-      <c r="G128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I128" s="7">
-        <v>318</v>
-      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="7"/>
       <c r="J128" s="8">
         <v>6</v>
       </c>
-      <c r="K128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M128" s="7">
-        <v>318</v>
-      </c>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7"/>
+      <c r="M128" s="7"/>
     </row>
     <row r="129" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B129" s="6">
-        <v>7</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="7">
-        <v>318</v>
-      </c>
+      <c r="B129" s="12">
+        <v>7</v>
+      </c>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
       <c r="F129" s="8">
         <v>7</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I129" s="7">
-        <v>318</v>
-      </c>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="7"/>
       <c r="J129" s="8">
         <v>7</v>
       </c>
-      <c r="K129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M129" s="7">
-        <v>318</v>
-      </c>
+      <c r="K129" s="7"/>
+      <c r="L129" s="7"/>
+      <c r="M129" s="7"/>
     </row>
     <row r="130" spans="2:13" ht="15.75">
-      <c r="B130" s="16"/>
-      <c r="C130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H130" s="16"/>
-      <c r="I130" s="16"/>
-      <c r="J130" s="16"/>
-      <c r="K130" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L130" s="16"/>
-      <c r="M130" s="16"/>
+      <c r="B130" s="13"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="13"/>
+      <c r="J130" s="13"/>
+      <c r="K130" s="4"/>
+      <c r="L130" s="13"/>
+      <c r="M130" s="13"/>
     </row>
     <row r="131" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B131" s="17"/>
-      <c r="C131" s="5">
-        <v>46308</v>
-      </c>
-      <c r="D131" s="17"/>
-      <c r="E131" s="17"/>
-      <c r="F131" s="17"/>
-      <c r="G131" s="5">
-        <v>46315</v>
-      </c>
-      <c r="H131" s="17"/>
-      <c r="I131" s="17"/>
-      <c r="J131" s="17"/>
-      <c r="K131" s="5">
-        <v>46322</v>
-      </c>
-      <c r="L131" s="17"/>
-      <c r="M131" s="17"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="14"/>
+      <c r="E131" s="14"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="14"/>
+      <c r="I131" s="14"/>
+      <c r="J131" s="14"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="14"/>
+      <c r="M131" s="14"/>
     </row>
     <row r="132" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B132" s="6">
+      <c r="B132" s="12">
         <v>1</v>
       </c>
       <c r="C132" s="7"/>
@@ -4051,7 +3487,7 @@
       <c r="M132" s="7"/>
     </row>
     <row r="133" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B133" s="6">
+      <c r="B133" s="12">
         <v>2</v>
       </c>
       <c r="C133" s="7"/>
@@ -4070,19 +3506,13 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B134" s="6">
-        <v>3</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="7">
-        <v>312</v>
-      </c>
+    <row r="134" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B134" s="12">
+        <v>3</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
       <c r="F134" s="8">
         <v>3</v>
       </c>
@@ -4096,80 +3526,48 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B135" s="6">
-        <v>4</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E135" s="7">
-        <v>423</v>
-      </c>
+    <row r="135" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B135" s="12">
+        <v>4</v>
+      </c>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
       <c r="F135" s="8">
         <v>4</v>
       </c>
-      <c r="G135" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
       <c r="I135" s="7"/>
       <c r="J135" s="8">
         <v>4</v>
       </c>
-      <c r="K135" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L135" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B136" s="6">
-        <v>5</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E136" s="7">
-        <v>423</v>
-      </c>
+    <row r="136" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B136" s="12">
+        <v>5</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
       <c r="F136" s="8">
         <v>5</v>
       </c>
-      <c r="G136" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I136" s="7">
-        <v>423</v>
-      </c>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
       <c r="J136" s="8">
         <v>5</v>
       </c>
-      <c r="K136" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L136" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M136" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="137" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B137" s="6">
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
+    </row>
+    <row r="137" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B137" s="12">
         <v>6</v>
       </c>
       <c r="C137" s="7"/>
@@ -4178,30 +3576,18 @@
       <c r="F137" s="8">
         <v>6</v>
       </c>
-      <c r="G137" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I137" s="7">
-        <v>423</v>
-      </c>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7"/>
       <c r="J137" s="8">
         <v>6</v>
       </c>
-      <c r="K137" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M137" s="7">
-        <v>423</v>
-      </c>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="7"/>
     </row>
     <row r="138" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B138" s="6">
+      <c r="B138" s="12">
         <v>7</v>
       </c>
       <c r="C138" s="7"/>
@@ -4210,100 +3596,80 @@
       <c r="F138" s="8">
         <v>7</v>
       </c>
-      <c r="G138" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
       <c r="I138" s="7"/>
       <c r="J138" s="8">
         <v>7</v>
       </c>
-      <c r="K138" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L138" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
     <row r="139" spans="2:13" ht="15.75">
-      <c r="B139" s="16"/>
-      <c r="C139" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="16"/>
-      <c r="G139" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H139" s="16"/>
-      <c r="I139" s="16"/>
-      <c r="J139" s="16"/>
-      <c r="K139" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L139" s="16"/>
-      <c r="M139" s="16"/>
+      <c r="B139" s="13"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13"/>
+      <c r="G139" s="10"/>
+      <c r="H139" s="13"/>
+      <c r="I139" s="13"/>
+      <c r="J139" s="13"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="13"/>
+      <c r="M139" s="13"/>
     </row>
     <row r="140" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B140" s="17"/>
-      <c r="C140" s="5">
-        <v>46309</v>
-      </c>
-      <c r="D140" s="17"/>
-      <c r="E140" s="17"/>
-      <c r="F140" s="17"/>
-      <c r="G140" s="11">
-        <v>46316</v>
-      </c>
-      <c r="H140" s="17"/>
-      <c r="I140" s="17"/>
-      <c r="J140" s="17"/>
-      <c r="K140" s="11">
-        <v>46323</v>
-      </c>
-      <c r="L140" s="17"/>
-      <c r="M140" s="17"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="14"/>
+      <c r="J140" s="14"/>
+      <c r="K140" s="11"/>
+      <c r="L140" s="14"/>
+      <c r="M140" s="14"/>
     </row>
     <row r="141" spans="2:13">
-      <c r="B141" s="16">
-        <v>1</v>
-      </c>
-      <c r="C141" s="14"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
-      <c r="F141" s="16">
-        <v>1</v>
-      </c>
-      <c r="G141" s="14"/>
-      <c r="H141" s="14"/>
-      <c r="I141" s="14"/>
-      <c r="J141" s="16">
-        <v>1</v>
-      </c>
-      <c r="K141" s="14"/>
-      <c r="L141" s="14"/>
-      <c r="M141" s="14"/>
+      <c r="B141" s="13">
+        <v>1</v>
+      </c>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="13">
+        <v>1</v>
+      </c>
+      <c r="G141" s="15"/>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+      <c r="J141" s="13">
+        <v>1</v>
+      </c>
+      <c r="K141" s="15"/>
+      <c r="L141" s="15"/>
+      <c r="M141" s="15"/>
     </row>
     <row r="142" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B142" s="17"/>
-      <c r="C142" s="15"/>
-      <c r="D142" s="15"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="17"/>
-      <c r="G142" s="15"/>
-      <c r="H142" s="15"/>
-      <c r="I142" s="15"/>
-      <c r="J142" s="17"/>
-      <c r="K142" s="15"/>
-      <c r="L142" s="15"/>
-      <c r="M142" s="15"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="14"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="16"/>
+      <c r="I142" s="16"/>
+      <c r="J142" s="14"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
+      <c r="M142" s="16"/>
     </row>
     <row r="143" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B143" s="6">
+      <c r="B143" s="12">
         <v>2</v>
       </c>
       <c r="C143" s="7"/>
@@ -4323,7 +3689,7 @@
       <c r="M143" s="7"/>
     </row>
     <row r="144" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B144" s="6">
+      <c r="B144" s="12">
         <v>3</v>
       </c>
       <c r="C144" s="7"/>
@@ -4343,7 +3709,7 @@
       <c r="M144" s="7"/>
     </row>
     <row r="145" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B145" s="6">
+      <c r="B145" s="12">
         <v>4</v>
       </c>
       <c r="C145" s="7"/>
@@ -4352,176 +3718,106 @@
       <c r="F145" s="8">
         <v>4</v>
       </c>
-      <c r="G145" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
       <c r="I145" s="7"/>
       <c r="J145" s="8">
         <v>4</v>
       </c>
-      <c r="K145" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L145" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B146" s="6">
-        <v>5</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E146" s="7">
-        <v>318</v>
-      </c>
+    <row r="146" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B146" s="12">
+        <v>5</v>
+      </c>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
       <c r="F146" s="8">
         <v>5</v>
       </c>
-      <c r="G146" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I146" s="7">
-        <v>423</v>
-      </c>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
       <c r="J146" s="8">
         <v>5</v>
       </c>
-      <c r="K146" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L146" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M146" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="147" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B147" s="6">
-        <v>6</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E147" s="7">
-        <v>318</v>
-      </c>
+      <c r="K146" s="7"/>
+      <c r="L146" s="7"/>
+      <c r="M146" s="7"/>
+    </row>
+    <row r="147" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B147" s="12">
+        <v>6</v>
+      </c>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
       <c r="F147" s="8">
         <v>6</v>
       </c>
-      <c r="G147" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I147" s="7">
-        <v>423</v>
-      </c>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
       <c r="J147" s="8">
         <v>6</v>
       </c>
-      <c r="K147" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L147" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M147" s="7">
-        <v>423</v>
-      </c>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7"/>
+      <c r="M147" s="7"/>
     </row>
     <row r="148" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B148" s="6">
-        <v>7</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="7">
-        <v>318</v>
-      </c>
+      <c r="B148" s="12">
+        <v>7</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
       <c r="F148" s="8">
         <v>7</v>
       </c>
-      <c r="G148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
       <c r="I148" s="7"/>
       <c r="J148" s="8">
         <v>7</v>
       </c>
-      <c r="K148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L148" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
       <c r="M148" s="7"/>
     </row>
     <row r="149" spans="2:13" ht="15.75">
-      <c r="B149" s="16"/>
-      <c r="C149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H149" s="16"/>
-      <c r="I149" s="16"/>
-      <c r="J149" s="16"/>
-      <c r="K149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L149" s="16"/>
-      <c r="M149" s="16"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="13"/>
+      <c r="K149" s="4"/>
+      <c r="L149" s="13"/>
+      <c r="M149" s="13"/>
     </row>
     <row r="150" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B150" s="17"/>
-      <c r="C150" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D150" s="17"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17"/>
-      <c r="G150" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H150" s="17"/>
-      <c r="I150" s="17"/>
-      <c r="J150" s="17"/>
-      <c r="K150" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L150" s="17"/>
-      <c r="M150" s="17"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="14"/>
+      <c r="E150" s="14"/>
+      <c r="F150" s="14"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="14"/>
+      <c r="I150" s="14"/>
+      <c r="J150" s="14"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="14"/>
+      <c r="M150" s="14"/>
     </row>
     <row r="151" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B151" s="6">
+      <c r="B151" s="12">
         <v>1</v>
       </c>
       <c r="C151" s="7"/>
@@ -4540,8 +3836,8 @@
       <c r="L151" s="9"/>
       <c r="M151" s="9"/>
     </row>
-    <row r="152" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B152" s="6">
+    <row r="152" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B152" s="12">
         <v>2</v>
       </c>
       <c r="C152" s="7"/>
@@ -4550,30 +3846,18 @@
       <c r="F152" s="8">
         <v>2</v>
       </c>
-      <c r="G152" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I152" s="7">
-        <v>312</v>
-      </c>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7"/>
       <c r="J152" s="8">
         <v>2</v>
       </c>
-      <c r="K152" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L152" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M152" s="7">
-        <v>304</v>
-      </c>
+      <c r="K152" s="7"/>
+      <c r="L152" s="7"/>
+      <c r="M152" s="7"/>
     </row>
     <row r="153" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B153" s="6">
+      <c r="B153" s="12">
         <v>3</v>
       </c>
       <c r="C153" s="7"/>
@@ -4582,115 +3866,63 @@
       <c r="F153" s="8">
         <v>3</v>
       </c>
-      <c r="G153" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I153" s="7">
-        <v>423</v>
-      </c>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7"/>
       <c r="J153" s="8">
         <v>3</v>
       </c>
-      <c r="K153" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L153" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K153" s="7"/>
+      <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
-    <row r="154" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B154" s="6">
-        <v>4</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E154" s="7">
-        <v>312</v>
-      </c>
+    <row r="154" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B154" s="12">
+        <v>4</v>
+      </c>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
       <c r="F154" s="8">
         <v>4</v>
       </c>
-      <c r="G154" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I154" s="7">
-        <v>423</v>
-      </c>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="7"/>
       <c r="J154" s="8">
         <v>4</v>
       </c>
-      <c r="K154" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L154" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M154" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="155" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B155" s="6">
-        <v>5</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E155" s="7">
-        <v>423</v>
-      </c>
+      <c r="K154" s="7"/>
+      <c r="L154" s="7"/>
+      <c r="M154" s="7"/>
+    </row>
+    <row r="155" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B155" s="12">
+        <v>5</v>
+      </c>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
       <c r="F155" s="8">
         <v>5</v>
       </c>
-      <c r="G155" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I155" s="7">
-        <v>423</v>
-      </c>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="7"/>
       <c r="J155" s="8">
         <v>5</v>
       </c>
-      <c r="K155" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L155" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M155" s="7">
-        <v>423</v>
-      </c>
+      <c r="K155" s="7"/>
+      <c r="L155" s="7"/>
+      <c r="M155" s="7"/>
     </row>
     <row r="156" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B156" s="6">
-        <v>6</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E156" s="7">
-        <v>423</v>
-      </c>
+      <c r="B156" s="12">
+        <v>6</v>
+      </c>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
       <c r="F156" s="8">
         <v>6</v>
       </c>
@@ -4705,15 +3937,11 @@
       <c r="M156" s="9"/>
     </row>
     <row r="157" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B157" s="6">
-        <v>7</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B157" s="12">
+        <v>7</v>
+      </c>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="8">
         <v>7</v>
@@ -4729,47 +3957,35 @@
       <c r="M157" s="9"/>
     </row>
     <row r="158" spans="2:13" ht="15.75">
-      <c r="B158" s="16"/>
-      <c r="C158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H158" s="16"/>
-      <c r="I158" s="16"/>
-      <c r="J158" s="16"/>
-      <c r="K158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L158" s="16"/>
-      <c r="M158" s="16"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="4"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="13"/>
+      <c r="J158" s="13"/>
+      <c r="K158" s="4"/>
+      <c r="L158" s="13"/>
+      <c r="M158" s="13"/>
     </row>
     <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="17"/>
-      <c r="C159" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D159" s="17"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="17"/>
-      <c r="G159" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
-      <c r="K159" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L159" s="17"/>
-      <c r="M159" s="17"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="14"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="14"/>
+      <c r="I159" s="14"/>
+      <c r="J159" s="14"/>
+      <c r="K159" s="5"/>
+      <c r="L159" s="14"/>
+      <c r="M159" s="14"/>
     </row>
     <row r="160" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B160" s="6">
+      <c r="B160" s="12">
         <v>1</v>
       </c>
       <c r="C160" s="7"/>
@@ -4778,16 +3994,10 @@
       <c r="F160" s="8">
         <v>1</v>
       </c>
-      <c r="G160" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I160" s="7">
-        <v>423</v>
-      </c>
-      <c r="J160" s="6">
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="12">
         <v>1</v>
       </c>
       <c r="K160" s="7"/>
@@ -4795,7 +4005,7 @@
       <c r="M160" s="7"/>
     </row>
     <row r="161" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B161" s="6">
+      <c r="B161" s="12">
         <v>2</v>
       </c>
       <c r="C161" s="7"/>
@@ -4804,16 +4014,10 @@
       <c r="F161" s="8">
         <v>2</v>
       </c>
-      <c r="G161" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I161" s="7">
-        <v>423</v>
-      </c>
-      <c r="J161" s="6">
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="12">
         <v>2</v>
       </c>
       <c r="K161" s="7"/>
@@ -4821,7 +4025,7 @@
       <c r="M161" s="7"/>
     </row>
     <row r="162" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B162" s="6">
+      <c r="B162" s="12">
         <v>3</v>
       </c>
       <c r="C162" s="7"/>
@@ -4833,119 +4037,79 @@
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
-      <c r="J162" s="6">
+      <c r="J162" s="12">
         <v>3</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B163" s="6">
-        <v>4</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E163" s="7">
-        <v>312</v>
-      </c>
+    <row r="163" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B163" s="12">
+        <v>4</v>
+      </c>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
       <c r="F163" s="8">
         <v>4</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
-      <c r="J163" s="6">
-        <v>4</v>
-      </c>
-      <c r="K163" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L163" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M163" s="7">
-        <v>312</v>
-      </c>
+      <c r="J163" s="12">
+        <v>4</v>
+      </c>
+      <c r="K163" s="7"/>
+      <c r="L163" s="7"/>
+      <c r="M163" s="7"/>
     </row>
     <row r="164" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B164" s="6">
-        <v>5</v>
-      </c>
-      <c r="C164" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E164" s="7">
-        <v>423</v>
-      </c>
+      <c r="B164" s="12">
+        <v>5</v>
+      </c>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
       <c r="F164" s="8">
         <v>5</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
-      <c r="J164" s="6">
-        <v>5</v>
-      </c>
-      <c r="K164" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L164" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M164" s="7">
-        <v>423</v>
-      </c>
+      <c r="J164" s="12">
+        <v>5</v>
+      </c>
+      <c r="K164" s="7"/>
+      <c r="L164" s="7"/>
+      <c r="M164" s="7"/>
     </row>
     <row r="165" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B165" s="6">
-        <v>6</v>
-      </c>
-      <c r="C165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E165" s="7">
-        <v>423</v>
-      </c>
+      <c r="B165" s="12">
+        <v>6</v>
+      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
       <c r="F165" s="8">
         <v>6</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
       <c r="I165" s="7"/>
-      <c r="J165" s="6">
-        <v>6</v>
-      </c>
-      <c r="K165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L165" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M165" s="7">
-        <v>423</v>
-      </c>
+      <c r="J165" s="12">
+        <v>6</v>
+      </c>
+      <c r="K165" s="7"/>
+      <c r="L165" s="7"/>
+      <c r="M165" s="7"/>
     </row>
     <row r="166" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B166" s="6">
-        <v>7</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D166" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B166" s="12">
+        <v>7</v>
+      </c>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="8">
         <v>4</v>
@@ -4953,71 +4117,55 @@
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
-      <c r="J166" s="6">
-        <v>7</v>
-      </c>
-      <c r="K166" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L166" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="J166" s="12">
+        <v>7</v>
+      </c>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
     <row r="167" spans="2:13" ht="15.75">
-      <c r="B167" s="16"/>
-      <c r="C167" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D167" s="16"/>
-      <c r="E167" s="16"/>
-      <c r="F167" s="16"/>
-      <c r="G167" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H167" s="16"/>
-      <c r="I167" s="16"/>
-      <c r="J167" s="16"/>
-      <c r="K167" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L167" s="16"/>
-      <c r="M167" s="16"/>
+      <c r="B167" s="13"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="13"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="13"/>
+      <c r="K167" s="4"/>
+      <c r="L167" s="13"/>
+      <c r="M167" s="13"/>
     </row>
     <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="17"/>
-      <c r="C168" s="5">
-        <v>46312</v>
-      </c>
-      <c r="D168" s="17"/>
-      <c r="E168" s="17"/>
-      <c r="F168" s="17"/>
-      <c r="G168" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H168" s="17"/>
-      <c r="I168" s="17"/>
-      <c r="J168" s="17"/>
-      <c r="K168" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L168" s="17"/>
-      <c r="M168" s="17"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="14"/>
+      <c r="E168" s="14"/>
+      <c r="F168" s="14"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="14"/>
+      <c r="I168" s="14"/>
+      <c r="J168" s="14"/>
+      <c r="K168" s="5"/>
+      <c r="L168" s="14"/>
+      <c r="M168" s="14"/>
     </row>
     <row r="169" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B169" s="6">
+      <c r="B169" s="12">
         <v>1</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
-      <c r="F169" s="6">
+      <c r="F169" s="12">
         <v>1</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
-      <c r="J169" s="6">
+      <c r="J169" s="12">
         <v>1</v>
       </c>
       <c r="K169" s="7"/>
@@ -5025,19 +4173,19 @@
       <c r="M169" s="7"/>
     </row>
     <row r="170" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B170" s="6">
+      <c r="B170" s="12">
         <v>2</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
-      <c r="F170" s="6">
+      <c r="F170" s="12">
         <v>2</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
-      <c r="J170" s="6">
+      <c r="J170" s="12">
         <v>2</v>
       </c>
       <c r="K170" s="7"/>
@@ -5045,191 +4193,269 @@
       <c r="M170" s="7"/>
     </row>
     <row r="171" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B171" s="6">
+      <c r="B171" s="12">
         <v>3</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="6">
+      <c r="F171" s="12">
         <v>3</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
-      <c r="J171" s="6">
+      <c r="J171" s="12">
         <v>3</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B172" s="6">
-        <v>4</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E172" s="7">
-        <v>312</v>
-      </c>
-      <c r="F172" s="6">
-        <v>4</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I172" s="7">
-        <v>312</v>
-      </c>
-      <c r="J172" s="6">
-        <v>4</v>
-      </c>
-      <c r="K172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M172" s="7">
-        <v>312</v>
-      </c>
+    <row r="172" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B172" s="12">
+        <v>4</v>
+      </c>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="12">
+        <v>4</v>
+      </c>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="12">
+        <v>4</v>
+      </c>
+      <c r="K172" s="7"/>
+      <c r="L172" s="7"/>
+      <c r="M172" s="7"/>
     </row>
     <row r="173" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B173" s="6">
-        <v>5</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E173" s="7">
-        <v>423</v>
-      </c>
-      <c r="F173" s="6">
-        <v>5</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I173" s="7">
-        <v>423</v>
-      </c>
-      <c r="J173" s="6">
-        <v>5</v>
-      </c>
-      <c r="K173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M173" s="7">
-        <v>423</v>
-      </c>
+      <c r="B173" s="12">
+        <v>5</v>
+      </c>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="12">
+        <v>5</v>
+      </c>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="12">
+        <v>5</v>
+      </c>
+      <c r="K173" s="7"/>
+      <c r="L173" s="7"/>
+      <c r="M173" s="7"/>
     </row>
     <row r="174" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B174" s="6">
-        <v>6</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E174" s="7">
-        <v>423</v>
-      </c>
-      <c r="F174" s="6">
-        <v>6</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I174" s="7">
-        <v>423</v>
-      </c>
-      <c r="J174" s="6">
-        <v>6</v>
-      </c>
-      <c r="K174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M174" s="7">
-        <v>423</v>
-      </c>
+      <c r="B174" s="12">
+        <v>6</v>
+      </c>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="12">
+        <v>6</v>
+      </c>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="12">
+        <v>6</v>
+      </c>
+      <c r="K174" s="7"/>
+      <c r="L174" s="7"/>
+      <c r="M174" s="7"/>
     </row>
     <row r="175" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B175" s="6">
-        <v>7</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B175" s="12">
+        <v>7</v>
+      </c>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
       <c r="E175" s="7"/>
-      <c r="F175" s="6">
-        <v>7</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="F175" s="12">
+        <v>7</v>
+      </c>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
       <c r="I175" s="7"/>
-      <c r="J175" s="6">
-        <v>7</v>
-      </c>
-      <c r="K175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="J175" s="12">
+        <v>7</v>
+      </c>
+      <c r="K175" s="7"/>
+      <c r="L175" s="7"/>
       <c r="M175" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="L158:L159"/>
-    <mergeCell ref="M158:M159"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="L167:L168"/>
-    <mergeCell ref="M167:M168"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="M71:M72"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="M99:M100"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="J108:J109"/>
+    <mergeCell ref="M108:M109"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="L99:L100"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="L108:L109"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="B119:M119"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="J121:J122"/>
+    <mergeCell ref="L121:L122"/>
+    <mergeCell ref="M121:M122"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="L139:L140"/>
+    <mergeCell ref="M139:M140"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="H130:H131"/>
     <mergeCell ref="L141:L142"/>
     <mergeCell ref="M141:M142"/>
     <mergeCell ref="B149:B150"/>
@@ -5251,168 +4477,24 @@
     <mergeCell ref="D141:D142"/>
     <mergeCell ref="E141:E142"/>
     <mergeCell ref="F141:F142"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="B119:M119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="L121:L122"/>
-    <mergeCell ref="M121:M122"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="L99:L100"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="L108:L109"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="M99:M100"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="J108:J109"/>
-    <mergeCell ref="M108:M109"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="M71:M72"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="I158:I159"/>
+    <mergeCell ref="J158:J159"/>
+    <mergeCell ref="L158:L159"/>
+    <mergeCell ref="M158:M159"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="L167:L168"/>
+    <mergeCell ref="M167:M168"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="E158:E159"/>
+    <mergeCell ref="F158:F159"/>
+    <mergeCell ref="H158:H159"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="25">
   <si>
     <t>№</t>
   </si>
@@ -81,13 +81,16 @@
     <t>Суббота</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Ту-255,254</t>
+    <t>Иностранный язык (зачёт)</t>
   </si>
   <si>
-    <t>Информатика</t>
+    <t>Расписание занятий заочного отделения групп Эу-485,486</t>
   </si>
   <si>
-    <t xml:space="preserve">Расписание занятий заочного отделения групп </t>
+    <t>Расписание занятий заочного отделения групп Эу-358,359,360</t>
+  </si>
+  <si>
+    <t>Расписание занятий заочного отделения групп Эу-245</t>
   </si>
 </sst>
 </file>
@@ -229,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -264,14 +267,11 @@
     <xf numFmtId="16" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -279,11 +279,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +583,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="7.28515625" customWidth="1"/>
     <col min="6" max="6" width="6.42578125" style="1" customWidth="1"/>
@@ -597,20 +597,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="B1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -651,44 +651,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="13"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="14"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
@@ -741,7 +741,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>6</v>
@@ -753,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>6</v>
@@ -767,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -779,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>8</v>
@@ -791,7 +791,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>8</v>
@@ -805,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>8</v>
@@ -817,7 +817,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>8</v>
@@ -829,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>8</v>
@@ -843,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>10</v>
@@ -915,44 +915,44 @@
       </c>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="13"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="14"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
@@ -970,9 +970,7 @@
       <c r="J14" s="8">
         <v>1</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
@@ -992,9 +990,7 @@
       <c r="J15" s="8">
         <v>2</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
@@ -1003,7 +999,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>12</v>
@@ -1020,9 +1016,7 @@
       <c r="J16" s="8">
         <v>3</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
@@ -1031,7 +1025,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>6</v>
@@ -1043,7 +1037,7 @@
         <v>4</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>8</v>
@@ -1065,7 +1059,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>6</v>
@@ -1077,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>6</v>
@@ -1109,7 +1103,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>6</v>
@@ -1159,78 +1153,78 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="13"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B22" s="14"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="5">
         <v>46309</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="11">
         <v>46316</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
       <c r="K22" s="11">
         <v>46323</v>
       </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="13">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="13">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="13">
-        <v>1</v>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
+      <c r="B23" s="16">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="16">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="16">
+        <v>1</v>
+      </c>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
     </row>
     <row r="24" spans="2:13" ht="7.5" customHeight="1" thickBot="1">
-      <c r="B24" s="14"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B25" s="6">
@@ -1411,44 +1405,44 @@
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="13"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
       <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B32" s="14"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="5">
         <v>46310</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="5">
         <v>46317</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
       <c r="K32" s="5">
         <v>46324</v>
       </c>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
@@ -1659,44 +1653,44 @@
       <c r="M39" s="9"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="13"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
       <c r="K40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B41" s="14"/>
+      <c r="B41" s="17"/>
       <c r="C41" s="5">
         <v>46311</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
       <c r="G41" s="5">
         <v>46318</v>
       </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
       <c r="K41" s="5">
         <v>46325</v>
       </c>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
@@ -1895,44 +1889,44 @@
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B49" s="13"/>
+      <c r="B49" s="16"/>
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
       <c r="K49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B50" s="14"/>
+      <c r="B50" s="17"/>
       <c r="C50" s="5">
         <v>46312</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="5">
         <v>46319</v>
       </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
       <c r="K50" s="5">
         <v>46326</v>
       </c>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
     </row>
     <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
@@ -2141,20 +2135,20 @@
       <c r="M57" s="7"/>
     </row>
     <row r="60" spans="2:13" ht="21" thickBot="1">
-      <c r="B60" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
+      <c r="B60" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" thickBot="1">
       <c r="B61" s="2" t="s">
@@ -2195,32 +2189,44 @@
       </c>
     </row>
     <row r="62" spans="2:13" ht="15.75">
-      <c r="B62" s="13"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
     </row>
     <row r="63" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B63" s="14"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="5">
+        <v>46307</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="5">
+        <v>46314</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="5">
+        <v>46321</v>
+      </c>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" thickBot="1">
       <c r="B64" s="6">
@@ -2262,7 +2268,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" thickBot="1">
+    <row r="66" spans="2:13" ht="30.75" thickBot="1">
       <c r="B66" s="6">
         <v>3</v>
       </c>
@@ -2272,123 +2278,219 @@
       <c r="F66" s="8">
         <v>3</v>
       </c>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
+      <c r="G66" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I66" s="7">
+        <v>423</v>
+      </c>
       <c r="J66" s="8">
         <v>3</v>
       </c>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
+      <c r="K66" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M66" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="67" spans="2:13" ht="15.75" thickBot="1">
       <c r="B67" s="6">
         <v>4</v>
       </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
+      <c r="C67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="7">
+        <v>318</v>
+      </c>
       <c r="F67" s="8">
         <v>4</v>
       </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
+      <c r="G67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I67" s="7">
+        <v>318</v>
+      </c>
       <c r="J67" s="8">
         <v>4</v>
       </c>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
+      <c r="K67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M67" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="68" spans="2:13" ht="15.75" thickBot="1">
       <c r="B68" s="6">
         <v>5</v>
       </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
+      <c r="C68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="7">
+        <v>318</v>
+      </c>
       <c r="F68" s="8">
         <v>5</v>
       </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
+      <c r="G68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I68" s="7">
+        <v>318</v>
+      </c>
       <c r="J68" s="8">
         <v>5</v>
       </c>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c r="K68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M68" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="69" spans="2:13" ht="15.75" thickBot="1">
       <c r="B69" s="6">
         <v>6</v>
       </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
+      <c r="C69" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="7">
+        <v>318</v>
+      </c>
       <c r="F69" s="8">
         <v>6</v>
       </c>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
+      <c r="G69" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="7">
+        <v>318</v>
+      </c>
       <c r="J69" s="8">
         <v>6</v>
       </c>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
+      <c r="K69" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="70" spans="2:13" ht="15.75" thickBot="1">
       <c r="B70" s="6">
         <v>7</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
+      <c r="C70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="7">
+        <v>318</v>
+      </c>
       <c r="F70" s="8">
         <v>7</v>
       </c>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
+      <c r="G70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I70" s="7">
+        <v>318</v>
+      </c>
       <c r="J70" s="8">
         <v>7</v>
       </c>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
+      <c r="K70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M70" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="71" spans="2:13" ht="15.75">
-      <c r="B71" s="13"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
     </row>
     <row r="72" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B72" s="14"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="5">
+        <v>46308</v>
+      </c>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="5">
+        <v>46315</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="5">
+        <v>46322</v>
+      </c>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
@@ -2430,13 +2532,19 @@
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" ht="15.75" thickBot="1">
+    <row r="75" spans="2:13" ht="30.75" thickBot="1">
       <c r="B75" s="6">
         <v>3</v>
       </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+      <c r="C75" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="7">
+        <v>312</v>
+      </c>
       <c r="F75" s="8">
         <v>3</v>
       </c>
@@ -2450,47 +2558,79 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" ht="15.75" thickBot="1">
+    <row r="76" spans="2:13" ht="30.75" thickBot="1">
       <c r="B76" s="6">
         <v>4</v>
       </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
+      <c r="C76" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="7">
+        <v>423</v>
+      </c>
       <c r="F76" s="8">
         <v>4</v>
       </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
+      <c r="G76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I76" s="7"/>
       <c r="J76" s="8">
         <v>4</v>
       </c>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
+      <c r="K76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" ht="15.75" thickBot="1">
+    <row r="77" spans="2:13" ht="30.75" thickBot="1">
       <c r="B77" s="6">
         <v>5</v>
       </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
+      <c r="C77" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" s="7">
+        <v>423</v>
+      </c>
       <c r="F77" s="8">
         <v>5</v>
       </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
+      <c r="G77" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="7">
+        <v>423</v>
+      </c>
       <c r="J77" s="8">
         <v>5</v>
       </c>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-    </row>
-    <row r="78" spans="2:13" ht="15.75" thickBot="1">
+      <c r="K77" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M77" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" ht="30.75" thickBot="1">
       <c r="B78" s="6">
         <v>6</v>
       </c>
@@ -2500,15 +2640,27 @@
       <c r="F78" s="8">
         <v>6</v>
       </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
+      <c r="G78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="7">
+        <v>423</v>
+      </c>
       <c r="J78" s="8">
         <v>6</v>
       </c>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
+      <c r="K78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M78" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="79" spans="2:13" ht="15.75" thickBot="1">
       <c r="B79" s="6">
@@ -2520,77 +2672,97 @@
       <c r="F79" s="8">
         <v>7</v>
       </c>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
+      <c r="G79" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I79" s="7"/>
       <c r="J79" s="8">
         <v>7</v>
       </c>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
+      <c r="K79" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="2:13" ht="15.75">
-      <c r="B80" s="13"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="13"/>
-      <c r="M80" s="13"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L80" s="16"/>
+      <c r="M80" s="16"/>
     </row>
     <row r="81" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B81" s="14"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="5">
+        <v>46309</v>
+      </c>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="11">
+        <v>46316</v>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="11">
+        <v>46323</v>
+      </c>
+      <c r="L81" s="17"/>
+      <c r="M81" s="17"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="13">
-        <v>1</v>
-      </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="13">
-        <v>1</v>
-      </c>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="13">
-        <v>1</v>
-      </c>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
-      <c r="M82" s="15"/>
+      <c r="B82" s="16">
+        <v>1</v>
+      </c>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="16">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="16">
+        <v>1</v>
+      </c>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
     </row>
     <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="14"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="17"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
     </row>
     <row r="84" spans="2:13" ht="15.75" thickBot="1">
       <c r="B84" s="6">
@@ -2642,103 +2814,173 @@
       <c r="F86" s="8">
         <v>4</v>
       </c>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
+      <c r="G86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I86" s="7"/>
       <c r="J86" s="8">
         <v>4</v>
       </c>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
+      <c r="K86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="15.75" thickBot="1">
+    <row r="87" spans="2:13" ht="30.75" thickBot="1">
       <c r="B87" s="6">
         <v>5</v>
       </c>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
+      <c r="C87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="7">
+        <v>318</v>
+      </c>
       <c r="F87" s="8">
         <v>5</v>
       </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
+      <c r="G87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87" s="7">
+        <v>423</v>
+      </c>
       <c r="J87" s="8">
         <v>5</v>
       </c>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
-    </row>
-    <row r="88" spans="2:13" ht="15.75" thickBot="1">
+      <c r="K87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M87" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" ht="30.75" thickBot="1">
       <c r="B88" s="6">
         <v>6</v>
       </c>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
+      <c r="C88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="7">
+        <v>318</v>
+      </c>
       <c r="F88" s="8">
         <v>6</v>
       </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
+      <c r="G88" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I88" s="7">
+        <v>423</v>
+      </c>
       <c r="J88" s="8">
         <v>6</v>
       </c>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
+      <c r="K88" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M88" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="89" spans="2:13" ht="15.75" thickBot="1">
       <c r="B89" s="6">
         <v>7</v>
       </c>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
+      <c r="C89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="7">
+        <v>318</v>
+      </c>
       <c r="F89" s="8">
         <v>7</v>
       </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
+      <c r="G89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I89" s="7"/>
       <c r="J89" s="8">
         <v>7</v>
       </c>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
+      <c r="K89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M89" s="7"/>
     </row>
     <row r="90" spans="2:13" ht="15.75">
-      <c r="B90" s="13"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="13"/>
-      <c r="M90" s="13"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="16"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L90" s="16"/>
+      <c r="M90" s="16"/>
     </row>
     <row r="91" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B91" s="14"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="14"/>
-      <c r="M91" s="14"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="5">
+        <v>46310</v>
+      </c>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="5">
+        <v>46317</v>
+      </c>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
+      <c r="K91" s="5">
+        <v>46324</v>
+      </c>
+      <c r="L91" s="17"/>
+      <c r="M91" s="17"/>
     </row>
     <row r="92" spans="2:13" ht="16.5" thickBot="1">
       <c r="B92" s="6">
@@ -2760,7 +3002,7 @@
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
     </row>
-    <row r="93" spans="2:13" ht="15.75" thickBot="1">
+    <row r="93" spans="2:13" ht="30.75" thickBot="1">
       <c r="B93" s="6">
         <v>2</v>
       </c>
@@ -2770,15 +3012,27 @@
       <c r="F93" s="8">
         <v>2</v>
       </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
+      <c r="G93" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" s="7">
+        <v>312</v>
+      </c>
       <c r="J93" s="8">
         <v>2</v>
       </c>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
+      <c r="K93" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M93" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="94" spans="2:13" ht="15.75" thickBot="1">
       <c r="B94" s="6">
@@ -2790,63 +3044,115 @@
       <c r="F94" s="8">
         <v>3</v>
       </c>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
+      <c r="G94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="7">
+        <v>423</v>
+      </c>
       <c r="J94" s="8">
         <v>3</v>
       </c>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
+      <c r="K94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L94" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="15.75" thickBot="1">
+    <row r="95" spans="2:13" ht="30.75" thickBot="1">
       <c r="B95" s="6">
         <v>4</v>
       </c>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+      <c r="C95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="7">
+        <v>312</v>
+      </c>
       <c r="F95" s="8">
         <v>4</v>
       </c>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
+      <c r="G95" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" s="7">
+        <v>423</v>
+      </c>
       <c r="J95" s="8">
         <v>4</v>
       </c>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
-    </row>
-    <row r="96" spans="2:13" ht="15.75" thickBot="1">
+      <c r="K95" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M95" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13" ht="30.75" thickBot="1">
       <c r="B96" s="6">
         <v>5</v>
       </c>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+      <c r="C96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="7">
+        <v>423</v>
+      </c>
       <c r="F96" s="8">
         <v>5</v>
       </c>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
+      <c r="G96" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I96" s="7">
+        <v>423</v>
+      </c>
       <c r="J96" s="8">
         <v>5</v>
       </c>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
+      <c r="K96" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M96" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="97" spans="2:13" ht="16.5" thickBot="1">
       <c r="B97" s="6">
         <v>6</v>
       </c>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
+      <c r="C97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="7">
+        <v>423</v>
+      </c>
       <c r="F97" s="8">
         <v>6</v>
       </c>
@@ -2864,8 +3170,12 @@
       <c r="B98" s="6">
         <v>7</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
+      <c r="C98" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E98" s="7"/>
       <c r="F98" s="8">
         <v>7</v>
@@ -2881,32 +3191,44 @@
       <c r="M98" s="9"/>
     </row>
     <row r="99" spans="2:13" ht="15.75">
-      <c r="B99" s="13"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="13"/>
-      <c r="M99" s="13"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+      <c r="K99" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99" s="16"/>
+      <c r="M99" s="16"/>
     </row>
     <row r="100" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B100" s="14"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="5">
+        <v>46311</v>
+      </c>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="5">
+        <v>46318</v>
+      </c>
+      <c r="H100" s="17"/>
+      <c r="I100" s="17"/>
+      <c r="J100" s="17"/>
+      <c r="K100" s="5">
+        <v>46325</v>
+      </c>
+      <c r="L100" s="17"/>
+      <c r="M100" s="17"/>
     </row>
     <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
@@ -2918,9 +3240,15 @@
       <c r="F101" s="8">
         <v>1</v>
       </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
+      <c r="G101" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I101" s="7">
+        <v>423</v>
+      </c>
       <c r="J101" s="6">
         <v>1</v>
       </c>
@@ -2938,9 +3266,15 @@
       <c r="F102" s="8">
         <v>2</v>
       </c>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
+      <c r="G102" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I102" s="7">
+        <v>423</v>
+      </c>
       <c r="J102" s="6">
         <v>2</v>
       </c>
@@ -2968,13 +3302,19 @@
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="15.75" thickBot="1">
+    <row r="104" spans="2:13" ht="30.75" thickBot="1">
       <c r="B104" s="6">
         <v>4</v>
       </c>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
+      <c r="C104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="7">
+        <v>312</v>
+      </c>
       <c r="F104" s="8">
         <v>4</v>
       </c>
@@ -2984,17 +3324,29 @@
       <c r="J104" s="6">
         <v>4</v>
       </c>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c r="K104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M104" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="105" spans="2:13" ht="15.75" thickBot="1">
       <c r="B105" s="6">
         <v>5</v>
       </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
+      <c r="C105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="7">
+        <v>423</v>
+      </c>
       <c r="F105" s="8">
         <v>5</v>
       </c>
@@ -3004,17 +3356,29 @@
       <c r="J105" s="6">
         <v>5</v>
       </c>
-      <c r="K105" s="7"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
+      <c r="K105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M105" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="106" spans="2:13" ht="15.75" thickBot="1">
       <c r="B106" s="6">
         <v>6</v>
       </c>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
+      <c r="C106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" s="7">
+        <v>423</v>
+      </c>
       <c r="F106" s="8">
         <v>6</v>
       </c>
@@ -3024,16 +3388,26 @@
       <c r="J106" s="6">
         <v>6</v>
       </c>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
+      <c r="K106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M106" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="107" spans="2:13" ht="15.75" thickBot="1">
       <c r="B107" s="6">
         <v>7</v>
       </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
+      <c r="C107" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E107" s="7"/>
       <c r="F107" s="8">
         <v>4</v>
@@ -3044,37 +3418,53 @@
       <c r="J107" s="6">
         <v>7</v>
       </c>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7"/>
+      <c r="K107" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="2:13" ht="15.75">
-      <c r="B108" s="13"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
-      <c r="J108" s="13"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="13"/>
-      <c r="M108" s="13"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="16"/>
+      <c r="I108" s="16"/>
+      <c r="J108" s="16"/>
+      <c r="K108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L108" s="16"/>
+      <c r="M108" s="16"/>
     </row>
     <row r="109" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B109" s="14"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="14"/>
-      <c r="I109" s="14"/>
-      <c r="J109" s="14"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="14"/>
-      <c r="M109" s="14"/>
+      <c r="B109" s="17"/>
+      <c r="C109" s="5">
+        <v>46312</v>
+      </c>
+      <c r="D109" s="17"/>
+      <c r="E109" s="17"/>
+      <c r="F109" s="17"/>
+      <c r="G109" s="5">
+        <v>46319</v>
+      </c>
+      <c r="H109" s="17"/>
+      <c r="I109" s="17"/>
+      <c r="J109" s="17"/>
+      <c r="K109" s="5">
+        <v>46326</v>
+      </c>
+      <c r="L109" s="17"/>
+      <c r="M109" s="17"/>
     </row>
     <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
@@ -3136,101 +3526,167 @@
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="15.75" thickBot="1">
+    <row r="113" spans="2:13" ht="30.75" thickBot="1">
       <c r="B113" s="6">
         <v>4</v>
       </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
+      <c r="C113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" s="7">
+        <v>312</v>
+      </c>
       <c r="F113" s="6">
         <v>4</v>
       </c>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
+      <c r="G113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" s="7">
+        <v>312</v>
+      </c>
       <c r="J113" s="6">
         <v>4</v>
       </c>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c r="K113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M113" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="114" spans="2:13" ht="15.75" thickBot="1">
       <c r="B114" s="6">
         <v>5</v>
       </c>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
+      <c r="C114" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" s="7">
+        <v>423</v>
+      </c>
       <c r="F114" s="6">
         <v>5</v>
       </c>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
+      <c r="G114" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I114" s="7">
+        <v>423</v>
+      </c>
       <c r="J114" s="6">
         <v>5</v>
       </c>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
+      <c r="K114" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M114" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="115" spans="2:13" ht="15.75" thickBot="1">
       <c r="B115" s="6">
         <v>6</v>
       </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
+      <c r="C115" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="7">
+        <v>423</v>
+      </c>
       <c r="F115" s="6">
         <v>6</v>
       </c>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
+      <c r="G115" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I115" s="7">
+        <v>423</v>
+      </c>
       <c r="J115" s="6">
         <v>6</v>
       </c>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
+      <c r="K115" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M115" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="116" spans="2:13" ht="15.75" thickBot="1">
       <c r="B116" s="6">
         <v>7</v>
       </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
+      <c r="C116" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E116" s="7"/>
       <c r="F116" s="6">
         <v>7</v>
       </c>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
+      <c r="G116" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I116" s="7"/>
       <c r="J116" s="6">
         <v>7</v>
       </c>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
+      <c r="K116" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L116" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M116" s="7"/>
     </row>
     <row r="119" spans="2:13" ht="21" thickBot="1">
-      <c r="B119" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C119" s="18"/>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18"/>
-      <c r="F119" s="18"/>
-      <c r="G119" s="18"/>
-      <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="18"/>
-      <c r="M119" s="18"/>
+      <c r="B119" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="13"/>
+      <c r="J119" s="13"/>
+      <c r="K119" s="13"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
     </row>
     <row r="120" spans="2:13" ht="15.75" thickBot="1">
       <c r="B120" s="2" t="s">
@@ -3271,35 +3727,47 @@
       </c>
     </row>
     <row r="121" spans="2:13" ht="15.75">
-      <c r="B121" s="13"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
-      <c r="J121" s="13"/>
-      <c r="K121" s="4"/>
-      <c r="L121" s="13"/>
-      <c r="M121" s="13"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="16"/>
+      <c r="G121" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H121" s="16"/>
+      <c r="I121" s="16"/>
+      <c r="J121" s="16"/>
+      <c r="K121" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L121" s="16"/>
+      <c r="M121" s="16"/>
     </row>
     <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="14"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="14"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="14"/>
-      <c r="I122" s="14"/>
-      <c r="J122" s="14"/>
-      <c r="K122" s="5"/>
-      <c r="L122" s="14"/>
-      <c r="M122" s="14"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="5">
+        <v>46307</v>
+      </c>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="17"/>
+      <c r="G122" s="5">
+        <v>46314</v>
+      </c>
+      <c r="H122" s="17"/>
+      <c r="I122" s="17"/>
+      <c r="J122" s="17"/>
+      <c r="K122" s="5">
+        <v>46321</v>
+      </c>
+      <c r="L122" s="17"/>
+      <c r="M122" s="17"/>
     </row>
     <row r="123" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B123" s="12">
+      <c r="B123" s="6">
         <v>1</v>
       </c>
       <c r="C123" s="7"/>
@@ -3319,7 +3787,7 @@
       <c r="M123" s="7"/>
     </row>
     <row r="124" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B124" s="12">
+      <c r="B124" s="6">
         <v>2</v>
       </c>
       <c r="C124" s="9"/>
@@ -3338,8 +3806,8 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B125" s="12">
+    <row r="125" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B125" s="6">
         <v>3</v>
       </c>
       <c r="C125" s="7"/>
@@ -3348,126 +3816,222 @@
       <c r="F125" s="8">
         <v>3</v>
       </c>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
+      <c r="G125" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I125" s="7">
+        <v>423</v>
+      </c>
       <c r="J125" s="8">
         <v>3</v>
       </c>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
+      <c r="K125" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L125" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M125" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="126" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B126" s="12">
-        <v>4</v>
-      </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
+      <c r="B126" s="6">
+        <v>4</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="7">
+        <v>318</v>
+      </c>
       <c r="F126" s="8">
         <v>4</v>
       </c>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
+      <c r="G126" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I126" s="7">
+        <v>318</v>
+      </c>
       <c r="J126" s="8">
         <v>4</v>
       </c>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
+      <c r="K126" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M126" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="127" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B127" s="12">
-        <v>5</v>
-      </c>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
+      <c r="B127" s="6">
+        <v>5</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="7">
+        <v>318</v>
+      </c>
       <c r="F127" s="8">
         <v>5</v>
       </c>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
+      <c r="G127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I127" s="7">
+        <v>318</v>
+      </c>
       <c r="J127" s="8">
         <v>5</v>
       </c>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
+      <c r="K127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M127" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="128" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B128" s="12">
-        <v>6</v>
-      </c>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
+      <c r="B128" s="6">
+        <v>6</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="7">
+        <v>318</v>
+      </c>
       <c r="F128" s="8">
         <v>6</v>
       </c>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
+      <c r="G128" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I128" s="7">
+        <v>318</v>
+      </c>
       <c r="J128" s="8">
         <v>6</v>
       </c>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c r="K128" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L128" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M128" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="129" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B129" s="12">
-        <v>7</v>
-      </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
+      <c r="B129" s="6">
+        <v>7</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" s="7">
+        <v>318</v>
+      </c>
       <c r="F129" s="8">
         <v>7</v>
       </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
+      <c r="G129" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I129" s="7">
+        <v>318</v>
+      </c>
       <c r="J129" s="8">
         <v>7</v>
       </c>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
+      <c r="K129" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M129" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="130" spans="2:13" ht="15.75">
-      <c r="B130" s="13"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="13"/>
-      <c r="J130" s="13"/>
-      <c r="K130" s="4"/>
-      <c r="L130" s="13"/>
-      <c r="M130" s="13"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H130" s="16"/>
+      <c r="I130" s="16"/>
+      <c r="J130" s="16"/>
+      <c r="K130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L130" s="16"/>
+      <c r="M130" s="16"/>
     </row>
     <row r="131" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B131" s="14"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="14"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="14"/>
-      <c r="I131" s="14"/>
-      <c r="J131" s="14"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="14"/>
-      <c r="M131" s="14"/>
+      <c r="B131" s="17"/>
+      <c r="C131" s="5">
+        <v>46308</v>
+      </c>
+      <c r="D131" s="17"/>
+      <c r="E131" s="17"/>
+      <c r="F131" s="17"/>
+      <c r="G131" s="5">
+        <v>46315</v>
+      </c>
+      <c r="H131" s="17"/>
+      <c r="I131" s="17"/>
+      <c r="J131" s="17"/>
+      <c r="K131" s="5">
+        <v>46322</v>
+      </c>
+      <c r="L131" s="17"/>
+      <c r="M131" s="17"/>
     </row>
     <row r="132" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B132" s="12">
+      <c r="B132" s="6">
         <v>1</v>
       </c>
       <c r="C132" s="7"/>
@@ -3487,7 +4051,7 @@
       <c r="M132" s="7"/>
     </row>
     <row r="133" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B133" s="12">
+      <c r="B133" s="6">
         <v>2</v>
       </c>
       <c r="C133" s="7"/>
@@ -3506,13 +4070,19 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B134" s="12">
-        <v>3</v>
-      </c>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
+    <row r="134" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B134" s="6">
+        <v>3</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="7">
+        <v>312</v>
+      </c>
       <c r="F134" s="8">
         <v>3</v>
       </c>
@@ -3526,48 +4096,80 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B135" s="12">
-        <v>4</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
+    <row r="135" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B135" s="6">
+        <v>4</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E135" s="7">
+        <v>423</v>
+      </c>
       <c r="F135" s="8">
         <v>4</v>
       </c>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
+      <c r="G135" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I135" s="7"/>
       <c r="J135" s="8">
         <v>4</v>
       </c>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
+      <c r="K135" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B136" s="12">
-        <v>5</v>
-      </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
+    <row r="136" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B136" s="6">
+        <v>5</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E136" s="7">
+        <v>423</v>
+      </c>
       <c r="F136" s="8">
         <v>5</v>
       </c>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7"/>
+      <c r="G136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I136" s="7">
+        <v>423</v>
+      </c>
       <c r="J136" s="8">
         <v>5</v>
       </c>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-    </row>
-    <row r="137" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B137" s="12">
+      <c r="K136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L136" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M136" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="137" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B137" s="6">
         <v>6</v>
       </c>
       <c r="C137" s="7"/>
@@ -3576,18 +4178,30 @@
       <c r="F137" s="8">
         <v>6</v>
       </c>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
+      <c r="G137" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I137" s="7">
+        <v>423</v>
+      </c>
       <c r="J137" s="8">
         <v>6</v>
       </c>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c r="K137" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M137" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="138" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B138" s="12">
+      <c r="B138" s="6">
         <v>7</v>
       </c>
       <c r="C138" s="7"/>
@@ -3596,80 +4210,100 @@
       <c r="F138" s="8">
         <v>7</v>
       </c>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
+      <c r="G138" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I138" s="7"/>
       <c r="J138" s="8">
         <v>7</v>
       </c>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
+      <c r="K138" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M138" s="7"/>
     </row>
     <row r="139" spans="2:13" ht="15.75">
-      <c r="B139" s="13"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
-      <c r="G139" s="10"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="13"/>
-      <c r="J139" s="13"/>
-      <c r="K139" s="10"/>
-      <c r="L139" s="13"/>
-      <c r="M139" s="13"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="16"/>
+      <c r="I139" s="16"/>
+      <c r="J139" s="16"/>
+      <c r="K139" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L139" s="16"/>
+      <c r="M139" s="16"/>
     </row>
     <row r="140" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B140" s="14"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="14"/>
-      <c r="E140" s="14"/>
-      <c r="F140" s="14"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="14"/>
-      <c r="I140" s="14"/>
-      <c r="J140" s="14"/>
-      <c r="K140" s="11"/>
-      <c r="L140" s="14"/>
-      <c r="M140" s="14"/>
+      <c r="B140" s="17"/>
+      <c r="C140" s="5">
+        <v>46309</v>
+      </c>
+      <c r="D140" s="17"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="17"/>
+      <c r="G140" s="11">
+        <v>46316</v>
+      </c>
+      <c r="H140" s="17"/>
+      <c r="I140" s="17"/>
+      <c r="J140" s="17"/>
+      <c r="K140" s="11">
+        <v>46323</v>
+      </c>
+      <c r="L140" s="17"/>
+      <c r="M140" s="17"/>
     </row>
     <row r="141" spans="2:13">
-      <c r="B141" s="13">
-        <v>1</v>
-      </c>
-      <c r="C141" s="15"/>
-      <c r="D141" s="15"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="13">
-        <v>1</v>
-      </c>
-      <c r="G141" s="15"/>
-      <c r="H141" s="15"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="13">
-        <v>1</v>
-      </c>
-      <c r="K141" s="15"/>
-      <c r="L141" s="15"/>
-      <c r="M141" s="15"/>
+      <c r="B141" s="16">
+        <v>1</v>
+      </c>
+      <c r="C141" s="14"/>
+      <c r="D141" s="14"/>
+      <c r="E141" s="14"/>
+      <c r="F141" s="16">
+        <v>1</v>
+      </c>
+      <c r="G141" s="14"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="14"/>
+      <c r="J141" s="16">
+        <v>1</v>
+      </c>
+      <c r="K141" s="14"/>
+      <c r="L141" s="14"/>
+      <c r="M141" s="14"/>
     </row>
     <row r="142" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B142" s="14"/>
-      <c r="C142" s="16"/>
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="14"/>
-      <c r="G142" s="16"/>
-      <c r="H142" s="16"/>
-      <c r="I142" s="16"/>
-      <c r="J142" s="14"/>
-      <c r="K142" s="16"/>
-      <c r="L142" s="16"/>
-      <c r="M142" s="16"/>
+      <c r="B142" s="17"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="17"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+      <c r="J142" s="17"/>
+      <c r="K142" s="15"/>
+      <c r="L142" s="15"/>
+      <c r="M142" s="15"/>
     </row>
     <row r="143" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B143" s="12">
+      <c r="B143" s="6">
         <v>2</v>
       </c>
       <c r="C143" s="7"/>
@@ -3689,7 +4323,7 @@
       <c r="M143" s="7"/>
     </row>
     <row r="144" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B144" s="12">
+      <c r="B144" s="6">
         <v>3</v>
       </c>
       <c r="C144" s="7"/>
@@ -3709,7 +4343,7 @@
       <c r="M144" s="7"/>
     </row>
     <row r="145" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B145" s="12">
+      <c r="B145" s="6">
         <v>4</v>
       </c>
       <c r="C145" s="7"/>
@@ -3718,106 +4352,176 @@
       <c r="F145" s="8">
         <v>4</v>
       </c>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
+      <c r="G145" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I145" s="7"/>
       <c r="J145" s="8">
         <v>4</v>
       </c>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7"/>
+      <c r="K145" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L145" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B146" s="12">
-        <v>5</v>
-      </c>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
+    <row r="146" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B146" s="6">
+        <v>5</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="7">
+        <v>318</v>
+      </c>
       <c r="F146" s="8">
         <v>5</v>
       </c>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="7"/>
+      <c r="G146" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I146" s="7">
+        <v>423</v>
+      </c>
       <c r="J146" s="8">
         <v>5</v>
       </c>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="7"/>
-    </row>
-    <row r="147" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B147" s="12">
-        <v>6</v>
-      </c>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
+      <c r="K146" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L146" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M146" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="147" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B147" s="6">
+        <v>6</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="7">
+        <v>318</v>
+      </c>
       <c r="F147" s="8">
         <v>6</v>
       </c>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
+      <c r="G147" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I147" s="7">
+        <v>423</v>
+      </c>
       <c r="J147" s="8">
         <v>6</v>
       </c>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
+      <c r="K147" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L147" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M147" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="148" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B148" s="12">
-        <v>7</v>
-      </c>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
+      <c r="B148" s="6">
+        <v>7</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="7">
+        <v>318</v>
+      </c>
       <c r="F148" s="8">
         <v>7</v>
       </c>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
+      <c r="G148" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I148" s="7"/>
       <c r="J148" s="8">
         <v>7</v>
       </c>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
+      <c r="K148" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L148" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M148" s="7"/>
     </row>
     <row r="149" spans="2:13" ht="15.75">
-      <c r="B149" s="13"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="13"/>
-      <c r="K149" s="4"/>
-      <c r="L149" s="13"/>
-      <c r="M149" s="13"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H149" s="16"/>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L149" s="16"/>
+      <c r="M149" s="16"/>
     </row>
     <row r="150" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B150" s="14"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="14"/>
-      <c r="E150" s="14"/>
-      <c r="F150" s="14"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="14"/>
-      <c r="I150" s="14"/>
-      <c r="J150" s="14"/>
-      <c r="K150" s="5"/>
-      <c r="L150" s="14"/>
-      <c r="M150" s="14"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="5">
+        <v>46310</v>
+      </c>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="5">
+        <v>46317</v>
+      </c>
+      <c r="H150" s="17"/>
+      <c r="I150" s="17"/>
+      <c r="J150" s="17"/>
+      <c r="K150" s="5">
+        <v>46324</v>
+      </c>
+      <c r="L150" s="17"/>
+      <c r="M150" s="17"/>
     </row>
     <row r="151" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B151" s="12">
+      <c r="B151" s="6">
         <v>1</v>
       </c>
       <c r="C151" s="7"/>
@@ -3836,8 +4540,8 @@
       <c r="L151" s="9"/>
       <c r="M151" s="9"/>
     </row>
-    <row r="152" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B152" s="12">
+    <row r="152" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B152" s="6">
         <v>2</v>
       </c>
       <c r="C152" s="7"/>
@@ -3846,18 +4550,30 @@
       <c r="F152" s="8">
         <v>2</v>
       </c>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-      <c r="I152" s="7"/>
+      <c r="G152" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" s="7">
+        <v>312</v>
+      </c>
       <c r="J152" s="8">
         <v>2</v>
       </c>
-      <c r="K152" s="7"/>
-      <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
+      <c r="K152" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L152" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M152" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="153" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B153" s="12">
+      <c r="B153" s="6">
         <v>3</v>
       </c>
       <c r="C153" s="7"/>
@@ -3866,63 +4582,115 @@
       <c r="F153" s="8">
         <v>3</v>
       </c>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-      <c r="I153" s="7"/>
+      <c r="G153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I153" s="7">
+        <v>423</v>
+      </c>
       <c r="J153" s="8">
         <v>3</v>
       </c>
-      <c r="K153" s="7"/>
-      <c r="L153" s="7"/>
+      <c r="K153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L153" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="M153" s="7"/>
     </row>
-    <row r="154" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B154" s="12">
-        <v>4</v>
-      </c>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+    <row r="154" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B154" s="6">
+        <v>4</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" s="7">
+        <v>312</v>
+      </c>
       <c r="F154" s="8">
         <v>4</v>
       </c>
-      <c r="G154" s="7"/>
-      <c r="H154" s="7"/>
-      <c r="I154" s="7"/>
+      <c r="G154" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I154" s="7">
+        <v>423</v>
+      </c>
       <c r="J154" s="8">
         <v>4</v>
       </c>
-      <c r="K154" s="7"/>
-      <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
-    </row>
-    <row r="155" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B155" s="12">
-        <v>5</v>
-      </c>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
+      <c r="K154" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L154" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M154" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="155" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B155" s="6">
+        <v>5</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="7">
+        <v>423</v>
+      </c>
       <c r="F155" s="8">
         <v>5</v>
       </c>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-      <c r="I155" s="7"/>
+      <c r="G155" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I155" s="7">
+        <v>423</v>
+      </c>
       <c r="J155" s="8">
         <v>5</v>
       </c>
-      <c r="K155" s="7"/>
-      <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c r="K155" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L155" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M155" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="156" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B156" s="12">
-        <v>6</v>
-      </c>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
+      <c r="B156" s="6">
+        <v>6</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="7">
+        <v>423</v>
+      </c>
       <c r="F156" s="8">
         <v>6</v>
       </c>
@@ -3937,11 +4705,15 @@
       <c r="M156" s="9"/>
     </row>
     <row r="157" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B157" s="12">
-        <v>7</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
+      <c r="B157" s="6">
+        <v>7</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E157" s="7"/>
       <c r="F157" s="8">
         <v>7</v>
@@ -3957,35 +4729,47 @@
       <c r="M157" s="9"/>
     </row>
     <row r="158" spans="2:13" ht="15.75">
-      <c r="B158" s="13"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="13"/>
-      <c r="E158" s="13"/>
-      <c r="F158" s="13"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
-      <c r="J158" s="13"/>
-      <c r="K158" s="4"/>
-      <c r="L158" s="13"/>
-      <c r="M158" s="13"/>
+      <c r="B158" s="16"/>
+      <c r="C158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" s="16"/>
+      <c r="I158" s="16"/>
+      <c r="J158" s="16"/>
+      <c r="K158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L158" s="16"/>
+      <c r="M158" s="16"/>
     </row>
     <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="14"/>
-      <c r="C159" s="5"/>
-      <c r="D159" s="14"/>
-      <c r="E159" s="14"/>
-      <c r="F159" s="14"/>
-      <c r="G159" s="5"/>
-      <c r="H159" s="14"/>
-      <c r="I159" s="14"/>
-      <c r="J159" s="14"/>
-      <c r="K159" s="5"/>
-      <c r="L159" s="14"/>
-      <c r="M159" s="14"/>
+      <c r="B159" s="17"/>
+      <c r="C159" s="5">
+        <v>46311</v>
+      </c>
+      <c r="D159" s="17"/>
+      <c r="E159" s="17"/>
+      <c r="F159" s="17"/>
+      <c r="G159" s="5">
+        <v>46318</v>
+      </c>
+      <c r="H159" s="17"/>
+      <c r="I159" s="17"/>
+      <c r="J159" s="17"/>
+      <c r="K159" s="5">
+        <v>46325</v>
+      </c>
+      <c r="L159" s="17"/>
+      <c r="M159" s="17"/>
     </row>
     <row r="160" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B160" s="12">
+      <c r="B160" s="6">
         <v>1</v>
       </c>
       <c r="C160" s="7"/>
@@ -3994,10 +4778,16 @@
       <c r="F160" s="8">
         <v>1</v>
       </c>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="12">
+      <c r="G160" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I160" s="7">
+        <v>423</v>
+      </c>
+      <c r="J160" s="6">
         <v>1</v>
       </c>
       <c r="K160" s="7"/>
@@ -4005,7 +4795,7 @@
       <c r="M160" s="7"/>
     </row>
     <row r="161" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B161" s="12">
+      <c r="B161" s="6">
         <v>2</v>
       </c>
       <c r="C161" s="7"/>
@@ -4014,10 +4804,16 @@
       <c r="F161" s="8">
         <v>2</v>
       </c>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="12">
+      <c r="G161" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I161" s="7">
+        <v>423</v>
+      </c>
+      <c r="J161" s="6">
         <v>2</v>
       </c>
       <c r="K161" s="7"/>
@@ -4025,7 +4821,7 @@
       <c r="M161" s="7"/>
     </row>
     <row r="162" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B162" s="12">
+      <c r="B162" s="6">
         <v>3</v>
       </c>
       <c r="C162" s="7"/>
@@ -4037,79 +4833,119 @@
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
-      <c r="J162" s="12">
+      <c r="J162" s="6">
         <v>3</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B163" s="12">
-        <v>4</v>
-      </c>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
+    <row r="163" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B163" s="6">
+        <v>4</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" s="7">
+        <v>312</v>
+      </c>
       <c r="F163" s="8">
         <v>4</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
-      <c r="J163" s="12">
-        <v>4</v>
-      </c>
-      <c r="K163" s="7"/>
-      <c r="L163" s="7"/>
-      <c r="M163" s="7"/>
+      <c r="J163" s="6">
+        <v>4</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L163" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M163" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="164" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B164" s="12">
-        <v>5</v>
-      </c>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
+      <c r="B164" s="6">
+        <v>5</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="7">
+        <v>423</v>
+      </c>
       <c r="F164" s="8">
         <v>5</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
-      <c r="J164" s="12">
-        <v>5</v>
-      </c>
-      <c r="K164" s="7"/>
-      <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c r="J164" s="6">
+        <v>5</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L164" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M164" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="165" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B165" s="12">
-        <v>6</v>
-      </c>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
+      <c r="B165" s="6">
+        <v>6</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" s="7">
+        <v>423</v>
+      </c>
       <c r="F165" s="8">
         <v>6</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
       <c r="I165" s="7"/>
-      <c r="J165" s="12">
-        <v>6</v>
-      </c>
-      <c r="K165" s="7"/>
-      <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c r="J165" s="6">
+        <v>6</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L165" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M165" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="166" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B166" s="12">
-        <v>7</v>
-      </c>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
+      <c r="B166" s="6">
+        <v>7</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E166" s="7"/>
       <c r="F166" s="8">
         <v>4</v>
@@ -4117,55 +4953,71 @@
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
-      <c r="J166" s="12">
-        <v>7</v>
-      </c>
-      <c r="K166" s="7"/>
-      <c r="L166" s="7"/>
+      <c r="J166" s="6">
+        <v>7</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L166" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M166" s="7"/>
     </row>
     <row r="167" spans="2:13" ht="15.75">
-      <c r="B167" s="13"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="13"/>
-      <c r="E167" s="13"/>
-      <c r="F167" s="13"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="13"/>
-      <c r="I167" s="13"/>
-      <c r="J167" s="13"/>
-      <c r="K167" s="4"/>
-      <c r="L167" s="13"/>
-      <c r="M167" s="13"/>
+      <c r="B167" s="16"/>
+      <c r="C167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="16"/>
+      <c r="E167" s="16"/>
+      <c r="F167" s="16"/>
+      <c r="G167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H167" s="16"/>
+      <c r="I167" s="16"/>
+      <c r="J167" s="16"/>
+      <c r="K167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L167" s="16"/>
+      <c r="M167" s="16"/>
     </row>
     <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="14"/>
-      <c r="C168" s="5"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="14"/>
-      <c r="F168" s="14"/>
-      <c r="G168" s="5"/>
-      <c r="H168" s="14"/>
-      <c r="I168" s="14"/>
-      <c r="J168" s="14"/>
-      <c r="K168" s="5"/>
-      <c r="L168" s="14"/>
-      <c r="M168" s="14"/>
+      <c r="B168" s="17"/>
+      <c r="C168" s="5">
+        <v>46312</v>
+      </c>
+      <c r="D168" s="17"/>
+      <c r="E168" s="17"/>
+      <c r="F168" s="17"/>
+      <c r="G168" s="5">
+        <v>46319</v>
+      </c>
+      <c r="H168" s="17"/>
+      <c r="I168" s="17"/>
+      <c r="J168" s="17"/>
+      <c r="K168" s="5">
+        <v>46326</v>
+      </c>
+      <c r="L168" s="17"/>
+      <c r="M168" s="17"/>
     </row>
     <row r="169" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B169" s="12">
+      <c r="B169" s="6">
         <v>1</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
-      <c r="F169" s="12">
+      <c r="F169" s="6">
         <v>1</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
-      <c r="J169" s="12">
+      <c r="J169" s="6">
         <v>1</v>
       </c>
       <c r="K169" s="7"/>
@@ -4173,19 +5025,19 @@
       <c r="M169" s="7"/>
     </row>
     <row r="170" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B170" s="12">
+      <c r="B170" s="6">
         <v>2</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
-      <c r="F170" s="12">
+      <c r="F170" s="6">
         <v>2</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
-      <c r="J170" s="12">
+      <c r="J170" s="6">
         <v>2</v>
       </c>
       <c r="K170" s="7"/>
@@ -4193,269 +5045,191 @@
       <c r="M170" s="7"/>
     </row>
     <row r="171" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B171" s="12">
+      <c r="B171" s="6">
         <v>3</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="12">
+      <c r="F171" s="6">
         <v>3</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
-      <c r="J171" s="12">
+      <c r="J171" s="6">
         <v>3</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B172" s="12">
-        <v>4</v>
-      </c>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="12">
-        <v>4</v>
-      </c>
-      <c r="G172" s="7"/>
-      <c r="H172" s="7"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="12">
-        <v>4</v>
-      </c>
-      <c r="K172" s="7"/>
-      <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+    <row r="172" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B172" s="6">
+        <v>4</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" s="7">
+        <v>312</v>
+      </c>
+      <c r="F172" s="6">
+        <v>4</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" s="7">
+        <v>312</v>
+      </c>
+      <c r="J172" s="6">
+        <v>4</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L172" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M172" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="173" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B173" s="12">
-        <v>5</v>
-      </c>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="12">
-        <v>5</v>
-      </c>
-      <c r="G173" s="7"/>
-      <c r="H173" s="7"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="12">
-        <v>5</v>
-      </c>
-      <c r="K173" s="7"/>
-      <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c r="B173" s="6">
+        <v>5</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="7">
+        <v>423</v>
+      </c>
+      <c r="F173" s="6">
+        <v>5</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I173" s="7">
+        <v>423</v>
+      </c>
+      <c r="J173" s="6">
+        <v>5</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M173" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="174" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B174" s="12">
-        <v>6</v>
-      </c>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="12">
-        <v>6</v>
-      </c>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
-      <c r="I174" s="7"/>
-      <c r="J174" s="12">
-        <v>6</v>
-      </c>
-      <c r="K174" s="7"/>
-      <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
+      <c r="B174" s="6">
+        <v>6</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="7">
+        <v>423</v>
+      </c>
+      <c r="F174" s="6">
+        <v>6</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I174" s="7">
+        <v>423</v>
+      </c>
+      <c r="J174" s="6">
+        <v>6</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M174" s="7">
+        <v>423</v>
+      </c>
     </row>
     <row r="175" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B175" s="12">
-        <v>7</v>
-      </c>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
+      <c r="B175" s="6">
+        <v>7</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E175" s="7"/>
-      <c r="F175" s="12">
-        <v>7</v>
-      </c>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
+      <c r="F175" s="6">
+        <v>7</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="I175" s="7"/>
-      <c r="J175" s="12">
-        <v>7</v>
-      </c>
-      <c r="K175" s="7"/>
-      <c r="L175" s="7"/>
+      <c r="J175" s="6">
+        <v>7</v>
+      </c>
+      <c r="K175" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L175" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="M175" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="M71:M72"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="M99:M100"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="J108:J109"/>
-    <mergeCell ref="M108:M109"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="L99:L100"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="L108:L109"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="B119:M119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="L121:L122"/>
-    <mergeCell ref="M121:M122"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="I158:I159"/>
+    <mergeCell ref="J158:J159"/>
+    <mergeCell ref="L158:L159"/>
+    <mergeCell ref="M158:M159"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="L167:L168"/>
+    <mergeCell ref="M167:M168"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="E158:E159"/>
+    <mergeCell ref="F158:F159"/>
+    <mergeCell ref="H158:H159"/>
     <mergeCell ref="L141:L142"/>
     <mergeCell ref="M141:M142"/>
     <mergeCell ref="B149:B150"/>
@@ -4477,24 +5251,168 @@
     <mergeCell ref="D141:D142"/>
     <mergeCell ref="E141:E142"/>
     <mergeCell ref="F141:F142"/>
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="L158:L159"/>
-    <mergeCell ref="M158:M159"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="L167:L168"/>
-    <mergeCell ref="M167:M168"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="L139:L140"/>
+    <mergeCell ref="M139:M140"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="B119:M119"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="J121:J122"/>
+    <mergeCell ref="L121:L122"/>
+    <mergeCell ref="M121:M122"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="L99:L100"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="L108:L109"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="M99:M100"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="J108:J109"/>
+    <mergeCell ref="M108:M109"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="M71:M72"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="25">
   <si>
     <t>№</t>
   </si>
@@ -267,11 +267,11 @@
     <xf numFmtId="16" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -279,11 +279,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,20 +597,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -651,44 +651,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="16"/>
+      <c r="B3" s="12"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="17"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
@@ -752,15 +752,9 @@
       <c r="J7" s="8">
         <v>3</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="7">
-        <v>423</v>
-      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B8" s="6">
@@ -790,15 +784,9 @@
       <c r="J8" s="8">
         <v>4</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="7">
-        <v>318</v>
-      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B9" s="6">
@@ -828,15 +816,9 @@
       <c r="J9" s="8">
         <v>5</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="7">
-        <v>318</v>
-      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B10" s="6">
@@ -866,15 +848,9 @@
       <c r="J10" s="8">
         <v>6</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="7">
-        <v>318</v>
-      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B11" s="6">
@@ -904,55 +880,49 @@
       <c r="J11" s="8">
         <v>7</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="7">
-        <v>318</v>
-      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="16"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="17"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
@@ -1046,12 +1016,8 @@
       <c r="J17" s="8">
         <v>4</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -1082,15 +1048,9 @@
       <c r="J18" s="8">
         <v>5</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M18" s="7">
-        <v>423</v>
-      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B19" s="6">
@@ -1114,15 +1074,9 @@
       <c r="J19" s="8">
         <v>6</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M19" s="7">
-        <v>423</v>
-      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B20" s="6">
@@ -1144,68 +1098,64 @@
       <c r="J20" s="8">
         <v>7</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="16"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B22" s="17"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="5">
         <v>46309</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="11">
         <v>46316</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
       <c r="K22" s="11">
         <v>46323</v>
       </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="16">
+      <c r="B23" s="12">
         <v>1</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
-      <c r="F23" s="16">
+      <c r="F23" s="12">
         <v>1</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="16">
+      <c r="J23" s="12">
         <v>1</v>
       </c>
       <c r="K23" s="14"/>
@@ -1213,15 +1163,15 @@
       <c r="M23" s="14"/>
     </row>
     <row r="24" spans="2:13" ht="7.5" customHeight="1" thickBot="1">
-      <c r="B24" s="17"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="13"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
-      <c r="J24" s="17"/>
+      <c r="J24" s="13"/>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
@@ -1286,12 +1236,8 @@
       <c r="J27" s="8">
         <v>4</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -1322,15 +1268,9 @@
       <c r="J28" s="8">
         <v>5</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M28" s="7">
-        <v>423</v>
-      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B29" s="6">
@@ -1360,15 +1300,9 @@
       <c r="J29" s="8">
         <v>6</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M29" s="7">
-        <v>423</v>
-      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B30" s="6">
@@ -1396,53 +1330,49 @@
       <c r="J30" s="8">
         <v>7</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="16"/>
+      <c r="B31" s="12"/>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
       <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B32" s="17"/>
+      <c r="B32" s="13"/>
       <c r="C32" s="5">
         <v>46310</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="5">
         <v>46317</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
       <c r="K32" s="5">
         <v>46324</v>
       </c>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
@@ -1486,15 +1416,9 @@
       <c r="J34" s="8">
         <v>2</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="7">
-        <v>304</v>
-      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
     </row>
     <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B35" s="6">
@@ -1518,12 +1442,8 @@
       <c r="J35" s="8">
         <v>3</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
     <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -1554,15 +1474,9 @@
       <c r="J36" s="8">
         <v>4</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M36" s="7">
-        <v>423</v>
-      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
     </row>
     <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B37" s="6">
@@ -1592,15 +1506,9 @@
       <c r="J37" s="8">
         <v>5</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M37" s="7">
-        <v>423</v>
-      </c>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
     </row>
     <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B38" s="6">
@@ -1653,44 +1561,44 @@
       <c r="M39" s="9"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="16"/>
+      <c r="B40" s="12"/>
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
       <c r="K40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B41" s="17"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="5">
         <v>46311</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="5">
         <v>46318</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
       <c r="K41" s="5">
         <v>46325</v>
       </c>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
@@ -1786,15 +1694,9 @@
       <c r="J45" s="6">
         <v>4</v>
       </c>
-      <c r="K45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M45" s="7">
-        <v>312</v>
-      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
     </row>
     <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B46" s="6">
@@ -1818,15 +1720,9 @@
       <c r="J46" s="6">
         <v>5</v>
       </c>
-      <c r="K46" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="7">
-        <v>423</v>
-      </c>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
     </row>
     <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B47" s="6">
@@ -1850,15 +1746,9 @@
       <c r="J47" s="6">
         <v>6</v>
       </c>
-      <c r="K47" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="7">
-        <v>423</v>
-      </c>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
     </row>
     <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B48" s="6">
@@ -1880,53 +1770,49 @@
       <c r="J48" s="6">
         <v>7</v>
       </c>
-      <c r="K48" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B49" s="16"/>
+      <c r="B49" s="12"/>
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B50" s="17"/>
+      <c r="B50" s="13"/>
       <c r="C50" s="5">
         <v>46312</v>
       </c>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
       <c r="G50" s="5">
         <v>46319</v>
       </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
       <c r="K50" s="5">
         <v>46326</v>
       </c>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
     </row>
     <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
@@ -2016,15 +1902,9 @@
       <c r="J54" s="6">
         <v>4</v>
       </c>
-      <c r="K54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M54" s="7">
-        <v>312</v>
-      </c>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B55" s="6">
@@ -2054,15 +1934,9 @@
       <c r="J55" s="6">
         <v>5</v>
       </c>
-      <c r="K55" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M55" s="7">
-        <v>423</v>
-      </c>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
     </row>
     <row r="56" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B56" s="6">
@@ -2092,15 +1966,9 @@
       <c r="J56" s="6">
         <v>6</v>
       </c>
-      <c r="K56" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M56" s="7">
-        <v>423</v>
-      </c>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
     </row>
     <row r="57" spans="2:13" ht="15.75" thickBot="1">
       <c r="B57" s="6">
@@ -2126,29 +1994,25 @@
       <c r="J57" s="6">
         <v>7</v>
       </c>
-      <c r="K57" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
     <row r="60" spans="2:13" ht="21" thickBot="1">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" thickBot="1">
       <c r="B61" s="2" t="s">
@@ -2189,44 +2053,44 @@
       </c>
     </row>
     <row r="62" spans="2:13" ht="15.75">
-      <c r="B62" s="16"/>
+      <c r="B62" s="12"/>
       <c r="C62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
       <c r="G62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
-      <c r="J62" s="16"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
       <c r="K62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
     </row>
     <row r="63" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B63" s="17"/>
+      <c r="B63" s="13"/>
       <c r="C63" s="5">
         <v>46307</v>
       </c>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
       <c r="G63" s="5">
         <v>46314</v>
       </c>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
       <c r="K63" s="5">
         <v>46321</v>
       </c>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" thickBot="1">
       <c r="B64" s="6">
@@ -2268,7 +2132,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="30.75" thickBot="1">
+    <row r="66" spans="2:13" ht="15.75" thickBot="1">
       <c r="B66" s="6">
         <v>3</v>
       </c>
@@ -2290,15 +2154,9 @@
       <c r="J66" s="8">
         <v>3</v>
       </c>
-      <c r="K66" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M66" s="7">
-        <v>423</v>
-      </c>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" spans="2:13" ht="15.75" thickBot="1">
       <c r="B67" s="6">
@@ -2328,15 +2186,9 @@
       <c r="J67" s="8">
         <v>4</v>
       </c>
-      <c r="K67" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M67" s="7">
-        <v>318</v>
-      </c>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
     </row>
     <row r="68" spans="2:13" ht="15.75" thickBot="1">
       <c r="B68" s="6">
@@ -2366,15 +2218,9 @@
       <c r="J68" s="8">
         <v>5</v>
       </c>
-      <c r="K68" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M68" s="7">
-        <v>318</v>
-      </c>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
     </row>
     <row r="69" spans="2:13" ht="15.75" thickBot="1">
       <c r="B69" s="6">
@@ -2404,15 +2250,9 @@
       <c r="J69" s="8">
         <v>6</v>
       </c>
-      <c r="K69" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M69" s="7">
-        <v>318</v>
-      </c>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
     </row>
     <row r="70" spans="2:13" ht="15.75" thickBot="1">
       <c r="B70" s="6">
@@ -2442,55 +2282,49 @@
       <c r="J70" s="8">
         <v>7</v>
       </c>
-      <c r="K70" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M70" s="7">
-        <v>318</v>
-      </c>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" spans="2:13" ht="15.75">
-      <c r="B71" s="16"/>
+      <c r="B71" s="12"/>
       <c r="C71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
       <c r="G71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
       <c r="K71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
     </row>
     <row r="72" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B72" s="17"/>
+      <c r="B72" s="13"/>
       <c r="C72" s="5">
         <v>46308</v>
       </c>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
       <c r="G72" s="5">
         <v>46315</v>
       </c>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
       <c r="K72" s="5">
         <v>46322</v>
       </c>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
@@ -2584,12 +2418,8 @@
       <c r="J76" s="8">
         <v>4</v>
       </c>
-      <c r="K76" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L76" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
     <row r="77" spans="2:13" ht="30.75" thickBot="1">
@@ -2620,17 +2450,11 @@
       <c r="J77" s="8">
         <v>5</v>
       </c>
-      <c r="K77" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M77" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+    </row>
+    <row r="78" spans="2:13" ht="15.75" thickBot="1">
       <c r="B78" s="6">
         <v>6</v>
       </c>
@@ -2652,15 +2476,9 @@
       <c r="J78" s="8">
         <v>6</v>
       </c>
-      <c r="K78" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M78" s="7">
-        <v>423</v>
-      </c>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" spans="2:13" ht="15.75" thickBot="1">
       <c r="B79" s="6">
@@ -2682,68 +2500,64 @@
       <c r="J79" s="8">
         <v>7</v>
       </c>
-      <c r="K79" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="2:13" ht="15.75">
-      <c r="B80" s="16"/>
+      <c r="B80" s="12"/>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
       <c r="G80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H80" s="16"/>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
       <c r="K80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
     </row>
     <row r="81" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B81" s="17"/>
+      <c r="B81" s="13"/>
       <c r="C81" s="5">
         <v>46309</v>
       </c>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
       <c r="G81" s="11">
         <v>46316</v>
       </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
       <c r="K81" s="11">
         <v>46323</v>
       </c>
-      <c r="L81" s="17"/>
-      <c r="M81" s="17"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="16">
+      <c r="B82" s="12">
         <v>1</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
-      <c r="F82" s="16">
+      <c r="F82" s="12">
         <v>1</v>
       </c>
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
-      <c r="J82" s="16">
+      <c r="J82" s="12">
         <v>1</v>
       </c>
       <c r="K82" s="14"/>
@@ -2751,15 +2565,15 @@
       <c r="M82" s="14"/>
     </row>
     <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="17"/>
+      <c r="B83" s="13"/>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
-      <c r="F83" s="17"/>
+      <c r="F83" s="13"/>
       <c r="G83" s="15"/>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
-      <c r="J83" s="17"/>
+      <c r="J83" s="13"/>
       <c r="K83" s="15"/>
       <c r="L83" s="15"/>
       <c r="M83" s="15"/>
@@ -2824,15 +2638,11 @@
       <c r="J86" s="8">
         <v>4</v>
       </c>
-      <c r="K86" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="30.75" thickBot="1">
+    <row r="87" spans="2:13" ht="15.75" thickBot="1">
       <c r="B87" s="6">
         <v>5</v>
       </c>
@@ -2860,17 +2670,11 @@
       <c r="J87" s="8">
         <v>5</v>
       </c>
-      <c r="K87" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M87" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" spans="2:13" ht="15.75" thickBot="1">
       <c r="B88" s="6">
         <v>6</v>
       </c>
@@ -2898,15 +2702,9 @@
       <c r="J88" s="8">
         <v>6</v>
       </c>
-      <c r="K88" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M88" s="7">
-        <v>423</v>
-      </c>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
+      <c r="M88" s="7"/>
     </row>
     <row r="89" spans="2:13" ht="15.75" thickBot="1">
       <c r="B89" s="6">
@@ -2934,53 +2732,49 @@
       <c r="J89" s="8">
         <v>7</v>
       </c>
-      <c r="K89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" spans="2:13" ht="15.75">
-      <c r="B90" s="16"/>
+      <c r="B90" s="12"/>
       <c r="C90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
       <c r="G90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
       <c r="K90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L90" s="16"/>
-      <c r="M90" s="16"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="12"/>
     </row>
     <row r="91" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B91" s="17"/>
+      <c r="B91" s="13"/>
       <c r="C91" s="5">
         <v>46310</v>
       </c>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
       <c r="G91" s="5">
         <v>46317</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
       <c r="K91" s="5">
         <v>46324</v>
       </c>
-      <c r="L91" s="17"/>
-      <c r="M91" s="17"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
     </row>
     <row r="92" spans="2:13" ht="16.5" thickBot="1">
       <c r="B92" s="6">
@@ -3002,7 +2796,7 @@
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
     </row>
-    <row r="93" spans="2:13" ht="30.75" thickBot="1">
+    <row r="93" spans="2:13" ht="15.75" thickBot="1">
       <c r="B93" s="6">
         <v>2</v>
       </c>
@@ -3024,15 +2818,9 @@
       <c r="J93" s="8">
         <v>2</v>
       </c>
-      <c r="K93" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L93" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M93" s="7">
-        <v>304</v>
-      </c>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
     </row>
     <row r="94" spans="2:13" ht="15.75" thickBot="1">
       <c r="B94" s="6">
@@ -3056,15 +2844,11 @@
       <c r="J94" s="8">
         <v>3</v>
       </c>
-      <c r="K94" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L94" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="30.75" thickBot="1">
+    <row r="95" spans="2:13" ht="15.75" thickBot="1">
       <c r="B95" s="6">
         <v>4</v>
       </c>
@@ -3092,17 +2876,11 @@
       <c r="J95" s="8">
         <v>4</v>
       </c>
-      <c r="K95" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M95" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+    </row>
+    <row r="96" spans="2:13" ht="15.75" thickBot="1">
       <c r="B96" s="6">
         <v>5</v>
       </c>
@@ -3130,15 +2908,9 @@
       <c r="J96" s="8">
         <v>5</v>
       </c>
-      <c r="K96" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M96" s="7">
-        <v>423</v>
-      </c>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
     </row>
     <row r="97" spans="2:13" ht="16.5" thickBot="1">
       <c r="B97" s="6">
@@ -3191,44 +2963,44 @@
       <c r="M98" s="9"/>
     </row>
     <row r="99" spans="2:13" ht="15.75">
-      <c r="B99" s="16"/>
+      <c r="B99" s="12"/>
       <c r="C99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
       <c r="G99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H99" s="16"/>
-      <c r="I99" s="16"/>
-      <c r="J99" s="16"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
       <c r="K99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L99" s="16"/>
-      <c r="M99" s="16"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
     </row>
     <row r="100" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B100" s="17"/>
+      <c r="B100" s="13"/>
       <c r="C100" s="5">
         <v>46311</v>
       </c>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="17"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
       <c r="G100" s="5">
         <v>46318</v>
       </c>
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-      <c r="J100" s="17"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
       <c r="K100" s="5">
         <v>46325</v>
       </c>
-      <c r="L100" s="17"/>
-      <c r="M100" s="17"/>
+      <c r="L100" s="13"/>
+      <c r="M100" s="13"/>
     </row>
     <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
@@ -3302,7 +3074,7 @@
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="30.75" thickBot="1">
+    <row r="104" spans="2:13" ht="15.75" thickBot="1">
       <c r="B104" s="6">
         <v>4</v>
       </c>
@@ -3324,15 +3096,9 @@
       <c r="J104" s="6">
         <v>4</v>
       </c>
-      <c r="K104" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M104" s="7">
-        <v>312</v>
-      </c>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
     </row>
     <row r="105" spans="2:13" ht="15.75" thickBot="1">
       <c r="B105" s="6">
@@ -3356,15 +3122,9 @@
       <c r="J105" s="6">
         <v>5</v>
       </c>
-      <c r="K105" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L105" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M105" s="7">
-        <v>423</v>
-      </c>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7"/>
     </row>
     <row r="106" spans="2:13" ht="15.75" thickBot="1">
       <c r="B106" s="6">
@@ -3388,15 +3148,9 @@
       <c r="J106" s="6">
         <v>6</v>
       </c>
-      <c r="K106" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M106" s="7">
-        <v>423</v>
-      </c>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7"/>
     </row>
     <row r="107" spans="2:13" ht="15.75" thickBot="1">
       <c r="B107" s="6">
@@ -3418,53 +3172,49 @@
       <c r="J107" s="6">
         <v>7</v>
       </c>
-      <c r="K107" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L107" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7"/>
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="2:13" ht="15.75">
-      <c r="B108" s="16"/>
+      <c r="B108" s="12"/>
       <c r="C108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
       <c r="G108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H108" s="16"/>
-      <c r="I108" s="16"/>
-      <c r="J108" s="16"/>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
       <c r="K108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L108" s="16"/>
-      <c r="M108" s="16"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
     </row>
     <row r="109" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B109" s="17"/>
+      <c r="B109" s="13"/>
       <c r="C109" s="5">
         <v>46312</v>
       </c>
-      <c r="D109" s="17"/>
-      <c r="E109" s="17"/>
-      <c r="F109" s="17"/>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="13"/>
       <c r="G109" s="5">
         <v>46319</v>
       </c>
-      <c r="H109" s="17"/>
-      <c r="I109" s="17"/>
-      <c r="J109" s="17"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="13"/>
+      <c r="J109" s="13"/>
       <c r="K109" s="5">
         <v>46326</v>
       </c>
-      <c r="L109" s="17"/>
-      <c r="M109" s="17"/>
+      <c r="L109" s="13"/>
+      <c r="M109" s="13"/>
     </row>
     <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
@@ -3526,7 +3276,7 @@
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="30.75" thickBot="1">
+    <row r="113" spans="2:13" ht="15.75" thickBot="1">
       <c r="B113" s="6">
         <v>4</v>
       </c>
@@ -3554,15 +3304,9 @@
       <c r="J113" s="6">
         <v>4</v>
       </c>
-      <c r="K113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L113" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M113" s="7">
-        <v>312</v>
-      </c>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" spans="2:13" ht="15.75" thickBot="1">
       <c r="B114" s="6">
@@ -3592,15 +3336,9 @@
       <c r="J114" s="6">
         <v>5</v>
       </c>
-      <c r="K114" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M114" s="7">
-        <v>423</v>
-      </c>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
     </row>
     <row r="115" spans="2:13" ht="15.75" thickBot="1">
       <c r="B115" s="6">
@@ -3630,15 +3368,9 @@
       <c r="J115" s="6">
         <v>6</v>
       </c>
-      <c r="K115" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M115" s="7">
-        <v>423</v>
-      </c>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7"/>
+      <c r="M115" s="7"/>
     </row>
     <row r="116" spans="2:13" ht="15.75" thickBot="1">
       <c r="B116" s="6">
@@ -3664,29 +3396,25 @@
       <c r="J116" s="6">
         <v>7</v>
       </c>
-      <c r="K116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L116" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7"/>
       <c r="M116" s="7"/>
     </row>
     <row r="119" spans="2:13" ht="21" thickBot="1">
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C119" s="13"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
-      <c r="J119" s="13"/>
-      <c r="K119" s="13"/>
-      <c r="L119" s="13"/>
-      <c r="M119" s="13"/>
+      <c r="C119" s="17"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="17"/>
+      <c r="F119" s="17"/>
+      <c r="G119" s="17"/>
+      <c r="H119" s="17"/>
+      <c r="I119" s="17"/>
+      <c r="J119" s="17"/>
+      <c r="K119" s="17"/>
+      <c r="L119" s="17"/>
+      <c r="M119" s="17"/>
     </row>
     <row r="120" spans="2:13" ht="15.75" thickBot="1">
       <c r="B120" s="2" t="s">
@@ -3727,44 +3455,44 @@
       </c>
     </row>
     <row r="121" spans="2:13" ht="15.75">
-      <c r="B121" s="16"/>
+      <c r="B121" s="12"/>
       <c r="C121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
-      <c r="F121" s="16"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
       <c r="G121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H121" s="16"/>
-      <c r="I121" s="16"/>
-      <c r="J121" s="16"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
       <c r="K121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L121" s="16"/>
-      <c r="M121" s="16"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
     </row>
     <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="17"/>
+      <c r="B122" s="13"/>
       <c r="C122" s="5">
         <v>46307</v>
       </c>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="17"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
       <c r="G122" s="5">
         <v>46314</v>
       </c>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="17"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
       <c r="K122" s="5">
         <v>46321</v>
       </c>
-      <c r="L122" s="17"/>
-      <c r="M122" s="17"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
     </row>
     <row r="123" spans="2:13" ht="15.75" thickBot="1">
       <c r="B123" s="6">
@@ -3806,7 +3534,7 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="30.75" thickBot="1">
+    <row r="125" spans="2:13" ht="15.75" thickBot="1">
       <c r="B125" s="6">
         <v>3</v>
       </c>
@@ -3828,15 +3556,9 @@
       <c r="J125" s="8">
         <v>3</v>
       </c>
-      <c r="K125" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L125" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M125" s="7">
-        <v>423</v>
-      </c>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7"/>
+      <c r="M125" s="7"/>
     </row>
     <row r="126" spans="2:13" ht="15.75" thickBot="1">
       <c r="B126" s="6">
@@ -3866,15 +3588,9 @@
       <c r="J126" s="8">
         <v>4</v>
       </c>
-      <c r="K126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L126" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M126" s="7">
-        <v>318</v>
-      </c>
+      <c r="K126" s="7"/>
+      <c r="L126" s="7"/>
+      <c r="M126" s="7"/>
     </row>
     <row r="127" spans="2:13" ht="15.75" thickBot="1">
       <c r="B127" s="6">
@@ -3904,15 +3620,9 @@
       <c r="J127" s="8">
         <v>5</v>
       </c>
-      <c r="K127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M127" s="7">
-        <v>318</v>
-      </c>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7"/>
+      <c r="M127" s="7"/>
     </row>
     <row r="128" spans="2:13" ht="15.75" thickBot="1">
       <c r="B128" s="6">
@@ -3942,15 +3652,9 @@
       <c r="J128" s="8">
         <v>6</v>
       </c>
-      <c r="K128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M128" s="7">
-        <v>318</v>
-      </c>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7"/>
+      <c r="M128" s="7"/>
     </row>
     <row r="129" spans="2:13" ht="15.75" thickBot="1">
       <c r="B129" s="6">
@@ -3980,55 +3684,49 @@
       <c r="J129" s="8">
         <v>7</v>
       </c>
-      <c r="K129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M129" s="7">
-        <v>318</v>
-      </c>
+      <c r="K129" s="7"/>
+      <c r="L129" s="7"/>
+      <c r="M129" s="7"/>
     </row>
     <row r="130" spans="2:13" ht="15.75">
-      <c r="B130" s="16"/>
+      <c r="B130" s="12"/>
       <c r="C130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
-      <c r="F130" s="16"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
       <c r="G130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H130" s="16"/>
-      <c r="I130" s="16"/>
-      <c r="J130" s="16"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
       <c r="K130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L130" s="16"/>
-      <c r="M130" s="16"/>
+      <c r="L130" s="12"/>
+      <c r="M130" s="12"/>
     </row>
     <row r="131" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B131" s="17"/>
+      <c r="B131" s="13"/>
       <c r="C131" s="5">
         <v>46308</v>
       </c>
-      <c r="D131" s="17"/>
-      <c r="E131" s="17"/>
-      <c r="F131" s="17"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13"/>
       <c r="G131" s="5">
         <v>46315</v>
       </c>
-      <c r="H131" s="17"/>
-      <c r="I131" s="17"/>
-      <c r="J131" s="17"/>
+      <c r="H131" s="13"/>
+      <c r="I131" s="13"/>
+      <c r="J131" s="13"/>
       <c r="K131" s="5">
         <v>46322</v>
       </c>
-      <c r="L131" s="17"/>
-      <c r="M131" s="17"/>
+      <c r="L131" s="13"/>
+      <c r="M131" s="13"/>
     </row>
     <row r="132" spans="2:13" ht="15.75" thickBot="1">
       <c r="B132" s="6">
@@ -4122,12 +3820,8 @@
       <c r="J135" s="8">
         <v>4</v>
       </c>
-      <c r="K135" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L135" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
     <row r="136" spans="2:13" ht="30.75" thickBot="1">
@@ -4158,17 +3852,11 @@
       <c r="J136" s="8">
         <v>5</v>
       </c>
-      <c r="K136" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L136" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M136" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="137" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
+    </row>
+    <row r="137" spans="2:13" ht="15.75" thickBot="1">
       <c r="B137" s="6">
         <v>6</v>
       </c>
@@ -4190,15 +3878,9 @@
       <c r="J137" s="8">
         <v>6</v>
       </c>
-      <c r="K137" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M137" s="7">
-        <v>423</v>
-      </c>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="7"/>
     </row>
     <row r="138" spans="2:13" ht="15.75" thickBot="1">
       <c r="B138" s="6">
@@ -4220,68 +3902,64 @@
       <c r="J138" s="8">
         <v>7</v>
       </c>
-      <c r="K138" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L138" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
     <row r="139" spans="2:13" ht="15.75">
-      <c r="B139" s="16"/>
+      <c r="B139" s="12"/>
       <c r="C139" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D139" s="16"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="16"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
       <c r="G139" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H139" s="16"/>
-      <c r="I139" s="16"/>
-      <c r="J139" s="16"/>
+      <c r="H139" s="12"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="12"/>
       <c r="K139" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L139" s="16"/>
-      <c r="M139" s="16"/>
+      <c r="L139" s="12"/>
+      <c r="M139" s="12"/>
     </row>
     <row r="140" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B140" s="17"/>
+      <c r="B140" s="13"/>
       <c r="C140" s="5">
         <v>46309</v>
       </c>
-      <c r="D140" s="17"/>
-      <c r="E140" s="17"/>
-      <c r="F140" s="17"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="13"/>
       <c r="G140" s="11">
         <v>46316</v>
       </c>
-      <c r="H140" s="17"/>
-      <c r="I140" s="17"/>
-      <c r="J140" s="17"/>
+      <c r="H140" s="13"/>
+      <c r="I140" s="13"/>
+      <c r="J140" s="13"/>
       <c r="K140" s="11">
         <v>46323</v>
       </c>
-      <c r="L140" s="17"/>
-      <c r="M140" s="17"/>
+      <c r="L140" s="13"/>
+      <c r="M140" s="13"/>
     </row>
     <row r="141" spans="2:13">
-      <c r="B141" s="16">
+      <c r="B141" s="12">
         <v>1</v>
       </c>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
       <c r="E141" s="14"/>
-      <c r="F141" s="16">
+      <c r="F141" s="12">
         <v>1</v>
       </c>
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
-      <c r="J141" s="16">
+      <c r="J141" s="12">
         <v>1</v>
       </c>
       <c r="K141" s="14"/>
@@ -4289,15 +3967,15 @@
       <c r="M141" s="14"/>
     </row>
     <row r="142" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B142" s="17"/>
+      <c r="B142" s="13"/>
       <c r="C142" s="15"/>
       <c r="D142" s="15"/>
       <c r="E142" s="15"/>
-      <c r="F142" s="17"/>
+      <c r="F142" s="13"/>
       <c r="G142" s="15"/>
       <c r="H142" s="15"/>
       <c r="I142" s="15"/>
-      <c r="J142" s="17"/>
+      <c r="J142" s="13"/>
       <c r="K142" s="15"/>
       <c r="L142" s="15"/>
       <c r="M142" s="15"/>
@@ -4362,15 +4040,11 @@
       <c r="J145" s="8">
         <v>4</v>
       </c>
-      <c r="K145" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L145" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="30.75" thickBot="1">
+    <row r="146" spans="2:13" ht="15.75" thickBot="1">
       <c r="B146" s="6">
         <v>5</v>
       </c>
@@ -4398,17 +4072,11 @@
       <c r="J146" s="8">
         <v>5</v>
       </c>
-      <c r="K146" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L146" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M146" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="147" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K146" s="7"/>
+      <c r="L146" s="7"/>
+      <c r="M146" s="7"/>
+    </row>
+    <row r="147" spans="2:13" ht="15.75" thickBot="1">
       <c r="B147" s="6">
         <v>6</v>
       </c>
@@ -4436,15 +4104,9 @@
       <c r="J147" s="8">
         <v>6</v>
       </c>
-      <c r="K147" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L147" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M147" s="7">
-        <v>423</v>
-      </c>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7"/>
+      <c r="M147" s="7"/>
     </row>
     <row r="148" spans="2:13" ht="15.75" thickBot="1">
       <c r="B148" s="6">
@@ -4472,53 +4134,49 @@
       <c r="J148" s="8">
         <v>7</v>
       </c>
-      <c r="K148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L148" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
       <c r="M148" s="7"/>
     </row>
     <row r="149" spans="2:13" ht="15.75">
-      <c r="B149" s="16"/>
+      <c r="B149" s="12"/>
       <c r="C149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
+      <c r="D149" s="12"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
       <c r="G149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H149" s="16"/>
-      <c r="I149" s="16"/>
-      <c r="J149" s="16"/>
+      <c r="H149" s="12"/>
+      <c r="I149" s="12"/>
+      <c r="J149" s="12"/>
       <c r="K149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L149" s="16"/>
-      <c r="M149" s="16"/>
+      <c r="L149" s="12"/>
+      <c r="M149" s="12"/>
     </row>
     <row r="150" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B150" s="17"/>
+      <c r="B150" s="13"/>
       <c r="C150" s="5">
         <v>46310</v>
       </c>
-      <c r="D150" s="17"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
       <c r="G150" s="5">
         <v>46317</v>
       </c>
-      <c r="H150" s="17"/>
-      <c r="I150" s="17"/>
-      <c r="J150" s="17"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="13"/>
       <c r="K150" s="5">
         <v>46324</v>
       </c>
-      <c r="L150" s="17"/>
-      <c r="M150" s="17"/>
+      <c r="L150" s="13"/>
+      <c r="M150" s="13"/>
     </row>
     <row r="151" spans="2:13" ht="16.5" thickBot="1">
       <c r="B151" s="6">
@@ -4540,7 +4198,7 @@
       <c r="L151" s="9"/>
       <c r="M151" s="9"/>
     </row>
-    <row r="152" spans="2:13" ht="30.75" thickBot="1">
+    <row r="152" spans="2:13" ht="15.75" thickBot="1">
       <c r="B152" s="6">
         <v>2</v>
       </c>
@@ -4562,15 +4220,9 @@
       <c r="J152" s="8">
         <v>2</v>
       </c>
-      <c r="K152" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L152" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M152" s="7">
-        <v>304</v>
-      </c>
+      <c r="K152" s="7"/>
+      <c r="L152" s="7"/>
+      <c r="M152" s="7"/>
     </row>
     <row r="153" spans="2:13" ht="15.75" thickBot="1">
       <c r="B153" s="6">
@@ -4594,15 +4246,11 @@
       <c r="J153" s="8">
         <v>3</v>
       </c>
-      <c r="K153" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L153" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="K153" s="7"/>
+      <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
-    <row r="154" spans="2:13" ht="30.75" thickBot="1">
+    <row r="154" spans="2:13" ht="15.75" thickBot="1">
       <c r="B154" s="6">
         <v>4</v>
       </c>
@@ -4630,17 +4278,11 @@
       <c r="J154" s="8">
         <v>4</v>
       </c>
-      <c r="K154" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L154" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M154" s="7">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="155" spans="2:13" ht="30.75" thickBot="1">
+      <c r="K154" s="7"/>
+      <c r="L154" s="7"/>
+      <c r="M154" s="7"/>
+    </row>
+    <row r="155" spans="2:13" ht="15.75" thickBot="1">
       <c r="B155" s="6">
         <v>5</v>
       </c>
@@ -4668,15 +4310,9 @@
       <c r="J155" s="8">
         <v>5</v>
       </c>
-      <c r="K155" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L155" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M155" s="7">
-        <v>423</v>
-      </c>
+      <c r="K155" s="7"/>
+      <c r="L155" s="7"/>
+      <c r="M155" s="7"/>
     </row>
     <row r="156" spans="2:13" ht="16.5" thickBot="1">
       <c r="B156" s="6">
@@ -4729,44 +4365,44 @@
       <c r="M157" s="9"/>
     </row>
     <row r="158" spans="2:13" ht="15.75">
-      <c r="B158" s="16"/>
+      <c r="B158" s="12"/>
       <c r="C158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
+      <c r="D158" s="12"/>
+      <c r="E158" s="12"/>
+      <c r="F158" s="12"/>
       <c r="G158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H158" s="16"/>
-      <c r="I158" s="16"/>
-      <c r="J158" s="16"/>
+      <c r="H158" s="12"/>
+      <c r="I158" s="12"/>
+      <c r="J158" s="12"/>
       <c r="K158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L158" s="16"/>
-      <c r="M158" s="16"/>
+      <c r="L158" s="12"/>
+      <c r="M158" s="12"/>
     </row>
     <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="17"/>
+      <c r="B159" s="13"/>
       <c r="C159" s="5">
         <v>46311</v>
       </c>
-      <c r="D159" s="17"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="17"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="13"/>
+      <c r="F159" s="13"/>
       <c r="G159" s="5">
         <v>46318</v>
       </c>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
+      <c r="H159" s="13"/>
+      <c r="I159" s="13"/>
+      <c r="J159" s="13"/>
       <c r="K159" s="5">
         <v>46325</v>
       </c>
-      <c r="L159" s="17"/>
-      <c r="M159" s="17"/>
+      <c r="L159" s="13"/>
+      <c r="M159" s="13"/>
     </row>
     <row r="160" spans="2:13" ht="15.75" thickBot="1">
       <c r="B160" s="6">
@@ -4840,7 +4476,7 @@
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="30.75" thickBot="1">
+    <row r="163" spans="2:13" ht="15.75" thickBot="1">
       <c r="B163" s="6">
         <v>4</v>
       </c>
@@ -4862,15 +4498,9 @@
       <c r="J163" s="6">
         <v>4</v>
       </c>
-      <c r="K163" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L163" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M163" s="7">
-        <v>312</v>
-      </c>
+      <c r="K163" s="7"/>
+      <c r="L163" s="7"/>
+      <c r="M163" s="7"/>
     </row>
     <row r="164" spans="2:13" ht="15.75" thickBot="1">
       <c r="B164" s="6">
@@ -4894,15 +4524,9 @@
       <c r="J164" s="6">
         <v>5</v>
       </c>
-      <c r="K164" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L164" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M164" s="7">
-        <v>423</v>
-      </c>
+      <c r="K164" s="7"/>
+      <c r="L164" s="7"/>
+      <c r="M164" s="7"/>
     </row>
     <row r="165" spans="2:13" ht="15.75" thickBot="1">
       <c r="B165" s="6">
@@ -4926,15 +4550,9 @@
       <c r="J165" s="6">
         <v>6</v>
       </c>
-      <c r="K165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L165" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M165" s="7">
-        <v>423</v>
-      </c>
+      <c r="K165" s="7"/>
+      <c r="L165" s="7"/>
+      <c r="M165" s="7"/>
     </row>
     <row r="166" spans="2:13" ht="15.75" thickBot="1">
       <c r="B166" s="6">
@@ -4956,53 +4574,49 @@
       <c r="J166" s="6">
         <v>7</v>
       </c>
-      <c r="K166" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L166" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
     <row r="167" spans="2:13" ht="15.75">
-      <c r="B167" s="16"/>
+      <c r="B167" s="12"/>
       <c r="C167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D167" s="16"/>
-      <c r="E167" s="16"/>
-      <c r="F167" s="16"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12"/>
+      <c r="F167" s="12"/>
       <c r="G167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H167" s="16"/>
-      <c r="I167" s="16"/>
-      <c r="J167" s="16"/>
+      <c r="H167" s="12"/>
+      <c r="I167" s="12"/>
+      <c r="J167" s="12"/>
       <c r="K167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L167" s="16"/>
-      <c r="M167" s="16"/>
+      <c r="L167" s="12"/>
+      <c r="M167" s="12"/>
     </row>
     <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="17"/>
+      <c r="B168" s="13"/>
       <c r="C168" s="5">
         <v>46312</v>
       </c>
-      <c r="D168" s="17"/>
-      <c r="E168" s="17"/>
-      <c r="F168" s="17"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="13"/>
+      <c r="F168" s="13"/>
       <c r="G168" s="5">
         <v>46319</v>
       </c>
-      <c r="H168" s="17"/>
-      <c r="I168" s="17"/>
-      <c r="J168" s="17"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="13"/>
       <c r="K168" s="5">
         <v>46326</v>
       </c>
-      <c r="L168" s="17"/>
-      <c r="M168" s="17"/>
+      <c r="L168" s="13"/>
+      <c r="M168" s="13"/>
     </row>
     <row r="169" spans="2:13" ht="15.75" thickBot="1">
       <c r="B169" s="6">
@@ -5064,7 +4678,7 @@
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="30.75" thickBot="1">
+    <row r="172" spans="2:13" ht="15.75" thickBot="1">
       <c r="B172" s="6">
         <v>4</v>
       </c>
@@ -5092,15 +4706,9 @@
       <c r="J172" s="6">
         <v>4</v>
       </c>
-      <c r="K172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M172" s="7">
-        <v>312</v>
-      </c>
+      <c r="K172" s="7"/>
+      <c r="L172" s="7"/>
+      <c r="M172" s="7"/>
     </row>
     <row r="173" spans="2:13" ht="15.75" thickBot="1">
       <c r="B173" s="6">
@@ -5130,15 +4738,9 @@
       <c r="J173" s="6">
         <v>5</v>
       </c>
-      <c r="K173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M173" s="7">
-        <v>423</v>
-      </c>
+      <c r="K173" s="7"/>
+      <c r="L173" s="7"/>
+      <c r="M173" s="7"/>
     </row>
     <row r="174" spans="2:13" ht="15.75" thickBot="1">
       <c r="B174" s="6">
@@ -5168,15 +4770,9 @@
       <c r="J174" s="6">
         <v>6</v>
       </c>
-      <c r="K174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="L174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M174" s="7">
-        <v>423</v>
-      </c>
+      <c r="K174" s="7"/>
+      <c r="L174" s="7"/>
+      <c r="M174" s="7"/>
     </row>
     <row r="175" spans="2:13" ht="15.75" thickBot="1">
       <c r="B175" s="6">
@@ -5202,34 +4798,174 @@
       <c r="J175" s="6">
         <v>7</v>
       </c>
-      <c r="K175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="K175" s="7"/>
+      <c r="L175" s="7"/>
       <c r="M175" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="201">
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="L158:L159"/>
-    <mergeCell ref="M158:M159"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="L167:L168"/>
-    <mergeCell ref="M167:M168"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="M71:M72"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="M99:M100"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="J108:J109"/>
+    <mergeCell ref="M108:M109"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="L99:L100"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="L108:L109"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="B119:M119"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="J121:J122"/>
+    <mergeCell ref="L121:L122"/>
+    <mergeCell ref="M121:M122"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="L139:L140"/>
+    <mergeCell ref="M139:M140"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="H130:H131"/>
     <mergeCell ref="L141:L142"/>
     <mergeCell ref="M141:M142"/>
     <mergeCell ref="B149:B150"/>
@@ -5251,168 +4987,24 @@
     <mergeCell ref="D141:D142"/>
     <mergeCell ref="E141:E142"/>
     <mergeCell ref="F141:F142"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="B119:M119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="L121:L122"/>
-    <mergeCell ref="M121:M122"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="L99:L100"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="L108:L109"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="M99:M100"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="J108:J109"/>
-    <mergeCell ref="M108:M109"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="M71:M72"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="I158:I159"/>
+    <mergeCell ref="J158:J159"/>
+    <mergeCell ref="L158:L159"/>
+    <mergeCell ref="M158:M159"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="L167:L168"/>
+    <mergeCell ref="M167:M168"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="E158:E159"/>
+    <mergeCell ref="F158:F159"/>
+    <mergeCell ref="H158:H159"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="46">
   <si>
     <t>№</t>
   </si>
@@ -84,13 +84,76 @@
     <t>Иностранный язык (зачёт)</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Эу-485,486</t>
-  </si>
-  <si>
     <t>Расписание занятий заочного отделения групп Эу-358,359,360</t>
   </si>
   <si>
     <t>Расписание занятий заочного отделения групп Эу-245</t>
+  </si>
+  <si>
+    <t>Расписание занятий заочного отделения групп Ту-449</t>
+  </si>
+  <si>
+    <t>МДК 03.01</t>
+  </si>
+  <si>
+    <t>Панова Н.В.</t>
+  </si>
+  <si>
+    <t>Охрана труда</t>
+  </si>
+  <si>
+    <t>Рязанова Е.В.</t>
+  </si>
+  <si>
+    <t>Марьинских М.М.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иностранный язык </t>
+  </si>
+  <si>
+    <t>(зачёт с оценкой)</t>
+  </si>
+  <si>
+    <t>БЖД</t>
+  </si>
+  <si>
+    <t>Бондаренко Т.В.</t>
+  </si>
+  <si>
+    <t>Выбор оборудования</t>
+  </si>
+  <si>
+    <t>Барихина Н.В.</t>
+  </si>
+  <si>
+    <t>ПМ 01, ПМ 06</t>
+  </si>
+  <si>
+    <t>Начало в 08:30</t>
+  </si>
+  <si>
+    <t>Квалификац экзамен</t>
+  </si>
+  <si>
+    <t>Панова Н.В</t>
+  </si>
+  <si>
+    <t>Барихина Н.В</t>
+  </si>
+  <si>
+    <t>Психология общения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Физическая культура </t>
+  </si>
+  <si>
+    <t>Кунгурова Е.А.</t>
+  </si>
+  <si>
+    <t>с/з</t>
+  </si>
+  <si>
+    <t>ПМ 02</t>
   </si>
 </sst>
 </file>
@@ -137,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -228,11 +291,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -267,15 +380,6 @@
     <xf numFmtId="16" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -284,6 +388,66 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,20 +761,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="B1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -651,44 +815,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="12"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="13"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
@@ -885,44 +1049,44 @@
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="12"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="13"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
@@ -1103,78 +1267,78 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="12"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B22" s="13"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="5">
         <v>46309</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
       <c r="G22" s="11">
         <v>46316</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
       <c r="K22" s="11">
         <v>46323</v>
       </c>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="12">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="12">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="12">
-        <v>1</v>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-    </row>
-    <row r="24" spans="2:13" ht="7.5" customHeight="1" thickBot="1">
-      <c r="B24" s="13"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
+      <c r="B23" s="17">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="17">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="17">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+    </row>
+    <row r="24" spans="2:13" ht="16.5" customHeight="1" thickBot="1">
+      <c r="B24" s="18"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B25" s="6">
@@ -1335,44 +1499,44 @@
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="12"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B32" s="13"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="5">
         <v>46310</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
       <c r="G32" s="5">
         <v>46317</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
       <c r="K32" s="5">
         <v>46324</v>
       </c>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
@@ -1561,44 +1725,44 @@
       <c r="M39" s="9"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="12"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
       <c r="K40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B41" s="13"/>
+      <c r="B41" s="18"/>
       <c r="C41" s="5">
         <v>46311</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="5">
         <v>46318</v>
       </c>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
       <c r="K41" s="5">
         <v>46325</v>
       </c>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
@@ -1775,44 +1939,44 @@
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B49" s="12"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
       <c r="K49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B50" s="13"/>
+      <c r="B50" s="18"/>
       <c r="C50" s="5">
         <v>46312</v>
       </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
       <c r="G50" s="5">
         <v>46319</v>
       </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
       <c r="K50" s="5">
         <v>46326</v>
       </c>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
     </row>
     <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
@@ -1999,20 +2163,20 @@
       <c r="M57" s="7"/>
     </row>
     <row r="60" spans="2:13" ht="21" thickBot="1">
-      <c r="B60" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
+      <c r="B60" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" thickBot="1">
       <c r="B61" s="2" t="s">
@@ -2053,44 +2217,44 @@
       </c>
     </row>
     <row r="62" spans="2:13" ht="15.75">
-      <c r="B62" s="12"/>
+      <c r="B62" s="17"/>
       <c r="C62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
       <c r="G62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
       <c r="K62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
     </row>
     <row r="63" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B63" s="13"/>
+      <c r="B63" s="18"/>
       <c r="C63" s="5">
         <v>46307</v>
       </c>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
       <c r="G63" s="5">
         <v>46314</v>
       </c>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
       <c r="K63" s="5">
         <v>46321</v>
       </c>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" thickBot="1">
       <c r="B64" s="6">
@@ -2287,44 +2451,44 @@
       <c r="M70" s="7"/>
     </row>
     <row r="71" spans="2:13" ht="15.75">
-      <c r="B71" s="12"/>
+      <c r="B71" s="17"/>
       <c r="C71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
       <c r="G71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
       <c r="K71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L71" s="12"/>
-      <c r="M71" s="12"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
     </row>
     <row r="72" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B72" s="13"/>
+      <c r="B72" s="18"/>
       <c r="C72" s="5">
         <v>46308</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
       <c r="G72" s="5">
         <v>46315</v>
       </c>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
       <c r="K72" s="5">
         <v>46322</v>
       </c>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
@@ -2505,78 +2669,78 @@
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="2:13" ht="15.75">
-      <c r="B80" s="12"/>
+      <c r="B80" s="17"/>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
       <c r="G80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
       <c r="K80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
+      <c r="L80" s="17"/>
+      <c r="M80" s="17"/>
     </row>
     <row r="81" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B81" s="13"/>
+      <c r="B81" s="18"/>
       <c r="C81" s="5">
         <v>46309</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
       <c r="G81" s="11">
         <v>46316</v>
       </c>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
       <c r="K81" s="11">
         <v>46323</v>
       </c>
-      <c r="L81" s="13"/>
-      <c r="M81" s="13"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="12">
-        <v>1</v>
-      </c>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="12">
-        <v>1</v>
-      </c>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="12">
-        <v>1</v>
-      </c>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
+      <c r="B82" s="17">
+        <v>1</v>
+      </c>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="17">
+        <v>1</v>
+      </c>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="17">
+        <v>1</v>
+      </c>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
     </row>
     <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="13"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
-      <c r="M83" s="15"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
+      <c r="M83" s="16"/>
     </row>
     <row r="84" spans="2:13" ht="15.75" thickBot="1">
       <c r="B84" s="6">
@@ -2737,44 +2901,44 @@
       <c r="M89" s="7"/>
     </row>
     <row r="90" spans="2:13" ht="15.75">
-      <c r="B90" s="12"/>
+      <c r="B90" s="17"/>
       <c r="C90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
       <c r="G90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H90" s="12"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
+      <c r="H90" s="17"/>
+      <c r="I90" s="17"/>
+      <c r="J90" s="17"/>
       <c r="K90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L90" s="12"/>
-      <c r="M90" s="12"/>
+      <c r="L90" s="17"/>
+      <c r="M90" s="17"/>
     </row>
     <row r="91" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B91" s="13"/>
+      <c r="B91" s="18"/>
       <c r="C91" s="5">
         <v>46310</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
       <c r="G91" s="5">
         <v>46317</v>
       </c>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
       <c r="K91" s="5">
         <v>46324</v>
       </c>
-      <c r="L91" s="13"/>
-      <c r="M91" s="13"/>
+      <c r="L91" s="18"/>
+      <c r="M91" s="18"/>
     </row>
     <row r="92" spans="2:13" ht="16.5" thickBot="1">
       <c r="B92" s="6">
@@ -2963,44 +3127,44 @@
       <c r="M98" s="9"/>
     </row>
     <row r="99" spans="2:13" ht="15.75">
-      <c r="B99" s="12"/>
+      <c r="B99" s="17"/>
       <c r="C99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="17"/>
+      <c r="F99" s="17"/>
       <c r="G99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
+      <c r="H99" s="17"/>
+      <c r="I99" s="17"/>
+      <c r="J99" s="17"/>
       <c r="K99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L99" s="12"/>
-      <c r="M99" s="12"/>
+      <c r="L99" s="17"/>
+      <c r="M99" s="17"/>
     </row>
     <row r="100" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B100" s="13"/>
+      <c r="B100" s="18"/>
       <c r="C100" s="5">
         <v>46311</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
       <c r="G100" s="5">
         <v>46318</v>
       </c>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
+      <c r="H100" s="18"/>
+      <c r="I100" s="18"/>
+      <c r="J100" s="18"/>
       <c r="K100" s="5">
         <v>46325</v>
       </c>
-      <c r="L100" s="13"/>
-      <c r="M100" s="13"/>
+      <c r="L100" s="18"/>
+      <c r="M100" s="18"/>
     </row>
     <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
@@ -3177,44 +3341,44 @@
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="2:13" ht="15.75">
-      <c r="B108" s="12"/>
+      <c r="B108" s="17"/>
       <c r="C108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D108" s="12"/>
-      <c r="E108" s="12"/>
-      <c r="F108" s="12"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="17"/>
+      <c r="F108" s="17"/>
       <c r="G108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H108" s="12"/>
-      <c r="I108" s="12"/>
-      <c r="J108" s="12"/>
+      <c r="H108" s="17"/>
+      <c r="I108" s="17"/>
+      <c r="J108" s="17"/>
       <c r="K108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L108" s="12"/>
-      <c r="M108" s="12"/>
+      <c r="L108" s="17"/>
+      <c r="M108" s="17"/>
     </row>
     <row r="109" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B109" s="13"/>
+      <c r="B109" s="18"/>
       <c r="C109" s="5">
         <v>46312</v>
       </c>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
       <c r="G109" s="5">
         <v>46319</v>
       </c>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
-      <c r="J109" s="13"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
       <c r="K109" s="5">
         <v>46326</v>
       </c>
-      <c r="L109" s="13"/>
-      <c r="M109" s="13"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
     </row>
     <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
@@ -3401,20 +3565,20 @@
       <c r="M116" s="7"/>
     </row>
     <row r="119" spans="2:13" ht="21" thickBot="1">
-      <c r="B119" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="17"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-      <c r="J119" s="17"/>
-      <c r="K119" s="17"/>
-      <c r="L119" s="17"/>
-      <c r="M119" s="17"/>
+      <c r="B119" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
     </row>
     <row r="120" spans="2:13" ht="15.75" thickBot="1">
       <c r="B120" s="2" t="s">
@@ -3455,58 +3619,58 @@
       </c>
     </row>
     <row r="121" spans="2:13" ht="15.75">
-      <c r="B121" s="12"/>
+      <c r="B121" s="17"/>
       <c r="C121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="12"/>
-      <c r="E121" s="12"/>
-      <c r="F121" s="12"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="17"/>
+      <c r="F121" s="17"/>
       <c r="G121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
+      <c r="H121" s="17"/>
+      <c r="I121" s="17"/>
+      <c r="J121" s="17"/>
       <c r="K121" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
+      <c r="L121" s="17"/>
+      <c r="M121" s="17"/>
     </row>
     <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="13"/>
+      <c r="B122" s="18"/>
       <c r="C122" s="5">
         <v>46307</v>
       </c>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
       <c r="G122" s="5">
         <v>46314</v>
       </c>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="13"/>
+      <c r="H122" s="18"/>
+      <c r="I122" s="18"/>
+      <c r="J122" s="18"/>
       <c r="K122" s="5">
         <v>46321</v>
       </c>
-      <c r="L122" s="13"/>
-      <c r="M122" s="13"/>
+      <c r="L122" s="18"/>
+      <c r="M122" s="18"/>
     </row>
     <row r="123" spans="2:13" ht="15.75" thickBot="1">
       <c r="B123" s="6">
         <v>1</v>
       </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
+      <c r="C123" s="21"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
       <c r="F123" s="8">
         <v>1</v>
       </c>
-      <c r="G123" s="8"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="22"/>
       <c r="J123" s="8">
         <v>1</v>
       </c>
@@ -3518,15 +3682,21 @@
       <c r="B124" s="6">
         <v>2</v>
       </c>
-      <c r="C124" s="9"/>
+      <c r="C124" s="23"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="8">
         <v>2</v>
       </c>
-      <c r="G124" s="8"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
+      <c r="G124" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" s="7">
+        <v>304</v>
+      </c>
       <c r="J124" s="8">
         <v>2</v>
       </c>
@@ -3538,20 +3708,26 @@
       <c r="B125" s="6">
         <v>3</v>
       </c>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
+      <c r="C125" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E125" s="7">
+        <v>308</v>
+      </c>
       <c r="F125" s="8">
         <v>3</v>
       </c>
-      <c r="G125" s="7" t="s">
-        <v>5</v>
+      <c r="G125" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I125" s="7">
-        <v>423</v>
+        <v>101</v>
       </c>
       <c r="J125" s="8">
         <v>3</v>
@@ -3564,26 +3740,26 @@
       <c r="B126" s="6">
         <v>4</v>
       </c>
-      <c r="C126" s="7" t="s">
-        <v>7</v>
+      <c r="C126" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E126" s="7">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F126" s="8">
         <v>4</v>
       </c>
-      <c r="G126" s="7" t="s">
-        <v>7</v>
+      <c r="G126" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="I126" s="7">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="J126" s="8">
         <v>4</v>
@@ -3596,26 +3772,20 @@
       <c r="B127" s="6">
         <v>5</v>
       </c>
-      <c r="C127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="7">
-        <v>318</v>
-      </c>
+      <c r="C127" s="12"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
       <c r="F127" s="8">
         <v>5</v>
       </c>
-      <c r="G127" s="7" t="s">
-        <v>7</v>
+      <c r="G127" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="I127" s="7">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="J127" s="8">
         <v>5</v>
@@ -3628,27 +3798,15 @@
       <c r="B128" s="6">
         <v>6</v>
       </c>
-      <c r="C128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="7">
-        <v>318</v>
-      </c>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
       <c r="F128" s="8">
         <v>6</v>
       </c>
-      <c r="G128" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I128" s="7">
-        <v>318</v>
-      </c>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="7"/>
       <c r="J128" s="8">
         <v>6</v>
       </c>
@@ -3660,27 +3818,15 @@
       <c r="B129" s="6">
         <v>7</v>
       </c>
-      <c r="C129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="7">
-        <v>318</v>
-      </c>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
       <c r="F129" s="8">
         <v>7</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I129" s="7">
-        <v>318</v>
-      </c>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="7"/>
       <c r="J129" s="8">
         <v>7</v>
       </c>
@@ -3689,58 +3835,58 @@
       <c r="M129" s="7"/>
     </row>
     <row r="130" spans="2:13" ht="15.75">
-      <c r="B130" s="12"/>
+      <c r="B130" s="17"/>
       <c r="C130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D130" s="12"/>
-      <c r="E130" s="12"/>
-      <c r="F130" s="12"/>
+      <c r="D130" s="17"/>
+      <c r="E130" s="17"/>
+      <c r="F130" s="17"/>
       <c r="G130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H130" s="12"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="12"/>
+      <c r="H130" s="17"/>
+      <c r="I130" s="17"/>
+      <c r="J130" s="17"/>
       <c r="K130" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L130" s="12"/>
-      <c r="M130" s="12"/>
+      <c r="L130" s="17"/>
+      <c r="M130" s="17"/>
     </row>
     <row r="131" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B131" s="13"/>
+      <c r="B131" s="18"/>
       <c r="C131" s="5">
         <v>46308</v>
       </c>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
-      <c r="F131" s="13"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
       <c r="G131" s="5">
         <v>46315</v>
       </c>
-      <c r="H131" s="13"/>
-      <c r="I131" s="13"/>
-      <c r="J131" s="13"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="18"/>
+      <c r="J131" s="18"/>
       <c r="K131" s="5">
         <v>46322</v>
       </c>
-      <c r="L131" s="13"/>
-      <c r="M131" s="13"/>
+      <c r="L131" s="18"/>
+      <c r="M131" s="18"/>
     </row>
     <row r="132" spans="2:13" ht="15.75" thickBot="1">
       <c r="B132" s="6">
         <v>1</v>
       </c>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
       <c r="F132" s="8">
         <v>1</v>
       </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
       <c r="J132" s="8">
         <v>1</v>
       </c>
@@ -3752,13 +3898,13 @@
       <c r="B133" s="6">
         <v>2</v>
       </c>
-      <c r="C133" s="7"/>
+      <c r="C133" s="12"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="8">
         <v>2</v>
       </c>
-      <c r="G133" s="7"/>
+      <c r="G133" s="12"/>
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="8">
@@ -3768,25 +3914,31 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="30.75" thickBot="1">
+    <row r="134" spans="2:13" ht="15.75" thickBot="1">
       <c r="B134" s="6">
         <v>3</v>
       </c>
-      <c r="C134" s="7" t="s">
-        <v>21</v>
+      <c r="C134" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E134" s="7">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F134" s="8">
         <v>3</v>
       </c>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
+      <c r="G134" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I134" s="7">
+        <v>308</v>
+      </c>
       <c r="J134" s="8">
         <v>3</v>
       </c>
@@ -3794,29 +3946,31 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="30.75" thickBot="1">
+    <row r="135" spans="2:13" ht="15.75" thickBot="1">
       <c r="B135" s="6">
         <v>4</v>
       </c>
-      <c r="C135" s="7" t="s">
-        <v>5</v>
+      <c r="C135" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E135" s="7">
-        <v>423</v>
+        <v>318</v>
       </c>
       <c r="F135" s="8">
         <v>4</v>
       </c>
-      <c r="G135" s="7" t="s">
-        <v>7</v>
+      <c r="G135" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="H135" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I135" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="I135" s="7">
+        <v>308</v>
+      </c>
       <c r="J135" s="8">
         <v>4</v>
       </c>
@@ -3824,30 +3978,30 @@
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="30.75" thickBot="1">
+    <row r="136" spans="2:13" ht="15.75" thickBot="1">
       <c r="B136" s="6">
         <v>5</v>
       </c>
-      <c r="C136" s="7" t="s">
-        <v>5</v>
+      <c r="C136" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E136" s="7">
-        <v>423</v>
+        <v>318</v>
       </c>
       <c r="F136" s="8">
         <v>5</v>
       </c>
-      <c r="G136" s="7" t="s">
-        <v>5</v>
+      <c r="G136" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I136" s="7">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="J136" s="8">
         <v>5</v>
@@ -3866,15 +4020,9 @@
       <c r="F137" s="8">
         <v>6</v>
       </c>
-      <c r="G137" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I137" s="7">
-        <v>423</v>
-      </c>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7"/>
       <c r="J137" s="8">
         <v>6</v>
       </c>
@@ -3892,12 +4040,8 @@
       <c r="F138" s="8">
         <v>7</v>
       </c>
-      <c r="G138" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
       <c r="I138" s="7"/>
       <c r="J138" s="8">
         <v>7</v>
@@ -3907,78 +4051,76 @@
       <c r="M138" s="7"/>
     </row>
     <row r="139" spans="2:13" ht="15.75">
-      <c r="B139" s="12"/>
+      <c r="B139" s="17"/>
       <c r="C139" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
-      <c r="F139" s="12"/>
+      <c r="D139" s="17"/>
+      <c r="E139" s="17"/>
+      <c r="F139" s="17"/>
       <c r="G139" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H139" s="12"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12"/>
+      <c r="H139" s="17"/>
+      <c r="I139" s="17"/>
+      <c r="J139" s="17"/>
       <c r="K139" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L139" s="12"/>
-      <c r="M139" s="12"/>
+      <c r="L139" s="17"/>
+      <c r="M139" s="17"/>
     </row>
     <row r="140" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B140" s="13"/>
+      <c r="B140" s="18"/>
       <c r="C140" s="5">
         <v>46309</v>
       </c>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="13"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
       <c r="G140" s="11">
         <v>46316</v>
       </c>
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
-      <c r="J140" s="13"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
       <c r="K140" s="11">
         <v>46323</v>
       </c>
-      <c r="L140" s="13"/>
-      <c r="M140" s="13"/>
-    </row>
-    <row r="141" spans="2:13">
-      <c r="B141" s="12">
-        <v>1</v>
-      </c>
-      <c r="C141" s="14"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
-      <c r="F141" s="12">
-        <v>1</v>
-      </c>
-      <c r="G141" s="14"/>
-      <c r="H141" s="14"/>
-      <c r="I141" s="14"/>
-      <c r="J141" s="12">
-        <v>1</v>
-      </c>
-      <c r="K141" s="14"/>
-      <c r="L141" s="14"/>
-      <c r="M141" s="14"/>
-    </row>
-    <row r="142" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B142" s="13"/>
-      <c r="C142" s="15"/>
-      <c r="D142" s="15"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="13"/>
-      <c r="G142" s="15"/>
-      <c r="H142" s="15"/>
-      <c r="I142" s="15"/>
-      <c r="J142" s="13"/>
-      <c r="K142" s="15"/>
-      <c r="L142" s="15"/>
-      <c r="M142" s="15"/>
+      <c r="L140" s="18"/>
+      <c r="M140" s="18"/>
+    </row>
+    <row r="141" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B141" s="17">
+        <v>1</v>
+      </c>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="17">
+        <v>1</v>
+      </c>
+      <c r="G141" s="15"/>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+      <c r="J141" s="17"/>
+      <c r="K141" s="15"/>
+      <c r="L141" s="15"/>
+      <c r="M141" s="15"/>
+    </row>
+    <row r="142" spans="2:13" ht="9.75" customHeight="1" thickBot="1">
+      <c r="B142" s="18"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="18"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="16"/>
+      <c r="I142" s="16"/>
+      <c r="J142" s="18"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
+      <c r="M142" s="16"/>
     </row>
     <row r="143" spans="2:13" ht="15.75" thickBot="1">
       <c r="B143" s="6">
@@ -3993,9 +4135,7 @@
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
       <c r="I143" s="7"/>
-      <c r="J143" s="8">
-        <v>2</v>
-      </c>
+      <c r="J143" s="8"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
@@ -4004,18 +4144,28 @@
       <c r="B144" s="6">
         <v>3</v>
       </c>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
+      <c r="C144" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E144" s="22">
+        <v>101</v>
+      </c>
       <c r="F144" s="8">
         <v>3</v>
       </c>
-      <c r="G144" s="8"/>
-      <c r="H144" s="7"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="8">
-        <v>3</v>
-      </c>
+      <c r="G144" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H144" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I144" s="22">
+        <v>101</v>
+      </c>
+      <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
@@ -4024,22 +4174,28 @@
       <c r="B145" s="6">
         <v>4</v>
       </c>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
+      <c r="C145" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E145" s="7">
+        <v>101</v>
+      </c>
       <c r="F145" s="8">
         <v>4</v>
       </c>
-      <c r="G145" s="7" t="s">
-        <v>7</v>
+      <c r="G145" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I145" s="7"/>
-      <c r="J145" s="8">
-        <v>4</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I145" s="7">
+        <v>101</v>
+      </c>
+      <c r="J145" s="8"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
@@ -4048,30 +4204,28 @@
       <c r="B146" s="6">
         <v>5</v>
       </c>
-      <c r="C146" s="7" t="s">
-        <v>7</v>
+      <c r="C146" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E146" s="7">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="F146" s="8">
         <v>5</v>
       </c>
-      <c r="G146" s="7" t="s">
-        <v>5</v>
+      <c r="G146" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I146" s="7">
-        <v>423</v>
-      </c>
-      <c r="J146" s="8">
-        <v>5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J146" s="8"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
@@ -4080,30 +4234,16 @@
       <c r="B147" s="6">
         <v>6</v>
       </c>
-      <c r="C147" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E147" s="7">
-        <v>318</v>
-      </c>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
       <c r="F147" s="8">
         <v>6</v>
       </c>
-      <c r="G147" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I147" s="7">
-        <v>423</v>
-      </c>
-      <c r="J147" s="8">
-        <v>6</v>
-      </c>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="8"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
@@ -4112,85 +4252,73 @@
       <c r="B148" s="6">
         <v>7</v>
       </c>
-      <c r="C148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="7">
-        <v>318</v>
-      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
       <c r="F148" s="8">
         <v>7</v>
       </c>
-      <c r="G148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
       <c r="I148" s="7"/>
-      <c r="J148" s="8">
-        <v>7</v>
-      </c>
+      <c r="J148" s="8"/>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c r="M148" s="7"/>
     </row>
     <row r="149" spans="2:13" ht="15.75">
-      <c r="B149" s="12"/>
+      <c r="B149" s="17"/>
       <c r="C149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="12"/>
-      <c r="E149" s="12"/>
-      <c r="F149" s="12"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="17"/>
       <c r="G149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="12"/>
+      <c r="H149" s="17"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17"/>
       <c r="K149" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L149" s="12"/>
-      <c r="M149" s="12"/>
+      <c r="L149" s="17"/>
+      <c r="M149" s="17"/>
     </row>
     <row r="150" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B150" s="13"/>
+      <c r="B150" s="18"/>
       <c r="C150" s="5">
         <v>46310</v>
       </c>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="18"/>
       <c r="G150" s="5">
         <v>46317</v>
       </c>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="13"/>
+      <c r="H150" s="18"/>
+      <c r="I150" s="18"/>
+      <c r="J150" s="18"/>
       <c r="K150" s="5">
         <v>46324</v>
       </c>
-      <c r="L150" s="13"/>
-      <c r="M150" s="13"/>
+      <c r="L150" s="18"/>
+      <c r="M150" s="18"/>
     </row>
     <row r="151" spans="2:13" ht="16.5" thickBot="1">
       <c r="B151" s="6">
         <v>1</v>
       </c>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
+      <c r="C151" s="21"/>
+      <c r="D151" s="22"/>
+      <c r="E151" s="22"/>
       <c r="F151" s="8">
         <v>1</v>
       </c>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
-      <c r="I151" s="9"/>
+      <c r="G151" s="33"/>
+      <c r="H151" s="34"/>
+      <c r="I151" s="34"/>
       <c r="J151" s="8">
         <v>1</v>
       </c>
@@ -4202,21 +4330,15 @@
       <c r="B152" s="6">
         <v>2</v>
       </c>
-      <c r="C152" s="7"/>
+      <c r="C152" s="19"/>
       <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
+      <c r="E152" s="20"/>
       <c r="F152" s="8">
         <v>2</v>
       </c>
-      <c r="G152" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I152" s="7">
-        <v>312</v>
-      </c>
+      <c r="G152" s="12"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7"/>
       <c r="J152" s="8">
         <v>2</v>
       </c>
@@ -4228,20 +4350,26 @@
       <c r="B153" s="6">
         <v>3</v>
       </c>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
+      <c r="C153" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E153" s="7">
+        <v>101</v>
+      </c>
       <c r="F153" s="8">
         <v>3</v>
       </c>
-      <c r="G153" s="7" t="s">
-        <v>7</v>
+      <c r="G153" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I153" s="7">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="J153" s="8">
         <v>3</v>
@@ -4254,27 +4382,25 @@
       <c r="B154" s="6">
         <v>4</v>
       </c>
-      <c r="C154" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" s="7" t="s">
+      <c r="C154" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" s="15">
+        <v>312</v>
+      </c>
+      <c r="F154" s="8">
+        <v>4</v>
+      </c>
+      <c r="G154" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H154" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E154" s="7">
-        <v>312</v>
-      </c>
-      <c r="F154" s="8">
-        <v>4</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I154" s="7">
-        <v>423</v>
-      </c>
+      <c r="I154" s="7"/>
       <c r="J154" s="8">
         <v>4</v>
       </c>
@@ -4286,26 +4412,22 @@
       <c r="B155" s="6">
         <v>5</v>
       </c>
-      <c r="C155" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E155" s="7">
-        <v>423</v>
-      </c>
+      <c r="C155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
       <c r="F155" s="8">
         <v>5</v>
       </c>
-      <c r="G155" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I155" s="7">
-        <v>423</v>
+      <c r="G155" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H155" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="J155" s="8">
         <v>5</v>
@@ -4318,21 +4440,23 @@
       <c r="B156" s="6">
         <v>6</v>
       </c>
-      <c r="C156" s="7" t="s">
-        <v>7</v>
+      <c r="C156" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E156" s="7">
-        <v>423</v>
+        <v>231</v>
       </c>
       <c r="F156" s="8">
         <v>6</v>
       </c>
-      <c r="G156" s="9"/>
-      <c r="H156" s="9"/>
-      <c r="I156" s="9"/>
+      <c r="G156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H156" s="16"/>
+      <c r="I156" s="16"/>
       <c r="J156" s="8">
         <v>6</v>
       </c>
@@ -4344,12 +4468,8 @@
       <c r="B157" s="6">
         <v>7</v>
       </c>
-      <c r="C157" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="8">
         <v>7</v>
@@ -4365,63 +4485,61 @@
       <c r="M157" s="9"/>
     </row>
     <row r="158" spans="2:13" ht="15.75">
-      <c r="B158" s="12"/>
+      <c r="B158" s="17"/>
       <c r="C158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D158" s="12"/>
-      <c r="E158" s="12"/>
-      <c r="F158" s="12"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="17"/>
       <c r="G158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H158" s="12"/>
-      <c r="I158" s="12"/>
-      <c r="J158" s="12"/>
+      <c r="H158" s="17"/>
+      <c r="I158" s="17"/>
+      <c r="J158" s="17"/>
       <c r="K158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L158" s="12"/>
-      <c r="M158" s="12"/>
+      <c r="L158" s="17"/>
+      <c r="M158" s="17"/>
     </row>
     <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="13"/>
+      <c r="B159" s="18"/>
       <c r="C159" s="5">
         <v>46311</v>
       </c>
-      <c r="D159" s="13"/>
-      <c r="E159" s="13"/>
-      <c r="F159" s="13"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18"/>
+      <c r="F159" s="18"/>
       <c r="G159" s="5">
         <v>46318</v>
       </c>
-      <c r="H159" s="13"/>
-      <c r="I159" s="13"/>
-      <c r="J159" s="13"/>
+      <c r="H159" s="18"/>
+      <c r="I159" s="18"/>
+      <c r="J159" s="18"/>
       <c r="K159" s="5">
         <v>46325</v>
       </c>
-      <c r="L159" s="13"/>
-      <c r="M159" s="13"/>
-    </row>
-    <row r="160" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L159" s="18"/>
+      <c r="M159" s="18"/>
+    </row>
+    <row r="160" spans="2:13" ht="16.5" thickBot="1">
       <c r="B160" s="6">
         <v>1</v>
       </c>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="22"/>
+      <c r="E160" s="22"/>
       <c r="F160" s="8">
         <v>1</v>
       </c>
-      <c r="G160" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="G160" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H160" s="25"/>
       <c r="I160" s="7">
-        <v>423</v>
+        <v>308</v>
       </c>
       <c r="J160" s="6">
         <v>1</v>
@@ -4430,25 +4548,23 @@
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" ht="15.75" thickBot="1">
+    <row r="161" spans="2:13" ht="16.5" thickBot="1">
       <c r="B161" s="6">
         <v>2</v>
       </c>
-      <c r="C161" s="7"/>
+      <c r="C161" s="12"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
-      <c r="F161" s="8">
-        <v>2</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I161" s="7">
-        <v>423</v>
-      </c>
+      <c r="F161" s="35">
+        <v>2</v>
+      </c>
+      <c r="G161" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H161" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I161" s="7"/>
       <c r="J161" s="6">
         <v>2</v>
       </c>
@@ -4456,18 +4572,28 @@
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" ht="15.75" thickBot="1">
+    <row r="162" spans="2:13" ht="16.5" thickBot="1">
       <c r="B162" s="6">
         <v>3</v>
       </c>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="8">
-        <v>3</v>
-      </c>
-      <c r="G162" s="7"/>
-      <c r="H162" s="7"/>
+      <c r="C162" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="7">
+        <v>309</v>
+      </c>
+      <c r="F162" s="35">
+        <v>3</v>
+      </c>
+      <c r="G162" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H162" s="31" t="s">
+        <v>40</v>
+      </c>
       <c r="I162" s="7"/>
       <c r="J162" s="6">
         <v>3</v>
@@ -4480,20 +4606,20 @@
       <c r="B163" s="6">
         <v>4</v>
       </c>
-      <c r="C163" s="7" t="s">
-        <v>17</v>
+      <c r="C163" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E163" s="7">
-        <v>312</v>
-      </c>
-      <c r="F163" s="8">
-        <v>4</v>
-      </c>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
+        <v>309</v>
+      </c>
+      <c r="F163" s="35">
+        <v>4</v>
+      </c>
+      <c r="G163" s="32"/>
+      <c r="H163" s="32"/>
       <c r="I163" s="7"/>
       <c r="J163" s="6">
         <v>4</v>
@@ -4506,14 +4632,14 @@
       <c r="B164" s="6">
         <v>5</v>
       </c>
-      <c r="C164" s="7" t="s">
-        <v>7</v>
+      <c r="C164" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E164" s="7">
-        <v>423</v>
+        <v>231</v>
       </c>
       <c r="F164" s="8">
         <v>5</v>
@@ -4532,15 +4658,9 @@
       <c r="B165" s="6">
         <v>6</v>
       </c>
-      <c r="C165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E165" s="7">
-        <v>423</v>
-      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
       <c r="F165" s="8">
         <v>6</v>
       </c>
@@ -4558,12 +4678,8 @@
       <c r="B166" s="6">
         <v>7</v>
       </c>
-      <c r="C166" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D166" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="8">
         <v>4</v>
@@ -4579,52 +4695,56 @@
       <c r="M166" s="7"/>
     </row>
     <row r="167" spans="2:13" ht="15.75">
-      <c r="B167" s="12"/>
+      <c r="B167" s="17"/>
       <c r="C167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D167" s="12"/>
-      <c r="E167" s="12"/>
-      <c r="F167" s="12"/>
+      <c r="D167" s="17"/>
+      <c r="E167" s="17"/>
+      <c r="F167" s="17"/>
       <c r="G167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H167" s="12"/>
-      <c r="I167" s="12"/>
-      <c r="J167" s="12"/>
+      <c r="H167" s="17"/>
+      <c r="I167" s="17"/>
+      <c r="J167" s="17"/>
       <c r="K167" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L167" s="12"/>
-      <c r="M167" s="12"/>
+      <c r="L167" s="17"/>
+      <c r="M167" s="17"/>
     </row>
     <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="13"/>
-      <c r="C168" s="5">
+      <c r="B168" s="18"/>
+      <c r="C168" s="28">
         <v>46312</v>
       </c>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
+      <c r="D168" s="18"/>
+      <c r="E168" s="18"/>
+      <c r="F168" s="18"/>
       <c r="G168" s="5">
         <v>46319</v>
       </c>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="13"/>
+      <c r="H168" s="18"/>
+      <c r="I168" s="18"/>
+      <c r="J168" s="18"/>
       <c r="K168" s="5">
         <v>46326</v>
       </c>
-      <c r="L168" s="13"/>
-      <c r="M168" s="13"/>
-    </row>
-    <row r="169" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B169" s="6">
-        <v>1</v>
-      </c>
-      <c r="C169" s="7"/>
+      <c r="L168" s="18"/>
+      <c r="M168" s="18"/>
+    </row>
+    <row r="169" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B169" s="27">
+        <v>1</v>
+      </c>
+      <c r="C169" s="29" t="s">
+        <v>38</v>
+      </c>
       <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
+      <c r="E169" s="7">
+        <v>308</v>
+      </c>
       <c r="F169" s="6">
         <v>1</v>
       </c>
@@ -4638,12 +4758,16 @@
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B170" s="6">
-        <v>2</v>
-      </c>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
+    <row r="170" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B170" s="27">
+        <v>2</v>
+      </c>
+      <c r="C170" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D170" s="26" t="s">
+        <v>39</v>
+      </c>
       <c r="E170" s="7"/>
       <c r="F170" s="6">
         <v>2</v>
@@ -4658,12 +4782,16 @@
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B171" s="6">
-        <v>3</v>
-      </c>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
+    <row r="171" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B171" s="27">
+        <v>3</v>
+      </c>
+      <c r="C171" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D171" s="26" t="s">
+        <v>40</v>
+      </c>
       <c r="E171" s="7"/>
       <c r="F171" s="6">
         <v>3</v>
@@ -4679,30 +4807,18 @@
       <c r="M171" s="7"/>
     </row>
     <row r="172" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B172" s="6">
-        <v>4</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E172" s="7">
-        <v>312</v>
-      </c>
+      <c r="B172" s="27">
+        <v>4</v>
+      </c>
+      <c r="C172" s="32"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
       <c r="F172" s="6">
         <v>4</v>
       </c>
-      <c r="G172" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I172" s="7">
-        <v>312</v>
-      </c>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="7"/>
       <c r="J172" s="6">
         <v>4</v>
       </c>
@@ -4714,27 +4830,15 @@
       <c r="B173" s="6">
         <v>5</v>
       </c>
-      <c r="C173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E173" s="7">
-        <v>423</v>
-      </c>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
       <c r="F173" s="6">
         <v>5</v>
       </c>
-      <c r="G173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I173" s="7">
-        <v>423</v>
-      </c>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="7"/>
       <c r="J173" s="6">
         <v>5</v>
       </c>
@@ -4746,27 +4850,15 @@
       <c r="B174" s="6">
         <v>6</v>
       </c>
-      <c r="C174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E174" s="7">
-        <v>423</v>
-      </c>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
       <c r="F174" s="6">
         <v>6</v>
       </c>
-      <c r="G174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I174" s="7">
-        <v>423</v>
-      </c>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="7"/>
       <c r="J174" s="6">
         <v>6</v>
       </c>
@@ -4778,22 +4870,14 @@
       <c r="B175" s="6">
         <v>7</v>
       </c>
-      <c r="C175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="6">
         <v>7</v>
       </c>
-      <c r="G175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
       <c r="I175" s="7"/>
       <c r="J175" s="6">
         <v>7</v>
@@ -4803,33 +4887,154 @@
       <c r="M175" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="201">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L49:L50"/>
+  <mergeCells count="205">
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="I158:I159"/>
+    <mergeCell ref="J158:J159"/>
+    <mergeCell ref="L158:L159"/>
+    <mergeCell ref="M158:M159"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="L167:L168"/>
+    <mergeCell ref="M167:M168"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="E158:E159"/>
+    <mergeCell ref="F158:F159"/>
+    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="L141:L142"/>
+    <mergeCell ref="M141:M142"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="D149:D150"/>
+    <mergeCell ref="E149:E150"/>
+    <mergeCell ref="F149:F150"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="J149:J150"/>
+    <mergeCell ref="L149:L150"/>
+    <mergeCell ref="M149:M150"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I141:I142"/>
+    <mergeCell ref="J141:J142"/>
+    <mergeCell ref="K141:K142"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:C142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="E141:E142"/>
+    <mergeCell ref="F141:F142"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="E139:E140"/>
+    <mergeCell ref="F139:F140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="L139:L140"/>
+    <mergeCell ref="M139:M140"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="B119:M119"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="J121:J122"/>
+    <mergeCell ref="L121:L122"/>
+    <mergeCell ref="M121:M122"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="L108:L109"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="L99:L100"/>
+    <mergeCell ref="M99:M100"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="J108:J109"/>
+    <mergeCell ref="M108:M109"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="M71:M72"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="E49:E50"/>
@@ -4854,6 +5059,32 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="H31:H32"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
     <mergeCell ref="I31:I32"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:C24"/>
@@ -4862,149 +5093,6 @@
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="M71:M72"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="M99:M100"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="J108:J109"/>
-    <mergeCell ref="M108:M109"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="L99:L100"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="L108:L109"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="B119:M119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="L121:L122"/>
-    <mergeCell ref="M121:M122"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="L141:L142"/>
-    <mergeCell ref="M141:M142"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="D149:D150"/>
-    <mergeCell ref="E149:E150"/>
-    <mergeCell ref="F149:F150"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="J149:J150"/>
-    <mergeCell ref="L149:L150"/>
-    <mergeCell ref="M149:M150"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I141:I142"/>
-    <mergeCell ref="J141:J142"/>
-    <mergeCell ref="K141:K142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="L158:L159"/>
-    <mergeCell ref="M158:M159"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="L167:L168"/>
-    <mergeCell ref="M167:M168"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="H158:H159"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -345,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -383,23 +383,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -448,6 +433,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -743,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:M175"/>
+  <dimension ref="B1:M173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
@@ -761,20 +773,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -815,44 +827,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="17"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="18"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
@@ -1049,44 +1061,44 @@
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="17"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="18"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
@@ -1267,78 +1279,78 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="17"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B22" s="18"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="5">
         <v>46309</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="11">
         <v>46316</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
       <c r="K22" s="11">
         <v>46323</v>
       </c>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="17">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="17">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="17">
-        <v>1</v>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
+      <c r="B23" s="34">
+        <v>1</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="34">
+        <v>1</v>
+      </c>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="34">
+        <v>1</v>
+      </c>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
     </row>
     <row r="24" spans="2:13" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B24" s="18"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B25" s="6">
@@ -1499,44 +1511,44 @@
       <c r="M30" s="7"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="17"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B32" s="18"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="5">
         <v>46310</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="5">
         <v>46317</v>
       </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
       <c r="K32" s="5">
         <v>46324</v>
       </c>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
@@ -1725,44 +1737,44 @@
       <c r="M39" s="9"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="17"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
       <c r="K40" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="34"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B41" s="18"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="5">
         <v>46311</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="5">
         <v>46318</v>
       </c>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
       <c r="K41" s="5">
         <v>46325</v>
       </c>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
@@ -1939,44 +1951,44 @@
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B49" s="17"/>
+      <c r="B49" s="34"/>
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
       <c r="G49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
       <c r="K49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="34"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B50" s="18"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="5">
         <v>46312</v>
       </c>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
       <c r="G50" s="5">
         <v>46319</v>
       </c>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
       <c r="K50" s="5">
         <v>46326</v>
       </c>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
     </row>
     <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
@@ -2163,20 +2175,20 @@
       <c r="M57" s="7"/>
     </row>
     <row r="60" spans="2:13" ht="21" thickBot="1">
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="37"/>
+      <c r="L60" s="37"/>
+      <c r="M60" s="37"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" thickBot="1">
       <c r="B61" s="2" t="s">
@@ -2217,44 +2229,44 @@
       </c>
     </row>
     <row r="62" spans="2:13" ht="15.75">
-      <c r="B62" s="17"/>
+      <c r="B62" s="34"/>
       <c r="C62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
       <c r="G62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
       <c r="K62" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="34"/>
     </row>
     <row r="63" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B63" s="18"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="5">
         <v>46307</v>
       </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
       <c r="G63" s="5">
         <v>46314</v>
       </c>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
       <c r="K63" s="5">
         <v>46321</v>
       </c>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" thickBot="1">
       <c r="B64" s="6">
@@ -2451,44 +2463,44 @@
       <c r="M70" s="7"/>
     </row>
     <row r="71" spans="2:13" ht="15.75">
-      <c r="B71" s="17"/>
+      <c r="B71" s="34"/>
       <c r="C71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
       <c r="G71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
       <c r="K71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="34"/>
     </row>
     <row r="72" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B72" s="18"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="5">
         <v>46308</v>
       </c>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
       <c r="G72" s="5">
         <v>46315</v>
       </c>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="35"/>
       <c r="K72" s="5">
         <v>46322</v>
       </c>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
+      <c r="L72" s="35"/>
+      <c r="M72" s="35"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
@@ -2669,138 +2681,156 @@
       <c r="M79" s="7"/>
     </row>
     <row r="80" spans="2:13" ht="15.75">
-      <c r="B80" s="17"/>
+      <c r="B80" s="34"/>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
       <c r="G80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
+      <c r="H80" s="34"/>
+      <c r="I80" s="34"/>
+      <c r="J80" s="34"/>
       <c r="K80" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L80" s="17"/>
-      <c r="M80" s="17"/>
-    </row>
-    <row r="81" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B81" s="18"/>
-      <c r="C81" s="5">
+      <c r="L80" s="34"/>
+      <c r="M80" s="34"/>
+    </row>
+    <row r="81" spans="2:13" ht="15.75">
+      <c r="B81" s="38"/>
+      <c r="C81" s="23">
         <v>46309</v>
       </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="11">
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="39">
         <v>46316</v>
       </c>
-      <c r="H81" s="18"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="11">
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="39">
         <v>46323</v>
       </c>
-      <c r="L81" s="18"/>
-      <c r="M81" s="18"/>
-    </row>
-    <row r="82" spans="2:13">
-      <c r="B82" s="17">
-        <v>1</v>
-      </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="17">
-        <v>1</v>
-      </c>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="17">
-        <v>1</v>
-      </c>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
-      <c r="M82" s="15"/>
-    </row>
-    <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="18"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
+      <c r="L81" s="38"/>
+      <c r="M81" s="38"/>
+    </row>
+    <row r="82" spans="2:13" ht="18.75" customHeight="1">
+      <c r="B82" s="40">
+        <v>1</v>
+      </c>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="40">
+        <v>1</v>
+      </c>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="40">
+        <v>1</v>
+      </c>
+      <c r="K82" s="27"/>
+      <c r="L82" s="27"/>
+      <c r="M82" s="27"/>
+    </row>
+    <row r="83" spans="2:13">
+      <c r="B83" s="40">
+        <v>2</v>
+      </c>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="40">
+        <v>2</v>
+      </c>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="40">
+        <v>2</v>
+      </c>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
+      <c r="M83" s="27"/>
     </row>
     <row r="84" spans="2:13" ht="15.75" thickBot="1">
       <c r="B84" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="8">
-        <v>2</v>
-      </c>
-      <c r="G84" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="G84" s="8"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
-        <v>2</v>
-      </c>
-      <c r="K84" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="K84" s="8"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
     <row r="85" spans="2:13" ht="15.75" thickBot="1">
       <c r="B85" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="8">
-        <v>3</v>
-      </c>
-      <c r="G85" s="8"/>
-      <c r="H85" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I85" s="7"/>
       <c r="J85" s="8">
-        <v>3</v>
-      </c>
-      <c r="K85" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
     <row r="86" spans="2:13" ht="15.75" thickBot="1">
       <c r="B86" s="6">
-        <v>4</v>
-      </c>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="7">
+        <v>318</v>
+      </c>
       <c r="F86" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I86" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="I86" s="7">
+        <v>423</v>
+      </c>
       <c r="J86" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -2808,7 +2838,7 @@
     </row>
     <row r="87" spans="2:13" ht="15.75" thickBot="1">
       <c r="B87" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>7</v>
@@ -2820,7 +2850,7 @@
         <v>318</v>
       </c>
       <c r="F87" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>5</v>
@@ -2832,7 +2862,7 @@
         <v>423</v>
       </c>
       <c r="J87" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -2840,147 +2870,141 @@
     </row>
     <row r="88" spans="2:13" ht="15.75" thickBot="1">
       <c r="B88" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E88" s="7">
         <v>318</v>
       </c>
       <c r="F88" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I88" s="7">
-        <v>423</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I88" s="7"/>
       <c r="J88" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
     </row>
-    <row r="89" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B89" s="6">
-        <v>7</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="7">
-        <v>318</v>
-      </c>
-      <c r="F89" s="8">
-        <v>7</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I89" s="7"/>
-      <c r="J89" s="8">
-        <v>7</v>
-      </c>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-    </row>
-    <row r="90" spans="2:13" ht="15.75">
-      <c r="B90" s="17"/>
-      <c r="C90" s="4" t="s">
+    <row r="89" spans="2:13" ht="15.75">
+      <c r="B89" s="34"/>
+      <c r="C89" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="17"/>
-      <c r="G90" s="4" t="s">
+      <c r="D89" s="34"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+      <c r="G89" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H90" s="17"/>
-      <c r="I90" s="17"/>
-      <c r="J90" s="17"/>
-      <c r="K90" s="4" t="s">
+      <c r="H89" s="34"/>
+      <c r="I89" s="34"/>
+      <c r="J89" s="34"/>
+      <c r="K89" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L90" s="17"/>
-      <c r="M90" s="17"/>
+      <c r="L89" s="34"/>
+      <c r="M89" s="34"/>
+    </row>
+    <row r="90" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B90" s="35"/>
+      <c r="C90" s="5">
+        <v>46310</v>
+      </c>
+      <c r="D90" s="35"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="5">
+        <v>46317</v>
+      </c>
+      <c r="H90" s="35"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="35"/>
+      <c r="K90" s="5">
+        <v>46324</v>
+      </c>
+      <c r="L90" s="35"/>
+      <c r="M90" s="35"/>
     </row>
     <row r="91" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B91" s="18"/>
-      <c r="C91" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H91" s="18"/>
-      <c r="I91" s="18"/>
-      <c r="J91" s="18"/>
-      <c r="K91" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L91" s="18"/>
-      <c r="M91" s="18"/>
-    </row>
-    <row r="92" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B91" s="6">
+        <v>1</v>
+      </c>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="8">
+        <v>1</v>
+      </c>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="8">
+        <v>1</v>
+      </c>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+    </row>
+    <row r="92" spans="2:13" ht="15.75" thickBot="1">
       <c r="B92" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="8">
-        <v>1</v>
-      </c>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" s="7">
+        <v>312</v>
+      </c>
       <c r="J92" s="8">
-        <v>1</v>
-      </c>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="7"/>
     </row>
     <row r="93" spans="2:13" ht="15.75" thickBot="1">
       <c r="B93" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I93" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="J93" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -2988,25 +3012,31 @@
     </row>
     <row r="94" spans="2:13" ht="15.75" thickBot="1">
       <c r="B94" s="6">
-        <v>3</v>
-      </c>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="7">
+        <v>312</v>
+      </c>
       <c r="F94" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I94" s="7">
         <v>423</v>
       </c>
       <c r="J94" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -3014,19 +3044,19 @@
     </row>
     <row r="95" spans="2:13" ht="15.75" thickBot="1">
       <c r="B95" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E95" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="F95" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G95" s="7" t="s">
         <v>5</v>
@@ -3038,15 +3068,15 @@
         <v>423</v>
       </c>
       <c r="J95" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
     </row>
-    <row r="96" spans="2:13" ht="15.75" thickBot="1">
+    <row r="96" spans="2:13" ht="16.5" thickBot="1">
       <c r="B96" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>7</v>
@@ -3058,123 +3088,117 @@
         <v>423</v>
       </c>
       <c r="F96" s="8">
-        <v>5</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I96" s="7">
-        <v>423</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
+      <c r="I96" s="9"/>
       <c r="J96" s="8">
-        <v>5</v>
-      </c>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="K96" s="9"/>
+      <c r="L96" s="9"/>
+      <c r="M96" s="9"/>
     </row>
     <row r="97" spans="2:13" ht="16.5" thickBot="1">
       <c r="B97" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="7">
-        <v>423</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E97" s="7"/>
       <c r="F97" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="9"/>
       <c r="J97" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K97" s="9"/>
       <c r="L97" s="9"/>
       <c r="M97" s="9"/>
     </row>
-    <row r="98" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B98" s="6">
-        <v>7</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="8">
-        <v>7</v>
-      </c>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="8">
-        <v>7</v>
-      </c>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-      <c r="M98" s="9"/>
-    </row>
-    <row r="99" spans="2:13" ht="15.75">
-      <c r="B99" s="17"/>
-      <c r="C99" s="4" t="s">
+    <row r="98" spans="2:13" ht="15.75">
+      <c r="B98" s="34"/>
+      <c r="C98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="17"/>
-      <c r="G99" s="4" t="s">
+      <c r="D98" s="34"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-      <c r="J99" s="17"/>
-      <c r="K99" s="4" t="s">
+      <c r="H98" s="34"/>
+      <c r="I98" s="34"/>
+      <c r="J98" s="34"/>
+      <c r="K98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L99" s="17"/>
-      <c r="M99" s="17"/>
-    </row>
-    <row r="100" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B100" s="18"/>
-      <c r="C100" s="5">
+      <c r="L98" s="34"/>
+      <c r="M98" s="34"/>
+    </row>
+    <row r="99" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B99" s="35"/>
+      <c r="C99" s="5">
         <v>46311</v>
       </c>
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
-      <c r="F100" s="18"/>
-      <c r="G100" s="5">
+      <c r="D99" s="35"/>
+      <c r="E99" s="35"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="5">
         <v>46318</v>
       </c>
-      <c r="H100" s="18"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="18"/>
-      <c r="K100" s="5">
+      <c r="H99" s="35"/>
+      <c r="I99" s="35"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="5">
         <v>46325</v>
       </c>
-      <c r="L100" s="18"/>
-      <c r="M100" s="18"/>
+      <c r="L99" s="35"/>
+      <c r="M99" s="35"/>
+    </row>
+    <row r="100" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B100" s="6">
+        <v>1</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="8">
+        <v>1</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I100" s="7">
+        <v>423</v>
+      </c>
+      <c r="J100" s="6">
+        <v>1</v>
+      </c>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
+      <c r="M100" s="7"/>
     </row>
     <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>5</v>
@@ -3186,7 +3210,7 @@
         <v>423</v>
       </c>
       <c r="J101" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -3194,25 +3218,19 @@
     </row>
     <row r="102" spans="2:13" ht="15.75" thickBot="1">
       <c r="B102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="8">
-        <v>2</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I102" s="7">
-        <v>423</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
       <c r="J102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -3220,19 +3238,25 @@
     </row>
     <row r="103" spans="2:13" ht="15.75" thickBot="1">
       <c r="B103" s="6">
-        <v>3</v>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="7">
+        <v>312</v>
+      </c>
       <c r="F103" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -3240,25 +3264,25 @@
     </row>
     <row r="104" spans="2:13" ht="15.75" thickBot="1">
       <c r="B104" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E104" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="F104" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -3266,7 +3290,7 @@
     </row>
     <row r="105" spans="2:13" ht="15.75" thickBot="1">
       <c r="B105" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>7</v>
@@ -3278,13 +3302,13 @@
         <v>423</v>
       </c>
       <c r="F105" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -3292,109 +3316,103 @@
     </row>
     <row r="106" spans="2:13" ht="15.75" thickBot="1">
       <c r="B106" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E106" s="7">
-        <v>423</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E106" s="7"/>
       <c r="F106" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
     </row>
-    <row r="107" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B107" s="6">
-        <v>7</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="8">
-        <v>4</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="6">
-        <v>7</v>
-      </c>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75">
-      <c r="B108" s="17"/>
-      <c r="C108" s="4" t="s">
+    <row r="107" spans="2:13" ht="15.75">
+      <c r="B107" s="34"/>
+      <c r="C107" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D108" s="17"/>
-      <c r="E108" s="17"/>
-      <c r="F108" s="17"/>
-      <c r="G108" s="4" t="s">
+      <c r="D107" s="34"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H108" s="17"/>
-      <c r="I108" s="17"/>
-      <c r="J108" s="17"/>
-      <c r="K108" s="4" t="s">
+      <c r="H107" s="34"/>
+      <c r="I107" s="34"/>
+      <c r="J107" s="34"/>
+      <c r="K107" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L108" s="17"/>
-      <c r="M108" s="17"/>
-    </row>
-    <row r="109" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B109" s="18"/>
-      <c r="C109" s="5">
+      <c r="L107" s="34"/>
+      <c r="M107" s="34"/>
+    </row>
+    <row r="108" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B108" s="35"/>
+      <c r="C108" s="5">
         <v>46312</v>
       </c>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="5">
+      <c r="D108" s="35"/>
+      <c r="E108" s="35"/>
+      <c r="F108" s="35"/>
+      <c r="G108" s="5">
         <v>46319</v>
       </c>
-      <c r="H109" s="18"/>
-      <c r="I109" s="18"/>
-      <c r="J109" s="18"/>
-      <c r="K109" s="5">
+      <c r="H108" s="35"/>
+      <c r="I108" s="35"/>
+      <c r="J108" s="35"/>
+      <c r="K108" s="5">
         <v>46326</v>
       </c>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18"/>
+      <c r="L108" s="35"/>
+      <c r="M108" s="35"/>
+    </row>
+    <row r="109" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B109" s="6">
+        <v>1</v>
+      </c>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="6">
+        <v>1</v>
+      </c>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="6">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7"/>
+      <c r="M109" s="7"/>
     </row>
     <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
       <c r="F110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -3402,19 +3420,19 @@
     </row>
     <row r="111" spans="2:13" ht="15.75" thickBot="1">
       <c r="B111" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
       <c r="F111" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -3422,19 +3440,31 @@
     </row>
     <row r="112" spans="2:13" ht="15.75" thickBot="1">
       <c r="B112" s="6">
-        <v>3</v>
-      </c>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="7">
+        <v>312</v>
+      </c>
       <c r="F112" s="6">
-        <v>3</v>
-      </c>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" s="7">
+        <v>312</v>
+      </c>
       <c r="J112" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -3442,31 +3472,31 @@
     </row>
     <row r="113" spans="2:13" ht="15.75" thickBot="1">
       <c r="B113" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E113" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="F113" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I113" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="J113" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -3474,7 +3504,7 @@
     </row>
     <row r="114" spans="2:13" ht="15.75" thickBot="1">
       <c r="B114" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>7</v>
@@ -3486,7 +3516,7 @@
         <v>423</v>
       </c>
       <c r="F114" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" s="7" t="s">
         <v>7</v>
@@ -3498,7 +3528,7 @@
         <v>423</v>
       </c>
       <c r="J114" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -3506,207 +3536,207 @@
     </row>
     <row r="115" spans="2:13" ht="15.75" thickBot="1">
       <c r="B115" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="7">
-        <v>423</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E115" s="7"/>
       <c r="F115" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I115" s="7">
-        <v>423</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I115" s="7"/>
       <c r="J115" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="7"/>
     </row>
-    <row r="116" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B116" s="6">
-        <v>7</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="6">
-        <v>7</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I116" s="7"/>
-      <c r="J116" s="6">
-        <v>7</v>
-      </c>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-    </row>
-    <row r="119" spans="2:13" ht="21" thickBot="1">
-      <c r="B119" s="13" t="s">
+    <row r="118" spans="2:13" ht="21" thickBot="1">
+      <c r="B118" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C119" s="14"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="14"/>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
-      <c r="I119" s="14"/>
-      <c r="J119" s="14"/>
-      <c r="K119" s="14"/>
-      <c r="L119" s="14"/>
-      <c r="M119" s="14"/>
-    </row>
-    <row r="120" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B120" s="2" t="s">
+      <c r="C118" s="37"/>
+      <c r="D118" s="37"/>
+      <c r="E118" s="37"/>
+      <c r="F118" s="37"/>
+      <c r="G118" s="37"/>
+      <c r="H118" s="37"/>
+      <c r="I118" s="37"/>
+      <c r="J118" s="37"/>
+      <c r="K118" s="37"/>
+      <c r="L118" s="37"/>
+      <c r="M118" s="37"/>
+    </row>
+    <row r="119" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B119" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F120" s="3" t="s">
+      <c r="C119" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J120" s="3" t="s">
+      <c r="G119" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J119" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K120" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L120" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M120" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="2:13" ht="15.75">
-      <c r="B121" s="17"/>
-      <c r="C121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-      <c r="G121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H121" s="17"/>
-      <c r="I121" s="17"/>
-      <c r="J121" s="17"/>
-      <c r="K121" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L121" s="17"/>
-      <c r="M121" s="17"/>
-    </row>
-    <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="18"/>
-      <c r="C122" s="5">
+      <c r="K119" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="2:13" ht="15.75">
+      <c r="B120" s="34"/>
+      <c r="C120" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="34"/>
+      <c r="E120" s="34"/>
+      <c r="F120" s="34"/>
+      <c r="G120" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H120" s="34"/>
+      <c r="I120" s="34"/>
+      <c r="J120" s="34"/>
+      <c r="K120" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L120" s="34"/>
+      <c r="M120" s="34"/>
+    </row>
+    <row r="121" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B121" s="35"/>
+      <c r="C121" s="5">
         <v>46307</v>
       </c>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="5">
+      <c r="D121" s="35"/>
+      <c r="E121" s="35"/>
+      <c r="F121" s="35"/>
+      <c r="G121" s="5">
         <v>46314</v>
       </c>
-      <c r="H122" s="18"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="18"/>
-      <c r="K122" s="5">
+      <c r="H121" s="35"/>
+      <c r="I121" s="35"/>
+      <c r="J121" s="35"/>
+      <c r="K121" s="5">
         <v>46321</v>
       </c>
-      <c r="L122" s="18"/>
-      <c r="M122" s="18"/>
-    </row>
-    <row r="123" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L121" s="35"/>
+      <c r="M121" s="35"/>
+    </row>
+    <row r="122" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B122" s="6">
+        <v>1</v>
+      </c>
+      <c r="C122" s="16"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="8">
+        <v>1</v>
+      </c>
+      <c r="G122" s="2"/>
+      <c r="H122" s="17"/>
+      <c r="I122" s="17"/>
+      <c r="J122" s="8">
+        <v>1</v>
+      </c>
+      <c r="K122" s="8"/>
+      <c r="L122" s="7"/>
+      <c r="M122" s="7"/>
+    </row>
+    <row r="123" spans="2:13" ht="16.5" thickBot="1">
       <c r="B123" s="6">
-        <v>1</v>
-      </c>
-      <c r="C123" s="21"/>
-      <c r="D123" s="22"/>
-      <c r="E123" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="C123" s="18"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
       <c r="F123" s="8">
-        <v>1</v>
-      </c>
-      <c r="G123" s="2"/>
-      <c r="H123" s="22"/>
-      <c r="I123" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" s="7">
+        <v>304</v>
+      </c>
       <c r="J123" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" s="8"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="2:13" ht="16.5" thickBot="1">
+    <row r="124" spans="2:13" ht="15.75" thickBot="1">
       <c r="B124" s="6">
-        <v>2</v>
-      </c>
-      <c r="C124" s="23"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" s="7">
+        <v>308</v>
+      </c>
       <c r="F124" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G124" s="12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I124" s="7">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="J124" s="8">
-        <v>2</v>
-      </c>
-      <c r="K124" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
     <row r="125" spans="2:13" ht="15.75" thickBot="1">
       <c r="B125" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>25</v>
@@ -3718,7 +3748,7 @@
         <v>308</v>
       </c>
       <c r="F125" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>9</v>
@@ -3730,7 +3760,7 @@
         <v>101</v>
       </c>
       <c r="J125" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -3738,19 +3768,13 @@
     </row>
     <row r="126" spans="2:13" ht="15.75" thickBot="1">
       <c r="B126" s="6">
-        <v>4</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E126" s="7">
-        <v>308</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C126" s="12"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
       <c r="F126" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>9</v>
@@ -3762,7 +3786,7 @@
         <v>101</v>
       </c>
       <c r="J126" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -3770,25 +3794,19 @@
     </row>
     <row r="127" spans="2:13" ht="15.75" thickBot="1">
       <c r="B127" s="6">
-        <v>5</v>
-      </c>
-      <c r="C127" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="8">
-        <v>5</v>
-      </c>
-      <c r="G127" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I127" s="7">
-        <v>101</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="7"/>
       <c r="J127" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -3796,99 +3814,99 @@
     </row>
     <row r="128" spans="2:13" ht="15.75" thickBot="1">
       <c r="B128" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
       <c r="F128" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
       <c r="I128" s="7"/>
       <c r="J128" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c r="M128" s="7"/>
     </row>
-    <row r="129" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B129" s="6">
-        <v>7</v>
-      </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="8">
-        <v>7</v>
-      </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="8">
-        <v>7</v>
-      </c>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-    </row>
-    <row r="130" spans="2:13" ht="15.75">
-      <c r="B130" s="17"/>
-      <c r="C130" s="4" t="s">
+    <row r="129" spans="2:13" ht="15.75">
+      <c r="B129" s="34"/>
+      <c r="C129" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D130" s="17"/>
-      <c r="E130" s="17"/>
-      <c r="F130" s="17"/>
-      <c r="G130" s="4" t="s">
+      <c r="D129" s="34"/>
+      <c r="E129" s="34"/>
+      <c r="F129" s="34"/>
+      <c r="G129" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H130" s="17"/>
-      <c r="I130" s="17"/>
-      <c r="J130" s="17"/>
-      <c r="K130" s="4" t="s">
+      <c r="H129" s="34"/>
+      <c r="I129" s="34"/>
+      <c r="J129" s="34"/>
+      <c r="K129" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L130" s="17"/>
-      <c r="M130" s="17"/>
-    </row>
-    <row r="131" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B131" s="18"/>
-      <c r="C131" s="5">
+      <c r="L129" s="34"/>
+      <c r="M129" s="34"/>
+    </row>
+    <row r="130" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B130" s="35"/>
+      <c r="C130" s="5">
         <v>46308</v>
       </c>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="5">
+      <c r="D130" s="35"/>
+      <c r="E130" s="35"/>
+      <c r="F130" s="35"/>
+      <c r="G130" s="5">
         <v>46315</v>
       </c>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="5">
+      <c r="H130" s="35"/>
+      <c r="I130" s="35"/>
+      <c r="J130" s="35"/>
+      <c r="K130" s="5">
         <v>46322</v>
       </c>
-      <c r="L131" s="18"/>
-      <c r="M131" s="18"/>
+      <c r="L130" s="35"/>
+      <c r="M130" s="35"/>
+    </row>
+    <row r="131" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B131" s="6">
+        <v>1</v>
+      </c>
+      <c r="C131" s="16"/>
+      <c r="D131" s="17"/>
+      <c r="E131" s="17"/>
+      <c r="F131" s="8">
+        <v>1</v>
+      </c>
+      <c r="G131" s="16"/>
+      <c r="H131" s="17"/>
+      <c r="I131" s="17"/>
+      <c r="J131" s="8">
+        <v>1</v>
+      </c>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
+      <c r="M131" s="7"/>
     </row>
     <row r="132" spans="2:13" ht="15.75" thickBot="1">
       <c r="B132" s="6">
-        <v>1</v>
-      </c>
-      <c r="C132" s="21"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="C132" s="12"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
       <c r="F132" s="8">
-        <v>1</v>
-      </c>
-      <c r="G132" s="21"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="G132" s="12"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
       <c r="J132" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -3896,19 +3914,31 @@
     </row>
     <row r="133" spans="2:13" ht="15.75" thickBot="1">
       <c r="B133" s="6">
-        <v>2</v>
-      </c>
-      <c r="C133" s="12"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E133" s="7">
+        <v>308</v>
+      </c>
       <c r="F133" s="8">
-        <v>2</v>
-      </c>
-      <c r="G133" s="12"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="G133" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I133" s="7">
+        <v>308</v>
+      </c>
       <c r="J133" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -3916,19 +3946,19 @@
     </row>
     <row r="134" spans="2:13" ht="15.75" thickBot="1">
       <c r="B134" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E134" s="7">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="F134" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>25</v>
@@ -3940,7 +3970,7 @@
         <v>308</v>
       </c>
       <c r="J134" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -3948,7 +3978,7 @@
     </row>
     <row r="135" spans="2:13" ht="15.75" thickBot="1">
       <c r="B135" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>27</v>
@@ -3960,7 +3990,7 @@
         <v>318</v>
       </c>
       <c r="F135" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>25</v>
@@ -3972,7 +4002,7 @@
         <v>308</v>
       </c>
       <c r="J135" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -3980,31 +4010,19 @@
     </row>
     <row r="136" spans="2:13" ht="15.75" thickBot="1">
       <c r="B136" s="6">
-        <v>5</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E136" s="7">
-        <v>318</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
       <c r="F136" s="8">
-        <v>5</v>
-      </c>
-      <c r="G136" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I136" s="7">
-        <v>308</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
       <c r="J136" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -4012,129 +4030,155 @@
     </row>
     <row r="137" spans="2:13" ht="15.75" thickBot="1">
       <c r="B137" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
       <c r="I137" s="7"/>
       <c r="J137" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
     </row>
-    <row r="138" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B138" s="6">
-        <v>7</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="8">
-        <v>7</v>
-      </c>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="8">
-        <v>7</v>
-      </c>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
+    <row r="138" spans="2:13" ht="15.75">
+      <c r="B138" s="34"/>
+      <c r="C138" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="34"/>
+      <c r="E138" s="34"/>
+      <c r="F138" s="34"/>
+      <c r="G138" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" s="34"/>
+      <c r="I138" s="34"/>
+      <c r="J138" s="34"/>
+      <c r="K138" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L138" s="34"/>
+      <c r="M138" s="34"/>
     </row>
     <row r="139" spans="2:13" ht="15.75">
-      <c r="B139" s="17"/>
-      <c r="C139" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="17"/>
-      <c r="E139" s="17"/>
-      <c r="F139" s="17"/>
-      <c r="G139" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H139" s="17"/>
-      <c r="I139" s="17"/>
-      <c r="J139" s="17"/>
-      <c r="K139" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L139" s="17"/>
-      <c r="M139" s="17"/>
-    </row>
-    <row r="140" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B140" s="18"/>
-      <c r="C140" s="5">
+      <c r="B139" s="38"/>
+      <c r="C139" s="23">
         <v>46309</v>
       </c>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="11">
+      <c r="D139" s="38"/>
+      <c r="E139" s="38"/>
+      <c r="F139" s="38"/>
+      <c r="G139" s="39">
         <v>46316</v>
       </c>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="11">
+      <c r="H139" s="38"/>
+      <c r="I139" s="38"/>
+      <c r="J139" s="38"/>
+      <c r="K139" s="39">
         <v>46323</v>
       </c>
-      <c r="L140" s="18"/>
-      <c r="M140" s="18"/>
-    </row>
-    <row r="141" spans="2:13" ht="14.25" customHeight="1">
-      <c r="B141" s="17">
-        <v>1</v>
-      </c>
-      <c r="C141" s="15"/>
-      <c r="D141" s="15"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="17">
-        <v>1</v>
-      </c>
-      <c r="G141" s="15"/>
-      <c r="H141" s="15"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="17"/>
-      <c r="K141" s="15"/>
-      <c r="L141" s="15"/>
-      <c r="M141" s="15"/>
-    </row>
-    <row r="142" spans="2:13" ht="9.75" customHeight="1" thickBot="1">
-      <c r="B142" s="18"/>
-      <c r="C142" s="16"/>
-      <c r="D142" s="16"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="18"/>
-      <c r="G142" s="16"/>
-      <c r="H142" s="16"/>
-      <c r="I142" s="16"/>
-      <c r="J142" s="18"/>
-      <c r="K142" s="16"/>
-      <c r="L142" s="16"/>
-      <c r="M142" s="16"/>
+      <c r="L139" s="38"/>
+      <c r="M139" s="38"/>
+    </row>
+    <row r="140" spans="2:13" ht="14.25" customHeight="1">
+      <c r="B140" s="40">
+        <v>1</v>
+      </c>
+      <c r="C140" s="40"/>
+      <c r="D140" s="40"/>
+      <c r="E140" s="40"/>
+      <c r="F140" s="40">
+        <v>1</v>
+      </c>
+      <c r="G140" s="40"/>
+      <c r="H140" s="40"/>
+      <c r="I140" s="40"/>
+      <c r="J140" s="40"/>
+      <c r="K140" s="40"/>
+      <c r="L140" s="40"/>
+      <c r="M140" s="40"/>
+    </row>
+    <row r="141" spans="2:13">
+      <c r="B141" s="40">
+        <v>2</v>
+      </c>
+      <c r="C141" s="40"/>
+      <c r="D141" s="40"/>
+      <c r="E141" s="40"/>
+      <c r="F141" s="40">
+        <v>2</v>
+      </c>
+      <c r="G141" s="40"/>
+      <c r="H141" s="40"/>
+      <c r="I141" s="40"/>
+      <c r="J141" s="40"/>
+      <c r="K141" s="40"/>
+      <c r="L141" s="40"/>
+      <c r="M141" s="40"/>
+    </row>
+    <row r="142" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B142" s="6">
+        <v>3</v>
+      </c>
+      <c r="C142" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E142" s="7">
+        <v>101</v>
+      </c>
+      <c r="F142" s="8">
+        <v>3</v>
+      </c>
+      <c r="G142" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I142" s="7">
+        <v>101</v>
+      </c>
+      <c r="J142" s="8"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="7"/>
+      <c r="M142" s="7"/>
     </row>
     <row r="143" spans="2:13" ht="15.75" thickBot="1">
       <c r="B143" s="6">
-        <v>2</v>
-      </c>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E143" s="7">
+        <v>101</v>
+      </c>
       <c r="F143" s="8">
-        <v>2</v>
-      </c>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
-      <c r="I143" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="G143" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I143" s="7">
+        <v>101</v>
+      </c>
       <c r="J143" s="8"/>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -4142,59 +4186,47 @@
     </row>
     <row r="144" spans="2:13" ht="15.75" thickBot="1">
       <c r="B144" s="6">
-        <v>3</v>
-      </c>
-      <c r="C144" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D144" s="22" t="s">
+      <c r="D144" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="22">
+      <c r="E144" s="7">
         <v>101</v>
       </c>
       <c r="F144" s="8">
-        <v>3</v>
-      </c>
-      <c r="G144" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G144" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H144" s="22" t="s">
+      <c r="H144" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I144" s="22">
+      <c r="I144" s="7">
         <v>101</v>
       </c>
       <c r="J144" s="8"/>
-      <c r="K144" s="8"/>
+      <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
     <row r="145" spans="2:13" ht="15.75" thickBot="1">
       <c r="B145" s="6">
-        <v>4</v>
-      </c>
-      <c r="C145" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D145" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E145" s="7">
-        <v>101</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
       <c r="F145" s="8">
-        <v>4</v>
-      </c>
-      <c r="G145" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I145" s="7">
-        <v>101</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="7"/>
       <c r="J145" s="8"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -4202,145 +4234,159 @@
     </row>
     <row r="146" spans="2:13" ht="15.75" thickBot="1">
       <c r="B146" s="6">
-        <v>5</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E146" s="7">
-        <v>101</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
       <c r="F146" s="8">
-        <v>5</v>
-      </c>
-      <c r="G146" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I146" s="7">
-        <v>101</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
       <c r="J146" s="8"/>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
     </row>
-    <row r="147" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B147" s="6">
-        <v>6</v>
-      </c>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="8">
-        <v>6</v>
-      </c>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="8"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-    </row>
-    <row r="148" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B148" s="6">
-        <v>7</v>
-      </c>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="8">
-        <v>7</v>
-      </c>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-      <c r="I148" s="7"/>
-      <c r="J148" s="8"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
-    </row>
-    <row r="149" spans="2:13" ht="15.75">
-      <c r="B149" s="17"/>
-      <c r="C149" s="4" t="s">
+    <row r="147" spans="2:13" ht="15.75">
+      <c r="B147" s="34"/>
+      <c r="C147" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D147" s="34"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="34"/>
+      <c r="G147" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H147" s="34"/>
+      <c r="I147" s="34"/>
+      <c r="J147" s="34"/>
+      <c r="K147" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L147" s="34"/>
+      <c r="M147" s="34"/>
+    </row>
+    <row r="148" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B148" s="35"/>
+      <c r="C148" s="5">
+        <v>46310</v>
+      </c>
+      <c r="D148" s="35"/>
+      <c r="E148" s="35"/>
+      <c r="F148" s="35"/>
+      <c r="G148" s="5">
+        <v>46317</v>
+      </c>
+      <c r="H148" s="35"/>
+      <c r="I148" s="35"/>
+      <c r="J148" s="35"/>
+      <c r="K148" s="5">
+        <v>46324</v>
+      </c>
+      <c r="L148" s="35"/>
+      <c r="M148" s="35"/>
+    </row>
+    <row r="149" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B149" s="6">
+        <v>1</v>
+      </c>
+      <c r="C149" s="16"/>
       <c r="D149" s="17"/>
       <c r="E149" s="17"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H149" s="17"/>
-      <c r="I149" s="17"/>
-      <c r="J149" s="17"/>
-      <c r="K149" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L149" s="17"/>
-      <c r="M149" s="17"/>
-    </row>
-    <row r="150" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B150" s="18"/>
-      <c r="C150" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D150" s="18"/>
-      <c r="E150" s="18"/>
-      <c r="F150" s="18"/>
-      <c r="G150" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H150" s="18"/>
-      <c r="I150" s="18"/>
-      <c r="J150" s="18"/>
-      <c r="K150" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L150" s="18"/>
-      <c r="M150" s="18"/>
-    </row>
-    <row r="151" spans="2:13" ht="16.5" thickBot="1">
+      <c r="F149" s="8">
+        <v>1</v>
+      </c>
+      <c r="G149" s="28"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="8">
+        <v>1</v>
+      </c>
+      <c r="K149" s="9"/>
+      <c r="L149" s="9"/>
+      <c r="M149" s="9"/>
+    </row>
+    <row r="150" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B150" s="6">
+        <v>2</v>
+      </c>
+      <c r="C150" s="14"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="15"/>
+      <c r="F150" s="8">
+        <v>2</v>
+      </c>
+      <c r="G150" s="12"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="8">
+        <v>2</v>
+      </c>
+      <c r="K150" s="7"/>
+      <c r="L150" s="7"/>
+      <c r="M150" s="7"/>
+    </row>
+    <row r="151" spans="2:13" ht="15.75" thickBot="1">
       <c r="B151" s="6">
-        <v>1</v>
-      </c>
-      <c r="C151" s="21"/>
-      <c r="D151" s="22"/>
-      <c r="E151" s="22"/>
+        <v>3</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E151" s="7">
+        <v>101</v>
+      </c>
       <c r="F151" s="8">
-        <v>1</v>
-      </c>
-      <c r="G151" s="33"/>
-      <c r="H151" s="34"/>
-      <c r="I151" s="34"/>
+        <v>3</v>
+      </c>
+      <c r="G151" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I151" s="7">
+        <v>308</v>
+      </c>
       <c r="J151" s="8">
-        <v>1</v>
-      </c>
-      <c r="K151" s="9"/>
-      <c r="L151" s="9"/>
-      <c r="M151" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="K151" s="7"/>
+      <c r="L151" s="7"/>
+      <c r="M151" s="7"/>
     </row>
     <row r="152" spans="2:13" ht="15.75" thickBot="1">
       <c r="B152" s="6">
-        <v>2</v>
-      </c>
-      <c r="C152" s="19"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D152" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" s="32">
+        <v>312</v>
+      </c>
       <c r="F152" s="8">
-        <v>2</v>
-      </c>
-      <c r="G152" s="12"/>
-      <c r="H152" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="G152" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="I152" s="7"/>
       <c r="J152" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -4348,255 +4394,245 @@
     </row>
     <row r="153" spans="2:13" ht="15.75" thickBot="1">
       <c r="B153" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E153" s="7">
-        <v>101</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D153" s="33"/>
+      <c r="E153" s="33"/>
       <c r="F153" s="8">
-        <v>3</v>
-      </c>
-      <c r="G153" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I153" s="7">
-        <v>308</v>
+        <v>5</v>
+      </c>
+      <c r="G153" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H153" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="J153" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
-    <row r="154" spans="2:13" ht="15.75" thickBot="1">
+    <row r="154" spans="2:13" ht="16.5" thickBot="1">
       <c r="B154" s="6">
-        <v>4</v>
-      </c>
-      <c r="C154" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D154" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E154" s="15">
-        <v>312</v>
+        <v>6</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E154" s="7">
+        <v>231</v>
       </c>
       <c r="F154" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I154" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="H154" s="33"/>
+      <c r="I154" s="33"/>
       <c r="J154" s="8">
-        <v>4</v>
-      </c>
-      <c r="K154" s="7"/>
-      <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
-    </row>
-    <row r="155" spans="2:13" ht="15.75" thickBot="1">
+        <v>6</v>
+      </c>
+      <c r="K154" s="9"/>
+      <c r="L154" s="9"/>
+      <c r="M154" s="9"/>
+    </row>
+    <row r="155" spans="2:13" ht="16.5" thickBot="1">
       <c r="B155" s="6">
-        <v>5</v>
-      </c>
-      <c r="C155" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
+        <v>7</v>
+      </c>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
       <c r="F155" s="8">
-        <v>5</v>
-      </c>
-      <c r="G155" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H155" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I155" s="15" t="s">
-        <v>44</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
+      <c r="I155" s="9"/>
       <c r="J155" s="8">
-        <v>5</v>
-      </c>
-      <c r="K155" s="7"/>
-      <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
-    </row>
-    <row r="156" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B156" s="6">
-        <v>6</v>
-      </c>
-      <c r="C156" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E156" s="7">
-        <v>231</v>
-      </c>
-      <c r="F156" s="8">
-        <v>6</v>
-      </c>
-      <c r="G156" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H156" s="16"/>
-      <c r="I156" s="16"/>
-      <c r="J156" s="8">
-        <v>6</v>
-      </c>
-      <c r="K156" s="9"/>
-      <c r="L156" s="9"/>
-      <c r="M156" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="K155" s="9"/>
+      <c r="L155" s="9"/>
+      <c r="M155" s="9"/>
+    </row>
+    <row r="156" spans="2:13" ht="15.75">
+      <c r="B156" s="34"/>
+      <c r="C156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="34"/>
+      <c r="E156" s="34"/>
+      <c r="F156" s="34"/>
+      <c r="G156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="34"/>
+      <c r="I156" s="34"/>
+      <c r="J156" s="34"/>
+      <c r="K156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L156" s="34"/>
+      <c r="M156" s="34"/>
     </row>
     <row r="157" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B157" s="6">
-        <v>7</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="8">
-        <v>7</v>
-      </c>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
-      <c r="I157" s="9"/>
-      <c r="J157" s="8">
-        <v>7</v>
-      </c>
-      <c r="K157" s="9"/>
-      <c r="L157" s="9"/>
-      <c r="M157" s="9"/>
-    </row>
-    <row r="158" spans="2:13" ht="15.75">
-      <c r="B158" s="17"/>
-      <c r="C158" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="B157" s="35"/>
+      <c r="C157" s="5">
+        <v>46311</v>
+      </c>
+      <c r="D157" s="35"/>
+      <c r="E157" s="35"/>
+      <c r="F157" s="35"/>
+      <c r="G157" s="5">
+        <v>46318</v>
+      </c>
+      <c r="H157" s="35"/>
+      <c r="I157" s="35"/>
+      <c r="J157" s="35"/>
+      <c r="K157" s="5">
+        <v>46325</v>
+      </c>
+      <c r="L157" s="35"/>
+      <c r="M157" s="35"/>
+    </row>
+    <row r="158" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B158" s="6">
+        <v>1</v>
+      </c>
+      <c r="C158" s="16"/>
       <c r="D158" s="17"/>
       <c r="E158" s="17"/>
-      <c r="F158" s="17"/>
-      <c r="G158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H158" s="17"/>
-      <c r="I158" s="17"/>
-      <c r="J158" s="17"/>
-      <c r="K158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L158" s="17"/>
-      <c r="M158" s="17"/>
+      <c r="F158" s="8">
+        <v>1</v>
+      </c>
+      <c r="G158" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H158" s="20"/>
+      <c r="I158" s="7">
+        <v>308</v>
+      </c>
+      <c r="J158" s="6">
+        <v>1</v>
+      </c>
+      <c r="K158" s="7"/>
+      <c r="L158" s="7"/>
+      <c r="M158" s="7"/>
     </row>
     <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="18"/>
-      <c r="C159" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D159" s="18"/>
-      <c r="E159" s="18"/>
-      <c r="F159" s="18"/>
-      <c r="G159" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H159" s="18"/>
-      <c r="I159" s="18"/>
-      <c r="J159" s="18"/>
-      <c r="K159" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L159" s="18"/>
-      <c r="M159" s="18"/>
+      <c r="B159" s="6">
+        <v>2</v>
+      </c>
+      <c r="C159" s="12"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="30">
+        <v>2</v>
+      </c>
+      <c r="G159" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H159" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I159" s="7"/>
+      <c r="J159" s="6">
+        <v>2</v>
+      </c>
+      <c r="K159" s="7"/>
+      <c r="L159" s="7"/>
+      <c r="M159" s="7"/>
     </row>
     <row r="160" spans="2:13" ht="16.5" thickBot="1">
       <c r="B160" s="6">
-        <v>1</v>
-      </c>
-      <c r="C160" s="21"/>
-      <c r="D160" s="22"/>
-      <c r="E160" s="22"/>
-      <c r="F160" s="8">
-        <v>1</v>
-      </c>
-      <c r="G160" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="H160" s="25"/>
-      <c r="I160" s="7">
-        <v>308</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="7">
+        <v>309</v>
+      </c>
+      <c r="F160" s="30">
+        <v>3</v>
+      </c>
+      <c r="G160" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H160" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I160" s="7"/>
       <c r="J160" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" ht="16.5" thickBot="1">
+    <row r="161" spans="2:13" ht="15.75" thickBot="1">
       <c r="B161" s="6">
-        <v>2</v>
-      </c>
-      <c r="C161" s="12"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="35">
-        <v>2</v>
-      </c>
-      <c r="G161" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="H161" s="31" t="s">
-        <v>39</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="7">
+        <v>309</v>
+      </c>
+      <c r="F161" s="30">
+        <v>4</v>
+      </c>
+      <c r="G161" s="27"/>
+      <c r="H161" s="27"/>
       <c r="I161" s="7"/>
       <c r="J161" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" ht="16.5" thickBot="1">
+    <row r="162" spans="2:13" ht="15.75" thickBot="1">
       <c r="B162" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E162" s="7">
-        <v>309</v>
-      </c>
-      <c r="F162" s="35">
-        <v>3</v>
-      </c>
-      <c r="G162" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="H162" s="31" t="s">
-        <v>40</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="F162" s="8">
+        <v>5</v>
+      </c>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -4604,25 +4640,19 @@
     </row>
     <row r="163" spans="2:13" ht="15.75" thickBot="1">
       <c r="B163" s="6">
-        <v>4</v>
-      </c>
-      <c r="C163" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E163" s="7">
-        <v>309</v>
-      </c>
-      <c r="F163" s="35">
-        <v>4</v>
-      </c>
-      <c r="G163" s="32"/>
-      <c r="H163" s="32"/>
+        <v>6</v>
+      </c>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="8">
+        <v>6</v>
+      </c>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
       <c r="I163" s="7"/>
       <c r="J163" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -4630,197 +4660,191 @@
     </row>
     <row r="164" spans="2:13" ht="15.75" thickBot="1">
       <c r="B164" s="6">
-        <v>5</v>
-      </c>
-      <c r="C164" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E164" s="7">
-        <v>231</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
       <c r="F164" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
       <c r="J164" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
     </row>
-    <row r="165" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B165" s="6">
-        <v>6</v>
-      </c>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="8">
-        <v>6</v>
-      </c>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-      <c r="I165" s="7"/>
-      <c r="J165" s="6">
-        <v>6</v>
-      </c>
-      <c r="K165" s="7"/>
-      <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
-    </row>
-    <row r="166" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B166" s="6">
-        <v>7</v>
-      </c>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="8">
-        <v>4</v>
-      </c>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="6">
-        <v>7</v>
-      </c>
-      <c r="K166" s="7"/>
-      <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
-    </row>
-    <row r="167" spans="2:13" ht="15.75">
-      <c r="B167" s="17"/>
-      <c r="C167" s="4" t="s">
+    <row r="165" spans="2:13" ht="15.75">
+      <c r="B165" s="34"/>
+      <c r="C165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D167" s="17"/>
-      <c r="E167" s="17"/>
-      <c r="F167" s="17"/>
-      <c r="G167" s="4" t="s">
+      <c r="D165" s="34"/>
+      <c r="E165" s="34"/>
+      <c r="F165" s="34"/>
+      <c r="G165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H167" s="17"/>
-      <c r="I167" s="17"/>
-      <c r="J167" s="17"/>
-      <c r="K167" s="4" t="s">
+      <c r="H165" s="34"/>
+      <c r="I165" s="34"/>
+      <c r="J165" s="34"/>
+      <c r="K165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L167" s="17"/>
-      <c r="M167" s="17"/>
+      <c r="L165" s="34"/>
+      <c r="M165" s="34"/>
+    </row>
+    <row r="166" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B166" s="35"/>
+      <c r="C166" s="23">
+        <v>46312</v>
+      </c>
+      <c r="D166" s="35"/>
+      <c r="E166" s="35"/>
+      <c r="F166" s="35"/>
+      <c r="G166" s="5">
+        <v>46319</v>
+      </c>
+      <c r="H166" s="35"/>
+      <c r="I166" s="35"/>
+      <c r="J166" s="35"/>
+      <c r="K166" s="5">
+        <v>46326</v>
+      </c>
+      <c r="L166" s="35"/>
+      <c r="M166" s="35"/>
+    </row>
+    <row r="167" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B167" s="22">
+        <v>1</v>
+      </c>
+      <c r="C167" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7">
+        <v>308</v>
+      </c>
+      <c r="F167" s="6">
+        <v>1</v>
+      </c>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="6">
+        <v>1</v>
+      </c>
+      <c r="K167" s="7"/>
+      <c r="L167" s="7"/>
+      <c r="M167" s="7"/>
     </row>
     <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="18"/>
-      <c r="C168" s="28">
-        <v>46312</v>
-      </c>
-      <c r="D168" s="18"/>
-      <c r="E168" s="18"/>
-      <c r="F168" s="18"/>
-      <c r="G168" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H168" s="18"/>
-      <c r="I168" s="18"/>
-      <c r="J168" s="18"/>
-      <c r="K168" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L168" s="18"/>
-      <c r="M168" s="18"/>
+      <c r="B168" s="22">
+        <v>2</v>
+      </c>
+      <c r="C168" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D168" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168" s="7"/>
+      <c r="F168" s="6">
+        <v>2</v>
+      </c>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="6">
+        <v>2</v>
+      </c>
+      <c r="K168" s="7"/>
+      <c r="L168" s="7"/>
+      <c r="M168" s="7"/>
     </row>
     <row r="169" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B169" s="27">
-        <v>1</v>
-      </c>
-      <c r="C169" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7">
-        <v>308</v>
-      </c>
+      <c r="B169" s="22">
+        <v>3</v>
+      </c>
+      <c r="C169" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D169" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E169" s="7"/>
       <c r="F169" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
       <c r="J169" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B170" s="27">
-        <v>2</v>
-      </c>
-      <c r="C170" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D170" s="26" t="s">
-        <v>39</v>
-      </c>
+    <row r="170" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B170" s="22">
+        <v>4</v>
+      </c>
+      <c r="C170" s="27"/>
+      <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
       <c r="J170" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B171" s="27">
-        <v>3</v>
-      </c>
-      <c r="C171" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D171" s="26" t="s">
-        <v>40</v>
-      </c>
+    <row r="171" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B171" s="6">
+        <v>5</v>
+      </c>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
       <c r="J171" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
     <row r="172" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B172" s="27">
-        <v>4</v>
-      </c>
-      <c r="C172" s="32"/>
+      <c r="B172" s="6">
+        <v>6</v>
+      </c>
+      <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
       <c r="J172" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -4828,213 +4852,60 @@
     </row>
     <row r="173" spans="2:13" ht="15.75" thickBot="1">
       <c r="B173" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
       <c r="F173" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G173" s="7"/>
       <c r="H173" s="7"/>
       <c r="I173" s="7"/>
       <c r="J173" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
     </row>
-    <row r="174" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B174" s="6">
-        <v>6</v>
-      </c>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="6">
-        <v>6</v>
-      </c>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
-      <c r="I174" s="7"/>
-      <c r="J174" s="6">
-        <v>6</v>
-      </c>
-      <c r="K174" s="7"/>
-      <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
-    </row>
-    <row r="175" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B175" s="6">
-        <v>7</v>
-      </c>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="6">
-        <v>7</v>
-      </c>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="6">
-        <v>7</v>
-      </c>
-      <c r="K175" s="7"/>
-      <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="L158:L159"/>
-    <mergeCell ref="M158:M159"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="I167:I168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="L167:L168"/>
-    <mergeCell ref="M167:M168"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="E158:E159"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="H158:H159"/>
-    <mergeCell ref="L141:L142"/>
-    <mergeCell ref="M141:M142"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="D149:D150"/>
-    <mergeCell ref="E149:E150"/>
-    <mergeCell ref="F149:F150"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="J149:J150"/>
-    <mergeCell ref="L149:L150"/>
-    <mergeCell ref="M149:M150"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I141:I142"/>
-    <mergeCell ref="J141:J142"/>
-    <mergeCell ref="K141:K142"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="C141:C142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="E141:E142"/>
-    <mergeCell ref="F141:F142"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="B139:B140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="E139:E140"/>
-    <mergeCell ref="F139:F140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="L139:L140"/>
-    <mergeCell ref="M139:M140"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="B119:M119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="L121:L122"/>
-    <mergeCell ref="M121:M122"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="L108:L109"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="L99:L100"/>
-    <mergeCell ref="M99:M100"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="J108:J109"/>
-    <mergeCell ref="M108:M109"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="M71:M72"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="M62:M63"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
+  <mergeCells count="181">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="L49:L50"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="E49:E50"/>
@@ -5059,40 +4930,129 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="H31:H32"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="M23:M24"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="M62:M63"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="M71:M72"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="F89:F90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="J89:J90"/>
+    <mergeCell ref="M89:M90"/>
+    <mergeCell ref="M98:M99"/>
+    <mergeCell ref="E107:E108"/>
+    <mergeCell ref="F107:F108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="J107:J108"/>
+    <mergeCell ref="M107:M108"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="L98:L99"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="L107:L108"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="L89:L90"/>
+    <mergeCell ref="B118:M118"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="E120:E121"/>
+    <mergeCell ref="F120:F121"/>
+    <mergeCell ref="H120:H121"/>
+    <mergeCell ref="I120:I121"/>
+    <mergeCell ref="J120:J121"/>
+    <mergeCell ref="L120:L121"/>
+    <mergeCell ref="M120:M121"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="J129:J130"/>
+    <mergeCell ref="L129:L130"/>
+    <mergeCell ref="M129:M130"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="L138:L139"/>
+    <mergeCell ref="M138:M139"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="D129:D130"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="F129:F130"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="D147:D148"/>
+    <mergeCell ref="E147:E148"/>
+    <mergeCell ref="F147:F148"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="J147:J148"/>
+    <mergeCell ref="L147:L148"/>
+    <mergeCell ref="M147:M148"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I156:I157"/>
+    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="L156:L157"/>
+    <mergeCell ref="M156:M157"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="D165:D166"/>
+    <mergeCell ref="E165:E166"/>
+    <mergeCell ref="F165:F166"/>
+    <mergeCell ref="H165:H166"/>
+    <mergeCell ref="I165:I166"/>
+    <mergeCell ref="J165:J166"/>
+    <mergeCell ref="L165:L166"/>
+    <mergeCell ref="M165:M166"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="E156:E157"/>
+    <mergeCell ref="F156:F157"/>
+    <mergeCell ref="H156:H157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="63">
   <si>
     <t>№</t>
   </si>
@@ -63,15 +63,9 @@
     <t>Четверг</t>
   </si>
   <si>
-    <t>Правовые основы в ПД</t>
-  </si>
-  <si>
     <t>Романова Н.Ю.</t>
   </si>
   <si>
-    <t xml:space="preserve">Психология общения </t>
-  </si>
-  <si>
     <t>Теплухина Ю.И.</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Суббота</t>
   </si>
   <si>
-    <t>Иностранный язык (зачёт)</t>
-  </si>
-  <si>
     <t>Расписание занятий заочного отделения групп Ту-449</t>
   </si>
   <si>
@@ -102,12 +93,6 @@
     <t>Марьинских М.М.</t>
   </si>
   <si>
-    <t xml:space="preserve">Иностранный язык </t>
-  </si>
-  <si>
-    <t>(зачёт с оценкой)</t>
-  </si>
-  <si>
     <t>БЖД</t>
   </si>
   <si>
@@ -138,9 +123,6 @@
     <t>Психология общения</t>
   </si>
   <si>
-    <t xml:space="preserve">Физическая культура </t>
-  </si>
-  <si>
     <t>Кунгурова Е.А.</t>
   </si>
   <si>
@@ -162,18 +144,9 @@
     <t>Пахтусов В.А.</t>
   </si>
   <si>
-    <t>Иностранный язык (зачёт с оценкой)</t>
-  </si>
-  <si>
-    <t>Физическая культура (зачёт с оценкой)</t>
-  </si>
-  <si>
     <t>Квалификац. экзам</t>
   </si>
   <si>
-    <t>Начало экзамена в 08:30</t>
-  </si>
-  <si>
     <t>Махов Ю.Н.,</t>
   </si>
   <si>
@@ -205,6 +178,33 @@
   </si>
   <si>
     <t>Начало в 12:10</t>
+  </si>
+  <si>
+    <t>Иностр язык (зачёт с оценкой)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иностр язык (зачёт с оценкой) </t>
+  </si>
+  <si>
+    <t>Физическ культ(зачёт с оценкой)</t>
+  </si>
+  <si>
+    <t>Правов основы в ПД</t>
+  </si>
+  <si>
+    <t>Начало экзам в 08:30</t>
+  </si>
+  <si>
+    <t>Физ культура (зачёт с оценкой)</t>
+  </si>
+  <si>
+    <t>Психол общения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Психол общения </t>
+  </si>
+  <si>
+    <t>Иностр язык (зачёт)</t>
   </si>
 </sst>
 </file>
@@ -494,17 +494,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -515,14 +515,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -836,20 +836,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
+      <c r="B1" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
@@ -1192,7 +1192,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>12</v>
@@ -1376,10 +1376,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I23" s="34">
         <v>318</v>
@@ -1402,10 +1402,10 @@
         <v>2</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I24" s="34"/>
       <c r="J24" s="34">
@@ -1426,7 +1426,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H25" s="25"/>
       <c r="I25" s="7"/>
@@ -1600,10 +1600,10 @@
         <v>2</v>
       </c>
       <c r="G33" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="I33" s="7">
         <v>304</v>
@@ -1644,10 +1644,10 @@
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="8">
@@ -1750,19 +1750,19 @@
     <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B39" s="39"/>
       <c r="C39" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D39" s="39"/>
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H39" s="39"/>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
       <c r="K39" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
@@ -1791,11 +1791,11 @@
       <c r="B41" s="6">
         <v>1</v>
       </c>
-      <c r="C41" s="44" t="s">
-        <v>50</v>
+      <c r="C41" s="38" t="s">
+        <v>42</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="8">
@@ -1822,10 +1822,10 @@
         <v>2</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="8">
@@ -1852,10 +1852,10 @@
         <v>3</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="8">
@@ -1954,19 +1954,19 @@
     <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="39"/>
       <c r="C48" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D48" s="39"/>
       <c r="E48" s="39"/>
       <c r="F48" s="39"/>
       <c r="G48" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H48" s="39"/>
       <c r="I48" s="39"/>
       <c r="J48" s="39"/>
       <c r="K48" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L48" s="39"/>
       <c r="M48" s="39"/>
@@ -1996,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="6">
@@ -2020,10 +2020,10 @@
         <v>2</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="6">
@@ -2044,10 +2044,10 @@
         <v>3</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="6">
@@ -2068,10 +2068,10 @@
         <v>4</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="6">
@@ -2148,20 +2148,20 @@
       <c r="M56" s="7"/>
     </row>
     <row r="59" spans="2:13" ht="21" thickBot="1">
-      <c r="B59" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="36"/>
-      <c r="M59" s="36"/>
+      <c r="B59" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+      <c r="L59" s="43"/>
+      <c r="M59" s="43"/>
     </row>
     <row r="60" spans="2:13" ht="15.75" thickBot="1">
       <c r="B60" s="2" t="s">
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="8">
@@ -2313,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="8">
@@ -2323,7 +2323,7 @@
         <v>7</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="8">
@@ -2341,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="8">
@@ -2351,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="8">
@@ -2489,7 +2489,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E74" s="7">
         <v>318</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="8">
@@ -2519,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="8">
@@ -2529,7 +2529,7 @@
         <v>7</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="8">
@@ -2544,10 +2544,10 @@
         <v>5</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E76" s="7">
         <v>401</v>
@@ -2559,7 +2559,7 @@
         <v>7</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="8">
@@ -2574,10 +2574,10 @@
         <v>6</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E77" s="7">
         <v>401</v>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="16"/>
-      <c r="E81" s="43"/>
+      <c r="E81" s="37"/>
       <c r="F81" s="34">
         <v>1</v>
       </c>
-      <c r="G81" s="42"/>
-      <c r="H81" s="43"/>
+      <c r="G81" s="36"/>
+      <c r="H81" s="37"/>
       <c r="I81" s="26"/>
       <c r="J81" s="34">
         <v>1</v>
@@ -2703,7 +2703,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E83" s="7">
         <v>318</v>
@@ -2715,7 +2715,7 @@
         <v>7</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="8">
@@ -2730,10 +2730,10 @@
         <v>4</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E84" s="7">
         <v>401</v>
@@ -2745,7 +2745,7 @@
         <v>7</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
@@ -2760,10 +2760,10 @@
         <v>5</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E85" s="7">
         <v>401</v>
@@ -2775,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="8">
@@ -2790,10 +2790,10 @@
         <v>6</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E86" s="7">
         <v>401</v>
@@ -2919,7 +2919,7 @@
         <v>7</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="8">
@@ -2929,7 +2929,7 @@
         <v>7</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="8">
@@ -2943,8 +2943,8 @@
       <c r="B93" s="6">
         <v>4</v>
       </c>
-      <c r="C93" s="31" t="s">
-        <v>48</v>
+      <c r="C93" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>12</v>
@@ -2956,10 +2956,10 @@
         <v>4</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I93" s="19"/>
       <c r="J93" s="8">
@@ -2974,10 +2974,10 @@
         <v>5</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E94" s="7">
         <v>401</v>
@@ -2986,13 +2986,13 @@
         <v>5</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I94" s="26" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J94" s="8">
         <v>5</v>
@@ -3006,10 +3006,10 @@
         <v>6</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E95" s="7">
         <v>401</v>
@@ -3050,19 +3050,19 @@
     <row r="97" spans="2:13" ht="15.75">
       <c r="B97" s="39"/>
       <c r="C97" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D97" s="39"/>
       <c r="E97" s="39"/>
       <c r="F97" s="39"/>
       <c r="G97" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H97" s="39"/>
       <c r="I97" s="39"/>
       <c r="J97" s="39"/>
       <c r="K97" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L97" s="39"/>
       <c r="M97" s="39"/>
@@ -3098,10 +3098,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="44" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="6">
@@ -3122,10 +3122,10 @@
         <v>2</v>
       </c>
       <c r="G100" s="26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H100" s="25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="6">
@@ -3143,7 +3143,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E101" s="7">
         <v>318</v>
@@ -3152,10 +3152,10 @@
         <v>3</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H101" s="25" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="6">
@@ -3170,10 +3170,10 @@
         <v>4</v>
       </c>
       <c r="C102" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E102" s="7">
         <v>401</v>
@@ -3196,10 +3196,10 @@
         <v>5</v>
       </c>
       <c r="C103" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E103" s="7">
         <v>401</v>
@@ -3222,10 +3222,10 @@
         <v>6</v>
       </c>
       <c r="C104" s="31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E104" s="7">
         <v>401</v>
@@ -3266,19 +3266,19 @@
     <row r="106" spans="2:13" ht="15.75">
       <c r="B106" s="39"/>
       <c r="C106" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D106" s="39"/>
       <c r="E106" s="39"/>
       <c r="F106" s="39"/>
       <c r="G106" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H106" s="41"/>
       <c r="I106" s="39"/>
       <c r="J106" s="39"/>
       <c r="K106" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L106" s="39"/>
       <c r="M106" s="39"/>
@@ -3444,20 +3444,20 @@
       <c r="M114" s="7"/>
     </row>
     <row r="117" spans="2:13" ht="21" thickBot="1">
-      <c r="B117" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-      <c r="G117" s="36"/>
-      <c r="H117" s="36"/>
-      <c r="I117" s="36"/>
-      <c r="J117" s="36"/>
-      <c r="K117" s="36"/>
-      <c r="L117" s="36"/>
-      <c r="M117" s="36"/>
+      <c r="B117" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" s="43"/>
+      <c r="D117" s="43"/>
+      <c r="E117" s="43"/>
+      <c r="F117" s="43"/>
+      <c r="G117" s="43"/>
+      <c r="H117" s="43"/>
+      <c r="I117" s="43"/>
+      <c r="J117" s="43"/>
+      <c r="K117" s="43"/>
+      <c r="L117" s="43"/>
+      <c r="M117" s="43"/>
     </row>
     <row r="118" spans="2:13" ht="15.75" thickBot="1">
       <c r="B118" s="2" t="s">
@@ -3567,11 +3567,11 @@
       <c r="F122" s="8">
         <v>2</v>
       </c>
-      <c r="G122" s="11" t="s">
+      <c r="G122" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H122" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="I122" s="7">
         <v>304</v>
@@ -3588,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E123" s="7">
         <v>308</v>
@@ -3603,7 +3603,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I123" s="7">
         <v>101</v>
@@ -3620,10 +3620,10 @@
         <v>4</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E124" s="7">
         <v>308</v>
@@ -3635,7 +3635,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I124" s="7">
         <v>101</v>
@@ -3661,7 +3661,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I125" s="7">
         <v>101</v>
@@ -3798,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E132" s="7">
         <v>308</v>
@@ -3810,10 +3810,10 @@
         <v>3</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I132" s="7">
         <v>308</v>
@@ -3830,10 +3830,10 @@
         <v>4</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E133" s="7">
         <v>318</v>
@@ -3842,10 +3842,10 @@
         <v>4</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I133" s="7">
         <v>308</v>
@@ -3862,10 +3862,10 @@
         <v>5</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E134" s="7">
         <v>318</v>
@@ -3874,10 +3874,10 @@
         <v>5</v>
       </c>
       <c r="G134" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I134" s="7">
         <v>308</v>
@@ -4013,7 +4013,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E141" s="7">
         <v>101</v>
@@ -4025,7 +4025,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I141" s="7">
         <v>101</v>
@@ -4043,7 +4043,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E142" s="7">
         <v>101</v>
@@ -4055,7 +4055,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I142" s="7">
         <v>101</v>
@@ -4073,7 +4073,7 @@
         <v>9</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E143" s="7">
         <v>101</v>
@@ -4085,7 +4085,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I143" s="7">
         <v>101</v>
@@ -4215,23 +4215,23 @@
       <c r="B150" s="6">
         <v>3</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C150" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E150" s="7">
+      <c r="D150" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E150" s="19">
         <v>101</v>
       </c>
       <c r="F150" s="8">
         <v>3</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I150" s="7">
         <v>308</v>
@@ -4243,29 +4243,29 @@
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
-    <row r="151" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B151" s="6">
-        <v>4</v>
-      </c>
-      <c r="C151" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D151" s="37" t="s">
+    <row r="151" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B151" s="21">
+        <v>4</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D151" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="E151" s="37">
+      <c r="E151" s="26">
         <v>312</v>
       </c>
       <c r="F151" s="8">
         <v>4</v>
       </c>
-      <c r="G151" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I151" s="7"/>
+      <c r="G151" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I151" s="19"/>
       <c r="J151" s="8">
         <v>4</v>
       </c>
@@ -4273,26 +4273,30 @@
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
-    <row r="152" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B152" s="6">
-        <v>5</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D152" s="38"/>
-      <c r="E152" s="38"/>
-      <c r="F152" s="8">
-        <v>5</v>
-      </c>
-      <c r="G152" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H152" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="I152" s="37" t="s">
-        <v>42</v>
+    <row r="152" spans="2:13" ht="30.75" thickBot="1">
+      <c r="B152" s="21">
+        <v>5</v>
+      </c>
+      <c r="C152" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D152" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" s="26">
+        <v>231</v>
+      </c>
+      <c r="F152" s="29">
+        <v>5</v>
+      </c>
+      <c r="G152" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H152" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I152" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="J152" s="8">
         <v>5</v>
@@ -4302,26 +4306,18 @@
       <c r="M152" s="7"/>
     </row>
     <row r="153" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B153" s="6">
-        <v>6</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E153" s="7">
-        <v>231</v>
-      </c>
-      <c r="F153" s="8">
-        <v>6</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H153" s="38"/>
-      <c r="I153" s="38"/>
+      <c r="B153" s="21">
+        <v>6</v>
+      </c>
+      <c r="C153" s="24"/>
+      <c r="D153" s="24"/>
+      <c r="E153" s="24"/>
+      <c r="F153" s="29">
+        <v>6</v>
+      </c>
+      <c r="G153" s="26"/>
+      <c r="H153" s="26"/>
+      <c r="I153" s="26"/>
       <c r="J153" s="8">
         <v>6</v>
       </c>
@@ -4330,12 +4326,12 @@
       <c r="M153" s="9"/>
     </row>
     <row r="154" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B154" s="6">
-        <v>7</v>
-      </c>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+      <c r="B154" s="21">
+        <v>7</v>
+      </c>
+      <c r="C154" s="26"/>
+      <c r="D154" s="26"/>
+      <c r="E154" s="26"/>
       <c r="F154" s="8">
         <v>7</v>
       </c>
@@ -4352,19 +4348,19 @@
     <row r="155" spans="2:13" ht="15.75">
       <c r="B155" s="39"/>
       <c r="C155" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D155" s="39"/>
-      <c r="E155" s="39"/>
+        <v>17</v>
+      </c>
+      <c r="D155" s="41"/>
+      <c r="E155" s="41"/>
       <c r="F155" s="39"/>
       <c r="G155" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H155" s="39"/>
       <c r="I155" s="39"/>
       <c r="J155" s="39"/>
       <c r="K155" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L155" s="39"/>
       <c r="M155" s="39"/>
@@ -4400,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H157" s="19"/>
       <c r="I157" s="7">
@@ -4424,10 +4420,10 @@
         <v>2</v>
       </c>
       <c r="G158" s="24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I158" s="7"/>
       <c r="J158" s="6">
@@ -4442,10 +4438,10 @@
         <v>3</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E159" s="7">
         <v>309</v>
@@ -4454,10 +4450,10 @@
         <v>3</v>
       </c>
       <c r="G159" s="25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H159" s="25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I159" s="7"/>
       <c r="J159" s="6">
@@ -4472,10 +4468,10 @@
         <v>4</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E160" s="7">
         <v>309</v>
@@ -4498,10 +4494,10 @@
         <v>5</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E161" s="7">
         <v>231</v>
@@ -4562,19 +4558,19 @@
     <row r="164" spans="2:13" ht="15.75">
       <c r="B164" s="39"/>
       <c r="C164" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D164" s="39"/>
       <c r="E164" s="39"/>
       <c r="F164" s="39"/>
       <c r="G164" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H164" s="39"/>
       <c r="I164" s="39"/>
       <c r="J164" s="39"/>
       <c r="K164" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L164" s="39"/>
       <c r="M164" s="39"/>
@@ -4604,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="C166" s="23" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D166" s="7"/>
       <c r="E166" s="7">
@@ -4628,10 +4624,10 @@
         <v>2</v>
       </c>
       <c r="C167" s="24" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D167" s="20" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="6">
@@ -4652,10 +4648,10 @@
         <v>3</v>
       </c>
       <c r="C168" s="25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D168" s="20" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E168" s="7"/>
       <c r="F168" s="6">
@@ -4752,130 +4748,33 @@
       <c r="M172" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
-    <mergeCell ref="D151:D152"/>
-    <mergeCell ref="E151:E152"/>
-    <mergeCell ref="H152:H153"/>
-    <mergeCell ref="I152:I153"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="J155:J156"/>
-    <mergeCell ref="L155:L156"/>
-    <mergeCell ref="M155:M156"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="F164:F165"/>
-    <mergeCell ref="H164:H165"/>
-    <mergeCell ref="I164:I165"/>
-    <mergeCell ref="J164:J165"/>
-    <mergeCell ref="L164:L165"/>
-    <mergeCell ref="M164:M165"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="E155:E156"/>
-    <mergeCell ref="F155:F156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="F146:F147"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="L146:L147"/>
-    <mergeCell ref="M146:M147"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="L128:L129"/>
-    <mergeCell ref="M128:M129"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="D137:D138"/>
-    <mergeCell ref="E137:E138"/>
-    <mergeCell ref="F137:F138"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="L137:L138"/>
-    <mergeCell ref="M137:M138"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="F119:F120"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="J119:J120"/>
-    <mergeCell ref="L119:L120"/>
-    <mergeCell ref="M119:M120"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="L106:L107"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="B117:M117"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="H79:H80"/>
-    <mergeCell ref="L79:L80"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="L97:L98"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="M88:M89"/>
-    <mergeCell ref="M97:M98"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="M106:M107"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="J79:J80"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="B59:M59"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
+  <mergeCells count="165">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L48:L49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
@@ -4896,32 +4795,125 @@
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="B59:M59"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="J79:J80"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="H79:H80"/>
+    <mergeCell ref="L79:L80"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="L97:L98"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="L106:L107"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="B117:M117"/>
+    <mergeCell ref="M88:M89"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="M106:M107"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="L119:L120"/>
+    <mergeCell ref="M119:M120"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="L128:L129"/>
+    <mergeCell ref="M128:M129"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="D137:D138"/>
+    <mergeCell ref="E137:E138"/>
+    <mergeCell ref="F137:F138"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="L137:L138"/>
+    <mergeCell ref="M137:M138"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="F146:F147"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="L146:L147"/>
+    <mergeCell ref="M146:M147"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="J155:J156"/>
+    <mergeCell ref="L155:L156"/>
+    <mergeCell ref="M155:M156"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="F164:F165"/>
+    <mergeCell ref="H164:H165"/>
+    <mergeCell ref="I164:I165"/>
+    <mergeCell ref="J164:J165"/>
+    <mergeCell ref="L164:L165"/>
+    <mergeCell ref="M164:M165"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="E155:E156"/>
+    <mergeCell ref="F155:F156"/>
+    <mergeCell ref="H155:H156"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Панова\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935"/>
   </bookViews>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="60">
   <si>
     <t>№</t>
   </si>
@@ -105,15 +110,9 @@
     <t>Барихина Н.В.</t>
   </si>
   <si>
-    <t>ПМ 01, ПМ 06</t>
-  </si>
-  <si>
     <t>Начало в 08:30</t>
   </si>
   <si>
-    <t>Квалификац экзамен</t>
-  </si>
-  <si>
     <t>Панова Н.В</t>
   </si>
   <si>
@@ -129,9 +128,6 @@
     <t>с/з</t>
   </si>
   <si>
-    <t>ПМ 02</t>
-  </si>
-  <si>
     <t>Расписание занятий заочного отделения групп Ру-418</t>
   </si>
   <si>
@@ -144,15 +140,6 @@
     <t>Пахтусов В.А.</t>
   </si>
   <si>
-    <t>Квалификац. экзам</t>
-  </si>
-  <si>
-    <t>Махов Ю.Н.,</t>
-  </si>
-  <si>
-    <t>Смолин Н.А.,</t>
-  </si>
-  <si>
     <t>Хасанов Д.Б</t>
   </si>
   <si>
@@ -174,9 +161,6 @@
     <t>Беляев С.В.</t>
   </si>
   <si>
-    <t>ПМ 05</t>
-  </si>
-  <si>
     <t>Начало в 12:10</t>
   </si>
   <si>
@@ -186,9 +170,6 @@
     <t xml:space="preserve">Иностр язык (зачёт с оценкой) </t>
   </si>
   <si>
-    <t>Физическ культ(зачёт с оценкой)</t>
-  </si>
-  <si>
     <t>Правов основы в ПД</t>
   </si>
   <si>
@@ -205,13 +186,28 @@
   </si>
   <si>
     <t>Иностр язык (зачёт)</t>
+  </si>
+  <si>
+    <t>Экзамен по ПМ 02</t>
+  </si>
+  <si>
+    <t>Экзамен по ПМ 05</t>
+  </si>
+  <si>
+    <t>Пахтусов В.А</t>
+  </si>
+  <si>
+    <t>Физическая культура(зачёт с оценкой)</t>
+  </si>
+  <si>
+    <t>Экзамен по ПМ 01, ПМ 06</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -455,15 +451,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -478,9 +470,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -503,8 +492,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -515,14 +510,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,6 +522,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -576,7 +576,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -608,9 +608,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -642,6 +643,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -817,9 +819,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:M172"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" customWidth="1"/>
@@ -835,23 +837,23 @@
     <col min="13" max="13" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-    </row>
-    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -889,47 +891,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="39"/>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="38"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-    </row>
-    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="40"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+    </row>
+    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="39"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-    </row>
-    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+    </row>
+    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>1</v>
       </c>
@@ -949,7 +951,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>2</v>
       </c>
@@ -969,7 +971,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>3</v>
       </c>
@@ -995,7 +997,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>4</v>
       </c>
@@ -1005,7 +1007,9 @@
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7">
+        <v>301</v>
+      </c>
       <c r="F8" s="8">
         <v>4</v>
       </c>
@@ -1023,7 +1027,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>5</v>
       </c>
@@ -1033,7 +1037,9 @@
       <c r="D9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7">
+        <v>301</v>
+      </c>
       <c r="F9" s="8">
         <v>5</v>
       </c>
@@ -1051,7 +1057,7 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>6</v>
       </c>
@@ -1061,7 +1067,9 @@
       <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7">
+        <v>301</v>
+      </c>
       <c r="F10" s="8">
         <v>6</v>
       </c>
@@ -1079,7 +1087,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>7</v>
       </c>
@@ -1089,7 +1097,9 @@
       <c r="D11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="7">
+        <v>301</v>
+      </c>
       <c r="F11" s="8">
         <v>7</v>
       </c>
@@ -1107,47 +1117,47 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="39"/>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="40"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="39"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>1</v>
       </c>
@@ -1167,7 +1177,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>2</v>
       </c>
@@ -1187,12 +1197,12 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>12</v>
@@ -1213,7 +1223,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>4</v>
       </c>
@@ -1243,7 +1253,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>5</v>
       </c>
@@ -1275,7 +1285,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>6</v>
       </c>
@@ -1301,7 +1311,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>7</v>
       </c>
@@ -1325,97 +1335,97 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="39"/>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="38"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="41"/>
-      <c r="C22" s="22">
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="21">
         <v>46309</v>
       </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="33">
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="30">
         <v>46316</v>
       </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="33">
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="30">
         <v>46323</v>
       </c>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="34">
-        <v>1</v>
-      </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34">
-        <v>1</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="34">
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="8">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="35">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="7">
         <v>318</v>
       </c>
-      <c r="J23" s="34">
-        <v>1</v>
-      </c>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="34">
-        <v>2</v>
-      </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34">
-        <v>2</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34">
-        <v>2</v>
-      </c>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="J23" s="31">
+        <v>1</v>
+      </c>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="35">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="35">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="31">
+        <v>2</v>
+      </c>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>3</v>
       </c>
@@ -1425,10 +1435,8 @@
       <c r="F25" s="8">
         <v>3</v>
       </c>
-      <c r="G25" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="25"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="8">
         <v>3</v>
@@ -1437,7 +1445,7 @@
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6">
         <v>4</v>
       </c>
@@ -1457,7 +1465,7 @@
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6">
         <v>5</v>
       </c>
@@ -1481,7 +1489,7 @@
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6">
         <v>6</v>
       </c>
@@ -1505,7 +1513,7 @@
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="6">
         <v>7</v>
       </c>
@@ -1529,47 +1537,47 @@
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="39"/>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="38"/>
       <c r="C30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
       <c r="G30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
       <c r="K30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B31" s="40"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="39"/>
       <c r="C31" s="5">
         <v>46310</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
       <c r="G31" s="5">
         <v>46317</v>
       </c>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
       <c r="K31" s="5">
         <v>46324</v>
       </c>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6">
         <v>1</v>
       </c>
@@ -1589,7 +1597,7 @@
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
     </row>
-    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="6">
         <v>2</v>
       </c>
@@ -1600,7 +1608,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>15</v>
@@ -1615,7 +1623,7 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="6">
         <v>3</v>
       </c>
@@ -1639,12 +1647,12 @@
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="6">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>16</v>
@@ -1669,7 +1677,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6">
         <v>5</v>
       </c>
@@ -1699,7 +1707,7 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="6">
         <v>6</v>
       </c>
@@ -1723,7 +1731,7 @@
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
     </row>
-    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="6">
         <v>7</v>
       </c>
@@ -1747,55 +1755,55 @@
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
     </row>
-    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="39"/>
+    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="38"/>
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
       <c r="G39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
       <c r="K39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-    </row>
-    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B40" s="40"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+    </row>
+    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="39"/>
       <c r="C40" s="5">
         <v>46311</v>
       </c>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="5">
         <v>46318</v>
       </c>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
       <c r="K40" s="5">
         <v>46325</v>
       </c>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-    </row>
-    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+    </row>
+    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="6">
         <v>1</v>
       </c>
-      <c r="C41" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>49</v>
+      <c r="C41" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="8">
@@ -1817,15 +1825,15 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="6">
         <v>2</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>47</v>
+      <c r="C42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="8">
@@ -1847,15 +1855,13 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="6">
         <v>3</v>
       </c>
-      <c r="C43" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>45</v>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="8">
@@ -1871,7 +1877,7 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="6">
         <v>4</v>
       </c>
@@ -1891,7 +1897,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="6">
         <v>5</v>
       </c>
@@ -1911,7 +1917,7 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="6">
         <v>6</v>
       </c>
@@ -1931,7 +1937,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="6">
         <v>7</v>
       </c>
@@ -1951,55 +1957,55 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B48" s="39"/>
+    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="38"/>
       <c r="C48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
       <c r="G48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
       <c r="K48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
-    </row>
-    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B49" s="40"/>
+      <c r="L48" s="38"/>
+      <c r="M48" s="38"/>
+    </row>
+    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="39"/>
       <c r="C49" s="5">
         <v>46312</v>
       </c>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="5">
         <v>46319</v>
       </c>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
       <c r="K49" s="5">
         <v>46326</v>
       </c>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-    </row>
-    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
+    </row>
+    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="6">
         <v>1</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="6">
@@ -2015,15 +2021,15 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="6">
         <v>2</v>
       </c>
-      <c r="C51" s="31" t="s">
-        <v>50</v>
+      <c r="C51" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="6">
@@ -2039,15 +2045,15 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="6">
         <v>3</v>
       </c>
-      <c r="C52" s="31" t="s">
-        <v>50</v>
+      <c r="C52" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="6">
@@ -2063,15 +2069,15 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="6">
         <v>4</v>
       </c>
-      <c r="C53" s="31" t="s">
-        <v>50</v>
+      <c r="C53" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="6">
@@ -2087,7 +2093,7 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="6">
         <v>5</v>
       </c>
@@ -2107,7 +2113,7 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="6">
         <v>6</v>
       </c>
@@ -2127,7 +2133,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1">
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="6">
         <v>7</v>
       </c>
@@ -2147,23 +2153,23 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="59" spans="2:13" ht="21" thickBot="1">
-      <c r="B59" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="43"/>
-      <c r="J59" s="43"/>
-      <c r="K59" s="43"/>
-      <c r="L59" s="43"/>
-      <c r="M59" s="43"/>
-    </row>
-    <row r="60" spans="2:13" ht="15.75" thickBot="1">
+    <row r="59" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
+      <c r="L59" s="37"/>
+      <c r="M59" s="37"/>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
         <v>0</v>
       </c>
@@ -2201,47 +2207,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="15.75">
-      <c r="B61" s="39"/>
+    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="38"/>
       <c r="C61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
       <c r="G61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
       <c r="K61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="39"/>
-      <c r="M61" s="39"/>
-    </row>
-    <row r="62" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B62" s="40"/>
+      <c r="L61" s="38"/>
+      <c r="M61" s="38"/>
+    </row>
+    <row r="62" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="39"/>
       <c r="C62" s="5">
         <v>46307</v>
       </c>
-      <c r="D62" s="40"/>
-      <c r="E62" s="40"/>
-      <c r="F62" s="40"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
       <c r="G62" s="5">
         <v>46314</v>
       </c>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="40"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
       <c r="K62" s="5">
         <v>46321</v>
       </c>
-      <c r="L62" s="40"/>
-      <c r="M62" s="40"/>
-    </row>
-    <row r="63" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+    </row>
+    <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="6">
         <v>1</v>
       </c>
@@ -2261,7 +2267,7 @@
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="2:13" ht="16.5" thickBot="1">
+    <row r="64" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="6">
         <v>2</v>
       </c>
@@ -2271,7 +2277,7 @@
       <c r="F64" s="8">
         <v>2</v>
       </c>
-      <c r="G64" s="32"/>
+      <c r="G64" s="29"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="8">
@@ -2281,21 +2287,21 @@
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1">
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="6">
         <v>3</v>
       </c>
-      <c r="C65" s="31"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="8">
         <v>3</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="8">
@@ -2305,25 +2311,27 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" thickBot="1">
+    <row r="66" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="6">
         <v>4</v>
       </c>
-      <c r="C66" s="31" t="s">
+      <c r="C66" s="28" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E66" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="E66" s="7">
+        <v>309</v>
+      </c>
       <c r="F66" s="8">
         <v>4</v>
       </c>
-      <c r="G66" s="31" t="s">
+      <c r="G66" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="8">
@@ -2333,25 +2341,27 @@
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="2:13" ht="15.75" thickBot="1">
+    <row r="67" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="6">
         <v>5</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="28" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E67" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="E67" s="7">
+        <v>309</v>
+      </c>
       <c r="F67" s="8">
         <v>5</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="8">
@@ -2361,7 +2371,7 @@
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="2:13" ht="15.75" thickBot="1">
+    <row r="68" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="6">
         <v>6</v>
       </c>
@@ -2381,7 +2391,7 @@
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="2:13" ht="15.75" thickBot="1">
+    <row r="69" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="6">
         <v>7</v>
       </c>
@@ -2401,47 +2411,47 @@
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="2:13" ht="15.75">
-      <c r="B70" s="39"/>
+    <row r="70" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="38"/>
       <c r="C70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
       <c r="G70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
       <c r="K70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L70" s="39"/>
-      <c r="M70" s="39"/>
-    </row>
-    <row r="71" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B71" s="40"/>
+      <c r="L70" s="38"/>
+      <c r="M70" s="38"/>
+    </row>
+    <row r="71" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="39"/>
       <c r="C71" s="5">
         <v>46308</v>
       </c>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
       <c r="G71" s="5">
         <v>46315</v>
       </c>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39"/>
       <c r="K71" s="5">
         <v>46322</v>
       </c>
-      <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
-    </row>
-    <row r="72" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L71" s="39"/>
+      <c r="M71" s="39"/>
+    </row>
+    <row r="72" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="6">
         <v>1</v>
       </c>
@@ -2461,17 +2471,17 @@
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="2:13" ht="15.75" thickBot="1">
+    <row r="73" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="6">
         <v>2</v>
       </c>
-      <c r="C73" s="31"/>
+      <c r="C73" s="28"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="8">
         <v>2</v>
       </c>
-      <c r="G73" s="31"/>
+      <c r="G73" s="28"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="8">
@@ -2481,15 +2491,15 @@
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1">
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="6">
         <v>3</v>
       </c>
-      <c r="C74" s="31" t="s">
+      <c r="C74" s="28" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E74" s="7">
         <v>318</v>
@@ -2497,11 +2507,11 @@
       <c r="F74" s="8">
         <v>3</v>
       </c>
-      <c r="G74" s="31" t="s">
+      <c r="G74" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="8">
@@ -2511,25 +2521,25 @@
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" ht="15.75" thickBot="1">
+    <row r="75" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="6">
         <v>4</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="28" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="8">
         <v>4</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="8">
@@ -2539,15 +2549,15 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" ht="15.75" thickBot="1">
+    <row r="76" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="6">
         <v>5</v>
       </c>
-      <c r="C76" s="31" t="s">
+      <c r="C76" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E76" s="7">
         <v>401</v>
@@ -2555,11 +2565,11 @@
       <c r="F76" s="8">
         <v>5</v>
       </c>
-      <c r="G76" s="31" t="s">
+      <c r="G76" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="8">
@@ -2569,15 +2579,15 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" ht="15.75" thickBot="1">
+    <row r="77" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="6">
         <v>6</v>
       </c>
-      <c r="C77" s="31" t="s">
+      <c r="C77" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E77" s="7">
         <v>401</v>
@@ -2595,7 +2605,7 @@
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="2:13" ht="15.75" thickBot="1">
+    <row r="78" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="6">
         <v>7</v>
       </c>
@@ -2615,95 +2625,95 @@
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="2:13" ht="15.75">
-      <c r="B79" s="39"/>
+    <row r="79" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="38"/>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D79" s="39"/>
-      <c r="E79" s="39"/>
-      <c r="F79" s="39"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
       <c r="G79" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
-      <c r="J79" s="39"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
       <c r="K79" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-    </row>
-    <row r="80" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B80" s="41"/>
-      <c r="C80" s="22">
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+    </row>
+    <row r="80" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="40"/>
+      <c r="C80" s="21">
         <v>46309</v>
       </c>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="33">
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="30">
         <v>46316</v>
       </c>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="41"/>
-      <c r="K80" s="33">
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="30">
         <v>46323</v>
       </c>
-      <c r="L80" s="41"/>
-      <c r="M80" s="41"/>
-    </row>
-    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B81" s="34">
+      <c r="L80" s="40"/>
+      <c r="M80" s="40"/>
+    </row>
+    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="31">
         <v>1</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="16"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="34">
-        <v>1</v>
-      </c>
-      <c r="G81" s="36"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="34">
-        <v>1</v>
-      </c>
-      <c r="K81" s="26"/>
-      <c r="L81" s="26"/>
-      <c r="M81" s="26"/>
-    </row>
-    <row r="82" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B82" s="34">
-        <v>2</v>
-      </c>
-      <c r="C82" s="31"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="31">
+        <v>1</v>
+      </c>
+      <c r="G81" s="33"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="24"/>
+      <c r="J81" s="31">
+        <v>1</v>
+      </c>
+      <c r="K81" s="24"/>
+      <c r="L81" s="24"/>
+      <c r="M81" s="24"/>
+    </row>
+    <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="31">
+        <v>2</v>
+      </c>
+      <c r="C82" s="28"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="34">
+      <c r="F82" s="31">
         <v>2</v>
       </c>
       <c r="G82" s="13"/>
       <c r="H82" s="14"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="34">
-        <v>2</v>
-      </c>
-      <c r="K82" s="26"/>
-      <c r="L82" s="26"/>
-      <c r="M82" s="26"/>
-    </row>
-    <row r="83" spans="2:13" ht="15.75" thickBot="1">
+      <c r="I82" s="24"/>
+      <c r="J82" s="31">
+        <v>2</v>
+      </c>
+      <c r="K82" s="24"/>
+      <c r="L82" s="24"/>
+      <c r="M82" s="24"/>
+    </row>
+    <row r="83" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="6">
         <v>3</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C83" s="28" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E83" s="7">
         <v>318</v>
@@ -2711,11 +2721,11 @@
       <c r="F83" s="8">
         <v>3</v>
       </c>
-      <c r="G83" s="31" t="s">
+      <c r="G83" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="8">
@@ -2725,15 +2735,15 @@
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="2:13" ht="15.75" thickBot="1">
+    <row r="84" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="6">
         <v>4</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C84" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E84" s="7">
         <v>401</v>
@@ -2741,11 +2751,11 @@
       <c r="F84" s="8">
         <v>4</v>
       </c>
-      <c r="G84" s="31" t="s">
+      <c r="G84" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
@@ -2755,15 +2765,15 @@
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="2:13" ht="15.75" thickBot="1">
+    <row r="85" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="6">
         <v>5</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E85" s="7">
         <v>401</v>
@@ -2771,11 +2781,11 @@
       <c r="F85" s="8">
         <v>5</v>
       </c>
-      <c r="G85" s="31" t="s">
+      <c r="G85" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="8">
@@ -2785,15 +2795,15 @@
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="2:13" ht="15.75" thickBot="1">
+    <row r="86" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="6">
         <v>6</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E86" s="7">
         <v>401</v>
@@ -2811,7 +2821,7 @@
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="15.75" thickBot="1">
+    <row r="87" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="6">
         <v>7</v>
       </c>
@@ -2831,47 +2841,47 @@
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="2:13" ht="15.75">
-      <c r="B88" s="39"/>
+    <row r="88" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="38"/>
       <c r="C88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="39"/>
-      <c r="E88" s="39"/>
-      <c r="F88" s="39"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
       <c r="G88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H88" s="39"/>
-      <c r="I88" s="39"/>
-      <c r="J88" s="39"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
       <c r="K88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L88" s="39"/>
-      <c r="M88" s="39"/>
-    </row>
-    <row r="89" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B89" s="40"/>
+      <c r="L88" s="38"/>
+      <c r="M88" s="38"/>
+    </row>
+    <row r="89" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="39"/>
       <c r="C89" s="5">
         <v>46310</v>
       </c>
-      <c r="D89" s="40"/>
-      <c r="E89" s="40"/>
-      <c r="F89" s="40"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
       <c r="G89" s="5">
         <v>46317</v>
       </c>
-      <c r="H89" s="40"/>
-      <c r="I89" s="40"/>
-      <c r="J89" s="40"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
       <c r="K89" s="5">
         <v>46324</v>
       </c>
-      <c r="L89" s="40"/>
-      <c r="M89" s="40"/>
-    </row>
-    <row r="90" spans="2:13" ht="16.5" thickBot="1">
+      <c r="L89" s="39"/>
+      <c r="M89" s="39"/>
+    </row>
+    <row r="90" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="6">
         <v>1</v>
       </c>
@@ -2881,9 +2891,9 @@
       <c r="F90" s="8">
         <v>1</v>
       </c>
-      <c r="G90" s="27"/>
-      <c r="H90" s="28"/>
-      <c r="I90" s="28"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="26"/>
+      <c r="I90" s="26"/>
       <c r="J90" s="8">
         <v>1</v>
       </c>
@@ -2891,7 +2901,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="2:13" ht="15.75" thickBot="1">
+    <row r="91" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="6">
         <v>2</v>
       </c>
@@ -2901,7 +2911,7 @@
       <c r="F91" s="8">
         <v>2</v>
       </c>
-      <c r="G91" s="31"/>
+      <c r="G91" s="28"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="8">
@@ -2911,7 +2921,7 @@
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="2:13" ht="15.75" thickBot="1">
+    <row r="92" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="6">
         <v>3</v>
       </c>
@@ -2919,17 +2929,17 @@
         <v>7</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E92" s="16"/>
       <c r="F92" s="8">
         <v>3</v>
       </c>
-      <c r="G92" s="31" t="s">
+      <c r="G92" s="28" t="s">
         <v>7</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="8">
@@ -2939,12 +2949,12 @@
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="2:13" ht="30.75" thickBot="1">
+    <row r="93" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="6">
         <v>4</v>
       </c>
-      <c r="C93" s="35" t="s">
-        <v>54</v>
+      <c r="C93" s="32" t="s">
+        <v>47</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>12</v>
@@ -2956,7 +2966,7 @@
         <v>4</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H93" s="19" t="s">
         <v>16</v>
@@ -2969,30 +2979,30 @@
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="2:13" ht="30.75" thickBot="1">
+    <row r="94" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="6">
         <v>5</v>
       </c>
-      <c r="C94" s="31" t="s">
+      <c r="C94" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E94" s="7">
         <v>401</v>
       </c>
-      <c r="F94" s="29">
-        <v>5</v>
-      </c>
-      <c r="G94" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="H94" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I94" s="26" t="s">
-        <v>36</v>
+      <c r="F94" s="27">
+        <v>5</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H94" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I94" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="J94" s="8">
         <v>5</v>
@@ -3001,25 +3011,25 @@
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="16.5" thickBot="1">
+    <row r="95" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="6">
         <v>6</v>
       </c>
-      <c r="C95" s="31" t="s">
+      <c r="C95" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E95" s="7">
         <v>401</v>
       </c>
-      <c r="F95" s="29">
-        <v>6</v>
-      </c>
-      <c r="G95" s="26"/>
-      <c r="H95" s="26"/>
-      <c r="I95" s="26"/>
+      <c r="F95" s="27">
+        <v>6</v>
+      </c>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
       <c r="J95" s="8">
         <v>6</v>
       </c>
@@ -3027,7 +3037,7 @@
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
     </row>
-    <row r="96" spans="2:13" ht="16.5" thickBot="1">
+    <row r="96" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="6">
         <v>7</v>
       </c>
@@ -3047,63 +3057,65 @@
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
     </row>
-    <row r="97" spans="2:13" ht="15.75">
-      <c r="B97" s="39"/>
+    <row r="97" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="38"/>
       <c r="C97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D97" s="39"/>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
       <c r="G97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
       <c r="K97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L97" s="39"/>
-      <c r="M97" s="39"/>
-    </row>
-    <row r="98" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B98" s="40"/>
+      <c r="L97" s="38"/>
+      <c r="M97" s="38"/>
+    </row>
+    <row r="98" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="39"/>
       <c r="C98" s="5">
         <v>46311</v>
       </c>
-      <c r="D98" s="40"/>
-      <c r="E98" s="40"/>
-      <c r="F98" s="40"/>
-      <c r="G98" s="22">
+      <c r="D98" s="39"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="21">
         <v>46318</v>
       </c>
-      <c r="H98" s="41"/>
-      <c r="I98" s="40"/>
-      <c r="J98" s="40"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="39"/>
       <c r="K98" s="5">
         <v>46325</v>
       </c>
-      <c r="L98" s="40"/>
-      <c r="M98" s="40"/>
-    </row>
-    <row r="99" spans="2:13" ht="16.5" thickBot="1">
+      <c r="L98" s="39"/>
+      <c r="M98" s="39"/>
+    </row>
+    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="6">
         <v>1</v>
       </c>
       <c r="C99" s="15"/>
       <c r="D99" s="16"/>
       <c r="E99" s="16"/>
-      <c r="F99" s="29">
-        <v>1</v>
-      </c>
-      <c r="G99" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="H99" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I99" s="7"/>
+      <c r="F99" s="27">
+        <v>1</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I99" s="7">
+        <v>401</v>
+      </c>
       <c r="J99" s="6">
         <v>1</v>
       </c>
@@ -3111,21 +3123,21 @@
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="2:13" ht="16.5" thickBot="1">
+    <row r="100" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="6">
         <v>2</v>
       </c>
-      <c r="C100" s="31"/>
+      <c r="C100" s="28"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
-      <c r="F100" s="29">
-        <v>2</v>
-      </c>
-      <c r="G100" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H100" s="25" t="s">
-        <v>44</v>
+      <c r="F100" s="27">
+        <v>2</v>
+      </c>
+      <c r="G100" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H100" s="32" t="s">
+        <v>57</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="6">
@@ -3135,28 +3147,24 @@
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="2:13" ht="16.5" thickBot="1">
+    <row r="101" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="6">
         <v>3</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C101" s="28" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E101" s="7">
         <v>318</v>
       </c>
-      <c r="F101" s="29">
-        <v>3</v>
-      </c>
-      <c r="G101" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="H101" s="25" t="s">
-        <v>45</v>
-      </c>
+      <c r="F101" s="27">
+        <v>3</v>
+      </c>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
       <c r="I101" s="7"/>
       <c r="J101" s="6">
         <v>3</v>
@@ -3165,24 +3173,24 @@
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="2:13" ht="15.75" thickBot="1">
+    <row r="102" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="6">
         <v>4</v>
       </c>
-      <c r="C102" s="31" t="s">
+      <c r="C102" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E102" s="7">
         <v>401</v>
       </c>
-      <c r="F102" s="29">
-        <v>4</v>
-      </c>
-      <c r="G102" s="26"/>
-      <c r="H102" s="26"/>
+      <c r="F102" s="27">
+        <v>4</v>
+      </c>
+      <c r="G102" s="32"/>
+      <c r="H102" s="32"/>
       <c r="I102" s="7"/>
       <c r="J102" s="6">
         <v>4</v>
@@ -3191,24 +3199,24 @@
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="2:13" ht="15.75" thickBot="1">
+    <row r="103" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="6">
         <v>5</v>
       </c>
-      <c r="C103" s="31" t="s">
+      <c r="C103" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E103" s="7">
         <v>401</v>
       </c>
-      <c r="F103" s="29">
-        <v>5</v>
-      </c>
-      <c r="G103" s="26"/>
-      <c r="H103" s="26"/>
+      <c r="F103" s="27">
+        <v>5</v>
+      </c>
+      <c r="G103" s="32"/>
+      <c r="H103" s="32"/>
       <c r="I103" s="7"/>
       <c r="J103" s="6">
         <v>5</v>
@@ -3217,24 +3225,24 @@
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="15.75" thickBot="1">
+    <row r="104" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="6">
         <v>6</v>
       </c>
-      <c r="C104" s="31" t="s">
+      <c r="C104" s="28" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E104" s="7">
         <v>401</v>
       </c>
-      <c r="F104" s="29">
-        <v>6</v>
-      </c>
-      <c r="G104" s="26"/>
-      <c r="H104" s="26"/>
+      <c r="F104" s="27">
+        <v>6</v>
+      </c>
+      <c r="G104" s="32"/>
+      <c r="H104" s="32"/>
       <c r="I104" s="7"/>
       <c r="J104" s="6">
         <v>6</v>
@@ -3243,18 +3251,18 @@
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="2:13" ht="15.75" thickBot="1">
+    <row r="105" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="6">
         <v>7</v>
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
-      <c r="F105" s="29">
-        <v>4</v>
-      </c>
-      <c r="G105" s="26"/>
-      <c r="H105" s="26"/>
+      <c r="F105" s="27">
+        <v>4</v>
+      </c>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
       <c r="I105" s="7"/>
       <c r="J105" s="6">
         <v>7</v>
@@ -3263,47 +3271,47 @@
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="2:13" ht="15.75">
-      <c r="B106" s="39"/>
+    <row r="106" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="38"/>
       <c r="C106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="39"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="38"/>
+      <c r="F106" s="38"/>
       <c r="G106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H106" s="41"/>
-      <c r="I106" s="39"/>
-      <c r="J106" s="39"/>
+      <c r="H106" s="40"/>
+      <c r="I106" s="38"/>
+      <c r="J106" s="38"/>
       <c r="K106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L106" s="39"/>
-      <c r="M106" s="39"/>
-    </row>
-    <row r="107" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B107" s="40"/>
+      <c r="L106" s="38"/>
+      <c r="M106" s="38"/>
+    </row>
+    <row r="107" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="39"/>
       <c r="C107" s="5">
         <v>46312</v>
       </c>
-      <c r="D107" s="40"/>
-      <c r="E107" s="40"/>
-      <c r="F107" s="40"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
       <c r="G107" s="5">
         <v>46319</v>
       </c>
-      <c r="H107" s="40"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="40"/>
+      <c r="H107" s="39"/>
+      <c r="I107" s="39"/>
+      <c r="J107" s="39"/>
       <c r="K107" s="5">
         <v>46326</v>
       </c>
-      <c r="L107" s="40"/>
-      <c r="M107" s="40"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L107" s="39"/>
+      <c r="M107" s="39"/>
+    </row>
+    <row r="108" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="6">
         <v>1</v>
       </c>
@@ -3323,7 +3331,7 @@
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="2:13" ht="15.75" thickBot="1">
+    <row r="109" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="6">
         <v>2</v>
       </c>
@@ -3343,7 +3351,7 @@
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="2:13" ht="15.75" thickBot="1">
+    <row r="110" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="6">
         <v>3</v>
       </c>
@@ -3363,7 +3371,7 @@
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="2:13" ht="15.75" thickBot="1">
+    <row r="111" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B111" s="6">
         <v>4</v>
       </c>
@@ -3383,7 +3391,7 @@
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="2:13" ht="15.75" thickBot="1">
+    <row r="112" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B112" s="6">
         <v>5</v>
       </c>
@@ -3403,7 +3411,7 @@
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="15.75" thickBot="1">
+    <row r="113" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B113" s="6">
         <v>6</v>
       </c>
@@ -3423,7 +3431,7 @@
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="2:13" ht="15.75" thickBot="1">
+    <row r="114" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B114" s="6">
         <v>7</v>
       </c>
@@ -3443,23 +3451,23 @@
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
-    <row r="117" spans="2:13" ht="21" thickBot="1">
-      <c r="B117" s="42" t="s">
+    <row r="117" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C117" s="43"/>
-      <c r="D117" s="43"/>
-      <c r="E117" s="43"/>
-      <c r="F117" s="43"/>
-      <c r="G117" s="43"/>
-      <c r="H117" s="43"/>
-      <c r="I117" s="43"/>
-      <c r="J117" s="43"/>
-      <c r="K117" s="43"/>
-      <c r="L117" s="43"/>
-      <c r="M117" s="43"/>
-    </row>
-    <row r="118" spans="2:13" ht="15.75" thickBot="1">
+      <c r="C117" s="37"/>
+      <c r="D117" s="37"/>
+      <c r="E117" s="37"/>
+      <c r="F117" s="37"/>
+      <c r="G117" s="37"/>
+      <c r="H117" s="37"/>
+      <c r="I117" s="37"/>
+      <c r="J117" s="37"/>
+      <c r="K117" s="37"/>
+      <c r="L117" s="37"/>
+      <c r="M117" s="37"/>
+    </row>
+    <row r="118" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B118" s="2" t="s">
         <v>0</v>
       </c>
@@ -3497,47 +3505,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="2:13" ht="15.75">
-      <c r="B119" s="39"/>
+    <row r="119" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="38"/>
       <c r="C119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="39"/>
-      <c r="E119" s="39"/>
-      <c r="F119" s="39"/>
+      <c r="D119" s="38"/>
+      <c r="E119" s="38"/>
+      <c r="F119" s="38"/>
       <c r="G119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H119" s="39"/>
-      <c r="I119" s="39"/>
-      <c r="J119" s="39"/>
+      <c r="H119" s="38"/>
+      <c r="I119" s="38"/>
+      <c r="J119" s="38"/>
       <c r="K119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L119" s="39"/>
-      <c r="M119" s="39"/>
-    </row>
-    <row r="120" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B120" s="40"/>
+      <c r="L119" s="38"/>
+      <c r="M119" s="38"/>
+    </row>
+    <row r="120" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="39"/>
       <c r="C120" s="5">
         <v>46307</v>
       </c>
-      <c r="D120" s="40"/>
-      <c r="E120" s="40"/>
-      <c r="F120" s="40"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="39"/>
       <c r="G120" s="5">
         <v>46314</v>
       </c>
-      <c r="H120" s="40"/>
-      <c r="I120" s="40"/>
-      <c r="J120" s="40"/>
+      <c r="H120" s="39"/>
+      <c r="I120" s="39"/>
+      <c r="J120" s="39"/>
       <c r="K120" s="5">
         <v>46321</v>
       </c>
-      <c r="L120" s="40"/>
-      <c r="M120" s="40"/>
-    </row>
-    <row r="121" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L120" s="39"/>
+      <c r="M120" s="39"/>
+    </row>
+    <row r="121" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B121" s="6">
         <v>1</v>
       </c>
@@ -3557,7 +3565,7 @@
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="2:13" ht="16.5" thickBot="1">
+    <row r="122" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B122" s="6">
         <v>2</v>
       </c>
@@ -3567,8 +3575,8 @@
       <c r="F122" s="8">
         <v>2</v>
       </c>
-      <c r="G122" s="35" t="s">
-        <v>57</v>
+      <c r="G122" s="32" t="s">
+        <v>49</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>15</v>
@@ -3583,7 +3591,7 @@
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="2:13" ht="15.75" thickBot="1">
+    <row r="123" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="6">
         <v>3</v>
       </c>
@@ -3615,7 +3623,7 @@
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="2:13" ht="15.75" thickBot="1">
+    <row r="124" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="6">
         <v>4</v>
       </c>
@@ -3647,7 +3655,7 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="15.75" thickBot="1">
+    <row r="125" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B125" s="6">
         <v>5</v>
       </c>
@@ -3673,7 +3681,7 @@
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="2:13" ht="15.75" thickBot="1">
+    <row r="126" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B126" s="6">
         <v>6</v>
       </c>
@@ -3693,7 +3701,7 @@
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="2:13" ht="15.75" thickBot="1">
+    <row r="127" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="6">
         <v>7</v>
       </c>
@@ -3713,47 +3721,47 @@
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="2:13" ht="15.75">
-      <c r="B128" s="39"/>
+    <row r="128" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B128" s="38"/>
       <c r="C128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D128" s="39"/>
-      <c r="E128" s="39"/>
-      <c r="F128" s="39"/>
+      <c r="D128" s="38"/>
+      <c r="E128" s="38"/>
+      <c r="F128" s="38"/>
       <c r="G128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H128" s="39"/>
-      <c r="I128" s="39"/>
-      <c r="J128" s="39"/>
+      <c r="H128" s="38"/>
+      <c r="I128" s="38"/>
+      <c r="J128" s="38"/>
       <c r="K128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L128" s="39"/>
-      <c r="M128" s="39"/>
-    </row>
-    <row r="129" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B129" s="40"/>
+      <c r="L128" s="38"/>
+      <c r="M128" s="38"/>
+    </row>
+    <row r="129" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="39"/>
       <c r="C129" s="5">
         <v>46308</v>
       </c>
-      <c r="D129" s="40"/>
-      <c r="E129" s="40"/>
-      <c r="F129" s="40"/>
+      <c r="D129" s="39"/>
+      <c r="E129" s="39"/>
+      <c r="F129" s="39"/>
       <c r="G129" s="5">
         <v>46315</v>
       </c>
-      <c r="H129" s="40"/>
-      <c r="I129" s="40"/>
-      <c r="J129" s="40"/>
+      <c r="H129" s="39"/>
+      <c r="I129" s="39"/>
+      <c r="J129" s="39"/>
       <c r="K129" s="5">
         <v>46322</v>
       </c>
-      <c r="L129" s="40"/>
-      <c r="M129" s="40"/>
-    </row>
-    <row r="130" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L129" s="39"/>
+      <c r="M129" s="39"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B130" s="6">
         <v>1</v>
       </c>
@@ -3773,7 +3781,7 @@
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="2:13" ht="15.75" thickBot="1">
+    <row r="131" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B131" s="6">
         <v>2</v>
       </c>
@@ -3793,7 +3801,7 @@
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="2:13" ht="15.75" thickBot="1">
+    <row r="132" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B132" s="6">
         <v>3</v>
       </c>
@@ -3825,7 +3833,7 @@
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="2:13" ht="15.75" thickBot="1">
+    <row r="133" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B133" s="6">
         <v>4</v>
       </c>
@@ -3857,7 +3865,7 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="15.75" thickBot="1">
+    <row r="134" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B134" s="6">
         <v>5</v>
       </c>
@@ -3889,7 +3897,7 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="15.75" thickBot="1">
+    <row r="135" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B135" s="6">
         <v>6</v>
       </c>
@@ -3909,7 +3917,7 @@
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="15.75" thickBot="1">
+    <row r="136" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B136" s="6">
         <v>7</v>
       </c>
@@ -3929,83 +3937,83 @@
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="2:13" ht="15.75">
-      <c r="B137" s="39"/>
+    <row r="137" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B137" s="38"/>
       <c r="C137" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D137" s="39"/>
-      <c r="E137" s="39"/>
-      <c r="F137" s="39"/>
+      <c r="D137" s="38"/>
+      <c r="E137" s="38"/>
+      <c r="F137" s="38"/>
       <c r="G137" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H137" s="39"/>
-      <c r="I137" s="39"/>
-      <c r="J137" s="39"/>
+      <c r="H137" s="38"/>
+      <c r="I137" s="38"/>
+      <c r="J137" s="38"/>
       <c r="K137" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L137" s="39"/>
-      <c r="M137" s="39"/>
-    </row>
-    <row r="138" spans="2:13" ht="15.75">
-      <c r="B138" s="41"/>
-      <c r="C138" s="22">
+      <c r="L137" s="38"/>
+      <c r="M137" s="38"/>
+    </row>
+    <row r="138" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B138" s="40"/>
+      <c r="C138" s="21">
         <v>46309</v>
       </c>
-      <c r="D138" s="41"/>
-      <c r="E138" s="41"/>
-      <c r="F138" s="41"/>
-      <c r="G138" s="33">
+      <c r="D138" s="40"/>
+      <c r="E138" s="40"/>
+      <c r="F138" s="40"/>
+      <c r="G138" s="30">
         <v>46316</v>
       </c>
-      <c r="H138" s="41"/>
-      <c r="I138" s="41"/>
-      <c r="J138" s="41"/>
-      <c r="K138" s="33">
+      <c r="H138" s="40"/>
+      <c r="I138" s="40"/>
+      <c r="J138" s="40"/>
+      <c r="K138" s="30">
         <v>46323</v>
       </c>
-      <c r="L138" s="41"/>
-      <c r="M138" s="41"/>
-    </row>
-    <row r="139" spans="2:13" ht="14.25" customHeight="1">
-      <c r="B139" s="34">
-        <v>1</v>
-      </c>
-      <c r="C139" s="34"/>
-      <c r="D139" s="34"/>
-      <c r="E139" s="34"/>
-      <c r="F139" s="34">
-        <v>1</v>
-      </c>
-      <c r="G139" s="34"/>
-      <c r="H139" s="34"/>
-      <c r="I139" s="34"/>
-      <c r="J139" s="34"/>
-      <c r="K139" s="34"/>
-      <c r="L139" s="34"/>
-      <c r="M139" s="34"/>
-    </row>
-    <row r="140" spans="2:13">
-      <c r="B140" s="34">
-        <v>2</v>
-      </c>
-      <c r="C140" s="34"/>
-      <c r="D140" s="34"/>
-      <c r="E140" s="34"/>
-      <c r="F140" s="34">
-        <v>2</v>
-      </c>
-      <c r="G140" s="34"/>
-      <c r="H140" s="34"/>
-      <c r="I140" s="34"/>
-      <c r="J140" s="34"/>
-      <c r="K140" s="34"/>
-      <c r="L140" s="34"/>
-      <c r="M140" s="34"/>
-    </row>
-    <row r="141" spans="2:13" ht="15.75" thickBot="1">
+      <c r="L138" s="40"/>
+      <c r="M138" s="40"/>
+    </row>
+    <row r="139" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="31">
+        <v>1</v>
+      </c>
+      <c r="C139" s="31"/>
+      <c r="D139" s="31"/>
+      <c r="E139" s="31"/>
+      <c r="F139" s="31">
+        <v>1</v>
+      </c>
+      <c r="G139" s="31"/>
+      <c r="H139" s="31"/>
+      <c r="I139" s="31"/>
+      <c r="J139" s="31"/>
+      <c r="K139" s="31"/>
+      <c r="L139" s="31"/>
+      <c r="M139" s="31"/>
+    </row>
+    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B140" s="31">
+        <v>2</v>
+      </c>
+      <c r="C140" s="31"/>
+      <c r="D140" s="31"/>
+      <c r="E140" s="31"/>
+      <c r="F140" s="31">
+        <v>2</v>
+      </c>
+      <c r="G140" s="31"/>
+      <c r="H140" s="31"/>
+      <c r="I140" s="31"/>
+      <c r="J140" s="31"/>
+      <c r="K140" s="31"/>
+      <c r="L140" s="31"/>
+      <c r="M140" s="31"/>
+    </row>
+    <row r="141" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B141" s="6">
         <v>3</v>
       </c>
@@ -4035,7 +4043,7 @@
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
     </row>
-    <row r="142" spans="2:13" ht="15.75" thickBot="1">
+    <row r="142" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B142" s="6">
         <v>4</v>
       </c>
@@ -4065,7 +4073,7 @@
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
     </row>
-    <row r="143" spans="2:13" ht="15.75" thickBot="1">
+    <row r="143" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B143" s="6">
         <v>5</v>
       </c>
@@ -4095,7 +4103,7 @@
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
     </row>
-    <row r="144" spans="2:13" ht="15.75" thickBot="1">
+    <row r="144" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B144" s="6">
         <v>6</v>
       </c>
@@ -4113,7 +4121,7 @@
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
-    <row r="145" spans="2:13" ht="15.75" thickBot="1">
+    <row r="145" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="6">
         <v>7</v>
       </c>
@@ -4131,47 +4139,47 @@
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="15.75">
-      <c r="B146" s="39"/>
+    <row r="146" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B146" s="38"/>
       <c r="C146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D146" s="39"/>
-      <c r="E146" s="39"/>
-      <c r="F146" s="39"/>
+      <c r="D146" s="38"/>
+      <c r="E146" s="38"/>
+      <c r="F146" s="38"/>
       <c r="G146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="39"/>
-      <c r="I146" s="39"/>
-      <c r="J146" s="39"/>
+      <c r="H146" s="38"/>
+      <c r="I146" s="38"/>
+      <c r="J146" s="38"/>
       <c r="K146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L146" s="39"/>
-      <c r="M146" s="39"/>
-    </row>
-    <row r="147" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B147" s="40"/>
+      <c r="L146" s="38"/>
+      <c r="M146" s="38"/>
+    </row>
+    <row r="147" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="39"/>
       <c r="C147" s="5">
         <v>46310</v>
       </c>
-      <c r="D147" s="40"/>
-      <c r="E147" s="40"/>
-      <c r="F147" s="40"/>
+      <c r="D147" s="39"/>
+      <c r="E147" s="39"/>
+      <c r="F147" s="39"/>
       <c r="G147" s="5">
         <v>46317</v>
       </c>
-      <c r="H147" s="40"/>
-      <c r="I147" s="40"/>
-      <c r="J147" s="40"/>
+      <c r="H147" s="39"/>
+      <c r="I147" s="39"/>
+      <c r="J147" s="39"/>
       <c r="K147" s="5">
         <v>46324</v>
       </c>
-      <c r="L147" s="40"/>
-      <c r="M147" s="40"/>
-    </row>
-    <row r="148" spans="2:13" ht="16.5" thickBot="1">
+      <c r="L147" s="39"/>
+      <c r="M147" s="39"/>
+    </row>
+    <row r="148" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B148" s="6">
         <v>1</v>
       </c>
@@ -4181,9 +4189,9 @@
       <c r="F148" s="8">
         <v>1</v>
       </c>
-      <c r="G148" s="27"/>
-      <c r="H148" s="28"/>
-      <c r="I148" s="28"/>
+      <c r="G148" s="25"/>
+      <c r="H148" s="26"/>
+      <c r="I148" s="26"/>
       <c r="J148" s="8">
         <v>1</v>
       </c>
@@ -4191,7 +4199,7 @@
       <c r="L148" s="9"/>
       <c r="M148" s="9"/>
     </row>
-    <row r="149" spans="2:13" ht="15.75" thickBot="1">
+    <row r="149" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B149" s="6">
         <v>2</v>
       </c>
@@ -4211,7 +4219,7 @@
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
-    <row r="150" spans="2:13" ht="15.75" thickBot="1">
+    <row r="150" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B150" s="6">
         <v>3</v>
       </c>
@@ -4243,24 +4251,24 @@
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
-    <row r="151" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B151" s="21">
-        <v>4</v>
-      </c>
-      <c r="C151" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D151" s="26" t="s">
+    <row r="151" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B151" s="20">
+        <v>4</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D151" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E151" s="26">
+      <c r="E151" s="24">
         <v>312</v>
       </c>
       <c r="F151" s="8">
         <v>4</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H151" s="19" t="s">
         <v>16</v>
@@ -4273,30 +4281,30 @@
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
-    <row r="152" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B152" s="21">
-        <v>5</v>
-      </c>
-      <c r="C152" s="26" t="s">
+    <row r="152" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="20">
+        <v>5</v>
+      </c>
+      <c r="C152" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D152" s="26" t="s">
+      <c r="D152" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E152" s="26">
+      <c r="E152" s="24">
         <v>231</v>
       </c>
-      <c r="F152" s="29">
-        <v>5</v>
-      </c>
-      <c r="G152" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="H152" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I152" s="26" t="s">
-        <v>36</v>
+      <c r="F152" s="27">
+        <v>5</v>
+      </c>
+      <c r="G152" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H152" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I152" s="24" t="s">
+        <v>34</v>
       </c>
       <c r="J152" s="8">
         <v>5</v>
@@ -4305,19 +4313,19 @@
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
-    <row r="153" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B153" s="21">
-        <v>6</v>
-      </c>
-      <c r="C153" s="24"/>
-      <c r="D153" s="24"/>
-      <c r="E153" s="24"/>
-      <c r="F153" s="29">
-        <v>6</v>
-      </c>
-      <c r="G153" s="26"/>
-      <c r="H153" s="26"/>
-      <c r="I153" s="26"/>
+    <row r="153" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="20">
+        <v>6</v>
+      </c>
+      <c r="C153" s="22"/>
+      <c r="D153" s="22"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="27">
+        <v>6</v>
+      </c>
+      <c r="G153" s="24"/>
+      <c r="H153" s="24"/>
+      <c r="I153" s="24"/>
       <c r="J153" s="8">
         <v>6</v>
       </c>
@@ -4325,13 +4333,13 @@
       <c r="L153" s="9"/>
       <c r="M153" s="9"/>
     </row>
-    <row r="154" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B154" s="21">
-        <v>7</v>
-      </c>
-      <c r="C154" s="26"/>
-      <c r="D154" s="26"/>
-      <c r="E154" s="26"/>
+    <row r="154" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="20">
+        <v>7</v>
+      </c>
+      <c r="C154" s="24"/>
+      <c r="D154" s="24"/>
+      <c r="E154" s="24"/>
       <c r="F154" s="8">
         <v>7</v>
       </c>
@@ -4345,47 +4353,47 @@
       <c r="L154" s="9"/>
       <c r="M154" s="9"/>
     </row>
-    <row r="155" spans="2:13" ht="15.75">
-      <c r="B155" s="39"/>
+    <row r="155" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B155" s="38"/>
       <c r="C155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D155" s="41"/>
-      <c r="E155" s="41"/>
-      <c r="F155" s="39"/>
+      <c r="D155" s="40"/>
+      <c r="E155" s="40"/>
+      <c r="F155" s="38"/>
       <c r="G155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H155" s="39"/>
-      <c r="I155" s="39"/>
-      <c r="J155" s="39"/>
+      <c r="H155" s="38"/>
+      <c r="I155" s="38"/>
+      <c r="J155" s="38"/>
       <c r="K155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L155" s="39"/>
-      <c r="M155" s="39"/>
-    </row>
-    <row r="156" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B156" s="40"/>
+      <c r="L155" s="38"/>
+      <c r="M155" s="38"/>
+    </row>
+    <row r="156" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="39"/>
       <c r="C156" s="5">
         <v>46311</v>
       </c>
-      <c r="D156" s="40"/>
-      <c r="E156" s="40"/>
-      <c r="F156" s="40"/>
+      <c r="D156" s="39"/>
+      <c r="E156" s="39"/>
+      <c r="F156" s="39"/>
       <c r="G156" s="5">
         <v>46318</v>
       </c>
-      <c r="H156" s="40"/>
-      <c r="I156" s="40"/>
-      <c r="J156" s="40"/>
+      <c r="H156" s="39"/>
+      <c r="I156" s="39"/>
+      <c r="J156" s="39"/>
       <c r="K156" s="5">
         <v>46325</v>
       </c>
-      <c r="L156" s="40"/>
-      <c r="M156" s="40"/>
-    </row>
-    <row r="157" spans="2:13" ht="16.5" thickBot="1">
+      <c r="L156" s="39"/>
+      <c r="M156" s="39"/>
+    </row>
+    <row r="157" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="6">
         <v>1</v>
       </c>
@@ -4395,10 +4403,12 @@
       <c r="F157" s="8">
         <v>1</v>
       </c>
-      <c r="G157" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H157" s="19"/>
+      <c r="G157" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H157" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="I157" s="7">
         <v>308</v>
       </c>
@@ -4409,21 +4419,21 @@
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
-    <row r="158" spans="2:13" ht="16.5" thickBot="1">
+    <row r="158" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B158" s="6">
         <v>2</v>
       </c>
       <c r="C158" s="11"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="29">
-        <v>2</v>
-      </c>
-      <c r="G158" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="H158" s="25" t="s">
-        <v>32</v>
+      <c r="F158" s="27">
+        <v>2</v>
+      </c>
+      <c r="G158" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H158" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="I158" s="7"/>
       <c r="J158" s="6">
@@ -4433,7 +4443,7 @@
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
     </row>
-    <row r="159" spans="2:13" ht="16.5" thickBot="1">
+    <row r="159" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B159" s="6">
         <v>3</v>
       </c>
@@ -4446,15 +4456,10 @@
       <c r="E159" s="7">
         <v>309</v>
       </c>
-      <c r="F159" s="29">
-        <v>3</v>
-      </c>
-      <c r="G159" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H159" s="25" t="s">
-        <v>33</v>
-      </c>
+      <c r="F159" s="27">
+        <v>3</v>
+      </c>
+      <c r="G159" s="23"/>
       <c r="I159" s="7"/>
       <c r="J159" s="6">
         <v>3</v>
@@ -4463,7 +4468,7 @@
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
-    <row r="160" spans="2:13" ht="15.75" thickBot="1">
+    <row r="160" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B160" s="6">
         <v>4</v>
       </c>
@@ -4476,11 +4481,11 @@
       <c r="E160" s="7">
         <v>309</v>
       </c>
-      <c r="F160" s="29">
-        <v>4</v>
-      </c>
-      <c r="G160" s="26"/>
-      <c r="H160" s="26"/>
+      <c r="F160" s="27">
+        <v>4</v>
+      </c>
+      <c r="G160" s="24"/>
+      <c r="H160" s="24"/>
       <c r="I160" s="7"/>
       <c r="J160" s="6">
         <v>4</v>
@@ -4489,7 +4494,7 @@
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" ht="15.75" thickBot="1">
+    <row r="161" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B161" s="6">
         <v>5</v>
       </c>
@@ -4515,7 +4520,7 @@
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" ht="15.75" thickBot="1">
+    <row r="162" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B162" s="6">
         <v>6</v>
       </c>
@@ -4535,7 +4540,7 @@
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="15.75" thickBot="1">
+    <row r="163" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="6">
         <v>7</v>
       </c>
@@ -4555,54 +4560,56 @@
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
-    <row r="164" spans="2:13" ht="15.75">
-      <c r="B164" s="39"/>
+    <row r="164" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B164" s="38"/>
       <c r="C164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D164" s="39"/>
-      <c r="E164" s="39"/>
-      <c r="F164" s="39"/>
+      <c r="D164" s="38"/>
+      <c r="E164" s="38"/>
+      <c r="F164" s="38"/>
       <c r="G164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H164" s="39"/>
-      <c r="I164" s="39"/>
-      <c r="J164" s="39"/>
+      <c r="H164" s="38"/>
+      <c r="I164" s="38"/>
+      <c r="J164" s="38"/>
       <c r="K164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L164" s="39"/>
-      <c r="M164" s="39"/>
-    </row>
-    <row r="165" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B165" s="40"/>
-      <c r="C165" s="22">
+      <c r="L164" s="38"/>
+      <c r="M164" s="38"/>
+    </row>
+    <row r="165" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="39"/>
+      <c r="C165" s="21">
         <v>46312</v>
       </c>
-      <c r="D165" s="40"/>
-      <c r="E165" s="40"/>
-      <c r="F165" s="40"/>
+      <c r="D165" s="39"/>
+      <c r="E165" s="39"/>
+      <c r="F165" s="39"/>
       <c r="G165" s="5">
         <v>46319</v>
       </c>
-      <c r="H165" s="40"/>
-      <c r="I165" s="40"/>
-      <c r="J165" s="40"/>
+      <c r="H165" s="39"/>
+      <c r="I165" s="39"/>
+      <c r="J165" s="39"/>
       <c r="K165" s="5">
         <v>46326</v>
       </c>
-      <c r="L165" s="40"/>
-      <c r="M165" s="40"/>
-    </row>
-    <row r="166" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B166" s="21">
-        <v>1</v>
-      </c>
-      <c r="C166" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D166" s="7"/>
+      <c r="L165" s="39"/>
+      <c r="M165" s="39"/>
+    </row>
+    <row r="166" spans="2:13" ht="31.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B166" s="20">
+        <v>1</v>
+      </c>
+      <c r="C166" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="E166" s="7">
         <v>308</v>
       </c>
@@ -4619,15 +4626,15 @@
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
-    <row r="167" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B167" s="21">
-        <v>2</v>
-      </c>
-      <c r="C167" s="24" t="s">
+    <row r="167" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="20">
+        <v>2</v>
+      </c>
+      <c r="C167" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D167" s="20" t="s">
-        <v>32</v>
+      <c r="D167" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="6">
@@ -4643,16 +4650,11 @@
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
-    <row r="168" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B168" s="21">
-        <v>3</v>
-      </c>
-      <c r="C168" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D168" s="20" t="s">
-        <v>33</v>
-      </c>
+    <row r="168" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B168" s="20">
+        <v>3</v>
+      </c>
+      <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="6">
         <v>3</v>
@@ -4667,11 +4669,11 @@
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
-    <row r="169" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B169" s="21">
-        <v>4</v>
-      </c>
-      <c r="C169" s="26"/>
+    <row r="169" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B169" s="20">
+        <v>4</v>
+      </c>
+      <c r="C169" s="24"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="6">
@@ -4687,7 +4689,7 @@
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" ht="15.75" thickBot="1">
+    <row r="170" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B170" s="6">
         <v>5</v>
       </c>
@@ -4707,7 +4709,7 @@
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" ht="15.75" thickBot="1">
+    <row r="171" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B171" s="6">
         <v>6</v>
       </c>
@@ -4727,7 +4729,7 @@
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="15.75" thickBot="1">
+    <row r="172" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B172" s="6">
         <v>7</v>
       </c>
@@ -4749,32 +4751,116 @@
     </row>
   </sheetData>
   <mergeCells count="165">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="J155:J156"/>
+    <mergeCell ref="L155:L156"/>
+    <mergeCell ref="M155:M156"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="F164:F165"/>
+    <mergeCell ref="H164:H165"/>
+    <mergeCell ref="I164:I165"/>
+    <mergeCell ref="J164:J165"/>
+    <mergeCell ref="L164:L165"/>
+    <mergeCell ref="M164:M165"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="E155:E156"/>
+    <mergeCell ref="F155:F156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="F146:F147"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="L146:L147"/>
+    <mergeCell ref="M146:M147"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="L128:L129"/>
+    <mergeCell ref="M128:M129"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="D137:D138"/>
+    <mergeCell ref="E137:E138"/>
+    <mergeCell ref="F137:F138"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="L137:L138"/>
+    <mergeCell ref="M137:M138"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="L119:L120"/>
+    <mergeCell ref="M119:M120"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="L106:L107"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="B117:M117"/>
+    <mergeCell ref="M88:M89"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="M106:M107"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="H79:H80"/>
+    <mergeCell ref="L79:L80"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="L97:L98"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="J79:J80"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="B59:M59"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="L61:L62"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
@@ -4799,121 +4885,37 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="H3:H4"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="B59:M59"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="J79:J80"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="H79:H80"/>
-    <mergeCell ref="L79:L80"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="L97:L98"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="L106:L107"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="B117:M117"/>
-    <mergeCell ref="M88:M89"/>
-    <mergeCell ref="M97:M98"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="M106:M107"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="F119:F120"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="J119:J120"/>
-    <mergeCell ref="L119:L120"/>
-    <mergeCell ref="M119:M120"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="L128:L129"/>
-    <mergeCell ref="M128:M129"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="D137:D138"/>
-    <mergeCell ref="E137:E138"/>
-    <mergeCell ref="F137:F138"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="L137:L138"/>
-    <mergeCell ref="M137:M138"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="F146:F147"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="L146:L147"/>
-    <mergeCell ref="M146:M147"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="J155:J156"/>
-    <mergeCell ref="L155:L156"/>
-    <mergeCell ref="M155:M156"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="F164:F165"/>
-    <mergeCell ref="H164:H165"/>
-    <mergeCell ref="I164:I165"/>
-    <mergeCell ref="J164:J165"/>
-    <mergeCell ref="L164:L165"/>
-    <mergeCell ref="M164:M165"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="E155:E156"/>
-    <mergeCell ref="F155:F156"/>
-    <mergeCell ref="H155:H156"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4921,18 +4923,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Панова\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935"/>
   </bookViews>
@@ -21,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="60">
   <si>
     <t>№</t>
   </si>
@@ -206,8 +201,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,6 +490,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -509,12 +510,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +571,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -608,10 +603,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -643,7 +637,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -819,9 +812,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:M172"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" customWidth="1"/>
@@ -837,23 +830,23 @@
     <col min="13" max="13" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="36" t="s">
+    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
+      <c r="B1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-    </row>
-    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+    </row>
+    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -891,47 +884,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="38"/>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="40"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-    </row>
-    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="39"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+    </row>
+    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B4" s="41"/>
       <c r="C4" s="5">
         <v>46307</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
       <c r="G4" s="5">
         <v>46314</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="5">
         <v>46321</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-    </row>
-    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+    </row>
+    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B5" s="6">
         <v>1</v>
       </c>
@@ -951,7 +944,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B6" s="6">
         <v>2</v>
       </c>
@@ -971,7 +964,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B7" s="6">
         <v>3</v>
       </c>
@@ -997,7 +990,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B8" s="6">
         <v>4</v>
       </c>
@@ -1027,7 +1020,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B9" s="6">
         <v>5</v>
       </c>
@@ -1057,7 +1050,7 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B10" s="6">
         <v>6</v>
       </c>
@@ -1087,7 +1080,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B11" s="6">
         <v>7</v>
       </c>
@@ -1117,47 +1110,47 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="40"/>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
       <c r="K12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="39"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B13" s="41"/>
       <c r="C13" s="5">
         <v>46308</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
       <c r="G13" s="5">
         <v>46315</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="5">
         <v>46322</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B14" s="6">
         <v>1</v>
       </c>
@@ -1177,7 +1170,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B15" s="6">
         <v>2</v>
       </c>
@@ -1197,7 +1190,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B16" s="6">
         <v>3</v>
       </c>
@@ -1213,8 +1206,12 @@
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8">
         <v>3</v>
@@ -1223,7 +1220,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B17" s="6">
         <v>4</v>
       </c>
@@ -1240,12 +1237,14 @@
         <v>4</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="I17" s="7">
+        <v>423</v>
+      </c>
       <c r="J17" s="8">
         <v>4</v>
       </c>
@@ -1253,7 +1252,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B18" s="6">
         <v>5</v>
       </c>
@@ -1285,7 +1284,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B19" s="6">
         <v>6</v>
       </c>
@@ -1311,7 +1310,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B20" s="6">
         <v>7</v>
       </c>
@@ -1335,47 +1334,47 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="38"/>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="40"/>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
       <c r="G21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
       <c r="K21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="42"/>
       <c r="C22" s="21">
         <v>46309</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
       <c r="G22" s="30">
         <v>46316</v>
       </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
       <c r="K22" s="30">
         <v>46323</v>
       </c>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B23" s="8">
         <v>1</v>
       </c>
@@ -1401,7 +1400,7 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B24" s="35">
         <v>2</v>
       </c>
@@ -1425,7 +1424,7 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B25" s="6">
         <v>3</v>
       </c>
@@ -1445,7 +1444,7 @@
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B26" s="6">
         <v>4</v>
       </c>
@@ -1465,7 +1464,7 @@
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B27" s="6">
         <v>5</v>
       </c>
@@ -1489,7 +1488,7 @@
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B28" s="6">
         <v>6</v>
       </c>
@@ -1513,7 +1512,7 @@
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B29" s="6">
         <v>7</v>
       </c>
@@ -1537,47 +1536,47 @@
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="38"/>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="40"/>
       <c r="C30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
       <c r="K30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="39"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B31" s="41"/>
       <c r="C31" s="5">
         <v>46310</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
       <c r="G31" s="5">
         <v>46317</v>
       </c>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
       <c r="K31" s="5">
         <v>46324</v>
       </c>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B32" s="6">
         <v>1</v>
       </c>
@@ -1597,7 +1596,7 @@
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
     </row>
-    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="6">
         <v>2</v>
       </c>
@@ -1623,7 +1622,7 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B34" s="6">
         <v>3</v>
       </c>
@@ -1647,7 +1646,7 @@
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B35" s="6">
         <v>4</v>
       </c>
@@ -1677,7 +1676,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B36" s="6">
         <v>5</v>
       </c>
@@ -1707,7 +1706,7 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B37" s="6">
         <v>6</v>
       </c>
@@ -1731,7 +1730,7 @@
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
     </row>
-    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B38" s="6">
         <v>7</v>
       </c>
@@ -1755,47 +1754,47 @@
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
     </row>
-    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="38"/>
+    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B39" s="40"/>
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
       <c r="G39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
       <c r="K39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-    </row>
-    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="39"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+    </row>
+    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B40" s="41"/>
       <c r="C40" s="5">
         <v>46311</v>
       </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
       <c r="G40" s="5">
         <v>46318</v>
       </c>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
       <c r="K40" s="5">
         <v>46325</v>
       </c>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-    </row>
-    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L40" s="41"/>
+      <c r="M40" s="41"/>
+    </row>
+    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B41" s="6">
         <v>1</v>
       </c>
@@ -1825,7 +1824,7 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B42" s="6">
         <v>2</v>
       </c>
@@ -1855,7 +1854,7 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B43" s="6">
         <v>3</v>
       </c>
@@ -1877,7 +1876,7 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B44" s="6">
         <v>4</v>
       </c>
@@ -1897,7 +1896,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B45" s="6">
         <v>5</v>
       </c>
@@ -1917,7 +1916,7 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B46" s="6">
         <v>6</v>
       </c>
@@ -1937,7 +1936,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B47" s="6">
         <v>7</v>
       </c>
@@ -1957,47 +1956,47 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="38"/>
+    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B48" s="40"/>
       <c r="C48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
       <c r="G48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
       <c r="K48" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
-    </row>
-    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="39"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+    </row>
+    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B49" s="41"/>
       <c r="C49" s="5">
         <v>46312</v>
       </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="5">
         <v>46319</v>
       </c>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="39"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
       <c r="K49" s="5">
         <v>46326</v>
       </c>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-    </row>
-    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+    </row>
+    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B50" s="6">
         <v>1</v>
       </c>
@@ -2021,7 +2020,7 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B51" s="6">
         <v>2</v>
       </c>
@@ -2045,7 +2044,7 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B52" s="6">
         <v>3</v>
       </c>
@@ -2069,7 +2068,7 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B53" s="6">
         <v>4</v>
       </c>
@@ -2093,7 +2092,7 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B54" s="6">
         <v>5</v>
       </c>
@@ -2113,7 +2112,7 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B55" s="6">
         <v>6</v>
       </c>
@@ -2133,7 +2132,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" ht="15.75" thickBot="1">
       <c r="B56" s="6">
         <v>7</v>
       </c>
@@ -2153,23 +2152,23 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="59" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="36" t="s">
+    <row r="59" spans="2:13" ht="21" thickBot="1">
+      <c r="B59" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
-      <c r="L59" s="37"/>
-      <c r="M59" s="37"/>
-    </row>
-    <row r="60" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" thickBot="1">
       <c r="B60" s="2" t="s">
         <v>0</v>
       </c>
@@ -2207,47 +2206,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="38"/>
+    <row r="61" spans="2:13" ht="15.75">
+      <c r="B61" s="40"/>
       <c r="C61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
       <c r="G61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
       <c r="K61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="38"/>
-      <c r="M61" s="38"/>
-    </row>
-    <row r="62" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="39"/>
+      <c r="L61" s="40"/>
+      <c r="M61" s="40"/>
+    </row>
+    <row r="62" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B62" s="41"/>
       <c r="C62" s="5">
         <v>46307</v>
       </c>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
       <c r="G62" s="5">
         <v>46314</v>
       </c>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
       <c r="K62" s="5">
         <v>46321</v>
       </c>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-    </row>
-    <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L62" s="41"/>
+      <c r="M62" s="41"/>
+    </row>
+    <row r="63" spans="2:13" ht="15.75" thickBot="1">
       <c r="B63" s="6">
         <v>1</v>
       </c>
@@ -2267,7 +2266,7 @@
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" ht="16.5" thickBot="1">
       <c r="B64" s="6">
         <v>2</v>
       </c>
@@ -2287,7 +2286,7 @@
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" ht="15.75" thickBot="1">
       <c r="B65" s="6">
         <v>3</v>
       </c>
@@ -2311,7 +2310,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" ht="15.75" thickBot="1">
       <c r="B66" s="6">
         <v>4</v>
       </c>
@@ -2341,7 +2340,7 @@
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" ht="15.75" thickBot="1">
       <c r="B67" s="6">
         <v>5</v>
       </c>
@@ -2371,7 +2370,7 @@
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" ht="15.75" thickBot="1">
       <c r="B68" s="6">
         <v>6</v>
       </c>
@@ -2391,7 +2390,7 @@
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" ht="15.75" thickBot="1">
       <c r="B69" s="6">
         <v>7</v>
       </c>
@@ -2411,47 +2410,47 @@
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="38"/>
+    <row r="70" spans="2:13" ht="15.75">
+      <c r="B70" s="40"/>
       <c r="C70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
       <c r="G70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
       <c r="K70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L70" s="38"/>
-      <c r="M70" s="38"/>
-    </row>
-    <row r="71" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="39"/>
+      <c r="L70" s="40"/>
+      <c r="M70" s="40"/>
+    </row>
+    <row r="71" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B71" s="41"/>
       <c r="C71" s="5">
         <v>46308</v>
       </c>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="5">
         <v>46315</v>
       </c>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
       <c r="K71" s="5">
         <v>46322</v>
       </c>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-    </row>
-    <row r="72" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L71" s="41"/>
+      <c r="M71" s="41"/>
+    </row>
+    <row r="72" spans="2:13" ht="15.75" thickBot="1">
       <c r="B72" s="6">
         <v>1</v>
       </c>
@@ -2471,7 +2470,7 @@
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" ht="15.75" thickBot="1">
       <c r="B73" s="6">
         <v>2</v>
       </c>
@@ -2491,7 +2490,7 @@
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" ht="15.75" thickBot="1">
       <c r="B74" s="6">
         <v>3</v>
       </c>
@@ -2521,7 +2520,7 @@
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" ht="15.75" thickBot="1">
       <c r="B75" s="6">
         <v>4</v>
       </c>
@@ -2549,7 +2548,7 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" ht="15.75" thickBot="1">
       <c r="B76" s="6">
         <v>5</v>
       </c>
@@ -2579,7 +2578,7 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" ht="15.75" thickBot="1">
       <c r="B77" s="6">
         <v>6</v>
       </c>
@@ -2605,7 +2604,7 @@
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" ht="15.75" thickBot="1">
       <c r="B78" s="6">
         <v>7</v>
       </c>
@@ -2625,47 +2624,47 @@
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="38"/>
+    <row r="79" spans="2:13" ht="15.75">
+      <c r="B79" s="40"/>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
       <c r="G79" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="40"/>
       <c r="K79" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L79" s="38"/>
-      <c r="M79" s="38"/>
-    </row>
-    <row r="80" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="40"/>
+      <c r="L79" s="40"/>
+      <c r="M79" s="40"/>
+    </row>
+    <row r="80" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B80" s="42"/>
       <c r="C80" s="21">
         <v>46309</v>
       </c>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
       <c r="G80" s="30">
         <v>46316</v>
       </c>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
       <c r="K80" s="30">
         <v>46323</v>
       </c>
-      <c r="L80" s="40"/>
-      <c r="M80" s="40"/>
-    </row>
-    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L80" s="42"/>
+      <c r="M80" s="42"/>
+    </row>
+    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1">
       <c r="B81" s="31">
         <v>1</v>
       </c>
@@ -2685,7 +2684,7 @@
       <c r="L81" s="24"/>
       <c r="M81" s="24"/>
     </row>
-    <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" ht="15.75" thickBot="1">
       <c r="B82" s="31">
         <v>2</v>
       </c>
@@ -2705,7 +2704,7 @@
       <c r="L82" s="24"/>
       <c r="M82" s="24"/>
     </row>
-    <row r="83" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:13" ht="15.75" thickBot="1">
       <c r="B83" s="6">
         <v>3</v>
       </c>
@@ -2735,7 +2734,7 @@
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" ht="15.75" thickBot="1">
       <c r="B84" s="6">
         <v>4</v>
       </c>
@@ -2765,7 +2764,7 @@
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:13" ht="15.75" thickBot="1">
       <c r="B85" s="6">
         <v>5</v>
       </c>
@@ -2795,7 +2794,7 @@
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" ht="15.75" thickBot="1">
       <c r="B86" s="6">
         <v>6</v>
       </c>
@@ -2821,7 +2820,7 @@
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:13" ht="15.75" thickBot="1">
       <c r="B87" s="6">
         <v>7</v>
       </c>
@@ -2841,47 +2840,47 @@
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="38"/>
+    <row r="88" spans="2:13" ht="15.75">
+      <c r="B88" s="40"/>
       <c r="C88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D88" s="38"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
       <c r="G88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H88" s="38"/>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
+      <c r="J88" s="40"/>
       <c r="K88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L88" s="38"/>
-      <c r="M88" s="38"/>
-    </row>
-    <row r="89" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="39"/>
+      <c r="L88" s="40"/>
+      <c r="M88" s="40"/>
+    </row>
+    <row r="89" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B89" s="41"/>
       <c r="C89" s="5">
         <v>46310</v>
       </c>
-      <c r="D89" s="39"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="41"/>
       <c r="G89" s="5">
         <v>46317</v>
       </c>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="39"/>
+      <c r="H89" s="41"/>
+      <c r="I89" s="41"/>
+      <c r="J89" s="41"/>
       <c r="K89" s="5">
         <v>46324</v>
       </c>
-      <c r="L89" s="39"/>
-      <c r="M89" s="39"/>
-    </row>
-    <row r="90" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L89" s="41"/>
+      <c r="M89" s="41"/>
+    </row>
+    <row r="90" spans="2:13" ht="16.5" thickBot="1">
       <c r="B90" s="6">
         <v>1</v>
       </c>
@@ -2901,7 +2900,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" ht="15.75" thickBot="1">
       <c r="B91" s="6">
         <v>2</v>
       </c>
@@ -2921,7 +2920,7 @@
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:13" ht="15.75" thickBot="1">
       <c r="B92" s="6">
         <v>3</v>
       </c>
@@ -2949,7 +2948,7 @@
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" ht="30.75" thickBot="1">
       <c r="B93" s="6">
         <v>4</v>
       </c>
@@ -2979,7 +2978,7 @@
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:13" ht="30.75" thickBot="1">
       <c r="B94" s="6">
         <v>5</v>
       </c>
@@ -3011,7 +3010,7 @@
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" ht="16.5" thickBot="1">
       <c r="B95" s="6">
         <v>6</v>
       </c>
@@ -3037,7 +3036,7 @@
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
     </row>
-    <row r="96" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:13" ht="16.5" thickBot="1">
       <c r="B96" s="6">
         <v>7</v>
       </c>
@@ -3057,47 +3056,47 @@
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
     </row>
-    <row r="97" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="38"/>
+    <row r="97" spans="2:13" ht="15.75">
+      <c r="B97" s="40"/>
       <c r="C97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="40"/>
+      <c r="F97" s="40"/>
       <c r="G97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H97" s="38"/>
-      <c r="I97" s="38"/>
-      <c r="J97" s="38"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="40"/>
+      <c r="J97" s="40"/>
       <c r="K97" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L97" s="38"/>
-      <c r="M97" s="38"/>
-    </row>
-    <row r="98" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="39"/>
+      <c r="L97" s="40"/>
+      <c r="M97" s="40"/>
+    </row>
+    <row r="98" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B98" s="41"/>
       <c r="C98" s="5">
         <v>46311</v>
       </c>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
       <c r="G98" s="21">
         <v>46318</v>
       </c>
-      <c r="H98" s="40"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="39"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="41"/>
       <c r="K98" s="5">
         <v>46325</v>
       </c>
-      <c r="L98" s="39"/>
-      <c r="M98" s="39"/>
-    </row>
-    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L98" s="41"/>
+      <c r="M98" s="41"/>
+    </row>
+    <row r="99" spans="2:13" ht="15.75" thickBot="1">
       <c r="B99" s="6">
         <v>1</v>
       </c>
@@ -3123,7 +3122,7 @@
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" ht="15.75" thickBot="1">
       <c r="B100" s="6">
         <v>2</v>
       </c>
@@ -3147,7 +3146,7 @@
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" ht="15.75" thickBot="1">
       <c r="B101" s="6">
         <v>3</v>
       </c>
@@ -3173,7 +3172,7 @@
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" ht="15.75" thickBot="1">
       <c r="B102" s="6">
         <v>4</v>
       </c>
@@ -3199,7 +3198,7 @@
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" ht="15.75" thickBot="1">
       <c r="B103" s="6">
         <v>5</v>
       </c>
@@ -3225,7 +3224,7 @@
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" ht="15.75" thickBot="1">
       <c r="B104" s="6">
         <v>6</v>
       </c>
@@ -3251,7 +3250,7 @@
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" ht="15.75" thickBot="1">
       <c r="B105" s="6">
         <v>7</v>
       </c>
@@ -3271,47 +3270,47 @@
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="38"/>
+    <row r="106" spans="2:13" ht="15.75">
+      <c r="B106" s="40"/>
       <c r="C106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="38"/>
-      <c r="E106" s="38"/>
-      <c r="F106" s="38"/>
+      <c r="D106" s="40"/>
+      <c r="E106" s="40"/>
+      <c r="F106" s="40"/>
       <c r="G106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H106" s="40"/>
-      <c r="I106" s="38"/>
-      <c r="J106" s="38"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="40"/>
+      <c r="J106" s="40"/>
       <c r="K106" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L106" s="38"/>
-      <c r="M106" s="38"/>
-    </row>
-    <row r="107" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="39"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="40"/>
+    </row>
+    <row r="107" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B107" s="41"/>
       <c r="C107" s="5">
         <v>46312</v>
       </c>
-      <c r="D107" s="39"/>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
+      <c r="F107" s="41"/>
       <c r="G107" s="5">
         <v>46319</v>
       </c>
-      <c r="H107" s="39"/>
-      <c r="I107" s="39"/>
-      <c r="J107" s="39"/>
+      <c r="H107" s="41"/>
+      <c r="I107" s="41"/>
+      <c r="J107" s="41"/>
       <c r="K107" s="5">
         <v>46326</v>
       </c>
-      <c r="L107" s="39"/>
-      <c r="M107" s="39"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L107" s="41"/>
+      <c r="M107" s="41"/>
+    </row>
+    <row r="108" spans="2:13" ht="15.75" thickBot="1">
       <c r="B108" s="6">
         <v>1</v>
       </c>
@@ -3331,7 +3330,7 @@
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" ht="15.75" thickBot="1">
       <c r="B109" s="6">
         <v>2</v>
       </c>
@@ -3351,7 +3350,7 @@
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" ht="15.75" thickBot="1">
       <c r="B110" s="6">
         <v>3</v>
       </c>
@@ -3371,7 +3370,7 @@
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" ht="15.75" thickBot="1">
       <c r="B111" s="6">
         <v>4</v>
       </c>
@@ -3391,7 +3390,7 @@
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" ht="15.75" thickBot="1">
       <c r="B112" s="6">
         <v>5</v>
       </c>
@@ -3411,7 +3410,7 @@
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" ht="15.75" thickBot="1">
       <c r="B113" s="6">
         <v>6</v>
       </c>
@@ -3431,7 +3430,7 @@
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" ht="15.75" thickBot="1">
       <c r="B114" s="6">
         <v>7</v>
       </c>
@@ -3451,23 +3450,23 @@
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
-    <row r="117" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="36" t="s">
+    <row r="117" spans="2:13" ht="21" thickBot="1">
+      <c r="B117" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C117" s="37"/>
-      <c r="D117" s="37"/>
-      <c r="E117" s="37"/>
-      <c r="F117" s="37"/>
-      <c r="G117" s="37"/>
-      <c r="H117" s="37"/>
-      <c r="I117" s="37"/>
-      <c r="J117" s="37"/>
-      <c r="K117" s="37"/>
-      <c r="L117" s="37"/>
-      <c r="M117" s="37"/>
-    </row>
-    <row r="118" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39"/>
+      <c r="H117" s="39"/>
+      <c r="I117" s="39"/>
+      <c r="J117" s="39"/>
+      <c r="K117" s="39"/>
+      <c r="L117" s="39"/>
+      <c r="M117" s="39"/>
+    </row>
+    <row r="118" spans="2:13" ht="15.75" thickBot="1">
       <c r="B118" s="2" t="s">
         <v>0</v>
       </c>
@@ -3505,47 +3504,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B119" s="38"/>
+    <row r="119" spans="2:13" ht="15.75">
+      <c r="B119" s="40"/>
       <c r="C119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="38"/>
-      <c r="E119" s="38"/>
-      <c r="F119" s="38"/>
+      <c r="D119" s="40"/>
+      <c r="E119" s="40"/>
+      <c r="F119" s="40"/>
       <c r="G119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H119" s="38"/>
-      <c r="I119" s="38"/>
-      <c r="J119" s="38"/>
+      <c r="H119" s="40"/>
+      <c r="I119" s="40"/>
+      <c r="J119" s="40"/>
       <c r="K119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L119" s="38"/>
-      <c r="M119" s="38"/>
-    </row>
-    <row r="120" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="39"/>
+      <c r="L119" s="40"/>
+      <c r="M119" s="40"/>
+    </row>
+    <row r="120" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B120" s="41"/>
       <c r="C120" s="5">
         <v>46307</v>
       </c>
-      <c r="D120" s="39"/>
-      <c r="E120" s="39"/>
-      <c r="F120" s="39"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="41"/>
       <c r="G120" s="5">
         <v>46314</v>
       </c>
-      <c r="H120" s="39"/>
-      <c r="I120" s="39"/>
-      <c r="J120" s="39"/>
+      <c r="H120" s="41"/>
+      <c r="I120" s="41"/>
+      <c r="J120" s="41"/>
       <c r="K120" s="5">
         <v>46321</v>
       </c>
-      <c r="L120" s="39"/>
-      <c r="M120" s="39"/>
-    </row>
-    <row r="121" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L120" s="41"/>
+      <c r="M120" s="41"/>
+    </row>
+    <row r="121" spans="2:13" ht="15.75" thickBot="1">
       <c r="B121" s="6">
         <v>1</v>
       </c>
@@ -3565,7 +3564,7 @@
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" ht="16.5" thickBot="1">
       <c r="B122" s="6">
         <v>2</v>
       </c>
@@ -3591,7 +3590,7 @@
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" ht="15.75" thickBot="1">
       <c r="B123" s="6">
         <v>3</v>
       </c>
@@ -3623,7 +3622,7 @@
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" ht="15.75" thickBot="1">
       <c r="B124" s="6">
         <v>4</v>
       </c>
@@ -3655,7 +3654,7 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" ht="15.75" thickBot="1">
       <c r="B125" s="6">
         <v>5</v>
       </c>
@@ -3681,7 +3680,7 @@
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" ht="15.75" thickBot="1">
       <c r="B126" s="6">
         <v>6</v>
       </c>
@@ -3701,7 +3700,7 @@
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" ht="15.75" thickBot="1">
       <c r="B127" s="6">
         <v>7</v>
       </c>
@@ -3721,47 +3720,47 @@
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B128" s="38"/>
+    <row r="128" spans="2:13" ht="15.75">
+      <c r="B128" s="40"/>
       <c r="C128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D128" s="38"/>
-      <c r="E128" s="38"/>
-      <c r="F128" s="38"/>
+      <c r="D128" s="40"/>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
       <c r="G128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H128" s="38"/>
-      <c r="I128" s="38"/>
-      <c r="J128" s="38"/>
+      <c r="H128" s="40"/>
+      <c r="I128" s="40"/>
+      <c r="J128" s="40"/>
       <c r="K128" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L128" s="38"/>
-      <c r="M128" s="38"/>
-    </row>
-    <row r="129" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="39"/>
+      <c r="L128" s="40"/>
+      <c r="M128" s="40"/>
+    </row>
+    <row r="129" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B129" s="41"/>
       <c r="C129" s="5">
         <v>46308</v>
       </c>
-      <c r="D129" s="39"/>
-      <c r="E129" s="39"/>
-      <c r="F129" s="39"/>
+      <c r="D129" s="41"/>
+      <c r="E129" s="41"/>
+      <c r="F129" s="41"/>
       <c r="G129" s="5">
         <v>46315</v>
       </c>
-      <c r="H129" s="39"/>
-      <c r="I129" s="39"/>
-      <c r="J129" s="39"/>
+      <c r="H129" s="41"/>
+      <c r="I129" s="41"/>
+      <c r="J129" s="41"/>
       <c r="K129" s="5">
         <v>46322</v>
       </c>
-      <c r="L129" s="39"/>
-      <c r="M129" s="39"/>
-    </row>
-    <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L129" s="41"/>
+      <c r="M129" s="41"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" thickBot="1">
       <c r="B130" s="6">
         <v>1</v>
       </c>
@@ -3781,7 +3780,7 @@
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" ht="15.75" thickBot="1">
       <c r="B131" s="6">
         <v>2</v>
       </c>
@@ -3801,7 +3800,7 @@
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" ht="15.75" thickBot="1">
       <c r="B132" s="6">
         <v>3</v>
       </c>
@@ -3833,7 +3832,7 @@
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" ht="15.75" thickBot="1">
       <c r="B133" s="6">
         <v>4</v>
       </c>
@@ -3865,7 +3864,7 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" ht="15.75" thickBot="1">
       <c r="B134" s="6">
         <v>5</v>
       </c>
@@ -3897,7 +3896,7 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" ht="15.75" thickBot="1">
       <c r="B135" s="6">
         <v>6</v>
       </c>
@@ -3917,7 +3916,7 @@
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" ht="15.75" thickBot="1">
       <c r="B136" s="6">
         <v>7</v>
       </c>
@@ -3937,47 +3936,47 @@
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B137" s="38"/>
+    <row r="137" spans="2:13" ht="15.75">
+      <c r="B137" s="40"/>
       <c r="C137" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D137" s="38"/>
-      <c r="E137" s="38"/>
-      <c r="F137" s="38"/>
+      <c r="D137" s="40"/>
+      <c r="E137" s="40"/>
+      <c r="F137" s="40"/>
       <c r="G137" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H137" s="38"/>
-      <c r="I137" s="38"/>
-      <c r="J137" s="38"/>
+      <c r="H137" s="40"/>
+      <c r="I137" s="40"/>
+      <c r="J137" s="40"/>
       <c r="K137" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L137" s="38"/>
-      <c r="M137" s="38"/>
-    </row>
-    <row r="138" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B138" s="40"/>
+      <c r="L137" s="40"/>
+      <c r="M137" s="40"/>
+    </row>
+    <row r="138" spans="2:13" ht="15.75">
+      <c r="B138" s="42"/>
       <c r="C138" s="21">
         <v>46309</v>
       </c>
-      <c r="D138" s="40"/>
-      <c r="E138" s="40"/>
-      <c r="F138" s="40"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42"/>
+      <c r="F138" s="42"/>
       <c r="G138" s="30">
         <v>46316</v>
       </c>
-      <c r="H138" s="40"/>
-      <c r="I138" s="40"/>
-      <c r="J138" s="40"/>
+      <c r="H138" s="42"/>
+      <c r="I138" s="42"/>
+      <c r="J138" s="42"/>
       <c r="K138" s="30">
         <v>46323</v>
       </c>
-      <c r="L138" s="40"/>
-      <c r="M138" s="40"/>
-    </row>
-    <row r="139" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L138" s="42"/>
+      <c r="M138" s="42"/>
+    </row>
+    <row r="139" spans="2:13" ht="14.25" customHeight="1">
       <c r="B139" s="31">
         <v>1</v>
       </c>
@@ -3995,7 +3994,7 @@
       <c r="L139" s="31"/>
       <c r="M139" s="31"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:13">
       <c r="B140" s="31">
         <v>2</v>
       </c>
@@ -4013,7 +4012,7 @@
       <c r="L140" s="31"/>
       <c r="M140" s="31"/>
     </row>
-    <row r="141" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" ht="15.75" thickBot="1">
       <c r="B141" s="6">
         <v>3</v>
       </c>
@@ -4043,7 +4042,7 @@
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
     </row>
-    <row r="142" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:13" ht="15.75" thickBot="1">
       <c r="B142" s="6">
         <v>4</v>
       </c>
@@ -4073,7 +4072,7 @@
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
     </row>
-    <row r="143" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:13" ht="15.75" thickBot="1">
       <c r="B143" s="6">
         <v>5</v>
       </c>
@@ -4103,7 +4102,7 @@
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
     </row>
-    <row r="144" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:13" ht="15.75" thickBot="1">
       <c r="B144" s="6">
         <v>6</v>
       </c>
@@ -4121,7 +4120,7 @@
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
-    <row r="145" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" ht="15.75" thickBot="1">
       <c r="B145" s="6">
         <v>7</v>
       </c>
@@ -4139,47 +4138,47 @@
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B146" s="38"/>
+    <row r="146" spans="2:13" ht="15.75">
+      <c r="B146" s="40"/>
       <c r="C146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D146" s="38"/>
-      <c r="E146" s="38"/>
-      <c r="F146" s="38"/>
+      <c r="D146" s="40"/>
+      <c r="E146" s="40"/>
+      <c r="F146" s="40"/>
       <c r="G146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="38"/>
-      <c r="I146" s="38"/>
-      <c r="J146" s="38"/>
+      <c r="H146" s="40"/>
+      <c r="I146" s="40"/>
+      <c r="J146" s="40"/>
       <c r="K146" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L146" s="38"/>
-      <c r="M146" s="38"/>
-    </row>
-    <row r="147" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="39"/>
+      <c r="L146" s="40"/>
+      <c r="M146" s="40"/>
+    </row>
+    <row r="147" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B147" s="41"/>
       <c r="C147" s="5">
         <v>46310</v>
       </c>
-      <c r="D147" s="39"/>
-      <c r="E147" s="39"/>
-      <c r="F147" s="39"/>
+      <c r="D147" s="41"/>
+      <c r="E147" s="41"/>
+      <c r="F147" s="41"/>
       <c r="G147" s="5">
         <v>46317</v>
       </c>
-      <c r="H147" s="39"/>
-      <c r="I147" s="39"/>
-      <c r="J147" s="39"/>
+      <c r="H147" s="41"/>
+      <c r="I147" s="41"/>
+      <c r="J147" s="41"/>
       <c r="K147" s="5">
         <v>46324</v>
       </c>
-      <c r="L147" s="39"/>
-      <c r="M147" s="39"/>
-    </row>
-    <row r="148" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L147" s="41"/>
+      <c r="M147" s="41"/>
+    </row>
+    <row r="148" spans="2:13" ht="16.5" thickBot="1">
       <c r="B148" s="6">
         <v>1</v>
       </c>
@@ -4199,7 +4198,7 @@
       <c r="L148" s="9"/>
       <c r="M148" s="9"/>
     </row>
-    <row r="149" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" ht="15.75" thickBot="1">
       <c r="B149" s="6">
         <v>2</v>
       </c>
@@ -4219,7 +4218,7 @@
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
-    <row r="150" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" ht="15.75" thickBot="1">
       <c r="B150" s="6">
         <v>3</v>
       </c>
@@ -4251,7 +4250,7 @@
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
-    <row r="151" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" ht="30.75" thickBot="1">
       <c r="B151" s="20">
         <v>4</v>
       </c>
@@ -4281,7 +4280,7 @@
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
-    <row r="152" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" ht="30.75" thickBot="1">
       <c r="B152" s="20">
         <v>5</v>
       </c>
@@ -4313,7 +4312,7 @@
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
-    <row r="153" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" ht="16.5" thickBot="1">
       <c r="B153" s="20">
         <v>6</v>
       </c>
@@ -4333,7 +4332,7 @@
       <c r="L153" s="9"/>
       <c r="M153" s="9"/>
     </row>
-    <row r="154" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:13" ht="16.5" thickBot="1">
       <c r="B154" s="20">
         <v>7</v>
       </c>
@@ -4353,47 +4352,47 @@
       <c r="L154" s="9"/>
       <c r="M154" s="9"/>
     </row>
-    <row r="155" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B155" s="38"/>
+    <row r="155" spans="2:13" ht="15.75">
+      <c r="B155" s="40"/>
       <c r="C155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D155" s="40"/>
-      <c r="E155" s="40"/>
-      <c r="F155" s="38"/>
+      <c r="D155" s="42"/>
+      <c r="E155" s="42"/>
+      <c r="F155" s="40"/>
       <c r="G155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H155" s="38"/>
-      <c r="I155" s="38"/>
-      <c r="J155" s="38"/>
+      <c r="H155" s="40"/>
+      <c r="I155" s="40"/>
+      <c r="J155" s="40"/>
       <c r="K155" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L155" s="38"/>
-      <c r="M155" s="38"/>
-    </row>
-    <row r="156" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B156" s="39"/>
+      <c r="L155" s="40"/>
+      <c r="M155" s="40"/>
+    </row>
+    <row r="156" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B156" s="41"/>
       <c r="C156" s="5">
         <v>46311</v>
       </c>
-      <c r="D156" s="39"/>
-      <c r="E156" s="39"/>
-      <c r="F156" s="39"/>
+      <c r="D156" s="41"/>
+      <c r="E156" s="41"/>
+      <c r="F156" s="41"/>
       <c r="G156" s="5">
         <v>46318</v>
       </c>
-      <c r="H156" s="39"/>
-      <c r="I156" s="39"/>
-      <c r="J156" s="39"/>
+      <c r="H156" s="41"/>
+      <c r="I156" s="41"/>
+      <c r="J156" s="41"/>
       <c r="K156" s="5">
         <v>46325</v>
       </c>
-      <c r="L156" s="39"/>
-      <c r="M156" s="39"/>
-    </row>
-    <row r="157" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L156" s="41"/>
+      <c r="M156" s="41"/>
+    </row>
+    <row r="157" spans="2:13" ht="16.5" thickBot="1">
       <c r="B157" s="6">
         <v>1</v>
       </c>
@@ -4403,7 +4402,7 @@
       <c r="F157" s="8">
         <v>1</v>
       </c>
-      <c r="G157" s="41" t="s">
+      <c r="G157" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H157" s="23" t="s">
@@ -4419,7 +4418,7 @@
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
-    <row r="158" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" ht="16.5" thickBot="1">
       <c r="B158" s="6">
         <v>2</v>
       </c>
@@ -4443,7 +4442,7 @@
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
     </row>
-    <row r="159" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" ht="16.5" thickBot="1">
       <c r="B159" s="6">
         <v>3</v>
       </c>
@@ -4468,7 +4467,7 @@
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
-    <row r="160" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:13" ht="15.75" thickBot="1">
       <c r="B160" s="6">
         <v>4</v>
       </c>
@@ -4494,7 +4493,7 @@
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:13" ht="15.75" thickBot="1">
       <c r="B161" s="6">
         <v>5</v>
       </c>
@@ -4520,7 +4519,7 @@
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:13" ht="15.75" thickBot="1">
       <c r="B162" s="6">
         <v>6</v>
       </c>
@@ -4540,7 +4539,7 @@
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:13" ht="15.75" thickBot="1">
       <c r="B163" s="6">
         <v>7</v>
       </c>
@@ -4560,51 +4559,51 @@
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
-    <row r="164" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B164" s="38"/>
+    <row r="164" spans="2:13" ht="15.75">
+      <c r="B164" s="40"/>
       <c r="C164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D164" s="38"/>
-      <c r="E164" s="38"/>
-      <c r="F164" s="38"/>
+      <c r="D164" s="40"/>
+      <c r="E164" s="40"/>
+      <c r="F164" s="40"/>
       <c r="G164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H164" s="38"/>
-      <c r="I164" s="38"/>
-      <c r="J164" s="38"/>
+      <c r="H164" s="40"/>
+      <c r="I164" s="40"/>
+      <c r="J164" s="40"/>
       <c r="K164" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L164" s="38"/>
-      <c r="M164" s="38"/>
-    </row>
-    <row r="165" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="39"/>
+      <c r="L164" s="40"/>
+      <c r="M164" s="40"/>
+    </row>
+    <row r="165" spans="2:13" ht="16.5" thickBot="1">
+      <c r="B165" s="41"/>
       <c r="C165" s="21">
         <v>46312</v>
       </c>
-      <c r="D165" s="39"/>
-      <c r="E165" s="39"/>
-      <c r="F165" s="39"/>
+      <c r="D165" s="41"/>
+      <c r="E165" s="41"/>
+      <c r="F165" s="41"/>
       <c r="G165" s="5">
         <v>46319</v>
       </c>
-      <c r="H165" s="39"/>
-      <c r="I165" s="39"/>
-      <c r="J165" s="39"/>
+      <c r="H165" s="41"/>
+      <c r="I165" s="41"/>
+      <c r="J165" s="41"/>
       <c r="K165" s="5">
         <v>46326</v>
       </c>
-      <c r="L165" s="39"/>
-      <c r="M165" s="39"/>
-    </row>
-    <row r="166" spans="2:13" ht="31.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L165" s="41"/>
+      <c r="M165" s="41"/>
+    </row>
+    <row r="166" spans="2:13" ht="31.5" thickBot="1">
       <c r="B166" s="20">
         <v>1</v>
       </c>
-      <c r="C166" s="42" t="s">
+      <c r="C166" s="37" t="s">
         <v>59</v>
       </c>
       <c r="D166" s="7" t="s">
@@ -4626,7 +4625,7 @@
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
-    <row r="167" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:13" ht="16.5" thickBot="1">
       <c r="B167" s="20">
         <v>2</v>
       </c>
@@ -4650,7 +4649,7 @@
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
-    <row r="168" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:13" ht="15.75" thickBot="1">
       <c r="B168" s="20">
         <v>3</v>
       </c>
@@ -4669,7 +4668,7 @@
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
-    <row r="169" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:13" ht="15.75" thickBot="1">
       <c r="B169" s="20">
         <v>4</v>
       </c>
@@ -4689,7 +4688,7 @@
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:13" ht="15.75" thickBot="1">
       <c r="B170" s="6">
         <v>5</v>
       </c>
@@ -4709,7 +4708,7 @@
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:13" ht="15.75" thickBot="1">
       <c r="B171" s="6">
         <v>6</v>
       </c>
@@ -4729,7 +4728,7 @@
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:13" ht="15.75" thickBot="1">
       <c r="B172" s="6">
         <v>7</v>
       </c>
@@ -4923,18 +4922,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Быкова\Documents\_2026_2027\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935"/>
   </bookViews>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="44">
   <si>
     <t>№</t>
   </si>
@@ -33,28 +38,10 @@
     <t>Понедельник</t>
   </si>
   <si>
-    <t>Курсовой проект</t>
-  </si>
-  <si>
-    <t>Чередниченко А.Г.</t>
-  </si>
-  <si>
     <t>МДК 01.01</t>
   </si>
   <si>
-    <t>Клевакина О.В.</t>
-  </si>
-  <si>
-    <t>МДК 04.01</t>
-  </si>
-  <si>
-    <t>Клевакин П.А.</t>
-  </si>
-  <si>
     <t>Вторник</t>
-  </si>
-  <si>
-    <t>Пономарёва Т.М.</t>
   </si>
   <si>
     <t>Среда</t>
@@ -63,25 +50,13 @@
     <t>Четверг</t>
   </si>
   <si>
-    <t>Романова Н.Ю.</t>
-  </si>
-  <si>
-    <t>Теплухина Ю.И.</t>
-  </si>
-  <si>
     <t>Пятница</t>
   </si>
   <si>
     <t>Суббота</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Ту-449</t>
-  </si>
-  <si>
     <t>МДК 03.01</t>
-  </si>
-  <si>
-    <t>Панова Н.В.</t>
   </si>
   <si>
     <t>Охрана труда</t>
@@ -90,119 +65,101 @@
     <t>Рязанова Е.В.</t>
   </si>
   <si>
-    <t>Марьинских М.М.</t>
-  </si>
-  <si>
-    <t>БЖД</t>
-  </si>
-  <si>
-    <t>Бондаренко Т.В.</t>
-  </si>
-  <si>
-    <t>Выбор оборудования</t>
-  </si>
-  <si>
-    <t>Барихина Н.В.</t>
-  </si>
-  <si>
-    <t>Начало в 08:30</t>
-  </si>
-  <si>
     <t>Панова Н.В</t>
-  </si>
-  <si>
-    <t>Барихина Н.В</t>
-  </si>
-  <si>
-    <t>Психология общения</t>
-  </si>
-  <si>
-    <t>Кунгурова Е.А.</t>
   </si>
   <si>
     <t>с/з</t>
   </si>
   <si>
-    <t>Расписание занятий заочного отделения групп Ру-418</t>
-  </si>
-  <si>
-    <t>Махов Ю.Н.</t>
-  </si>
-  <si>
-    <t>Гончарова Г.И.</t>
-  </si>
-  <si>
-    <t>Пахтусов В.А.</t>
-  </si>
-  <si>
     <t>Хасанов Д.Б</t>
-  </si>
-  <si>
-    <t>Расписание занятий заочного отделения групп Эу-485,486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Клевакина О.В., </t>
-  </si>
-  <si>
-    <t>Начало в 13:50</t>
   </si>
   <si>
     <t>Чередниченко А.Г</t>
   </si>
   <si>
-    <t>МДК 01.02</t>
-  </si>
-  <si>
-    <t>Беляев С.В.</t>
-  </si>
-  <si>
-    <t>Начало в 12:10</t>
-  </si>
-  <si>
-    <t>Иностр язык (зачёт с оценкой)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Иностр язык (зачёт с оценкой) </t>
-  </si>
-  <si>
-    <t>Правов основы в ПД</t>
-  </si>
-  <si>
-    <t>Начало экзам в 08:30</t>
-  </si>
-  <si>
-    <t>Физ культура (зачёт с оценкой)</t>
-  </si>
-  <si>
-    <t>Психол общения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Психол общения </t>
-  </si>
-  <si>
-    <t>Иностр язык (зачёт)</t>
-  </si>
-  <si>
-    <t>Экзамен по ПМ 02</t>
-  </si>
-  <si>
-    <t>Экзамен по ПМ 05</t>
-  </si>
-  <si>
     <t>Пахтусов В.А</t>
   </si>
   <si>
-    <t>Физическая культура(зачёт с оценкой)</t>
+    <t>Расписание занятий заочного отделения групп Эу-388</t>
   </si>
   <si>
-    <t>Экзамен по ПМ 01, ПМ 06</t>
+    <t>Расписание занятий заочного отделения групп Ру-319</t>
+  </si>
+  <si>
+    <t>Расписание занятий заочного отделения групп Ту-350</t>
+  </si>
+  <si>
+    <t>МДК 02.01</t>
+  </si>
+  <si>
+    <t>Тищенко Е.А.</t>
+  </si>
+  <si>
+    <t>Клевакина О.В</t>
+  </si>
+  <si>
+    <t>МДК 02.02</t>
+  </si>
+  <si>
+    <t>Махов Ю.Н</t>
+  </si>
+  <si>
+    <t>Праздничный день</t>
+  </si>
+  <si>
+    <t>МДК 05.01</t>
+  </si>
+  <si>
+    <t>Гончарова Г.И</t>
+  </si>
+  <si>
+    <t>МДК 06.01</t>
+  </si>
+  <si>
+    <t>МДК 03.02</t>
+  </si>
+  <si>
+    <t>Тищенко Е.А</t>
+  </si>
+  <si>
+    <t>Иностранный язык (зачет)</t>
+  </si>
+  <si>
+    <t>Пономарева Т.М</t>
+  </si>
+  <si>
+    <t>Физическая культура (зачет)</t>
+  </si>
+  <si>
+    <t>Кунгурова Е.А</t>
+  </si>
+  <si>
+    <t>Романова Н.Ю</t>
+  </si>
+  <si>
+    <t>Правовые основы профессиональной деятельности</t>
+  </si>
+  <si>
+    <t>Рязанова Е.В</t>
+  </si>
+  <si>
+    <t>Смолин Н.А</t>
+  </si>
+  <si>
+    <t>Основы финансовой грамотности</t>
+  </si>
+  <si>
+    <t>Реутова О.М</t>
+  </si>
+  <si>
+    <t>Основы экономики</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,26 +302,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -377,17 +323,34 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -419,52 +382,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -472,35 +403,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -510,6 +426,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,7 +493,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -603,9 +525,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -637,6 +560,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -812,9 +736,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:M172"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" customWidth="1"/>
@@ -830,23 +754,23 @@
     <col min="13" max="13" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1">
-      <c r="B1" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-    </row>
-    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+    </row>
+    <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -884,47 +808,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="40"/>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="23"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-    </row>
-    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="41"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="24"/>
       <c r="C4" s="5">
-        <v>46307</v>
-      </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+        <v>46328</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="5">
-        <v>46314</v>
-      </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
+        <v>46335</v>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="5">
-        <v>46321</v>
-      </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-    </row>
-    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+        <v>46342</v>
+      </c>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+    </row>
+    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>1</v>
       </c>
@@ -944,7 +868,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>2</v>
       </c>
@@ -964,24 +888,28 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8">
         <v>3</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I7" s="7">
-        <v>423</v>
+        <v>318</v>
       </c>
       <c r="J7" s="8">
         <v>3</v>
@@ -990,27 +918,25 @@
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7">
-        <v>301</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E8" s="7"/>
       <c r="F8" s="8">
         <v>4</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="8">
@@ -1020,27 +946,25 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="7">
-        <v>301</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="8">
         <v>5</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="8">
@@ -1050,28 +974,18 @@
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>6</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="7">
-        <v>301</v>
-      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="8">
         <v>6</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="8">
         <v>6</v>
@@ -1080,28 +994,18 @@
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>7</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="7">
-        <v>301</v>
-      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="8">
         <v>7</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="8">
         <v>7</v>
@@ -1110,47 +1014,47 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="40"/>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="23"/>
       <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
       <c r="K12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B13" s="41"/>
+        <v>6</v>
+      </c>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="24"/>
       <c r="C13" s="5">
-        <v>46308</v>
-      </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
+        <v>46329</v>
+      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="5">
-        <v>46315</v>
-      </c>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
+        <v>46336</v>
+      </c>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
       <c r="K13" s="5">
-        <v>46322</v>
-      </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+        <v>46343</v>
+      </c>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>1</v>
       </c>
@@ -1170,7 +1074,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>2</v>
       </c>
@@ -1190,27 +1094,27 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E16" s="7">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="F16" s="8">
         <v>3</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8">
@@ -1220,15 +1124,15 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E17" s="7">
         <v>423</v>
@@ -1237,14 +1141,12 @@
         <v>4</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I17" s="7">
-        <v>423</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I17" s="7"/>
       <c r="J17" s="8">
         <v>4</v>
       </c>
@@ -1252,27 +1154,25 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="7">
-        <v>423</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E18" s="7"/>
       <c r="F18" s="8">
         <v>5</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I18" s="7">
         <v>423</v>
@@ -1284,21 +1184,25 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>6</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="C19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8">
         <v>6</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I19" s="7">
         <v>423</v>
@@ -1310,7 +1214,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>7</v>
       </c>
@@ -1320,12 +1224,8 @@
       <c r="F20" s="8">
         <v>7</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="8">
         <v>7</v>
@@ -1334,108 +1234,104 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="40"/>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
       <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
       <c r="K21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="42"/>
-      <c r="C22" s="21">
-        <v>46309</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="30">
-        <v>46316</v>
-      </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="30">
-        <v>46323</v>
-      </c>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B23" s="8">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="35">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="7">
-        <v>318</v>
-      </c>
-      <c r="J23" s="31">
-        <v>1</v>
-      </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B24" s="35">
+        <v>7</v>
+      </c>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="25"/>
+      <c r="C22" s="13">
+        <v>46330</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="15">
+        <v>46337</v>
+      </c>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="15">
+        <v>46344</v>
+      </c>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="19">
+        <v>1</v>
+      </c>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="17">
         <v>2</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="35">
-        <v>2</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="F24" s="17">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="31">
-        <v>2</v>
-      </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="J24" s="19">
+        <v>2</v>
+      </c>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="21"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>3</v>
       </c>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="8">
         <v>3</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="8">
         <v>3</v>
@@ -1444,7 +1340,7 @@
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="6">
         <v>4</v>
       </c>
@@ -1454,9 +1350,15 @@
       <c r="F26" s="8">
         <v>4</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
+      <c r="G26" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="7">
+        <v>318</v>
+      </c>
       <c r="J26" s="8">
         <v>4</v>
       </c>
@@ -1464,22 +1366,22 @@
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6">
         <v>5</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="8">
         <v>5</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="I27" s="7"/>
       <c r="J27" s="8">
         <v>5</v>
@@ -1488,22 +1390,22 @@
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6">
         <v>6</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="8">
         <v>6</v>
       </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="G28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="I28" s="7"/>
       <c r="J28" s="8">
         <v>6</v>
@@ -1512,16 +1414,12 @@
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="6">
         <v>7</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="8">
         <v>7</v>
@@ -1536,47 +1434,47 @@
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="40"/>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="23"/>
       <c r="C30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
       <c r="G30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
       <c r="K30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B31" s="41"/>
+        <v>8</v>
+      </c>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="24"/>
       <c r="C31" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
+        <v>46331</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
       <c r="G31" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
+        <v>46338</v>
+      </c>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
       <c r="K31" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+        <v>46345</v>
+      </c>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6">
         <v>1</v>
       </c>
@@ -1596,7 +1494,7 @@
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
     </row>
-    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="6">
         <v>2</v>
       </c>
@@ -1606,15 +1504,9 @@
       <c r="F33" s="8">
         <v>2</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="7">
-        <v>304</v>
-      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
       <c r="J33" s="8">
         <v>2</v>
       </c>
@@ -1622,21 +1514,25 @@
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="6">
         <v>3</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="C34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="E34" s="7"/>
       <c r="F34" s="8">
         <v>3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="8">
@@ -1646,29 +1542,27 @@
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="6">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="8">
         <v>4</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I35" s="7">
-        <v>423</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I35" s="7"/>
       <c r="J35" s="8">
         <v>4</v>
       </c>
@@ -1676,29 +1570,27 @@
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="6">
         <v>5</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="8">
         <v>5</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I36" s="7">
-        <v>423</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I36" s="7"/>
       <c r="J36" s="8">
         <v>5</v>
       </c>
@@ -1706,15 +1598,15 @@
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="6">
         <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="8">
@@ -1730,16 +1622,12 @@
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
     </row>
-    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="6">
         <v>7</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="8">
         <v>7</v>
@@ -1754,69 +1642,63 @@
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
     </row>
-    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="40"/>
+    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="23"/>
       <c r="C39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
       <c r="G39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
       <c r="K39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-    </row>
-    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B40" s="41"/>
+        <v>9</v>
+      </c>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+    </row>
+    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="24"/>
       <c r="C40" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
+        <v>46332</v>
+      </c>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
       <c r="G40" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
+        <v>46339</v>
+      </c>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
       <c r="K40" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L40" s="41"/>
-      <c r="M40" s="41"/>
-    </row>
-    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+        <v>46346</v>
+      </c>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+    </row>
+    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="6">
         <v>1</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>43</v>
-      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="8">
         <v>1</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I41" s="7">
-        <v>423</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I41" s="7"/>
       <c r="J41" s="6">
         <v>1</v>
       </c>
@@ -1824,29 +1706,23 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="6">
         <v>2</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="8">
         <v>2</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I42" s="7">
-        <v>423</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I42" s="7"/>
       <c r="J42" s="6">
         <v>2</v>
       </c>
@@ -1854,14 +1730,12 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="43" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="6">
         <v>3</v>
       </c>
       <c r="C43" s="7"/>
-      <c r="D43" s="7" t="s">
-        <v>39</v>
-      </c>
+      <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="8">
         <v>3</v>
@@ -1876,12 +1750,16 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="6">
         <v>4</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="C44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="E44" s="7"/>
       <c r="F44" s="8">
         <v>4</v>
@@ -1896,13 +1774,19 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="45" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="6">
         <v>5</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="C45" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="7">
+        <v>423</v>
+      </c>
       <c r="F45" s="8">
         <v>5</v>
       </c>
@@ -1916,13 +1800,19 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="46" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="6">
         <v>6</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="C46" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="7">
+        <v>423</v>
+      </c>
       <c r="F46" s="8">
         <v>6</v>
       </c>
@@ -1936,7 +1826,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="47" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="6">
         <v>7</v>
       </c>
@@ -1956,55 +1846,55 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B48" s="40"/>
+    <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="23"/>
       <c r="C48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
       <c r="K48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-    </row>
-    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B49" s="41"/>
+        <v>10</v>
+      </c>
+      <c r="L48" s="23"/>
+      <c r="M48" s="23"/>
+    </row>
+    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="24"/>
       <c r="C49" s="5">
-        <v>46312</v>
-      </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
+        <v>46333</v>
+      </c>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
       <c r="G49" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
+        <v>46340</v>
+      </c>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
       <c r="K49" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-    </row>
-    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+        <v>46347</v>
+      </c>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+    </row>
+    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="6">
         <v>1</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>45</v>
+      <c r="C50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="6">
@@ -2020,15 +1910,15 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="51" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="6">
         <v>2</v>
       </c>
-      <c r="C51" s="28" t="s">
-        <v>44</v>
+      <c r="C51" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="6">
@@ -2044,15 +1934,15 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="52" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="6">
         <v>3</v>
       </c>
-      <c r="C52" s="28" t="s">
-        <v>44</v>
+      <c r="C52" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="6">
@@ -2068,16 +1958,12 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="53" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="6">
         <v>4</v>
       </c>
-      <c r="C53" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="6">
         <v>4</v>
@@ -2092,7 +1978,7 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="54" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="6">
         <v>5</v>
       </c>
@@ -2112,7 +1998,7 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="55" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="6">
         <v>6</v>
       </c>
@@ -2132,7 +2018,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="2:13" ht="15.75" thickBot="1">
+    <row r="56" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="6">
         <v>7</v>
       </c>
@@ -2152,23 +2038,23 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
-    <row r="59" spans="2:13" ht="21" thickBot="1">
-      <c r="B59" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-    </row>
-    <row r="60" spans="2:13" ht="15.75" thickBot="1">
+    <row r="59" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
         <v>0</v>
       </c>
@@ -2206,59 +2092,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="15.75">
-      <c r="B61" s="40"/>
+    <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="23"/>
       <c r="C61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="40"/>
-      <c r="E61" s="40"/>
-      <c r="F61" s="40"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
       <c r="G61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
       <c r="K61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
-    </row>
-    <row r="62" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B62" s="41"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="23"/>
+    </row>
+    <row r="62" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="24"/>
       <c r="C62" s="5">
-        <v>46307</v>
-      </c>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
+        <v>46328</v>
+      </c>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
       <c r="G62" s="5">
-        <v>46314</v>
-      </c>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
+        <v>46335</v>
+      </c>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="24"/>
       <c r="K62" s="5">
-        <v>46321</v>
-      </c>
-      <c r="L62" s="41"/>
-      <c r="M62" s="41"/>
-    </row>
-    <row r="63" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="16"/>
+        <v>46342</v>
+      </c>
+      <c r="L62" s="24"/>
+      <c r="M62" s="24"/>
+    </row>
+    <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="18">
+        <v>1</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="8">
         <v>1</v>
       </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
       <c r="J63" s="8">
         <v>1</v>
       </c>
@@ -2266,17 +2152,17 @@
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B64" s="6">
-        <v>2</v>
-      </c>
-      <c r="C64" s="17"/>
+    <row r="64" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="18">
+        <v>2</v>
+      </c>
+      <c r="C64" s="9"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="8">
         <v>2</v>
       </c>
-      <c r="G64" s="29"/>
+      <c r="G64" s="8"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="8">
@@ -2286,23 +2172,25 @@
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B65" s="6">
-        <v>3</v>
-      </c>
-      <c r="C65" s="28"/>
+    <row r="65" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="18">
+        <v>3</v>
+      </c>
+      <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="8">
         <v>3</v>
       </c>
-      <c r="G65" s="28" t="s">
-        <v>7</v>
+      <c r="G65" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I65" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="I65" s="7">
+        <v>304</v>
+      </c>
       <c r="J65" s="8">
         <v>3</v>
       </c>
@@ -2310,27 +2198,25 @@
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B66" s="6">
-        <v>4</v>
-      </c>
-      <c r="C66" s="28" t="s">
-        <v>7</v>
+    <row r="66" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="18">
+        <v>4</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E66" s="7">
-        <v>309</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E66" s="7"/>
       <c r="F66" s="8">
         <v>4</v>
       </c>
-      <c r="G66" s="28" t="s">
-        <v>7</v>
+      <c r="G66" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="8">
@@ -2340,27 +2226,25 @@
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B67" s="6">
-        <v>5</v>
-      </c>
-      <c r="C67" s="28" t="s">
-        <v>7</v>
+    <row r="67" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="18">
+        <v>5</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E67" s="7">
-        <v>309</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E67" s="7"/>
       <c r="F67" s="8">
         <v>5</v>
       </c>
-      <c r="G67" s="28" t="s">
-        <v>7</v>
+      <c r="G67" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="8">
@@ -2370,8 +2254,8 @@
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B68" s="6">
+    <row r="68" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="18">
         <v>6</v>
       </c>
       <c r="C68" s="7"/>
@@ -2380,8 +2264,12 @@
       <c r="F68" s="8">
         <v>6</v>
       </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
+      <c r="G68" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="I68" s="7"/>
       <c r="J68" s="8">
         <v>6</v>
@@ -2390,8 +2278,8 @@
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B69" s="6">
+    <row r="69" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="18">
         <v>7</v>
       </c>
       <c r="C69" s="7"/>
@@ -2410,58 +2298,58 @@
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="2:13" ht="15.75">
-      <c r="B70" s="40"/>
+    <row r="70" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="23"/>
       <c r="C70" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
       <c r="G70" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
+      <c r="J70" s="23"/>
       <c r="K70" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L70" s="40"/>
-      <c r="M70" s="40"/>
-    </row>
-    <row r="71" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B71" s="41"/>
+        <v>6</v>
+      </c>
+      <c r="L70" s="23"/>
+      <c r="M70" s="23"/>
+    </row>
+    <row r="71" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="24"/>
       <c r="C71" s="5">
-        <v>46308</v>
-      </c>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
+        <v>46329</v>
+      </c>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
       <c r="G71" s="5">
-        <v>46315</v>
-      </c>
-      <c r="H71" s="41"/>
-      <c r="I71" s="41"/>
-      <c r="J71" s="41"/>
+        <v>46336</v>
+      </c>
+      <c r="H71" s="24"/>
+      <c r="I71" s="24"/>
+      <c r="J71" s="24"/>
       <c r="K71" s="5">
-        <v>46322</v>
-      </c>
-      <c r="L71" s="41"/>
-      <c r="M71" s="41"/>
-    </row>
-    <row r="72" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B72" s="6">
-        <v>1</v>
-      </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
+        <v>46343</v>
+      </c>
+      <c r="L71" s="24"/>
+      <c r="M71" s="24"/>
+    </row>
+    <row r="72" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="18">
+        <v>1</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
       <c r="F72" s="8">
         <v>1</v>
       </c>
-      <c r="G72" s="15"/>
-      <c r="H72" s="16"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="8">
         <v>1</v>
@@ -2470,17 +2358,17 @@
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B73" s="6">
-        <v>2</v>
-      </c>
-      <c r="C73" s="28"/>
+    <row r="73" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="18">
+        <v>2</v>
+      </c>
+      <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="8">
         <v>2</v>
       </c>
-      <c r="G73" s="28"/>
+      <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="8">
@@ -2490,27 +2378,25 @@
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B74" s="6">
-        <v>3</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>9</v>
+    <row r="74" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="18">
+        <v>3</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E74" s="7">
-        <v>318</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E74" s="7"/>
       <c r="F74" s="8">
         <v>3</v>
       </c>
-      <c r="G74" s="28" t="s">
-        <v>7</v>
+      <c r="G74" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="8">
@@ -2520,25 +2406,25 @@
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B75" s="6">
-        <v>4</v>
-      </c>
-      <c r="C75" s="28" t="s">
-        <v>7</v>
+    <row r="75" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="18">
+        <v>4</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="8">
         <v>4</v>
       </c>
-      <c r="G75" s="28" t="s">
-        <v>7</v>
+      <c r="G75" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="8">
@@ -2548,15 +2434,15 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B76" s="6">
-        <v>5</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>20</v>
+    <row r="76" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="18">
+        <v>5</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E76" s="7">
         <v>401</v>
@@ -2564,11 +2450,11 @@
       <c r="F76" s="8">
         <v>5</v>
       </c>
-      <c r="G76" s="28" t="s">
-        <v>7</v>
+      <c r="G76" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="8">
@@ -2578,15 +2464,15 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B77" s="6">
-        <v>6</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>20</v>
+    <row r="77" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="18">
+        <v>6</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E77" s="7">
         <v>401</v>
@@ -2604,8 +2490,8 @@
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B78" s="6">
+    <row r="78" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="18">
         <v>7</v>
       </c>
       <c r="C78" s="7"/>
@@ -2624,137 +2510,129 @@
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="2:13" ht="15.75">
-      <c r="B79" s="40"/>
+    <row r="79" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="23"/>
       <c r="C79" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
       <c r="G79" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="40"/>
-      <c r="I79" s="40"/>
-      <c r="J79" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
       <c r="K79" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L79" s="40"/>
-      <c r="M79" s="40"/>
-    </row>
-    <row r="80" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B80" s="42"/>
-      <c r="C80" s="21">
-        <v>46309</v>
-      </c>
-      <c r="D80" s="42"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="30">
-        <v>46316</v>
-      </c>
-      <c r="H80" s="42"/>
-      <c r="I80" s="42"/>
-      <c r="J80" s="42"/>
-      <c r="K80" s="30">
-        <v>46323</v>
-      </c>
-      <c r="L80" s="42"/>
-      <c r="M80" s="42"/>
-    </row>
-    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B81" s="31">
-        <v>1</v>
-      </c>
-      <c r="C81" s="15"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="34"/>
-      <c r="F81" s="31">
-        <v>1</v>
-      </c>
-      <c r="G81" s="33"/>
-      <c r="H81" s="34"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="31">
-        <v>1</v>
-      </c>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
-    </row>
-    <row r="82" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B82" s="31">
-        <v>2</v>
-      </c>
-      <c r="C82" s="28"/>
+        <v>7</v>
+      </c>
+      <c r="L79" s="23"/>
+      <c r="M79" s="23"/>
+    </row>
+    <row r="80" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="25"/>
+      <c r="C80" s="13">
+        <v>46330</v>
+      </c>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="15">
+        <v>46337</v>
+      </c>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="15">
+        <v>46344</v>
+      </c>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+    </row>
+    <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="2">
+        <v>1</v>
+      </c>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="2">
+        <v>1</v>
+      </c>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="19">
+        <v>1</v>
+      </c>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="21"/>
+    </row>
+    <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="18">
+        <v>2</v>
+      </c>
+      <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="31">
-        <v>2</v>
-      </c>
-      <c r="G82" s="13"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="31">
-        <v>2</v>
-      </c>
-      <c r="K82" s="24"/>
-      <c r="L82" s="24"/>
-      <c r="M82" s="24"/>
-    </row>
-    <row r="83" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B83" s="6">
-        <v>3</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="F82" s="18">
+        <v>2</v>
+      </c>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="19">
+        <v>2</v>
+      </c>
+      <c r="K82" s="20"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="21"/>
+    </row>
+    <row r="83" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="18">
+        <v>3</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="8">
+        <v>3</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H83" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E83" s="7">
-        <v>318</v>
-      </c>
-      <c r="F83" s="8">
-        <v>3</v>
-      </c>
-      <c r="G83" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I83" s="7"/>
-      <c r="J83" s="8">
+      <c r="I83" s="7">
+        <v>304</v>
+      </c>
+      <c r="J83" s="18">
         <v>3</v>
       </c>
       <c r="K83" s="8"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B84" s="6">
-        <v>4</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E84" s="7">
-        <v>401</v>
-      </c>
+    <row r="84" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="18">
+        <v>4</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
       <c r="F84" s="8">
         <v>4</v>
       </c>
-      <c r="G84" s="28" t="s">
-        <v>7</v>
+      <c r="G84" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="8">
@@ -2764,27 +2642,21 @@
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B85" s="6">
-        <v>5</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" s="7">
-        <v>401</v>
-      </c>
+    <row r="85" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="18">
+        <v>5</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
       <c r="F85" s="8">
         <v>5</v>
       </c>
-      <c r="G85" s="28" t="s">
-        <v>7</v>
+      <c r="G85" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="8">
@@ -2794,19 +2666,13 @@
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B86" s="6">
-        <v>6</v>
-      </c>
-      <c r="C86" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" s="7">
-        <v>401</v>
-      </c>
+    <row r="86" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="18">
+        <v>6</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
       <c r="F86" s="8">
         <v>6</v>
       </c>
@@ -2820,8 +2686,8 @@
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B87" s="6">
+    <row r="87" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="18">
         <v>7</v>
       </c>
       <c r="C87" s="7"/>
@@ -2840,48 +2706,48 @@
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="2:13" ht="15.75">
-      <c r="B88" s="40"/>
+    <row r="88" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="23"/>
       <c r="C88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
       <c r="G88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" s="40"/>
-      <c r="I88" s="40"/>
-      <c r="J88" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
       <c r="K88" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L88" s="40"/>
-      <c r="M88" s="40"/>
-    </row>
-    <row r="89" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B89" s="41"/>
+        <v>8</v>
+      </c>
+      <c r="L88" s="23"/>
+      <c r="M88" s="23"/>
+    </row>
+    <row r="89" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="24"/>
       <c r="C89" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D89" s="41"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
+        <v>46331</v>
+      </c>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H89" s="41"/>
-      <c r="I89" s="41"/>
-      <c r="J89" s="41"/>
+        <v>46338</v>
+      </c>
+      <c r="H89" s="24"/>
+      <c r="I89" s="24"/>
+      <c r="J89" s="24"/>
       <c r="K89" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L89" s="41"/>
-      <c r="M89" s="41"/>
-    </row>
-    <row r="90" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B90" s="6">
+        <v>46345</v>
+      </c>
+      <c r="L89" s="24"/>
+      <c r="M89" s="24"/>
+    </row>
+    <row r="90" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="18">
         <v>1</v>
       </c>
       <c r="C90" s="7"/>
@@ -2890,9 +2756,9 @@
       <c r="F90" s="8">
         <v>1</v>
       </c>
-      <c r="G90" s="25"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="26"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
       <c r="J90" s="8">
         <v>1</v>
       </c>
@@ -2900,8 +2766,8 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B91" s="6">
+    <row r="91" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="18">
         <v>2</v>
       </c>
       <c r="C91" s="7"/>
@@ -2910,7 +2776,7 @@
       <c r="F91" s="8">
         <v>2</v>
       </c>
-      <c r="G91" s="28"/>
+      <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="8">
@@ -2920,25 +2786,25 @@
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B92" s="6">
-        <v>3</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92" s="16"/>
+    <row r="92" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="18">
+        <v>3</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="7"/>
       <c r="F92" s="8">
         <v>3</v>
       </c>
-      <c r="G92" s="28" t="s">
-        <v>7</v>
+      <c r="G92" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="8">
@@ -2948,29 +2814,29 @@
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B93" s="6">
-        <v>4</v>
-      </c>
-      <c r="C93" s="32" t="s">
-        <v>47</v>
+    <row r="93" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="18">
+        <v>4</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="7">
-        <v>312</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E93" s="7"/>
       <c r="F93" s="8">
         <v>4</v>
       </c>
-      <c r="G93" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H93" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" s="19"/>
+      <c r="G93" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I93" s="7">
+        <v>305</v>
+      </c>
       <c r="J93" s="8">
         <v>4</v>
       </c>
@@ -2978,30 +2844,30 @@
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B94" s="6">
-        <v>5</v>
-      </c>
-      <c r="C94" s="28" t="s">
-        <v>20</v>
+    <row r="94" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="18">
+        <v>5</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E94" s="7">
         <v>401</v>
       </c>
-      <c r="F94" s="27">
-        <v>5</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I94" s="24" t="s">
-        <v>34</v>
+      <c r="F94" s="8">
+        <v>5</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I94" s="7">
+        <v>305</v>
       </c>
       <c r="J94" s="8">
         <v>5</v>
@@ -3010,25 +2876,25 @@
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B95" s="6">
-        <v>6</v>
-      </c>
-      <c r="C95" s="28" t="s">
-        <v>20</v>
+    <row r="95" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="18">
+        <v>6</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E95" s="7">
         <v>401</v>
       </c>
-      <c r="F95" s="27">
-        <v>6</v>
-      </c>
-      <c r="G95" s="24"/>
-      <c r="H95" s="24"/>
-      <c r="I95" s="24"/>
+      <c r="F95" s="8">
+        <v>6</v>
+      </c>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
       <c r="J95" s="8">
         <v>6</v>
       </c>
@@ -3036,8 +2902,8 @@
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
     </row>
-    <row r="96" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B96" s="6">
+    <row r="96" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="18">
         <v>7</v>
       </c>
       <c r="C96" s="7"/>
@@ -3056,417 +2922,433 @@
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
     </row>
-    <row r="97" spans="2:13" ht="15.75">
-      <c r="B97" s="40"/>
+    <row r="97" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="23"/>
       <c r="C97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97" s="40"/>
-      <c r="E97" s="40"/>
-      <c r="F97" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="D97" s="23"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
       <c r="G97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H97" s="40"/>
-      <c r="I97" s="40"/>
-      <c r="J97" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
       <c r="K97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L97" s="40"/>
-      <c r="M97" s="40"/>
-    </row>
-    <row r="98" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B98" s="41"/>
+        <v>9</v>
+      </c>
+      <c r="L97" s="23"/>
+      <c r="M97" s="23"/>
+    </row>
+    <row r="98" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="24"/>
       <c r="C98" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="21">
-        <v>46318</v>
-      </c>
-      <c r="H98" s="42"/>
-      <c r="I98" s="41"/>
-      <c r="J98" s="41"/>
+        <v>46332</v>
+      </c>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="5">
+        <v>46339</v>
+      </c>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="24"/>
       <c r="K98" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L98" s="41"/>
-      <c r="M98" s="41"/>
-    </row>
-    <row r="99" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B99" s="6">
-        <v>1</v>
-      </c>
-      <c r="C99" s="15"/>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="27">
-        <v>1</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H99" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I99" s="7">
-        <v>401</v>
-      </c>
-      <c r="J99" s="6">
+        <v>46346</v>
+      </c>
+      <c r="L98" s="24"/>
+      <c r="M98" s="24"/>
+    </row>
+    <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="18">
+        <v>1</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="8">
+        <v>1</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I99" s="7"/>
+      <c r="J99" s="18">
         <v>1</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B100" s="6">
-        <v>2</v>
-      </c>
-      <c r="C100" s="28"/>
+    <row r="100" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="18">
+        <v>2</v>
+      </c>
+      <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
-      <c r="F100" s="27">
-        <v>2</v>
-      </c>
-      <c r="G100" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H100" s="32" t="s">
-        <v>57</v>
+      <c r="F100" s="8">
+        <v>2</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="I100" s="7"/>
-      <c r="J100" s="6">
+      <c r="J100" s="18">
         <v>2</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B101" s="6">
-        <v>3</v>
-      </c>
-      <c r="C101" s="28" t="s">
-        <v>9</v>
+    <row r="101" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="18">
+        <v>3</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E101" s="7">
-        <v>318</v>
-      </c>
-      <c r="F101" s="27">
-        <v>3</v>
-      </c>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
+        <v>32</v>
+      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="8">
+        <v>3</v>
+      </c>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
       <c r="I101" s="7"/>
-      <c r="J101" s="6">
+      <c r="J101" s="18">
         <v>3</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B102" s="6">
-        <v>4</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>20</v>
+    <row r="102" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="18">
+        <v>4</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E102" s="7">
         <v>401</v>
       </c>
-      <c r="F102" s="27">
-        <v>4</v>
-      </c>
-      <c r="G102" s="32"/>
-      <c r="H102" s="32"/>
+      <c r="F102" s="8">
+        <v>4</v>
+      </c>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
       <c r="I102" s="7"/>
-      <c r="J102" s="6">
+      <c r="J102" s="18">
         <v>4</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B103" s="6">
-        <v>5</v>
-      </c>
-      <c r="C103" s="28" t="s">
-        <v>20</v>
+    <row r="103" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="18">
+        <v>5</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E103" s="7">
         <v>401</v>
       </c>
-      <c r="F103" s="27">
-        <v>5</v>
-      </c>
-      <c r="G103" s="32"/>
-      <c r="H103" s="32"/>
+      <c r="F103" s="8">
+        <v>5</v>
+      </c>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
       <c r="I103" s="7"/>
-      <c r="J103" s="6">
+      <c r="J103" s="18">
         <v>5</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B104" s="6">
-        <v>6</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>20</v>
+    <row r="104" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="18">
+        <v>6</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E104" s="7">
         <v>401</v>
       </c>
-      <c r="F104" s="27">
-        <v>6</v>
-      </c>
-      <c r="G104" s="32"/>
-      <c r="H104" s="32"/>
+      <c r="F104" s="8">
+        <v>6</v>
+      </c>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
       <c r="I104" s="7"/>
-      <c r="J104" s="6">
+      <c r="J104" s="18">
         <v>6</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B105" s="6">
+    <row r="105" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="18">
         <v>7</v>
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
-      <c r="F105" s="27">
-        <v>4</v>
-      </c>
-      <c r="G105" s="32"/>
-      <c r="H105" s="32"/>
+      <c r="F105" s="8">
+        <v>4</v>
+      </c>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
       <c r="I105" s="7"/>
-      <c r="J105" s="6">
+      <c r="J105" s="18">
         <v>7</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="2:13" ht="15.75">
-      <c r="B106" s="40"/>
+    <row r="106" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="23"/>
       <c r="C106" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D106" s="40"/>
-      <c r="E106" s="40"/>
-      <c r="F106" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="D106" s="23"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="23"/>
       <c r="G106" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H106" s="42"/>
-      <c r="I106" s="40"/>
-      <c r="J106" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="23"/>
       <c r="K106" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L106" s="40"/>
-      <c r="M106" s="40"/>
-    </row>
-    <row r="107" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B107" s="41"/>
+        <v>10</v>
+      </c>
+      <c r="L106" s="23"/>
+      <c r="M106" s="23"/>
+    </row>
+    <row r="107" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="24"/>
       <c r="C107" s="5">
-        <v>46312</v>
-      </c>
-      <c r="D107" s="41"/>
-      <c r="E107" s="41"/>
-      <c r="F107" s="41"/>
+        <v>46333</v>
+      </c>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
       <c r="G107" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H107" s="41"/>
-      <c r="I107" s="41"/>
-      <c r="J107" s="41"/>
+        <v>46340</v>
+      </c>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
       <c r="K107" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L107" s="41"/>
-      <c r="M107" s="41"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B108" s="6">
-        <v>1</v>
-      </c>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
+        <v>46347</v>
+      </c>
+      <c r="L107" s="24"/>
+      <c r="M107" s="24"/>
+    </row>
+    <row r="108" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="18">
+        <v>1</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="6">
+      <c r="F108" s="18">
         <v>1</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
-      <c r="J108" s="6">
+      <c r="J108" s="18">
         <v>1</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B109" s="6">
-        <v>2</v>
-      </c>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
+    <row r="109" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B109" s="18">
+        <v>2</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="E109" s="7"/>
-      <c r="F109" s="6">
+      <c r="F109" s="18">
         <v>2</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
-      <c r="J109" s="6">
+      <c r="J109" s="18">
         <v>2</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B110" s="6">
-        <v>3</v>
-      </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="6">
+    <row r="110" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="18">
+        <v>3</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E110" s="7">
+        <v>312</v>
+      </c>
+      <c r="F110" s="18">
         <v>3</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
-      <c r="J110" s="6">
+      <c r="J110" s="18">
         <v>3</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B111" s="6">
-        <v>4</v>
-      </c>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="6">
+    <row r="111" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B111" s="18">
+        <v>4</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="18">
         <v>4</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
-      <c r="J111" s="6">
+      <c r="J111" s="18">
         <v>4</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B112" s="6">
+    <row r="112" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="18">
         <v>5</v>
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
-      <c r="F112" s="6">
+      <c r="F112" s="18">
         <v>5</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
-      <c r="J112" s="6">
+      <c r="J112" s="18">
         <v>5</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B113" s="6">
+    <row r="113" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="18">
         <v>6</v>
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
-      <c r="F113" s="6">
+      <c r="F113" s="18">
         <v>6</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
-      <c r="J113" s="6">
+      <c r="J113" s="18">
         <v>6</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B114" s="6">
+    <row r="114" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B114" s="18">
         <v>7</v>
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
-      <c r="F114" s="6">
+      <c r="F114" s="18">
         <v>7</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
-      <c r="J114" s="6">
+      <c r="J114" s="18">
         <v>7</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
-    <row r="117" spans="2:13" ht="21" thickBot="1">
-      <c r="B117" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="39"/>
-      <c r="D117" s="39"/>
-      <c r="E117" s="39"/>
-      <c r="F117" s="39"/>
-      <c r="G117" s="39"/>
-      <c r="H117" s="39"/>
-      <c r="I117" s="39"/>
-      <c r="J117" s="39"/>
-      <c r="K117" s="39"/>
-      <c r="L117" s="39"/>
-      <c r="M117" s="39"/>
-    </row>
-    <row r="118" spans="2:13" ht="15.75" thickBot="1">
+    <row r="117" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="27"/>
+      <c r="D117" s="27"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27"/>
+      <c r="G117" s="27"/>
+      <c r="H117" s="27"/>
+      <c r="I117" s="27"/>
+      <c r="J117" s="27"/>
+      <c r="K117" s="27"/>
+      <c r="L117" s="27"/>
+      <c r="M117" s="27"/>
+    </row>
+    <row r="118" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B118" s="2" t="s">
         <v>0</v>
       </c>
@@ -3504,59 +3386,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="2:13" ht="15.75">
-      <c r="B119" s="40"/>
+    <row r="119" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="23"/>
       <c r="C119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="40"/>
-      <c r="E119" s="40"/>
-      <c r="F119" s="40"/>
+      <c r="D119" s="23"/>
+      <c r="E119" s="23"/>
+      <c r="F119" s="23"/>
       <c r="G119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H119" s="40"/>
-      <c r="I119" s="40"/>
-      <c r="J119" s="40"/>
+      <c r="H119" s="23"/>
+      <c r="I119" s="23"/>
+      <c r="J119" s="23"/>
       <c r="K119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L119" s="40"/>
-      <c r="M119" s="40"/>
-    </row>
-    <row r="120" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B120" s="41"/>
+      <c r="L119" s="23"/>
+      <c r="M119" s="23"/>
+    </row>
+    <row r="120" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="24"/>
       <c r="C120" s="5">
-        <v>46307</v>
-      </c>
-      <c r="D120" s="41"/>
-      <c r="E120" s="41"/>
-      <c r="F120" s="41"/>
+        <v>46328</v>
+      </c>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
       <c r="G120" s="5">
-        <v>46314</v>
-      </c>
-      <c r="H120" s="41"/>
-      <c r="I120" s="41"/>
-      <c r="J120" s="41"/>
+        <v>46335</v>
+      </c>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="24"/>
       <c r="K120" s="5">
-        <v>46321</v>
-      </c>
-      <c r="L120" s="41"/>
-      <c r="M120" s="41"/>
-    </row>
-    <row r="121" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B121" s="6">
-        <v>1</v>
-      </c>
-      <c r="C121" s="15"/>
-      <c r="D121" s="16"/>
-      <c r="E121" s="16"/>
+        <v>46342</v>
+      </c>
+      <c r="L120" s="24"/>
+      <c r="M120" s="24"/>
+    </row>
+    <row r="121" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="18">
+        <v>1</v>
+      </c>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
       <c r="F121" s="8">
         <v>1</v>
       </c>
-      <c r="G121" s="2"/>
-      <c r="H121" s="16"/>
-      <c r="I121" s="16"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
       <c r="J121" s="8">
         <v>1</v>
       </c>
@@ -3564,25 +3446,19 @@
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B122" s="6">
-        <v>2</v>
-      </c>
-      <c r="C122" s="17"/>
+    <row r="122" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="18">
+        <v>2</v>
+      </c>
+      <c r="C122" s="9"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
       <c r="F122" s="8">
         <v>2</v>
       </c>
-      <c r="G122" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I122" s="7">
-        <v>304</v>
-      </c>
+      <c r="G122" s="8"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7"/>
       <c r="J122" s="8">
         <v>2</v>
       </c>
@@ -3590,31 +3466,19 @@
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B123" s="6">
-        <v>3</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E123" s="7">
-        <v>308</v>
-      </c>
+    <row r="123" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="18">
+        <v>3</v>
+      </c>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
       <c r="F123" s="8">
         <v>3</v>
       </c>
-      <c r="G123" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I123" s="7">
-        <v>101</v>
-      </c>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
       <c r="J123" s="8">
         <v>3</v>
       </c>
@@ -3622,15 +3486,15 @@
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B124" s="6">
-        <v>4</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>20</v>
+    <row r="124" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="18">
+        <v>4</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E124" s="7">
         <v>308</v>
@@ -3638,14 +3502,14 @@
       <c r="F124" s="8">
         <v>4</v>
       </c>
-      <c r="G124" s="11" t="s">
-        <v>9</v>
+      <c r="G124" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I124" s="7">
-        <v>101</v>
+        <v>418</v>
       </c>
       <c r="J124" s="8">
         <v>4</v>
@@ -3654,24 +3518,30 @@
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B125" s="6">
-        <v>5</v>
-      </c>
-      <c r="C125" s="11"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
+    <row r="125" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="18">
+        <v>5</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" s="7">
+        <v>308</v>
+      </c>
       <c r="F125" s="8">
         <v>5</v>
       </c>
-      <c r="G125" s="11" t="s">
-        <v>9</v>
+      <c r="G125" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I125" s="7">
-        <v>101</v>
+        <v>418</v>
       </c>
       <c r="J125" s="8">
         <v>5</v>
@@ -3680,8 +3550,8 @@
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B126" s="6">
+    <row r="126" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="18">
         <v>6</v>
       </c>
       <c r="C126" s="7"/>
@@ -3700,8 +3570,8 @@
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B127" s="6">
+    <row r="127" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="18">
         <v>7</v>
       </c>
       <c r="C127" s="7"/>
@@ -3720,59 +3590,59 @@
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="2:13" ht="15.75">
-      <c r="B128" s="40"/>
+    <row r="128" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B128" s="23"/>
       <c r="C128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
       <c r="G128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="23"/>
       <c r="K128" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L128" s="40"/>
-      <c r="M128" s="40"/>
-    </row>
-    <row r="129" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B129" s="41"/>
+        <v>6</v>
+      </c>
+      <c r="L128" s="23"/>
+      <c r="M128" s="23"/>
+    </row>
+    <row r="129" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="24"/>
       <c r="C129" s="5">
-        <v>46308</v>
-      </c>
-      <c r="D129" s="41"/>
-      <c r="E129" s="41"/>
-      <c r="F129" s="41"/>
+        <v>46329</v>
+      </c>
+      <c r="D129" s="24"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
       <c r="G129" s="5">
-        <v>46315</v>
-      </c>
-      <c r="H129" s="41"/>
-      <c r="I129" s="41"/>
-      <c r="J129" s="41"/>
+        <v>46336</v>
+      </c>
+      <c r="H129" s="24"/>
+      <c r="I129" s="24"/>
+      <c r="J129" s="24"/>
       <c r="K129" s="5">
-        <v>46322</v>
-      </c>
-      <c r="L129" s="41"/>
-      <c r="M129" s="41"/>
-    </row>
-    <row r="130" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B130" s="6">
-        <v>1</v>
-      </c>
-      <c r="C130" s="15"/>
-      <c r="D130" s="16"/>
-      <c r="E130" s="16"/>
+        <v>46343</v>
+      </c>
+      <c r="L129" s="24"/>
+      <c r="M129" s="24"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B130" s="18">
+        <v>1</v>
+      </c>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
       <c r="F130" s="8">
         <v>1</v>
       </c>
-      <c r="G130" s="15"/>
-      <c r="H130" s="16"/>
-      <c r="I130" s="16"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="7"/>
       <c r="J130" s="8">
         <v>1</v>
       </c>
@@ -3780,17 +3650,17 @@
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B131" s="6">
-        <v>2</v>
-      </c>
-      <c r="C131" s="11"/>
+    <row r="131" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="18">
+        <v>2</v>
+      </c>
+      <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="8">
         <v>2</v>
       </c>
-      <c r="G131" s="11"/>
+      <c r="G131" s="7"/>
       <c r="H131" s="7"/>
       <c r="I131" s="7"/>
       <c r="J131" s="8">
@@ -3800,31 +3670,19 @@
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B132" s="6">
-        <v>3</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E132" s="7">
-        <v>308</v>
-      </c>
+    <row r="132" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B132" s="18">
+        <v>3</v>
+      </c>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
       <c r="F132" s="8">
         <v>3</v>
       </c>
-      <c r="G132" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I132" s="7">
-        <v>308</v>
-      </c>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
       <c r="J132" s="8">
         <v>3</v>
       </c>
@@ -3832,27 +3690,27 @@
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B133" s="6">
-        <v>4</v>
-      </c>
-      <c r="C133" s="11" t="s">
+    <row r="133" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B133" s="18">
+        <v>4</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E133" s="7">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F133" s="8">
         <v>4</v>
       </c>
-      <c r="G133" s="11" t="s">
-        <v>20</v>
+      <c r="G133" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I133" s="7">
         <v>308</v>
@@ -3864,27 +3722,27 @@
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B134" s="6">
-        <v>5</v>
-      </c>
-      <c r="C134" s="11" t="s">
+    <row r="134" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B134" s="18">
+        <v>5</v>
+      </c>
+      <c r="C134" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E134" s="7">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F134" s="8">
         <v>5</v>
       </c>
-      <c r="G134" s="11" t="s">
-        <v>20</v>
+      <c r="G134" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I134" s="7">
         <v>308</v>
@@ -3896,19 +3754,31 @@
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B135" s="6">
-        <v>6</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
+    <row r="135" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B135" s="18">
+        <v>6</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" s="7">
+        <v>308</v>
+      </c>
       <c r="F135" s="8">
         <v>6</v>
       </c>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
+      <c r="G135" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" s="7">
+        <v>308</v>
+      </c>
       <c r="J135" s="8">
         <v>6</v>
       </c>
@@ -3916,8 +3786,8 @@
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B136" s="6">
+    <row r="136" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="18">
         <v>7</v>
       </c>
       <c r="C136" s="7"/>
@@ -3936,174 +3806,168 @@
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="2:13" ht="15.75">
-      <c r="B137" s="40"/>
+    <row r="137" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B137" s="23"/>
       <c r="C137" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="40"/>
-      <c r="E137" s="40"/>
-      <c r="F137" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
       <c r="G137" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H137" s="40"/>
-      <c r="I137" s="40"/>
-      <c r="J137" s="40"/>
+        <v>7</v>
+      </c>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
       <c r="K137" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L137" s="40"/>
-      <c r="M137" s="40"/>
-    </row>
-    <row r="138" spans="2:13" ht="15.75">
-      <c r="B138" s="42"/>
-      <c r="C138" s="21">
-        <v>46309</v>
-      </c>
-      <c r="D138" s="42"/>
-      <c r="E138" s="42"/>
-      <c r="F138" s="42"/>
-      <c r="G138" s="30">
-        <v>46316</v>
-      </c>
-      <c r="H138" s="42"/>
-      <c r="I138" s="42"/>
-      <c r="J138" s="42"/>
-      <c r="K138" s="30">
-        <v>46323</v>
-      </c>
-      <c r="L138" s="42"/>
-      <c r="M138" s="42"/>
-    </row>
-    <row r="139" spans="2:13" ht="14.25" customHeight="1">
-      <c r="B139" s="31">
-        <v>1</v>
-      </c>
-      <c r="C139" s="31"/>
-      <c r="D139" s="31"/>
-      <c r="E139" s="31"/>
-      <c r="F139" s="31">
-        <v>1</v>
-      </c>
-      <c r="G139" s="31"/>
-      <c r="H139" s="31"/>
-      <c r="I139" s="31"/>
-      <c r="J139" s="31"/>
-      <c r="K139" s="31"/>
-      <c r="L139" s="31"/>
-      <c r="M139" s="31"/>
-    </row>
-    <row r="140" spans="2:13">
-      <c r="B140" s="31">
-        <v>2</v>
-      </c>
-      <c r="C140" s="31"/>
-      <c r="D140" s="31"/>
-      <c r="E140" s="31"/>
-      <c r="F140" s="31">
-        <v>2</v>
-      </c>
-      <c r="G140" s="31"/>
-      <c r="H140" s="31"/>
-      <c r="I140" s="31"/>
-      <c r="J140" s="31"/>
-      <c r="K140" s="31"/>
-      <c r="L140" s="31"/>
-      <c r="M140" s="31"/>
-    </row>
-    <row r="141" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B141" s="6">
-        <v>3</v>
-      </c>
-      <c r="C141" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E141" s="7">
-        <v>101</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L137" s="23"/>
+      <c r="M137" s="23"/>
+    </row>
+    <row r="138" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B138" s="25"/>
+      <c r="C138" s="13">
+        <v>46330</v>
+      </c>
+      <c r="D138" s="25"/>
+      <c r="E138" s="25"/>
+      <c r="F138" s="25"/>
+      <c r="G138" s="15">
+        <v>46337</v>
+      </c>
+      <c r="H138" s="25"/>
+      <c r="I138" s="25"/>
+      <c r="J138" s="25"/>
+      <c r="K138" s="15">
+        <v>46344</v>
+      </c>
+      <c r="L138" s="25"/>
+      <c r="M138" s="25"/>
+    </row>
+    <row r="139" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B139" s="2">
+        <v>1</v>
+      </c>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="2">
+        <v>1</v>
+      </c>
+      <c r="G139" s="12"/>
+      <c r="H139" s="12"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="20">
+        <v>1</v>
+      </c>
+      <c r="K139" s="20"/>
+      <c r="L139" s="20"/>
+      <c r="M139" s="21"/>
+    </row>
+    <row r="140" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="18">
+        <v>2</v>
+      </c>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="18">
+        <v>2</v>
+      </c>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="19">
+        <v>2</v>
+      </c>
+      <c r="K140" s="20"/>
+      <c r="L140" s="20"/>
+      <c r="M140" s="21"/>
+    </row>
+    <row r="141" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B141" s="18">
+        <v>3</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
       <c r="F141" s="8">
         <v>3</v>
       </c>
-      <c r="G141" s="12" t="s">
-        <v>9</v>
+      <c r="G141" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I141" s="7">
-        <v>101</v>
-      </c>
-      <c r="J141" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="J141" s="8">
+        <v>3</v>
+      </c>
       <c r="K141" s="8"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
     </row>
-    <row r="142" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B142" s="6">
-        <v>4</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E142" s="7">
-        <v>101</v>
-      </c>
+    <row r="142" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B142" s="18">
+        <v>4</v>
+      </c>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
       <c r="F142" s="8">
         <v>4</v>
       </c>
-      <c r="G142" s="11" t="s">
-        <v>9</v>
+      <c r="G142" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I142" s="7">
-        <v>101</v>
-      </c>
-      <c r="J142" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="J142" s="8">
+        <v>4</v>
+      </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
     </row>
-    <row r="143" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B143" s="6">
-        <v>5</v>
-      </c>
-      <c r="C143" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E143" s="7">
-        <v>101</v>
-      </c>
+    <row r="143" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B143" s="18">
+        <v>5</v>
+      </c>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
       <c r="F143" s="8">
         <v>5</v>
       </c>
-      <c r="G143" s="11" t="s">
-        <v>9</v>
+      <c r="G143" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I143" s="7">
-        <v>101</v>
-      </c>
-      <c r="J143" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="J143" s="8">
+        <v>5</v>
+      </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
     </row>
-    <row r="144" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B144" s="6">
+    <row r="144" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B144" s="18">
         <v>6</v>
       </c>
       <c r="C144" s="7"/>
@@ -4115,13 +3979,15 @@
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
-      <c r="J144" s="8"/>
+      <c r="J144" s="8">
+        <v>6</v>
+      </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
-    <row r="145" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B145" s="6">
+    <row r="145" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B145" s="18">
         <v>7</v>
       </c>
       <c r="C145" s="7"/>
@@ -4133,64 +3999,66 @@
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
       <c r="I145" s="7"/>
-      <c r="J145" s="8"/>
+      <c r="J145" s="8">
+        <v>7</v>
+      </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
-    <row r="146" spans="2:13" ht="15.75">
-      <c r="B146" s="40"/>
+    <row r="146" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B146" s="23"/>
       <c r="C146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D146" s="40"/>
-      <c r="E146" s="40"/>
-      <c r="F146" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="D146" s="23"/>
+      <c r="E146" s="23"/>
+      <c r="F146" s="23"/>
       <c r="G146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="40"/>
-      <c r="I146" s="40"/>
-      <c r="J146" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="H146" s="23"/>
+      <c r="I146" s="23"/>
+      <c r="J146" s="23"/>
       <c r="K146" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L146" s="40"/>
-      <c r="M146" s="40"/>
-    </row>
-    <row r="147" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B147" s="41"/>
+        <v>8</v>
+      </c>
+      <c r="L146" s="23"/>
+      <c r="M146" s="23"/>
+    </row>
+    <row r="147" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="24"/>
       <c r="C147" s="5">
-        <v>46310</v>
-      </c>
-      <c r="D147" s="41"/>
-      <c r="E147" s="41"/>
-      <c r="F147" s="41"/>
+        <v>46331</v>
+      </c>
+      <c r="D147" s="24"/>
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
       <c r="G147" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H147" s="41"/>
-      <c r="I147" s="41"/>
-      <c r="J147" s="41"/>
+        <v>46338</v>
+      </c>
+      <c r="H147" s="24"/>
+      <c r="I147" s="24"/>
+      <c r="J147" s="24"/>
       <c r="K147" s="5">
-        <v>46324</v>
-      </c>
-      <c r="L147" s="41"/>
-      <c r="M147" s="41"/>
-    </row>
-    <row r="148" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B148" s="6">
-        <v>1</v>
-      </c>
-      <c r="C148" s="15"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
+        <v>46345</v>
+      </c>
+      <c r="L147" s="24"/>
+      <c r="M147" s="24"/>
+    </row>
+    <row r="148" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B148" s="18">
+        <v>1</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
       <c r="F148" s="8">
         <v>1</v>
       </c>
-      <c r="G148" s="25"/>
-      <c r="H148" s="26"/>
-      <c r="I148" s="26"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="9"/>
+      <c r="I148" s="9"/>
       <c r="J148" s="8">
         <v>1</v>
       </c>
@@ -4198,17 +4066,17 @@
       <c r="L148" s="9"/>
       <c r="M148" s="9"/>
     </row>
-    <row r="149" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B149" s="6">
-        <v>2</v>
-      </c>
-      <c r="C149" s="13"/>
+    <row r="149" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B149" s="18">
+        <v>2</v>
+      </c>
+      <c r="C149" s="7"/>
       <c r="D149" s="7"/>
-      <c r="E149" s="14"/>
+      <c r="E149" s="7"/>
       <c r="F149" s="8">
         <v>2</v>
       </c>
-      <c r="G149" s="11"/>
+      <c r="G149" s="7"/>
       <c r="H149" s="7"/>
       <c r="I149" s="7"/>
       <c r="J149" s="8">
@@ -4218,31 +4086,25 @@
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
-    <row r="150" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B150" s="6">
-        <v>3</v>
-      </c>
-      <c r="C150" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D150" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E150" s="19">
-        <v>101</v>
+    <row r="150" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="18">
+        <v>3</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="7">
+        <v>308</v>
       </c>
       <c r="F150" s="8">
         <v>3</v>
       </c>
-      <c r="G150" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I150" s="7">
-        <v>308</v>
-      </c>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="7"/>
       <c r="J150" s="8">
         <v>3</v>
       </c>
@@ -4250,29 +4112,31 @@
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
-    <row r="151" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B151" s="20">
-        <v>4</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D151" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" s="24">
-        <v>312</v>
+    <row r="151" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B151" s="18">
+        <v>4</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" s="7">
+        <v>308</v>
       </c>
       <c r="F151" s="8">
         <v>4</v>
       </c>
-      <c r="G151" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H151" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I151" s="19"/>
+      <c r="G151" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I151" s="7">
+        <v>308</v>
+      </c>
       <c r="J151" s="8">
         <v>4</v>
       </c>
@@ -4280,30 +4144,30 @@
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
-    <row r="152" spans="2:13" ht="30.75" thickBot="1">
-      <c r="B152" s="20">
-        <v>5</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D152" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E152" s="24">
-        <v>231</v>
-      </c>
-      <c r="F152" s="27">
-        <v>5</v>
-      </c>
-      <c r="G152" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H152" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I152" s="24" t="s">
-        <v>34</v>
+    <row r="152" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="18">
+        <v>5</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E152" s="7">
+        <v>418</v>
+      </c>
+      <c r="F152" s="8">
+        <v>5</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I152" s="7">
+        <v>308</v>
       </c>
       <c r="J152" s="8">
         <v>5</v>
@@ -4312,19 +4176,25 @@
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
-    <row r="153" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B153" s="20">
-        <v>6</v>
-      </c>
-      <c r="C153" s="22"/>
-      <c r="D153" s="22"/>
-      <c r="E153" s="22"/>
-      <c r="F153" s="27">
-        <v>6</v>
-      </c>
-      <c r="G153" s="24"/>
-      <c r="H153" s="24"/>
-      <c r="I153" s="24"/>
+    <row r="153" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="18">
+        <v>6</v>
+      </c>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="8">
+        <v>6</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I153" s="7">
+        <v>308</v>
+      </c>
       <c r="J153" s="8">
         <v>6</v>
       </c>
@@ -4332,13 +4202,13 @@
       <c r="L153" s="9"/>
       <c r="M153" s="9"/>
     </row>
-    <row r="154" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B154" s="20">
-        <v>7</v>
-      </c>
-      <c r="C154" s="24"/>
-      <c r="D154" s="24"/>
-      <c r="E154" s="24"/>
+    <row r="154" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="18">
+        <v>7</v>
+      </c>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
       <c r="F154" s="8">
         <v>7</v>
       </c>
@@ -4352,159 +4222,156 @@
       <c r="L154" s="9"/>
       <c r="M154" s="9"/>
     </row>
-    <row r="155" spans="2:13" ht="15.75">
-      <c r="B155" s="40"/>
+    <row r="155" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B155" s="23"/>
       <c r="C155" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" s="42"/>
-      <c r="E155" s="42"/>
-      <c r="F155" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
+      <c r="F155" s="23"/>
       <c r="G155" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H155" s="40"/>
-      <c r="I155" s="40"/>
-      <c r="J155" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="H155" s="23"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="23"/>
       <c r="K155" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L155" s="40"/>
-      <c r="M155" s="40"/>
-    </row>
-    <row r="156" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B156" s="41"/>
+        <v>9</v>
+      </c>
+      <c r="L155" s="23"/>
+      <c r="M155" s="23"/>
+    </row>
+    <row r="156" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="24"/>
       <c r="C156" s="5">
-        <v>46311</v>
-      </c>
-      <c r="D156" s="41"/>
-      <c r="E156" s="41"/>
-      <c r="F156" s="41"/>
+        <v>46332</v>
+      </c>
+      <c r="D156" s="24"/>
+      <c r="E156" s="24"/>
+      <c r="F156" s="24"/>
       <c r="G156" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H156" s="41"/>
-      <c r="I156" s="41"/>
-      <c r="J156" s="41"/>
+        <v>46339</v>
+      </c>
+      <c r="H156" s="24"/>
+      <c r="I156" s="24"/>
+      <c r="J156" s="24"/>
       <c r="K156" s="5">
-        <v>46325</v>
-      </c>
-      <c r="L156" s="41"/>
-      <c r="M156" s="41"/>
-    </row>
-    <row r="157" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B157" s="6">
-        <v>1</v>
-      </c>
-      <c r="C157" s="15"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
+        <v>46346</v>
+      </c>
+      <c r="L156" s="24"/>
+      <c r="M156" s="24"/>
+    </row>
+    <row r="157" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="18">
+        <v>1</v>
+      </c>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
       <c r="F157" s="8">
         <v>1</v>
       </c>
-      <c r="G157" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="H157" s="23" t="s">
-        <v>30</v>
+      <c r="G157" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="I157" s="7">
         <v>308</v>
       </c>
-      <c r="J157" s="6">
+      <c r="J157" s="18">
         <v>1</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
-    <row r="158" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B158" s="6">
-        <v>2</v>
-      </c>
-      <c r="C158" s="11"/>
+    <row r="158" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="18">
+        <v>2</v>
+      </c>
+      <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
-      <c r="F158" s="27">
-        <v>2</v>
-      </c>
-      <c r="G158" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H158" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I158" s="7"/>
-      <c r="J158" s="6">
+      <c r="F158" s="8">
+        <v>2</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158" s="7">
+        <v>308</v>
+      </c>
+      <c r="J158" s="18">
         <v>2</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
     </row>
-    <row r="159" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B159" s="6">
-        <v>3</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E159" s="7">
-        <v>309</v>
-      </c>
-      <c r="F159" s="27">
-        <v>3</v>
-      </c>
-      <c r="G159" s="23"/>
+    <row r="159" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="18">
+        <v>3</v>
+      </c>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="8">
+        <v>3</v>
+      </c>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
       <c r="I159" s="7"/>
-      <c r="J159" s="6">
+      <c r="J159" s="18">
         <v>3</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
-    <row r="160" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B160" s="6">
-        <v>4</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>27</v>
+    <row r="160" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="18">
+        <v>4</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E160" s="7">
-        <v>309</v>
-      </c>
-      <c r="F160" s="27">
-        <v>4</v>
-      </c>
-      <c r="G160" s="24"/>
-      <c r="H160" s="24"/>
+        <v>308</v>
+      </c>
+      <c r="F160" s="8">
+        <v>4</v>
+      </c>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
       <c r="I160" s="7"/>
-      <c r="J160" s="6">
+      <c r="J160" s="18">
         <v>4</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
-    <row r="161" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B161" s="6">
-        <v>5</v>
-      </c>
-      <c r="C161" s="11" t="s">
-        <v>25</v>
+    <row r="161" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="18">
+        <v>5</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E161" s="7">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="F161" s="8">
         <v>5</v>
@@ -4512,35 +4379,41 @@
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
-      <c r="J161" s="6">
+      <c r="J161" s="18">
         <v>5</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
-    <row r="162" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B162" s="6">
-        <v>6</v>
-      </c>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
+    <row r="162" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="18">
+        <v>6</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="7">
+        <v>308</v>
+      </c>
       <c r="F162" s="8">
         <v>6</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
-      <c r="J162" s="6">
+      <c r="J162" s="18">
         <v>6</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
-    <row r="163" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B163" s="6">
+    <row r="163" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="18">
         <v>7</v>
       </c>
       <c r="C163" s="7"/>
@@ -4552,196 +4425,211 @@
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
-      <c r="J163" s="6">
+      <c r="J163" s="18">
         <v>7</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
-    <row r="164" spans="2:13" ht="15.75">
-      <c r="B164" s="40"/>
+    <row r="164" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B164" s="23"/>
       <c r="C164" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D164" s="40"/>
-      <c r="E164" s="40"/>
-      <c r="F164" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
+      <c r="F164" s="23"/>
       <c r="G164" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H164" s="40"/>
-      <c r="I164" s="40"/>
-      <c r="J164" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="H164" s="23"/>
+      <c r="I164" s="23"/>
+      <c r="J164" s="23"/>
       <c r="K164" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L164" s="40"/>
-      <c r="M164" s="40"/>
-    </row>
-    <row r="165" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B165" s="41"/>
-      <c r="C165" s="21">
-        <v>46312</v>
-      </c>
-      <c r="D165" s="41"/>
-      <c r="E165" s="41"/>
-      <c r="F165" s="41"/>
+        <v>10</v>
+      </c>
+      <c r="L164" s="23"/>
+      <c r="M164" s="23"/>
+    </row>
+    <row r="165" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="24"/>
+      <c r="C165" s="5">
+        <v>46333</v>
+      </c>
+      <c r="D165" s="24"/>
+      <c r="E165" s="24"/>
+      <c r="F165" s="24"/>
       <c r="G165" s="5">
-        <v>46319</v>
-      </c>
-      <c r="H165" s="41"/>
-      <c r="I165" s="41"/>
-      <c r="J165" s="41"/>
+        <v>46340</v>
+      </c>
+      <c r="H165" s="24"/>
+      <c r="I165" s="24"/>
+      <c r="J165" s="24"/>
       <c r="K165" s="5">
-        <v>46326</v>
-      </c>
-      <c r="L165" s="41"/>
-      <c r="M165" s="41"/>
-    </row>
-    <row r="166" spans="2:13" ht="31.5" thickBot="1">
-      <c r="B166" s="20">
-        <v>1</v>
-      </c>
-      <c r="C166" s="37" t="s">
-        <v>59</v>
+        <v>46347</v>
+      </c>
+      <c r="L165" s="24"/>
+      <c r="M165" s="24"/>
+    </row>
+    <row r="166" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B166" s="18">
+        <v>1</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E166" s="7">
         <v>308</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="18">
         <v>1</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
-      <c r="J166" s="6">
+      <c r="J166" s="18">
         <v>1</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
-    <row r="167" spans="2:13" ht="16.5" thickBot="1">
-      <c r="B167" s="20">
-        <v>2</v>
-      </c>
-      <c r="C167" s="23" t="s">
-        <v>29</v>
+    <row r="167" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="18">
+        <v>2</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E167" s="7"/>
-      <c r="F167" s="6">
+        <v>14</v>
+      </c>
+      <c r="E167" s="7">
+        <v>308</v>
+      </c>
+      <c r="F167" s="18">
         <v>2</v>
       </c>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
-      <c r="J167" s="6">
+      <c r="J167" s="18">
         <v>2</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
-    <row r="168" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B168" s="20">
-        <v>3</v>
-      </c>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="6">
+    <row r="168" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B168" s="18">
+        <v>3</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E168" s="7">
+        <v>312</v>
+      </c>
+      <c r="F168" s="18">
         <v>3</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
       <c r="I168" s="7"/>
-      <c r="J168" s="6">
+      <c r="J168" s="18">
         <v>3</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
-    <row r="169" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B169" s="20">
-        <v>4</v>
-      </c>
-      <c r="C169" s="24"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="6">
+    <row r="169" spans="2:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B169" s="18">
+        <v>4</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E169" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F169" s="18">
         <v>4</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
-      <c r="J169" s="6">
+      <c r="J169" s="18">
         <v>4</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
-    <row r="170" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B170" s="6">
+    <row r="170" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B170" s="18">
         <v>5</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
-      <c r="F170" s="6">
+      <c r="F170" s="18">
         <v>5</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
-      <c r="J170" s="6">
+      <c r="J170" s="18">
         <v>5</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
-    <row r="171" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B171" s="6">
+    <row r="171" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B171" s="18">
         <v>6</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="6">
+      <c r="F171" s="18">
         <v>6</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
-      <c r="J171" s="6">
+      <c r="J171" s="18">
         <v>6</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
-    <row r="172" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B172" s="6">
+    <row r="172" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B172" s="18">
         <v>7</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="6">
+      <c r="F172" s="18">
         <v>7</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
-      <c r="J172" s="6">
+      <c r="J172" s="18">
         <v>7</v>
       </c>
       <c r="K172" s="7"/>
@@ -4750,116 +4638,37 @@
     </row>
   </sheetData>
   <mergeCells count="165">
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="J155:J156"/>
-    <mergeCell ref="L155:L156"/>
-    <mergeCell ref="M155:M156"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="E164:E165"/>
-    <mergeCell ref="F164:F165"/>
-    <mergeCell ref="H164:H165"/>
-    <mergeCell ref="I164:I165"/>
-    <mergeCell ref="J164:J165"/>
-    <mergeCell ref="L164:L165"/>
-    <mergeCell ref="M164:M165"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="E155:E156"/>
-    <mergeCell ref="F155:F156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="F146:F147"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="L146:L147"/>
-    <mergeCell ref="M146:M147"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="L128:L129"/>
-    <mergeCell ref="M128:M129"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="D137:D138"/>
-    <mergeCell ref="E137:E138"/>
-    <mergeCell ref="F137:F138"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="L137:L138"/>
-    <mergeCell ref="M137:M138"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="F119:F120"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="J119:J120"/>
-    <mergeCell ref="L119:L120"/>
-    <mergeCell ref="M119:M120"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="L106:L107"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="L88:L89"/>
-    <mergeCell ref="B117:M117"/>
-    <mergeCell ref="M88:M89"/>
-    <mergeCell ref="M97:M98"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="M106:M107"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="H79:H80"/>
-    <mergeCell ref="L79:L80"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="L97:L98"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="J79:J80"/>
-    <mergeCell ref="M79:M80"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="M61:M62"/>
-    <mergeCell ref="B59:M59"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="M48:M49"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L48:L49"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
@@ -4884,37 +4693,116 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="M48:M49"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="M61:M62"/>
+    <mergeCell ref="B59:M59"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="J79:J80"/>
+    <mergeCell ref="M79:M80"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="H79:H80"/>
+    <mergeCell ref="L79:L80"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="L97:L98"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="L106:L107"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="L88:L89"/>
+    <mergeCell ref="B117:M117"/>
+    <mergeCell ref="M88:M89"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="M106:M107"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="L119:L120"/>
+    <mergeCell ref="M119:M120"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="L128:L129"/>
+    <mergeCell ref="M128:M129"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="D137:D138"/>
+    <mergeCell ref="E137:E138"/>
+    <mergeCell ref="F137:F138"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="L137:L138"/>
+    <mergeCell ref="M137:M138"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="F146:F147"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="L146:L147"/>
+    <mergeCell ref="M146:M147"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="J155:J156"/>
+    <mergeCell ref="L155:L156"/>
+    <mergeCell ref="M155:M156"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="E164:E165"/>
+    <mergeCell ref="F164:F165"/>
+    <mergeCell ref="H164:H165"/>
+    <mergeCell ref="I164:I165"/>
+    <mergeCell ref="J164:J165"/>
+    <mergeCell ref="L164:L165"/>
+    <mergeCell ref="M164:M165"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="E155:E156"/>
+    <mergeCell ref="F155:F156"/>
+    <mergeCell ref="H155:H156"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4922,18 +4810,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/зо.xlsx
+++ b/зо.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="44">
   <si>
     <t>№</t>
   </si>
@@ -199,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -346,11 +346,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -417,6 +430,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -755,20 +774,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
@@ -809,44 +828,44 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="23"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="24"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="5">
         <v>46328</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="5">
         <v>46335</v>
       </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
       <c r="K4" s="5">
         <v>46342</v>
       </c>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
@@ -928,7 +947,9 @@
       <c r="D8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7">
+        <v>414</v>
+      </c>
       <c r="F8" s="8">
         <v>4</v>
       </c>
@@ -956,7 +977,9 @@
       <c r="D9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7">
+        <v>414</v>
+      </c>
       <c r="F9" s="8">
         <v>5</v>
       </c>
@@ -966,7 +989,9 @@
       <c r="H9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="I9" s="7">
+        <v>414</v>
+      </c>
       <c r="J9" s="8">
         <v>5</v>
       </c>
@@ -1015,44 +1040,44 @@
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="23"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
       <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="24"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="5">
         <v>46329</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="5">
         <v>46336</v>
       </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="5">
         <v>46343</v>
       </c>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
@@ -1116,7 +1141,9 @@
       <c r="H16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="7"/>
+      <c r="I16" s="7">
+        <v>414</v>
+      </c>
       <c r="J16" s="8">
         <v>3</v>
       </c>
@@ -1188,12 +1215,8 @@
       <c r="B19" s="6">
         <v>6</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8">
         <v>6</v>
@@ -1235,44 +1258,44 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
+      <c r="B21" s="27"/>
       <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
       <c r="K21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="13">
         <v>46330</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
       <c r="G22" s="15">
         <v>46337</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
       <c r="K22" s="15">
         <v>46344</v>
       </c>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
@@ -1332,7 +1355,9 @@
       <c r="H25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="7"/>
+      <c r="I25" s="7">
+        <v>414</v>
+      </c>
       <c r="J25" s="8">
         <v>3</v>
       </c>
@@ -1435,44 +1460,44 @@
       <c r="M29" s="7"/>
     </row>
     <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="23"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
       <c r="K30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="24"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="5">
         <v>46331</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="5">
         <v>46338</v>
       </c>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
       <c r="K31" s="5">
         <v>46345</v>
       </c>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6">
@@ -1534,7 +1559,9 @@
       <c r="H34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I34" s="7"/>
+      <c r="I34" s="7">
+        <v>414</v>
+      </c>
       <c r="J34" s="8">
         <v>3</v>
       </c>
@@ -1602,12 +1629,8 @@
       <c r="B37" s="6">
         <v>6</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="8">
         <v>6</v>
@@ -1643,44 +1666,44 @@
       <c r="M38" s="9"/>
     </row>
     <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="23"/>
+      <c r="B39" s="27"/>
       <c r="C39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
       <c r="G39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
       <c r="K39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="24"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="5">
         <v>46332</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="5">
         <v>46339</v>
       </c>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
       <c r="K40" s="5">
         <v>46346</v>
       </c>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="6">
@@ -1760,7 +1783,9 @@
       <c r="D44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="7"/>
+      <c r="E44" s="7">
+        <v>414</v>
+      </c>
       <c r="F44" s="8">
         <v>4</v>
       </c>
@@ -1847,44 +1872,44 @@
       <c r="M47" s="7"/>
     </row>
     <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="23"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
       <c r="G48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
       <c r="K48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
     </row>
     <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="24"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="5">
         <v>46333</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
       <c r="G49" s="5">
         <v>46340</v>
       </c>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
       <c r="K49" s="5">
         <v>46347</v>
       </c>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
     </row>
     <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="6">
@@ -1896,7 +1921,9 @@
       <c r="D50" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7">
+        <v>414</v>
+      </c>
       <c r="F50" s="6">
         <v>1</v>
       </c>
@@ -1920,7 +1947,9 @@
       <c r="D51" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7">
+        <v>414</v>
+      </c>
       <c r="F51" s="6">
         <v>2</v>
       </c>
@@ -2039,20 +2068,20 @@
       <c r="M56" s="7"/>
     </row>
     <row r="59" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="26" t="s">
+      <c r="B59" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="31"/>
+      <c r="K59" s="31"/>
+      <c r="L59" s="31"/>
+      <c r="M59" s="31"/>
     </row>
     <row r="60" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
@@ -2093,44 +2122,44 @@
       </c>
     </row>
     <row r="61" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="23"/>
+      <c r="B61" s="27"/>
       <c r="C61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
       <c r="G61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
       <c r="K61" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
     </row>
     <row r="62" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="24"/>
+      <c r="B62" s="28"/>
       <c r="C62" s="5">
         <v>46328</v>
       </c>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
       <c r="G62" s="5">
         <v>46335</v>
       </c>
-      <c r="H62" s="24"/>
-      <c r="I62" s="24"/>
-      <c r="J62" s="24"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="28"/>
       <c r="K62" s="5">
         <v>46342</v>
       </c>
-      <c r="L62" s="24"/>
-      <c r="M62" s="24"/>
+      <c r="L62" s="28"/>
+      <c r="M62" s="28"/>
     </row>
     <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="18">
@@ -2172,7 +2201,7 @@
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="18">
         <v>3</v>
       </c>
@@ -2182,15 +2211,9 @@
       <c r="F65" s="8">
         <v>3</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I65" s="7">
-        <v>304</v>
-      </c>
+      <c r="G65" s="23"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="24"/>
       <c r="J65" s="8">
         <v>3</v>
       </c>
@@ -2218,7 +2241,9 @@
       <c r="H66" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I66" s="7"/>
+      <c r="I66" s="7">
+        <v>414</v>
+      </c>
       <c r="J66" s="8">
         <v>4</v>
       </c>
@@ -2299,44 +2324,44 @@
       <c r="M69" s="7"/>
     </row>
     <row r="70" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="23"/>
+      <c r="B70" s="27"/>
       <c r="C70" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
       <c r="G70" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="23"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
       <c r="K70" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
+      <c r="L70" s="27"/>
+      <c r="M70" s="27"/>
     </row>
     <row r="71" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="24"/>
+      <c r="B71" s="28"/>
       <c r="C71" s="5">
         <v>46329</v>
       </c>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
       <c r="G71" s="5">
         <v>46336</v>
       </c>
-      <c r="H71" s="24"/>
-      <c r="I71" s="24"/>
-      <c r="J71" s="24"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28"/>
+      <c r="J71" s="28"/>
       <c r="K71" s="5">
         <v>46343</v>
       </c>
-      <c r="L71" s="24"/>
-      <c r="M71" s="24"/>
+      <c r="L71" s="28"/>
+      <c r="M71" s="28"/>
     </row>
     <row r="72" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="18">
@@ -2416,7 +2441,9 @@
       <c r="D75" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E75" s="7"/>
+      <c r="E75" s="7">
+        <v>414</v>
+      </c>
       <c r="F75" s="8">
         <v>4</v>
       </c>
@@ -2426,7 +2453,9 @@
       <c r="H75" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I75" s="7"/>
+      <c r="I75" s="7">
+        <v>414</v>
+      </c>
       <c r="J75" s="8">
         <v>4</v>
       </c>
@@ -2456,7 +2485,9 @@
       <c r="H76" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I76" s="7"/>
+      <c r="I76" s="7">
+        <v>414</v>
+      </c>
       <c r="J76" s="8">
         <v>5</v>
       </c>
@@ -2511,44 +2542,44 @@
       <c r="M78" s="7"/>
     </row>
     <row r="79" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="23"/>
+      <c r="B79" s="27"/>
       <c r="C79" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
       <c r="G79" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="27"/>
       <c r="K79" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
+      <c r="L79" s="27"/>
+      <c r="M79" s="27"/>
     </row>
     <row r="80" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="25"/>
+      <c r="B80" s="29"/>
       <c r="C80" s="13">
         <v>46330</v>
       </c>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
       <c r="G80" s="15">
         <v>46337</v>
       </c>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
       <c r="K80" s="15">
         <v>46344</v>
       </c>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
+      <c r="L80" s="29"/>
+      <c r="M80" s="29"/>
     </row>
     <row r="81" spans="2:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
@@ -2563,12 +2594,12 @@
       <c r="G81" s="12"/>
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
-      <c r="J81" s="19">
-        <v>1</v>
-      </c>
-      <c r="K81" s="20"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="21"/>
+      <c r="J81" s="26">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="3"/>
     </row>
     <row r="82" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="18">
@@ -2583,12 +2614,12 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
-      <c r="J82" s="19">
-        <v>2</v>
-      </c>
-      <c r="K82" s="20"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="21"/>
+      <c r="J82" s="26">
+        <v>2</v>
+      </c>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="3"/>
     </row>
     <row r="83" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="18">
@@ -2634,7 +2665,9 @@
       <c r="H84" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I84" s="7"/>
+      <c r="I84" s="7">
+        <v>414</v>
+      </c>
       <c r="J84" s="8">
         <v>4</v>
       </c>
@@ -2658,7 +2691,9 @@
       <c r="H85" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I85" s="7"/>
+      <c r="I85" s="7">
+        <v>414</v>
+      </c>
       <c r="J85" s="8">
         <v>5</v>
       </c>
@@ -2707,44 +2742,44 @@
       <c r="M87" s="7"/>
     </row>
     <row r="88" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="23"/>
+      <c r="B88" s="27"/>
       <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
       <c r="G88" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="23"/>
+      <c r="H88" s="27"/>
+      <c r="I88" s="27"/>
+      <c r="J88" s="27"/>
       <c r="K88" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L88" s="23"/>
-      <c r="M88" s="23"/>
+      <c r="L88" s="27"/>
+      <c r="M88" s="27"/>
     </row>
     <row r="89" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="24"/>
+      <c r="B89" s="28"/>
       <c r="C89" s="5">
         <v>46331</v>
       </c>
-      <c r="D89" s="24"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="24"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
       <c r="G89" s="5">
         <v>46338</v>
       </c>
-      <c r="H89" s="24"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="24"/>
+      <c r="H89" s="28"/>
+      <c r="I89" s="28"/>
+      <c r="J89" s="28"/>
       <c r="K89" s="5">
         <v>46345</v>
       </c>
-      <c r="L89" s="24"/>
-      <c r="M89" s="24"/>
+      <c r="L89" s="28"/>
+      <c r="M89" s="28"/>
     </row>
     <row r="90" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="18">
@@ -2766,7 +2801,7 @@
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
     </row>
-    <row r="91" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:13" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="18">
         <v>2</v>
       </c>
@@ -2776,9 +2811,15 @@
       <c r="F91" s="8">
         <v>2</v>
       </c>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
+      <c r="G91" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I91" s="7">
+        <v>304</v>
+      </c>
       <c r="J91" s="8">
         <v>2</v>
       </c>
@@ -2796,7 +2837,9 @@
       <c r="D92" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E92" s="7"/>
+      <c r="E92" s="7">
+        <v>414</v>
+      </c>
       <c r="F92" s="8">
         <v>3</v>
       </c>
@@ -2824,7 +2867,9 @@
       <c r="D93" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E93" s="7"/>
+      <c r="E93" s="7">
+        <v>414</v>
+      </c>
       <c r="F93" s="8">
         <v>4</v>
       </c>
@@ -2923,44 +2968,44 @@
       <c r="M96" s="9"/>
     </row>
     <row r="97" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="23"/>
+      <c r="B97" s="27"/>
       <c r="C97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D97" s="23"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
       <c r="G97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H97" s="23"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="23"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="27"/>
+      <c r="J97" s="27"/>
       <c r="K97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L97" s="23"/>
-      <c r="M97" s="23"/>
+      <c r="L97" s="27"/>
+      <c r="M97" s="27"/>
     </row>
     <row r="98" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="24"/>
+      <c r="B98" s="28"/>
       <c r="C98" s="5">
         <v>46332</v>
       </c>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
       <c r="G98" s="5">
         <v>46339</v>
       </c>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28"/>
+      <c r="J98" s="28"/>
       <c r="K98" s="5">
         <v>46346</v>
       </c>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
+      <c r="L98" s="28"/>
+      <c r="M98" s="28"/>
     </row>
     <row r="99" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="18">
@@ -2978,7 +3023,9 @@
       <c r="H99" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I99" s="7"/>
+      <c r="I99" s="7">
+        <v>414</v>
+      </c>
       <c r="J99" s="18">
         <v>1</v>
       </c>
@@ -3002,7 +3049,9 @@
       <c r="H100" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I100" s="7"/>
+      <c r="I100" s="7">
+        <v>414</v>
+      </c>
       <c r="J100" s="18">
         <v>2</v>
       </c>
@@ -3020,7 +3069,9 @@
       <c r="D101" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="7"/>
+      <c r="E101" s="7">
+        <v>414</v>
+      </c>
       <c r="F101" s="8">
         <v>3</v>
       </c>
@@ -3133,44 +3184,44 @@
       <c r="M105" s="7"/>
     </row>
     <row r="106" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="23"/>
+      <c r="B106" s="27"/>
       <c r="C106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
       <c r="G106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H106" s="23"/>
-      <c r="I106" s="23"/>
-      <c r="J106" s="23"/>
+      <c r="H106" s="27"/>
+      <c r="I106" s="27"/>
+      <c r="J106" s="27"/>
       <c r="K106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L106" s="23"/>
-      <c r="M106" s="23"/>
+      <c r="L106" s="27"/>
+      <c r="M106" s="27"/>
     </row>
     <row r="107" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="24"/>
+      <c r="B107" s="28"/>
       <c r="C107" s="5">
         <v>46333</v>
       </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="28"/>
       <c r="G107" s="5">
         <v>46340</v>
       </c>
-      <c r="H107" s="24"/>
-      <c r="I107" s="24"/>
-      <c r="J107" s="24"/>
+      <c r="H107" s="28"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="28"/>
       <c r="K107" s="5">
         <v>46347</v>
       </c>
-      <c r="L107" s="24"/>
-      <c r="M107" s="24"/>
+      <c r="L107" s="28"/>
+      <c r="M107" s="28"/>
     </row>
     <row r="108" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="18">
@@ -3333,20 +3384,20 @@
       <c r="M114" s="7"/>
     </row>
     <row r="117" spans="2:13" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="26" t="s">
+      <c r="B117" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C117" s="27"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="27"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="27"/>
-      <c r="H117" s="27"/>
-      <c r="I117" s="27"/>
-      <c r="J117" s="27"/>
-      <c r="K117" s="27"/>
-      <c r="L117" s="27"/>
-      <c r="M117" s="27"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="31"/>
+      <c r="E117" s="31"/>
+      <c r="F117" s="31"/>
+      <c r="G117" s="31"/>
+      <c r="H117" s="31"/>
+      <c r="I117" s="31"/>
+      <c r="J117" s="31"/>
+      <c r="K117" s="31"/>
+      <c r="L117" s="31"/>
+      <c r="M117" s="31"/>
     </row>
     <row r="118" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B118" s="2" t="s">
@@ -3387,44 +3438,44 @@
       </c>
     </row>
     <row r="119" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B119" s="23"/>
+      <c r="B119" s="27"/>
       <c r="C119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="23"/>
-      <c r="E119" s="23"/>
-      <c r="F119" s="23"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
       <c r="G119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H119" s="23"/>
-      <c r="I119" s="23"/>
-      <c r="J119" s="23"/>
+      <c r="H119" s="27"/>
+      <c r="I119" s="27"/>
+      <c r="J119" s="27"/>
       <c r="K119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L119" s="23"/>
-      <c r="M119" s="23"/>
+      <c r="L119" s="27"/>
+      <c r="M119" s="27"/>
     </row>
     <row r="120" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="24"/>
+      <c r="B120" s="28"/>
       <c r="C120" s="5">
         <v>46328</v>
       </c>
-      <c r="D120" s="24"/>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
+      <c r="D120" s="28"/>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
       <c r="G120" s="5">
         <v>46335</v>
       </c>
-      <c r="H120" s="24"/>
-      <c r="I120" s="24"/>
-      <c r="J120" s="24"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="28"/>
+      <c r="J120" s="28"/>
       <c r="K120" s="5">
         <v>46342</v>
       </c>
-      <c r="L120" s="24"/>
-      <c r="M120" s="24"/>
+      <c r="L120" s="28"/>
+      <c r="M120" s="28"/>
     </row>
     <row r="121" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B121" s="18">
@@ -3591,44 +3642,44 @@
       <c r="M127" s="7"/>
     </row>
     <row r="128" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B128" s="23"/>
+      <c r="B128" s="27"/>
       <c r="C128" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D128" s="23"/>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
+      <c r="D128" s="27"/>
+      <c r="E128" s="27"/>
+      <c r="F128" s="27"/>
       <c r="G128" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H128" s="23"/>
-      <c r="I128" s="23"/>
-      <c r="J128" s="23"/>
+      <c r="H128" s="27"/>
+      <c r="I128" s="27"/>
+      <c r="J128" s="27"/>
       <c r="K128" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L128" s="23"/>
-      <c r="M128" s="23"/>
+      <c r="L128" s="27"/>
+      <c r="M128" s="27"/>
     </row>
     <row r="129" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="24"/>
+      <c r="B129" s="28"/>
       <c r="C129" s="5">
         <v>46329</v>
       </c>
-      <c r="D129" s="24"/>
-      <c r="E129" s="24"/>
-      <c r="F129" s="24"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="28"/>
       <c r="G129" s="5">
         <v>46336</v>
       </c>
-      <c r="H129" s="24"/>
-      <c r="I129" s="24"/>
-      <c r="J129" s="24"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="28"/>
+      <c r="J129" s="28"/>
       <c r="K129" s="5">
         <v>46343</v>
       </c>
-      <c r="L129" s="24"/>
-      <c r="M129" s="24"/>
+      <c r="L129" s="28"/>
+      <c r="M129" s="28"/>
     </row>
     <row r="130" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B130" s="18">
@@ -3660,9 +3711,15 @@
       <c r="F131" s="8">
         <v>2</v>
       </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
+      <c r="G131" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" s="7">
+        <v>308</v>
+      </c>
       <c r="J131" s="8">
         <v>2</v>
       </c>
@@ -3680,9 +3737,15 @@
       <c r="F132" s="8">
         <v>3</v>
       </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
+      <c r="G132" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="7">
+        <v>308</v>
+      </c>
       <c r="J132" s="8">
         <v>3</v>
       </c>
@@ -3738,15 +3801,9 @@
       <c r="F134" s="8">
         <v>5</v>
       </c>
-      <c r="G134" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I134" s="7">
-        <v>308</v>
-      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
       <c r="J134" s="8">
         <v>5</v>
       </c>
@@ -3770,15 +3827,9 @@
       <c r="F135" s="8">
         <v>6</v>
       </c>
-      <c r="G135" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I135" s="7">
-        <v>308</v>
-      </c>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
       <c r="J135" s="8">
         <v>6</v>
       </c>
@@ -3807,44 +3858,44 @@
       <c r="M136" s="7"/>
     </row>
     <row r="137" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B137" s="23"/>
+      <c r="B137" s="27"/>
       <c r="C137" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D137" s="23"/>
-      <c r="E137" s="23"/>
-      <c r="F137" s="23"/>
+      <c r="D137" s="27"/>
+      <c r="E137" s="27"/>
+      <c r="F137" s="27"/>
       <c r="G137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="23"/>
-      <c r="I137" s="23"/>
-      <c r="J137" s="23"/>
+      <c r="H137" s="27"/>
+      <c r="I137" s="27"/>
+      <c r="J137" s="27"/>
       <c r="K137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L137" s="23"/>
-      <c r="M137" s="23"/>
+      <c r="L137" s="27"/>
+      <c r="M137" s="27"/>
     </row>
     <row r="138" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="25"/>
+      <c r="B138" s="29"/>
       <c r="C138" s="13">
         <v>46330</v>
       </c>
-      <c r="D138" s="25"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
+      <c r="D138" s="29"/>
+      <c r="E138" s="29"/>
+      <c r="F138" s="29"/>
       <c r="G138" s="15">
         <v>46337</v>
       </c>
-      <c r="H138" s="25"/>
-      <c r="I138" s="25"/>
-      <c r="J138" s="25"/>
+      <c r="H138" s="29"/>
+      <c r="I138" s="29"/>
+      <c r="J138" s="29"/>
       <c r="K138" s="15">
         <v>46344</v>
       </c>
-      <c r="L138" s="25"/>
-      <c r="M138" s="25"/>
+      <c r="L138" s="29"/>
+      <c r="M138" s="29"/>
     </row>
     <row r="139" spans="2:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B139" s="2">
@@ -4007,44 +4058,44 @@
       <c r="M145" s="7"/>
     </row>
     <row r="146" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B146" s="23"/>
+      <c r="B146" s="27"/>
       <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="23"/>
-      <c r="E146" s="23"/>
-      <c r="F146" s="23"/>
+      <c r="D146" s="27"/>
+      <c r="E146" s="27"/>
+      <c r="F146" s="27"/>
       <c r="G146" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H146" s="23"/>
-      <c r="I146" s="23"/>
-      <c r="J146" s="23"/>
+      <c r="H146" s="27"/>
+      <c r="I146" s="27"/>
+      <c r="J146" s="27"/>
       <c r="K146" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L146" s="23"/>
-      <c r="M146" s="23"/>
+      <c r="L146" s="27"/>
+      <c r="M146" s="27"/>
     </row>
     <row r="147" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="24"/>
+      <c r="B147" s="28"/>
       <c r="C147" s="5">
         <v>46331</v>
       </c>
-      <c r="D147" s="24"/>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
+      <c r="D147" s="28"/>
+      <c r="E147" s="28"/>
+      <c r="F147" s="28"/>
       <c r="G147" s="5">
         <v>46338</v>
       </c>
-      <c r="H147" s="24"/>
-      <c r="I147" s="24"/>
-      <c r="J147" s="24"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="28"/>
+      <c r="J147" s="28"/>
       <c r="K147" s="5">
         <v>46345</v>
       </c>
-      <c r="L147" s="24"/>
-      <c r="M147" s="24"/>
+      <c r="L147" s="28"/>
+      <c r="M147" s="28"/>
     </row>
     <row r="148" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B148" s="18">
@@ -4223,44 +4274,44 @@
       <c r="M154" s="9"/>
     </row>
     <row r="155" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B155" s="23"/>
+      <c r="B155" s="27"/>
       <c r="C155" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D155" s="23"/>
-      <c r="E155" s="23"/>
-      <c r="F155" s="23"/>
+      <c r="D155" s="27"/>
+      <c r="E155" s="27"/>
+      <c r="F155" s="27"/>
       <c r="G155" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H155" s="23"/>
-      <c r="I155" s="23"/>
-      <c r="J155" s="23"/>
+      <c r="H155" s="27"/>
+      <c r="I155" s="27"/>
+      <c r="J155" s="27"/>
       <c r="K155" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L155" s="23"/>
-      <c r="M155" s="23"/>
+      <c r="L155" s="27"/>
+      <c r="M155" s="27"/>
     </row>
     <row r="156" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B156" s="24"/>
+      <c r="B156" s="28"/>
       <c r="C156" s="5">
         <v>46332</v>
       </c>
-      <c r="D156" s="24"/>
-      <c r="E156" s="24"/>
-      <c r="F156" s="24"/>
+      <c r="D156" s="28"/>
+      <c r="E156" s="28"/>
+      <c r="F156" s="28"/>
       <c r="G156" s="5">
         <v>46339</v>
       </c>
-      <c r="H156" s="24"/>
-      <c r="I156" s="24"/>
-      <c r="J156" s="24"/>
+      <c r="H156" s="28"/>
+      <c r="I156" s="28"/>
+      <c r="J156" s="28"/>
       <c r="K156" s="5">
         <v>46346</v>
       </c>
-      <c r="L156" s="24"/>
-      <c r="M156" s="24"/>
+      <c r="L156" s="28"/>
+      <c r="M156" s="28"/>
     </row>
     <row r="157" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="18">
@@ -4433,44 +4484,44 @@
       <c r="M163" s="7"/>
     </row>
     <row r="164" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B164" s="23"/>
+      <c r="B164" s="27"/>
       <c r="C164" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D164" s="23"/>
-      <c r="E164" s="23"/>
-      <c r="F164" s="23"/>
+      <c r="D164" s="27"/>
+      <c r="E164" s="27"/>
+      <c r="F164" s="27"/>
       <c r="G164" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H164" s="23"/>
-      <c r="I164" s="23"/>
-      <c r="J164" s="23"/>
+      <c r="H164" s="27"/>
+      <c r="I164" s="27"/>
+      <c r="J164" s="27"/>
       <c r="K164" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L164" s="23"/>
-      <c r="M164" s="23"/>
+      <c r="L164" s="27"/>
+      <c r="M164" s="27"/>
     </row>
     <row r="165" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="24"/>
+      <c r="B165" s="28"/>
       <c r="C165" s="5">
         <v>46333</v>
       </c>
-      <c r="D165" s="24"/>
-      <c r="E165" s="24"/>
-      <c r="F165" s="24"/>
+      <c r="D165" s="28"/>
+      <c r="E165" s="28"/>
+      <c r="F165" s="28"/>
       <c r="G165" s="5">
         <v>46340</v>
       </c>
-      <c r="H165" s="24"/>
-      <c r="I165" s="24"/>
-      <c r="J165" s="24"/>
+      <c r="H165" s="28"/>
+      <c r="I165" s="28"/>
+      <c r="J165" s="28"/>
       <c r="K165" s="5">
         <v>46347</v>
       </c>
-      <c r="L165" s="24"/>
-      <c r="M165" s="24"/>
+      <c r="L165" s="28"/>
+      <c r="M165" s="28"/>
     </row>
     <row r="166" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B166" s="18">
